--- a/data/EOAT_data.xlsx
+++ b/data/EOAT_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\procesos.CAZEL\Desktop\Becario Procesos\EOAT Project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{350AD91D-7A2F-4587-B066-0AE14BB1F080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C913F5D-FC98-4674-A950-30813C06CF0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{440E3869-3C3F-4E8C-A8BD-ADEB8E2EA552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="267">
   <si>
     <t>I-1937</t>
   </si>
@@ -2380,6 +2380,9 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>68</v>
+      </c>
       <c r="B59" t="s">
         <v>68</v>
       </c>
@@ -2394,6 +2397,9 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>68</v>
+      </c>
       <c r="B60" t="s">
         <v>68</v>
       </c>
@@ -2408,6 +2414,9 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>68</v>
+      </c>
       <c r="B61" t="s">
         <v>68</v>
       </c>
@@ -2422,6 +2431,9 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>68</v>
+      </c>
       <c r="B62" t="s">
         <v>68</v>
       </c>
@@ -2836,6 +2848,9 @@
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>94</v>
+      </c>
       <c r="B83" t="s">
         <v>94</v>
       </c>
@@ -2850,6 +2865,9 @@
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>94</v>
+      </c>
       <c r="B84" t="s">
         <v>94</v>
       </c>
@@ -2864,6 +2882,9 @@
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>94</v>
+      </c>
       <c r="B85" t="s">
         <v>94</v>
       </c>
@@ -3638,6 +3659,9 @@
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>94</v>
+      </c>
       <c r="B124" t="s">
         <v>94</v>
       </c>
@@ -3652,6 +3676,9 @@
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>94</v>
+      </c>
       <c r="B125" t="s">
         <v>94</v>
       </c>
@@ -3666,6 +3693,9 @@
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>94</v>
+      </c>
       <c r="B126" t="s">
         <v>94</v>
       </c>
@@ -3680,6 +3710,9 @@
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>94</v>
+      </c>
       <c r="B127" t="s">
         <v>94</v>
       </c>
@@ -3694,6 +3727,9 @@
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>94</v>
+      </c>
       <c r="B128" t="s">
         <v>94</v>
       </c>
@@ -3707,7 +3743,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>94</v>
+      </c>
       <c r="B129" t="s">
         <v>94</v>
       </c>
@@ -3721,7 +3760,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="130" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>94</v>
+      </c>
       <c r="B130" t="s">
         <v>94</v>
       </c>
@@ -3735,7 +3777,10 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>94</v>
+      </c>
       <c r="B131" t="s">
         <v>94</v>
       </c>
@@ -3749,7 +3794,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="132" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>94</v>
+      </c>
       <c r="B132" t="s">
         <v>94</v>
       </c>

--- a/data/EOAT_data.xlsx
+++ b/data/EOAT_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\procesos.CAZEL\Desktop\Becario Procesos\EOAT Project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C913F5D-FC98-4674-A950-30813C06CF0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{647626B9-F884-4F9C-B616-1ADAAB8F39B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{440E3869-3C3F-4E8C-A8BD-ADEB8E2EA552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1042" uniqueCount="619">
   <si>
     <t>I-1937</t>
   </si>
@@ -837,16 +837,1078 @@
   </si>
   <si>
     <t>EOAT</t>
+  </si>
+  <si>
+    <t>I-1360</t>
+  </si>
+  <si>
+    <t>I-1360.jpeg</t>
+  </si>
+  <si>
+    <t>I-1361</t>
+  </si>
+  <si>
+    <t>I-1366</t>
+  </si>
+  <si>
+    <t>I-1367</t>
+  </si>
+  <si>
+    <t>I-1368</t>
+  </si>
+  <si>
+    <t>I-1370</t>
+  </si>
+  <si>
+    <t>I-1424</t>
+  </si>
+  <si>
+    <t>I-1455</t>
+  </si>
+  <si>
+    <t>I-1361.jpeg</t>
+  </si>
+  <si>
+    <t>I-1366.jpeg</t>
+  </si>
+  <si>
+    <t>I-1367.jpeg</t>
+  </si>
+  <si>
+    <t>I-1368.jpeg</t>
+  </si>
+  <si>
+    <t>I-1370.jpeg</t>
+  </si>
+  <si>
+    <t>I-1424.jpeg</t>
+  </si>
+  <si>
+    <t>I-1455.jpeg</t>
+  </si>
+  <si>
+    <t>I-1468</t>
+  </si>
+  <si>
+    <t>I-1474</t>
+  </si>
+  <si>
+    <t>I-1493</t>
+  </si>
+  <si>
+    <t>I-1494</t>
+  </si>
+  <si>
+    <t>I-1514</t>
+  </si>
+  <si>
+    <t>I-1516</t>
+  </si>
+  <si>
+    <t>I-1538</t>
+  </si>
+  <si>
+    <t>I-1545</t>
+  </si>
+  <si>
+    <t>I-1556</t>
+  </si>
+  <si>
+    <t>I-1557</t>
+  </si>
+  <si>
+    <t>I-1558</t>
+  </si>
+  <si>
+    <t>I-1559</t>
+  </si>
+  <si>
+    <t>I-1560</t>
+  </si>
+  <si>
+    <t>I-1562</t>
+  </si>
+  <si>
+    <t>I-1572</t>
+  </si>
+  <si>
+    <t>I-1573</t>
+  </si>
+  <si>
+    <t>I-1574</t>
+  </si>
+  <si>
+    <t>I-1584</t>
+  </si>
+  <si>
+    <t>I-1586</t>
+  </si>
+  <si>
+    <t>I-1587</t>
+  </si>
+  <si>
+    <t>I-1588</t>
+  </si>
+  <si>
+    <t>I-1589</t>
+  </si>
+  <si>
+    <t>I-1594</t>
+  </si>
+  <si>
+    <t>I-1600</t>
+  </si>
+  <si>
+    <t>I-1605</t>
+  </si>
+  <si>
+    <t>I-1606</t>
+  </si>
+  <si>
+    <t>I-1607</t>
+  </si>
+  <si>
+    <t>I-1611</t>
+  </si>
+  <si>
+    <t>I-1615</t>
+  </si>
+  <si>
+    <t>I-1616</t>
+  </si>
+  <si>
+    <t>I-1617</t>
+  </si>
+  <si>
+    <t>I-1618</t>
+  </si>
+  <si>
+    <t>I-1621</t>
+  </si>
+  <si>
+    <t>I-1624</t>
+  </si>
+  <si>
+    <t>I-1625</t>
+  </si>
+  <si>
+    <t>I-1627</t>
+  </si>
+  <si>
+    <t>I-1631</t>
+  </si>
+  <si>
+    <t>I-1632</t>
+  </si>
+  <si>
+    <t>I-1633</t>
+  </si>
+  <si>
+    <t>I-1636</t>
+  </si>
+  <si>
+    <t>I-1637</t>
+  </si>
+  <si>
+    <t>I-1638</t>
+  </si>
+  <si>
+    <t>I-1639</t>
+  </si>
+  <si>
+    <t>I-1642</t>
+  </si>
+  <si>
+    <t>I-1643</t>
+  </si>
+  <si>
+    <t>I-1644</t>
+  </si>
+  <si>
+    <t>I-1645</t>
+  </si>
+  <si>
+    <t>I-1646</t>
+  </si>
+  <si>
+    <t>I-1647</t>
+  </si>
+  <si>
+    <t>I-1648</t>
+  </si>
+  <si>
+    <t>I-1649</t>
+  </si>
+  <si>
+    <t>I-1650</t>
+  </si>
+  <si>
+    <t>I-1651</t>
+  </si>
+  <si>
+    <t>I-1652</t>
+  </si>
+  <si>
+    <t>I-1653</t>
+  </si>
+  <si>
+    <t>I-1654</t>
+  </si>
+  <si>
+    <t>I-1655</t>
+  </si>
+  <si>
+    <t>I-1656</t>
+  </si>
+  <si>
+    <t>I-1658</t>
+  </si>
+  <si>
+    <t>I-1659</t>
+  </si>
+  <si>
+    <t>I-1660</t>
+  </si>
+  <si>
+    <t>I-1661</t>
+  </si>
+  <si>
+    <t>I-1662</t>
+  </si>
+  <si>
+    <t>I-1664</t>
+  </si>
+  <si>
+    <t>I-1665</t>
+  </si>
+  <si>
+    <t>I-1667</t>
+  </si>
+  <si>
+    <t>I-1669</t>
+  </si>
+  <si>
+    <t>I-1670</t>
+  </si>
+  <si>
+    <t>I-1671</t>
+  </si>
+  <si>
+    <t>I-1672</t>
+  </si>
+  <si>
+    <t>I-1673</t>
+  </si>
+  <si>
+    <t>I-1674</t>
+  </si>
+  <si>
+    <t>I-1675</t>
+  </si>
+  <si>
+    <t>I-1676</t>
+  </si>
+  <si>
+    <t>I-1677</t>
+  </si>
+  <si>
+    <t>I-1679</t>
+  </si>
+  <si>
+    <t>I-1681</t>
+  </si>
+  <si>
+    <t>I-1687</t>
+  </si>
+  <si>
+    <t>I-1690</t>
+  </si>
+  <si>
+    <t>I-1708</t>
+  </si>
+  <si>
+    <t>I-1709</t>
+  </si>
+  <si>
+    <t>I-1710</t>
+  </si>
+  <si>
+    <t>I-1715</t>
+  </si>
+  <si>
+    <t>I-1716</t>
+  </si>
+  <si>
+    <t>I-1717</t>
+  </si>
+  <si>
+    <t>I-1721</t>
+  </si>
+  <si>
+    <t>I-1722</t>
+  </si>
+  <si>
+    <t>I-1725</t>
+  </si>
+  <si>
+    <t>I-1728</t>
+  </si>
+  <si>
+    <t>I-1729</t>
+  </si>
+  <si>
+    <t>I-1730</t>
+  </si>
+  <si>
+    <t>I-1731</t>
+  </si>
+  <si>
+    <t>I-1732</t>
+  </si>
+  <si>
+    <t>I-1733</t>
+  </si>
+  <si>
+    <t>I-1734</t>
+  </si>
+  <si>
+    <t>I-1735</t>
+  </si>
+  <si>
+    <t>I-1751</t>
+  </si>
+  <si>
+    <t>I-1766</t>
+  </si>
+  <si>
+    <t>I-1767</t>
+  </si>
+  <si>
+    <t>I-1771</t>
+  </si>
+  <si>
+    <t>I-1772</t>
+  </si>
+  <si>
+    <t>I-1773</t>
+  </si>
+  <si>
+    <t>I-1775</t>
+  </si>
+  <si>
+    <t>I-1776</t>
+  </si>
+  <si>
+    <t>I-1777</t>
+  </si>
+  <si>
+    <t>I-1778</t>
+  </si>
+  <si>
+    <t>I-1779</t>
+  </si>
+  <si>
+    <t>I-1780</t>
+  </si>
+  <si>
+    <t>I-1782</t>
+  </si>
+  <si>
+    <t>I-1783</t>
+  </si>
+  <si>
+    <t>I-1784</t>
+  </si>
+  <si>
+    <t>I-1785</t>
+  </si>
+  <si>
+    <t>I-1786</t>
+  </si>
+  <si>
+    <t>I-1787</t>
+  </si>
+  <si>
+    <t>I-1813</t>
+  </si>
+  <si>
+    <t>I-1814</t>
+  </si>
+  <si>
+    <t>I-1815</t>
+  </si>
+  <si>
+    <t>I-1818</t>
+  </si>
+  <si>
+    <t>I-1819</t>
+  </si>
+  <si>
+    <t>I-1822</t>
+  </si>
+  <si>
+    <t>I-1823</t>
+  </si>
+  <si>
+    <t>I-1827</t>
+  </si>
+  <si>
+    <t>I-1828</t>
+  </si>
+  <si>
+    <t>I-1830</t>
+  </si>
+  <si>
+    <t>I-1833</t>
+  </si>
+  <si>
+    <t>I-1841</t>
+  </si>
+  <si>
+    <t>I-1842</t>
+  </si>
+  <si>
+    <t>I-1843</t>
+  </si>
+  <si>
+    <t>I-1845</t>
+  </si>
+  <si>
+    <t>I-1847</t>
+  </si>
+  <si>
+    <t>I-1848</t>
+  </si>
+  <si>
+    <t>I-1849</t>
+  </si>
+  <si>
+    <t>I-1851</t>
+  </si>
+  <si>
+    <t>I-1852</t>
+  </si>
+  <si>
+    <t>I-1853</t>
+  </si>
+  <si>
+    <t>I-1854</t>
+  </si>
+  <si>
+    <t>I-1855</t>
+  </si>
+  <si>
+    <t>I-1865</t>
+  </si>
+  <si>
+    <t>I-1872</t>
+  </si>
+  <si>
+    <t>I-1873</t>
+  </si>
+  <si>
+    <t>I-1874</t>
+  </si>
+  <si>
+    <t>I-1876</t>
+  </si>
+  <si>
+    <t>I-1877</t>
+  </si>
+  <si>
+    <t>I-1878</t>
+  </si>
+  <si>
+    <t>I-1889</t>
+  </si>
+  <si>
+    <t>I-1890</t>
+  </si>
+  <si>
+    <t>I-1891</t>
+  </si>
+  <si>
+    <t>I-1892</t>
+  </si>
+  <si>
+    <t>I-1893</t>
+  </si>
+  <si>
+    <t>I-1894</t>
+  </si>
+  <si>
+    <t>I-1895</t>
+  </si>
+  <si>
+    <t>I-1897</t>
+  </si>
+  <si>
+    <t>I-1899</t>
+  </si>
+  <si>
+    <t>I-1900</t>
+  </si>
+  <si>
+    <t>I-1902</t>
+  </si>
+  <si>
+    <t>I-1909</t>
+  </si>
+  <si>
+    <t>I-1910</t>
+  </si>
+  <si>
+    <t>I-1912</t>
+  </si>
+  <si>
+    <t>I-1915</t>
+  </si>
+  <si>
+    <t>I-1924</t>
+  </si>
+  <si>
+    <t>I-1925</t>
+  </si>
+  <si>
+    <t>I-1934</t>
+  </si>
+  <si>
+    <t>I-1935</t>
+  </si>
+  <si>
+    <t>I-1922</t>
+  </si>
+  <si>
+    <t>I-1933</t>
+  </si>
+  <si>
+    <t>I-1928</t>
+  </si>
+  <si>
+    <t>I-1921</t>
+  </si>
+  <si>
+    <t>I-1614</t>
+  </si>
+  <si>
+    <t>I-1468.jpeg</t>
+  </si>
+  <si>
+    <t>I-1474.jpeg</t>
+  </si>
+  <si>
+    <t>I-1493.jpeg</t>
+  </si>
+  <si>
+    <t>I-1494.jpeg</t>
+  </si>
+  <si>
+    <t>I-1514.jpeg</t>
+  </si>
+  <si>
+    <t>I-1516.jpeg</t>
+  </si>
+  <si>
+    <t>I-1538.jpeg</t>
+  </si>
+  <si>
+    <t>I-1545.jpeg</t>
+  </si>
+  <si>
+    <t>I-1556.jpeg</t>
+  </si>
+  <si>
+    <t>I-1557.jpeg</t>
+  </si>
+  <si>
+    <t>I-1558.jpeg</t>
+  </si>
+  <si>
+    <t>I-1559.jpeg</t>
+  </si>
+  <si>
+    <t>I-1560.jpeg</t>
+  </si>
+  <si>
+    <t>I-1562.jpeg</t>
+  </si>
+  <si>
+    <t>I-1572.jpeg</t>
+  </si>
+  <si>
+    <t>I-1573.jpeg</t>
+  </si>
+  <si>
+    <t>I-1574.jpeg</t>
+  </si>
+  <si>
+    <t>I-1584.jpeg</t>
+  </si>
+  <si>
+    <t>I-1586.jpeg</t>
+  </si>
+  <si>
+    <t>I-1587.jpeg</t>
+  </si>
+  <si>
+    <t>I-1588.jpeg</t>
+  </si>
+  <si>
+    <t>I-1589.jpeg</t>
+  </si>
+  <si>
+    <t>I-1594.jpeg</t>
+  </si>
+  <si>
+    <t>I-1600.jpeg</t>
+  </si>
+  <si>
+    <t>I-1605.jpeg</t>
+  </si>
+  <si>
+    <t>I-1606.jpeg</t>
+  </si>
+  <si>
+    <t>I-1607.jpeg</t>
+  </si>
+  <si>
+    <t>I-1611.jpeg</t>
+  </si>
+  <si>
+    <t>I-1615.jpeg</t>
+  </si>
+  <si>
+    <t>I-1616.jpeg</t>
+  </si>
+  <si>
+    <t>I-1617.jpeg</t>
+  </si>
+  <si>
+    <t>I-1618.jpeg</t>
+  </si>
+  <si>
+    <t>I-1621.jpeg</t>
+  </si>
+  <si>
+    <t>I-1624.jpeg</t>
+  </si>
+  <si>
+    <t>I-1625.jpeg</t>
+  </si>
+  <si>
+    <t>I-1627.jpeg</t>
+  </si>
+  <si>
+    <t>I-1631.jpeg</t>
+  </si>
+  <si>
+    <t>I-1632.jpeg</t>
+  </si>
+  <si>
+    <t>I-1633.jpeg</t>
+  </si>
+  <si>
+    <t>I-1636.jpeg</t>
+  </si>
+  <si>
+    <t>I-1637.jpeg</t>
+  </si>
+  <si>
+    <t>I-1638.jpeg</t>
+  </si>
+  <si>
+    <t>I-1639.jpeg</t>
+  </si>
+  <si>
+    <t>I-1642.jpeg</t>
+  </si>
+  <si>
+    <t>I-1643.jpeg</t>
+  </si>
+  <si>
+    <t>I-1644.jpeg</t>
+  </si>
+  <si>
+    <t>I-1645.jpeg</t>
+  </si>
+  <si>
+    <t>I-1646.jpeg</t>
+  </si>
+  <si>
+    <t>I-1647.jpeg</t>
+  </si>
+  <si>
+    <t>I-1648.jpeg</t>
+  </si>
+  <si>
+    <t>I-1649.jpeg</t>
+  </si>
+  <si>
+    <t>I-1650.jpeg</t>
+  </si>
+  <si>
+    <t>I-1651.jpeg</t>
+  </si>
+  <si>
+    <t>I-1652.jpeg</t>
+  </si>
+  <si>
+    <t>I-1653.jpeg</t>
+  </si>
+  <si>
+    <t>I-1654.jpeg</t>
+  </si>
+  <si>
+    <t>I-1655.jpeg</t>
+  </si>
+  <si>
+    <t>I-1656.jpeg</t>
+  </si>
+  <si>
+    <t>I-1658.jpeg</t>
+  </si>
+  <si>
+    <t>I-1659.jpeg</t>
+  </si>
+  <si>
+    <t>I-1660.jpeg</t>
+  </si>
+  <si>
+    <t>I-1661.jpeg</t>
+  </si>
+  <si>
+    <t>I-1662.jpeg</t>
+  </si>
+  <si>
+    <t>I-1664.jpeg</t>
+  </si>
+  <si>
+    <t>I-1665.jpeg</t>
+  </si>
+  <si>
+    <t>I-1667.jpeg</t>
+  </si>
+  <si>
+    <t>I-1669.jpeg</t>
+  </si>
+  <si>
+    <t>I-1670.jpeg</t>
+  </si>
+  <si>
+    <t>I-1671.jpeg</t>
+  </si>
+  <si>
+    <t>I-1672.jpeg</t>
+  </si>
+  <si>
+    <t>I-1673.jpeg</t>
+  </si>
+  <si>
+    <t>I-1674.jpeg</t>
+  </si>
+  <si>
+    <t>I-1675.jpeg</t>
+  </si>
+  <si>
+    <t>I-1676.jpeg</t>
+  </si>
+  <si>
+    <t>I-1677.jpeg</t>
+  </si>
+  <si>
+    <t>I-1679.jpeg</t>
+  </si>
+  <si>
+    <t>I-1681.jpeg</t>
+  </si>
+  <si>
+    <t>I-1687.jpeg</t>
+  </si>
+  <si>
+    <t>I-1690.jpeg</t>
+  </si>
+  <si>
+    <t>I-1708.jpeg</t>
+  </si>
+  <si>
+    <t>I-1709.jpeg</t>
+  </si>
+  <si>
+    <t>I-1710.jpeg</t>
+  </si>
+  <si>
+    <t>I-1715.jpeg</t>
+  </si>
+  <si>
+    <t>I-1716.jpeg</t>
+  </si>
+  <si>
+    <t>I-1717.jpeg</t>
+  </si>
+  <si>
+    <t>I-1721.jpeg</t>
+  </si>
+  <si>
+    <t>I-1722.jpeg</t>
+  </si>
+  <si>
+    <t>I-1725.jpeg</t>
+  </si>
+  <si>
+    <t>I-1728.jpeg</t>
+  </si>
+  <si>
+    <t>I-1729.jpeg</t>
+  </si>
+  <si>
+    <t>I-1730.jpeg</t>
+  </si>
+  <si>
+    <t>I-1731.jpeg</t>
+  </si>
+  <si>
+    <t>I-1732.jpeg</t>
+  </si>
+  <si>
+    <t>I-1733.jpeg</t>
+  </si>
+  <si>
+    <t>I-1734.jpeg</t>
+  </si>
+  <si>
+    <t>I-1735.jpeg</t>
+  </si>
+  <si>
+    <t>I-1751.jpeg</t>
+  </si>
+  <si>
+    <t>I-1766.jpeg</t>
+  </si>
+  <si>
+    <t>I-1767.jpeg</t>
+  </si>
+  <si>
+    <t>I-1771.jpeg</t>
+  </si>
+  <si>
+    <t>I-1772.jpeg</t>
+  </si>
+  <si>
+    <t>I-1773.jpeg</t>
+  </si>
+  <si>
+    <t>I-1775.jpeg</t>
+  </si>
+  <si>
+    <t>I-1776.jpeg</t>
+  </si>
+  <si>
+    <t>I-1777.jpeg</t>
+  </si>
+  <si>
+    <t>I-1778.jpeg</t>
+  </si>
+  <si>
+    <t>I-1779.jpeg</t>
+  </si>
+  <si>
+    <t>I-1780.jpeg</t>
+  </si>
+  <si>
+    <t>I-1782.jpeg</t>
+  </si>
+  <si>
+    <t>I-1783.jpeg</t>
+  </si>
+  <si>
+    <t>I-1784.jpeg</t>
+  </si>
+  <si>
+    <t>I-1785.jpeg</t>
+  </si>
+  <si>
+    <t>I-1786.jpeg</t>
+  </si>
+  <si>
+    <t>I-1787.jpeg</t>
+  </si>
+  <si>
+    <t>I-1813.jpeg</t>
+  </si>
+  <si>
+    <t>I-1814.jpeg</t>
+  </si>
+  <si>
+    <t>I-1815.jpeg</t>
+  </si>
+  <si>
+    <t>I-1818.jpeg</t>
+  </si>
+  <si>
+    <t>I-1819.jpeg</t>
+  </si>
+  <si>
+    <t>I-1822.jpeg</t>
+  </si>
+  <si>
+    <t>I-1823.jpeg</t>
+  </si>
+  <si>
+    <t>I-1827.jpeg</t>
+  </si>
+  <si>
+    <t>I-1828.jpeg</t>
+  </si>
+  <si>
+    <t>I-1830.jpeg</t>
+  </si>
+  <si>
+    <t>I-1833.jpeg</t>
+  </si>
+  <si>
+    <t>I-1841.jpeg</t>
+  </si>
+  <si>
+    <t>I-1842.jpeg</t>
+  </si>
+  <si>
+    <t>I-1843.jpeg</t>
+  </si>
+  <si>
+    <t>I-1845.jpeg</t>
+  </si>
+  <si>
+    <t>I-1847.jpeg</t>
+  </si>
+  <si>
+    <t>I-1848.jpeg</t>
+  </si>
+  <si>
+    <t>I-1849.jpeg</t>
+  </si>
+  <si>
+    <t>I-1851.jpeg</t>
+  </si>
+  <si>
+    <t>I-1852.jpeg</t>
+  </si>
+  <si>
+    <t>I-1853.jpeg</t>
+  </si>
+  <si>
+    <t>I-1854.jpeg</t>
+  </si>
+  <si>
+    <t>I-1855.jpeg</t>
+  </si>
+  <si>
+    <t>I-1865.jpeg</t>
+  </si>
+  <si>
+    <t>I-1872.jpeg</t>
+  </si>
+  <si>
+    <t>I-1873.jpeg</t>
+  </si>
+  <si>
+    <t>I-1874.jpeg</t>
+  </si>
+  <si>
+    <t>I-1876.jpeg</t>
+  </si>
+  <si>
+    <t>I-1877.jpeg</t>
+  </si>
+  <si>
+    <t>I-1878.jpeg</t>
+  </si>
+  <si>
+    <t>I-1889.jpeg</t>
+  </si>
+  <si>
+    <t>I-1890.jpeg</t>
+  </si>
+  <si>
+    <t>I-1891.jpeg</t>
+  </si>
+  <si>
+    <t>I-1892.jpeg</t>
+  </si>
+  <si>
+    <t>I-1893.jpeg</t>
+  </si>
+  <si>
+    <t>I-1894.jpeg</t>
+  </si>
+  <si>
+    <t>I-1895.jpeg</t>
+  </si>
+  <si>
+    <t>I-1897.jpeg</t>
+  </si>
+  <si>
+    <t>I-1899.jpeg</t>
+  </si>
+  <si>
+    <t>I-1900.jpeg</t>
+  </si>
+  <si>
+    <t>I-1902.jpeg</t>
+  </si>
+  <si>
+    <t>I-1909.jpeg</t>
+  </si>
+  <si>
+    <t>I-1910.jpeg</t>
+  </si>
+  <si>
+    <t>I-1912.jpeg</t>
+  </si>
+  <si>
+    <t>I-1915.jpeg</t>
+  </si>
+  <si>
+    <t>I-1924.jpeg</t>
+  </si>
+  <si>
+    <t>I-1925.jpeg</t>
+  </si>
+  <si>
+    <t>I-1934.jpeg</t>
+  </si>
+  <si>
+    <t>I-1935.jpeg</t>
+  </si>
+  <si>
+    <t>I-1922.jpeg</t>
+  </si>
+  <si>
+    <t>I-1933.jpeg</t>
+  </si>
+  <si>
+    <t>I-1928.jpeg</t>
+  </si>
+  <si>
+    <t>I-1921.jpeg</t>
+  </si>
+  <si>
+    <t>I-1614.jpeg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1208,7 +2270,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B6791C-A8A7-4753-A504-FAA9E3EE8745}">
-  <dimension ref="A1:F132"/>
+  <dimension ref="A1:F308"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -1241,2577 +2303,5048 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>445</v>
       </c>
       <c r="B2" t="s">
         <v>266</v>
       </c>
       <c r="C2">
-        <v>3</v>
-      </c>
-      <c r="D2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>145</v>
+        <v>613</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>444</v>
       </c>
       <c r="B3" t="s">
         <v>266</v>
       </c>
       <c r="C3">
-        <v>3</v>
-      </c>
-      <c r="D3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>146</v>
+        <v>612</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>447</v>
       </c>
       <c r="B4" t="s">
         <v>266</v>
       </c>
       <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>147</v>
+        <v>615</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>448</v>
       </c>
       <c r="B5" t="s">
         <v>266</v>
       </c>
       <c r="C5">
-        <v>3</v>
-      </c>
-      <c r="D5" t="s">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>148</v>
+        <v>616</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>443</v>
       </c>
       <c r="B6" t="s">
         <v>266</v>
       </c>
       <c r="C6">
-        <v>3</v>
-      </c>
-      <c r="D6" t="s">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>149</v>
+        <v>611</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>442</v>
       </c>
       <c r="B7" t="s">
         <v>266</v>
       </c>
       <c r="C7">
-        <v>3</v>
-      </c>
-      <c r="D7" t="s">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>150</v>
+        <v>610</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>446</v>
       </c>
       <c r="B8" t="s">
         <v>266</v>
       </c>
       <c r="C8">
-        <v>3</v>
-      </c>
-      <c r="D8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E8">
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>151</v>
+        <v>614</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>449</v>
       </c>
       <c r="B9" t="s">
         <v>266</v>
       </c>
       <c r="C9">
-        <v>3</v>
-      </c>
-      <c r="D9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9">
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>152</v>
+        <v>617</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>441</v>
       </c>
       <c r="B10" t="s">
         <v>266</v>
       </c>
       <c r="C10">
-        <v>3</v>
-      </c>
-      <c r="D10" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>153</v>
+        <v>609</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>440</v>
       </c>
       <c r="B11" t="s">
         <v>266</v>
       </c>
       <c r="C11">
-        <v>3</v>
-      </c>
-      <c r="D11" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>154</v>
+        <v>608</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>439</v>
       </c>
       <c r="B12" t="s">
         <v>266</v>
       </c>
       <c r="C12">
-        <v>3</v>
-      </c>
-      <c r="D12" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>155</v>
+        <v>607</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>438</v>
       </c>
       <c r="B13" t="s">
         <v>266</v>
       </c>
       <c r="C13">
-        <v>3</v>
-      </c>
-      <c r="D13" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>156</v>
+        <v>606</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>437</v>
       </c>
       <c r="B14" t="s">
         <v>266</v>
       </c>
       <c r="C14">
-        <v>3</v>
-      </c>
-      <c r="D14" t="s">
-        <v>15</v>
-      </c>
-      <c r="E14">
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>157</v>
+        <v>605</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>436</v>
       </c>
       <c r="B15" t="s">
         <v>266</v>
       </c>
       <c r="C15">
-        <v>3</v>
-      </c>
-      <c r="D15" t="s">
-        <v>15</v>
-      </c>
-      <c r="E15">
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>158</v>
+        <v>604</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>435</v>
       </c>
       <c r="B16" t="s">
         <v>266</v>
       </c>
       <c r="C16">
-        <v>3</v>
-      </c>
-      <c r="D16" t="s">
-        <v>15</v>
-      </c>
-      <c r="E16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" t="s">
-        <v>159</v>
+        <v>603</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>434</v>
       </c>
       <c r="B17" t="s">
         <v>266</v>
       </c>
       <c r="C17">
-        <v>3</v>
-      </c>
-      <c r="D17" t="s">
-        <v>15</v>
-      </c>
-      <c r="E17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>160</v>
+        <v>602</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>433</v>
       </c>
       <c r="B18" t="s">
         <v>266</v>
       </c>
       <c r="C18">
-        <v>3</v>
-      </c>
-      <c r="D18" t="s">
-        <v>15</v>
-      </c>
-      <c r="E18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>161</v>
+        <v>601</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>432</v>
       </c>
       <c r="B19" t="s">
         <v>266</v>
       </c>
       <c r="C19">
-        <v>3</v>
-      </c>
-      <c r="D19" t="s">
-        <v>15</v>
-      </c>
-      <c r="E19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F19" t="s">
-        <v>162</v>
+        <v>600</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>431</v>
       </c>
       <c r="B20" t="s">
         <v>266</v>
       </c>
       <c r="C20">
-        <v>3</v>
-      </c>
-      <c r="D20" t="s">
-        <v>15</v>
-      </c>
-      <c r="E20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>163</v>
+        <v>599</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>430</v>
       </c>
       <c r="B21" t="s">
         <v>266</v>
       </c>
       <c r="C21">
-        <v>3</v>
-      </c>
-      <c r="D21" t="s">
-        <v>23</v>
-      </c>
-      <c r="E21">
         <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>164</v>
+        <v>598</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>429</v>
       </c>
       <c r="B22" t="s">
         <v>266</v>
       </c>
       <c r="C22">
-        <v>3</v>
-      </c>
-      <c r="D22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E22">
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>165</v>
+        <v>597</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>428</v>
       </c>
       <c r="B23" t="s">
         <v>266</v>
       </c>
       <c r="C23">
-        <v>3</v>
-      </c>
-      <c r="D23" t="s">
-        <v>23</v>
-      </c>
-      <c r="E23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23" t="s">
-        <v>166</v>
+        <v>596</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>427</v>
       </c>
       <c r="B24" t="s">
         <v>266</v>
       </c>
       <c r="C24">
-        <v>3</v>
-      </c>
-      <c r="D24" t="s">
-        <v>23</v>
-      </c>
-      <c r="E24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>167</v>
+        <v>595</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>27</v>
+        <v>426</v>
       </c>
       <c r="B25" t="s">
         <v>266</v>
       </c>
       <c r="C25">
-        <v>3</v>
-      </c>
-      <c r="D25" t="s">
-        <v>23</v>
-      </c>
-      <c r="E25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F25" t="s">
-        <v>168</v>
+        <v>594</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>28</v>
+        <v>425</v>
       </c>
       <c r="B26" t="s">
         <v>266</v>
       </c>
       <c r="C26">
-        <v>3</v>
-      </c>
-      <c r="D26" t="s">
-        <v>23</v>
-      </c>
-      <c r="E26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>169</v>
+        <v>593</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>29</v>
+        <v>424</v>
       </c>
       <c r="B27" t="s">
         <v>266</v>
       </c>
       <c r="C27">
-        <v>3</v>
-      </c>
-      <c r="D27" t="s">
-        <v>30</v>
-      </c>
-      <c r="E27">
         <v>1</v>
       </c>
       <c r="F27" t="s">
-        <v>170</v>
+        <v>592</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>31</v>
+        <v>423</v>
       </c>
       <c r="B28" t="s">
         <v>266</v>
       </c>
       <c r="C28">
-        <v>3</v>
-      </c>
-      <c r="D28" t="s">
-        <v>30</v>
-      </c>
-      <c r="E28">
         <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>171</v>
+        <v>591</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>32</v>
+        <v>422</v>
       </c>
       <c r="B29" t="s">
         <v>266</v>
       </c>
       <c r="C29">
-        <v>3</v>
-      </c>
-      <c r="D29" t="s">
-        <v>30</v>
-      </c>
-      <c r="E29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F29" t="s">
-        <v>172</v>
+        <v>590</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>33</v>
+        <v>421</v>
       </c>
       <c r="B30" t="s">
         <v>266</v>
       </c>
       <c r="C30">
-        <v>3</v>
-      </c>
-      <c r="D30" t="s">
-        <v>30</v>
-      </c>
-      <c r="E30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F30" t="s">
-        <v>173</v>
+        <v>589</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>34</v>
+        <v>420</v>
       </c>
       <c r="B31" t="s">
         <v>266</v>
       </c>
       <c r="C31">
-        <v>3</v>
-      </c>
-      <c r="D31" t="s">
-        <v>30</v>
-      </c>
-      <c r="E31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F31" t="s">
-        <v>174</v>
+        <v>588</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>35</v>
+        <v>419</v>
       </c>
       <c r="B32" t="s">
         <v>266</v>
       </c>
       <c r="C32">
-        <v>3</v>
-      </c>
-      <c r="D32" t="s">
-        <v>30</v>
-      </c>
-      <c r="E32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>175</v>
+        <v>587</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>36</v>
+        <v>418</v>
       </c>
       <c r="B33" t="s">
         <v>266</v>
       </c>
       <c r="C33">
-        <v>3</v>
-      </c>
-      <c r="D33" t="s">
-        <v>37</v>
-      </c>
-      <c r="E33">
         <v>1</v>
       </c>
       <c r="F33" t="s">
-        <v>176</v>
+        <v>586</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>38</v>
+        <v>417</v>
       </c>
       <c r="B34" t="s">
         <v>266</v>
       </c>
       <c r="C34">
-        <v>3</v>
-      </c>
-      <c r="D34" t="s">
-        <v>37</v>
-      </c>
-      <c r="E34">
         <v>1</v>
       </c>
       <c r="F34" t="s">
-        <v>177</v>
+        <v>585</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>39</v>
+        <v>416</v>
       </c>
       <c r="B35" t="s">
         <v>266</v>
       </c>
       <c r="C35">
-        <v>3</v>
-      </c>
-      <c r="D35" t="s">
-        <v>37</v>
-      </c>
-      <c r="E35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F35" t="s">
-        <v>178</v>
+        <v>584</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>40</v>
+        <v>415</v>
       </c>
       <c r="B36" t="s">
         <v>266</v>
       </c>
       <c r="C36">
-        <v>3</v>
-      </c>
-      <c r="D36" t="s">
-        <v>37</v>
-      </c>
-      <c r="E36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F36" t="s">
-        <v>179</v>
+        <v>583</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>41</v>
+        <v>414</v>
       </c>
       <c r="B37" t="s">
         <v>266</v>
       </c>
       <c r="C37">
-        <v>3</v>
-      </c>
-      <c r="D37" t="s">
-        <v>37</v>
-      </c>
-      <c r="E37">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F37" t="s">
-        <v>180</v>
+        <v>582</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>42</v>
+        <v>413</v>
       </c>
       <c r="B38" t="s">
         <v>266</v>
       </c>
       <c r="C38">
-        <v>3</v>
-      </c>
-      <c r="D38" t="s">
-        <v>37</v>
-      </c>
-      <c r="E38">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F38" t="s">
-        <v>181</v>
+        <v>581</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>43</v>
+        <v>412</v>
       </c>
       <c r="B39" t="s">
         <v>266</v>
       </c>
       <c r="C39">
-        <v>3</v>
-      </c>
-      <c r="D39" t="s">
-        <v>44</v>
-      </c>
-      <c r="E39">
         <v>1</v>
       </c>
       <c r="F39" t="s">
-        <v>182</v>
+        <v>580</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>45</v>
+        <v>411</v>
       </c>
       <c r="B40" t="s">
         <v>266</v>
       </c>
       <c r="C40">
-        <v>3</v>
-      </c>
-      <c r="D40" t="s">
-        <v>44</v>
-      </c>
-      <c r="E40">
         <v>1</v>
       </c>
       <c r="F40" t="s">
-        <v>183</v>
+        <v>579</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>46</v>
+        <v>410</v>
       </c>
       <c r="B41" t="s">
         <v>266</v>
       </c>
       <c r="C41">
-        <v>3</v>
-      </c>
-      <c r="D41" t="s">
-        <v>44</v>
-      </c>
-      <c r="E41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F41" t="s">
-        <v>184</v>
+        <v>578</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>47</v>
+        <v>409</v>
       </c>
       <c r="B42" t="s">
         <v>266</v>
       </c>
       <c r="C42">
-        <v>3</v>
-      </c>
-      <c r="D42" t="s">
-        <v>44</v>
-      </c>
-      <c r="E42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>185</v>
+        <v>577</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>48</v>
+        <v>408</v>
       </c>
       <c r="B43" t="s">
         <v>266</v>
       </c>
       <c r="C43">
-        <v>3</v>
-      </c>
-      <c r="D43" t="s">
-        <v>44</v>
-      </c>
-      <c r="E43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F43" t="s">
-        <v>186</v>
+        <v>576</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>49</v>
+        <v>407</v>
       </c>
       <c r="B44" t="s">
         <v>266</v>
       </c>
       <c r="C44">
-        <v>3</v>
-      </c>
-      <c r="D44" t="s">
-        <v>50</v>
-      </c>
-      <c r="E44">
         <v>1</v>
       </c>
       <c r="F44" t="s">
-        <v>187</v>
+        <v>575</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>51</v>
+        <v>406</v>
       </c>
       <c r="B45" t="s">
         <v>266</v>
       </c>
       <c r="C45">
-        <v>3</v>
-      </c>
-      <c r="D45" t="s">
-        <v>50</v>
-      </c>
-      <c r="E45">
         <v>1</v>
       </c>
       <c r="F45" t="s">
-        <v>188</v>
+        <v>574</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>52</v>
+        <v>405</v>
       </c>
       <c r="B46" t="s">
         <v>266</v>
       </c>
       <c r="C46">
-        <v>3</v>
-      </c>
-      <c r="D46" t="s">
-        <v>50</v>
-      </c>
-      <c r="E46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F46" t="s">
-        <v>189</v>
+        <v>573</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>53</v>
+        <v>404</v>
       </c>
       <c r="B47" t="s">
         <v>266</v>
       </c>
       <c r="C47">
-        <v>3</v>
-      </c>
-      <c r="D47" t="s">
-        <v>50</v>
-      </c>
-      <c r="E47">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F47" t="s">
-        <v>190</v>
+        <v>572</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>54</v>
+        <v>403</v>
       </c>
       <c r="B48" t="s">
         <v>266</v>
       </c>
       <c r="C48">
-        <v>3</v>
-      </c>
-      <c r="D48" t="s">
-        <v>50</v>
-      </c>
-      <c r="E48">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F48" t="s">
-        <v>191</v>
+        <v>571</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>55</v>
+        <v>402</v>
       </c>
       <c r="B49" t="s">
         <v>266</v>
       </c>
       <c r="C49">
-        <v>3</v>
-      </c>
-      <c r="D49" t="s">
-        <v>56</v>
-      </c>
-      <c r="E49">
         <v>1</v>
       </c>
       <c r="F49" t="s">
-        <v>192</v>
+        <v>570</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>57</v>
+        <v>401</v>
       </c>
       <c r="B50" t="s">
         <v>266</v>
       </c>
       <c r="C50">
-        <v>3</v>
-      </c>
-      <c r="D50" t="s">
-        <v>56</v>
-      </c>
-      <c r="E50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F50" t="s">
-        <v>193</v>
+        <v>569</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>58</v>
+        <v>400</v>
       </c>
       <c r="B51" t="s">
         <v>266</v>
       </c>
       <c r="C51">
-        <v>3</v>
-      </c>
-      <c r="D51" t="s">
-        <v>56</v>
-      </c>
-      <c r="E51">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F51" t="s">
-        <v>194</v>
+        <v>568</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>59</v>
+        <v>399</v>
       </c>
       <c r="B52" t="s">
         <v>266</v>
       </c>
       <c r="C52">
-        <v>3</v>
-      </c>
-      <c r="D52" t="s">
-        <v>60</v>
-      </c>
-      <c r="E52">
         <v>1</v>
       </c>
       <c r="F52" t="s">
-        <v>195</v>
+        <v>567</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>61</v>
+        <v>398</v>
       </c>
       <c r="B53" t="s">
         <v>266</v>
       </c>
       <c r="C53">
-        <v>3</v>
-      </c>
-      <c r="D53" t="s">
-        <v>60</v>
-      </c>
-      <c r="E53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F53" t="s">
-        <v>196</v>
+        <v>566</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>62</v>
+        <v>397</v>
       </c>
       <c r="B54" t="s">
         <v>266</v>
       </c>
       <c r="C54">
-        <v>3</v>
-      </c>
-      <c r="D54" t="s">
-        <v>60</v>
-      </c>
-      <c r="E54">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F54" t="s">
-        <v>197</v>
+        <v>565</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>63</v>
+        <v>396</v>
       </c>
       <c r="B55" t="s">
         <v>266</v>
       </c>
       <c r="C55">
-        <v>3</v>
-      </c>
-      <c r="D55" t="s">
-        <v>60</v>
-      </c>
-      <c r="E55">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F55" t="s">
-        <v>198</v>
+        <v>564</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>64</v>
+        <v>395</v>
       </c>
       <c r="B56" t="s">
         <v>266</v>
       </c>
       <c r="C56">
-        <v>3</v>
-      </c>
-      <c r="D56" t="s">
-        <v>65</v>
-      </c>
-      <c r="E56">
         <v>1</v>
       </c>
       <c r="F56" t="s">
-        <v>199</v>
+        <v>563</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>66</v>
+        <v>394</v>
       </c>
       <c r="B57" t="s">
         <v>266</v>
       </c>
       <c r="C57">
-        <v>3</v>
-      </c>
-      <c r="D57" t="s">
-        <v>65</v>
-      </c>
-      <c r="E57">
         <v>1</v>
       </c>
       <c r="F57" t="s">
-        <v>200</v>
+        <v>562</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>67</v>
+        <v>393</v>
       </c>
       <c r="B58" t="s">
         <v>266</v>
       </c>
       <c r="C58">
-        <v>3</v>
-      </c>
-      <c r="D58" t="s">
-        <v>65</v>
-      </c>
-      <c r="E58">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F58" t="s">
-        <v>201</v>
+        <v>561</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>68</v>
+        <v>392</v>
       </c>
       <c r="B59" t="s">
-        <v>68</v>
+        <v>266</v>
       </c>
       <c r="C59">
-        <v>3</v>
-      </c>
-      <c r="D59" t="s">
-        <v>65</v>
-      </c>
-      <c r="E59">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="F59" t="s">
+        <v>560</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>68</v>
+        <v>391</v>
       </c>
       <c r="B60" t="s">
-        <v>68</v>
+        <v>266</v>
       </c>
       <c r="C60">
-        <v>3</v>
-      </c>
-      <c r="D60" t="s">
-        <v>69</v>
-      </c>
-      <c r="E60">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="F60" t="s">
+        <v>559</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>68</v>
+        <v>390</v>
       </c>
       <c r="B61" t="s">
-        <v>68</v>
+        <v>266</v>
       </c>
       <c r="C61">
-        <v>3</v>
-      </c>
-      <c r="D61" t="s">
-        <v>69</v>
-      </c>
-      <c r="E61">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F61" t="s">
+        <v>558</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>68</v>
+        <v>389</v>
       </c>
       <c r="B62" t="s">
-        <v>68</v>
+        <v>266</v>
       </c>
       <c r="C62">
-        <v>3</v>
-      </c>
-      <c r="D62" t="s">
-        <v>69</v>
-      </c>
-      <c r="E62">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="F62" t="s">
+        <v>557</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>70</v>
+        <v>388</v>
       </c>
       <c r="B63" t="s">
         <v>266</v>
       </c>
       <c r="C63">
-        <v>2</v>
-      </c>
-      <c r="D63" t="s">
-        <v>71</v>
-      </c>
-      <c r="E63">
         <v>1</v>
       </c>
       <c r="F63" t="s">
-        <v>202</v>
+        <v>556</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>72</v>
+        <v>387</v>
       </c>
       <c r="B64" t="s">
         <v>266</v>
       </c>
       <c r="C64">
-        <v>2</v>
-      </c>
-      <c r="D64" t="s">
-        <v>71</v>
-      </c>
-      <c r="E64">
         <v>1</v>
       </c>
       <c r="F64" t="s">
-        <v>203</v>
+        <v>555</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>73</v>
+        <v>386</v>
       </c>
       <c r="B65" t="s">
         <v>266</v>
       </c>
       <c r="C65">
-        <v>2</v>
-      </c>
-      <c r="D65" t="s">
-        <v>71</v>
-      </c>
-      <c r="E65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F65" t="s">
-        <v>204</v>
+        <v>554</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>74</v>
+        <v>385</v>
       </c>
       <c r="B66" t="s">
         <v>266</v>
       </c>
       <c r="C66">
-        <v>2</v>
-      </c>
-      <c r="D66" t="s">
-        <v>71</v>
-      </c>
-      <c r="E66">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F66" t="s">
-        <v>205</v>
+        <v>553</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>75</v>
+        <v>384</v>
       </c>
       <c r="B67" t="s">
         <v>266</v>
       </c>
       <c r="C67">
-        <v>2</v>
-      </c>
-      <c r="D67" t="s">
-        <v>71</v>
-      </c>
-      <c r="E67">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F67" t="s">
-        <v>206</v>
+        <v>552</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>76</v>
+        <v>383</v>
       </c>
       <c r="B68" t="s">
         <v>266</v>
       </c>
       <c r="C68">
-        <v>2</v>
-      </c>
-      <c r="D68" t="s">
-        <v>77</v>
-      </c>
-      <c r="E68">
         <v>1</v>
       </c>
       <c r="F68" t="s">
-        <v>207</v>
+        <v>551</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>78</v>
+        <v>382</v>
       </c>
       <c r="B69" t="s">
         <v>266</v>
       </c>
       <c r="C69">
-        <v>2</v>
-      </c>
-      <c r="D69" t="s">
-        <v>77</v>
-      </c>
-      <c r="E69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F69" t="s">
-        <v>208</v>
+        <v>550</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>79</v>
+        <v>381</v>
       </c>
       <c r="B70" t="s">
         <v>266</v>
       </c>
       <c r="C70">
-        <v>2</v>
-      </c>
-      <c r="D70" t="s">
-        <v>77</v>
-      </c>
-      <c r="E70">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F70" t="s">
-        <v>209</v>
+        <v>549</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>80</v>
+        <v>380</v>
       </c>
       <c r="B71" t="s">
         <v>266</v>
       </c>
       <c r="C71">
-        <v>2</v>
-      </c>
-      <c r="D71" t="s">
-        <v>81</v>
-      </c>
-      <c r="E71">
         <v>1</v>
       </c>
       <c r="F71" t="s">
-        <v>210</v>
+        <v>548</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>82</v>
+        <v>379</v>
       </c>
       <c r="B72" t="s">
         <v>266</v>
       </c>
       <c r="C72">
-        <v>2</v>
-      </c>
-      <c r="D72" t="s">
-        <v>81</v>
-      </c>
-      <c r="E72">
         <v>1</v>
       </c>
       <c r="F72" t="s">
-        <v>211</v>
+        <v>547</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>83</v>
+        <v>378</v>
       </c>
       <c r="B73" t="s">
         <v>266</v>
       </c>
       <c r="C73">
-        <v>2</v>
-      </c>
-      <c r="D73" t="s">
-        <v>81</v>
-      </c>
-      <c r="E73">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F73" t="s">
-        <v>212</v>
+        <v>546</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>84</v>
+        <v>377</v>
       </c>
       <c r="B74" t="s">
         <v>266</v>
       </c>
       <c r="C74">
-        <v>2</v>
-      </c>
-      <c r="D74" t="s">
-        <v>81</v>
-      </c>
-      <c r="E74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F74" t="s">
-        <v>213</v>
+        <v>545</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>85</v>
+        <v>376</v>
       </c>
       <c r="B75" t="s">
         <v>266</v>
       </c>
       <c r="C75">
-        <v>2</v>
-      </c>
-      <c r="D75" t="s">
-        <v>81</v>
-      </c>
-      <c r="E75">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F75" t="s">
-        <v>214</v>
+        <v>544</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>86</v>
+        <v>375</v>
       </c>
       <c r="B76" t="s">
         <v>266</v>
       </c>
       <c r="C76">
-        <v>2</v>
-      </c>
-      <c r="D76" t="s">
-        <v>81</v>
-      </c>
-      <c r="E76">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F76" t="s">
-        <v>215</v>
+        <v>543</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>87</v>
+        <v>374</v>
       </c>
       <c r="B77" t="s">
         <v>266</v>
       </c>
       <c r="C77">
-        <v>2</v>
-      </c>
-      <c r="D77" t="s">
-        <v>88</v>
-      </c>
-      <c r="E77">
         <v>1</v>
       </c>
       <c r="F77" t="s">
-        <v>216</v>
+        <v>542</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>89</v>
+        <v>373</v>
       </c>
       <c r="B78" t="s">
         <v>266</v>
       </c>
       <c r="C78">
-        <v>2</v>
-      </c>
-      <c r="D78" t="s">
-        <v>88</v>
-      </c>
-      <c r="E78">
         <v>1</v>
       </c>
       <c r="F78" t="s">
-        <v>217</v>
+        <v>541</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>90</v>
+        <v>372</v>
       </c>
       <c r="B79" t="s">
         <v>266</v>
       </c>
       <c r="C79">
-        <v>2</v>
-      </c>
-      <c r="D79" t="s">
-        <v>88</v>
-      </c>
-      <c r="E79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F79" t="s">
-        <v>218</v>
+        <v>540</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>91</v>
+        <v>371</v>
       </c>
       <c r="B80" t="s">
         <v>266</v>
       </c>
       <c r="C80">
-        <v>2</v>
-      </c>
-      <c r="D80" t="s">
-        <v>88</v>
-      </c>
-      <c r="E80">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F80" t="s">
-        <v>219</v>
+        <v>539</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>92</v>
+        <v>370</v>
       </c>
       <c r="B81" t="s">
         <v>266</v>
       </c>
       <c r="C81">
-        <v>2</v>
-      </c>
-      <c r="D81" t="s">
-        <v>88</v>
-      </c>
-      <c r="E81">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F81" t="s">
-        <v>220</v>
+        <v>538</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>93</v>
+        <v>369</v>
       </c>
       <c r="B82" t="s">
         <v>266</v>
       </c>
       <c r="C82">
-        <v>2</v>
-      </c>
-      <c r="D82" t="s">
-        <v>88</v>
-      </c>
-      <c r="E82">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F82" t="s">
-        <v>221</v>
+        <v>537</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>94</v>
+        <v>368</v>
       </c>
       <c r="B83" t="s">
-        <v>94</v>
+        <v>266</v>
       </c>
       <c r="C83">
-        <v>3</v>
-      </c>
-      <c r="D83" t="s">
-        <v>95</v>
-      </c>
-      <c r="E83">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="F83" t="s">
+        <v>536</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>94</v>
+        <v>367</v>
       </c>
       <c r="B84" t="s">
-        <v>94</v>
+        <v>266</v>
       </c>
       <c r="C84">
-        <v>3</v>
-      </c>
-      <c r="D84" t="s">
-        <v>95</v>
-      </c>
-      <c r="E84">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F84" t="s">
+        <v>535</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>94</v>
+        <v>366</v>
       </c>
       <c r="B85" t="s">
-        <v>94</v>
+        <v>266</v>
       </c>
       <c r="C85">
-        <v>3</v>
-      </c>
-      <c r="D85" t="s">
-        <v>95</v>
-      </c>
-      <c r="E85">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="F85" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>96</v>
+        <v>365</v>
       </c>
       <c r="B86" t="s">
         <v>266</v>
       </c>
       <c r="C86">
-        <v>3</v>
-      </c>
-      <c r="D86" t="s">
-        <v>97</v>
-      </c>
-      <c r="E86">
         <v>1</v>
       </c>
       <c r="F86" t="s">
-        <v>222</v>
+        <v>533</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>98</v>
+        <v>364</v>
       </c>
       <c r="B87" t="s">
         <v>266</v>
       </c>
       <c r="C87">
-        <v>3</v>
-      </c>
-      <c r="D87" t="s">
-        <v>97</v>
-      </c>
-      <c r="E87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F87" t="s">
-        <v>223</v>
+        <v>532</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>99</v>
+        <v>363</v>
       </c>
       <c r="B88" t="s">
         <v>266</v>
       </c>
       <c r="C88">
-        <v>3</v>
-      </c>
-      <c r="D88" t="s">
-        <v>97</v>
-      </c>
-      <c r="E88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F88" t="s">
-        <v>224</v>
+        <v>531</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>100</v>
+        <v>362</v>
       </c>
       <c r="B89" t="s">
         <v>266</v>
       </c>
       <c r="C89">
-        <v>3</v>
-      </c>
-      <c r="D89" t="s">
-        <v>97</v>
-      </c>
-      <c r="E89">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F89" t="s">
-        <v>225</v>
+        <v>530</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>101</v>
+        <v>361</v>
       </c>
       <c r="B90" t="s">
         <v>266</v>
       </c>
       <c r="C90">
-        <v>3</v>
-      </c>
-      <c r="D90" t="s">
-        <v>102</v>
-      </c>
-      <c r="E90">
         <v>1</v>
       </c>
       <c r="F90" t="s">
-        <v>226</v>
+        <v>529</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>103</v>
+        <v>360</v>
       </c>
       <c r="B91" t="s">
         <v>266</v>
       </c>
       <c r="C91">
-        <v>3</v>
-      </c>
-      <c r="D91" t="s">
-        <v>102</v>
-      </c>
-      <c r="E91">
         <v>1</v>
       </c>
       <c r="F91" t="s">
-        <v>227</v>
+        <v>528</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>104</v>
+        <v>359</v>
       </c>
       <c r="B92" t="s">
         <v>266</v>
       </c>
       <c r="C92">
-        <v>3</v>
-      </c>
-      <c r="D92" t="s">
-        <v>102</v>
-      </c>
-      <c r="E92">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F92" t="s">
-        <v>228</v>
+        <v>527</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>105</v>
+        <v>358</v>
       </c>
       <c r="B93" t="s">
         <v>266</v>
       </c>
       <c r="C93">
-        <v>3</v>
-      </c>
-      <c r="D93" t="s">
-        <v>102</v>
-      </c>
-      <c r="E93">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F93" t="s">
-        <v>229</v>
+        <v>526</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>106</v>
+        <v>357</v>
       </c>
       <c r="B94" t="s">
         <v>266</v>
       </c>
       <c r="C94">
-        <v>3</v>
-      </c>
-      <c r="D94" t="s">
-        <v>102</v>
-      </c>
-      <c r="E94">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F94" t="s">
-        <v>230</v>
+        <v>525</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>107</v>
+        <v>356</v>
       </c>
       <c r="B95" t="s">
         <v>266</v>
       </c>
       <c r="C95">
-        <v>3</v>
-      </c>
-      <c r="D95" t="s">
-        <v>108</v>
-      </c>
-      <c r="E95">
         <v>1</v>
       </c>
       <c r="F95" t="s">
-        <v>231</v>
+        <v>524</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>109</v>
+        <v>355</v>
       </c>
       <c r="B96" t="s">
         <v>266</v>
       </c>
       <c r="C96">
-        <v>3</v>
-      </c>
-      <c r="D96" t="s">
-        <v>108</v>
-      </c>
-      <c r="E96">
         <v>1</v>
       </c>
       <c r="F96" t="s">
-        <v>232</v>
+        <v>523</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>110</v>
+        <v>354</v>
       </c>
       <c r="B97" t="s">
         <v>266</v>
       </c>
       <c r="C97">
-        <v>3</v>
-      </c>
-      <c r="D97" t="s">
-        <v>108</v>
-      </c>
-      <c r="E97">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F97" t="s">
-        <v>233</v>
+        <v>522</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>111</v>
+        <v>353</v>
       </c>
       <c r="B98" t="s">
         <v>266</v>
       </c>
       <c r="C98">
-        <v>3</v>
-      </c>
-      <c r="D98" t="s">
-        <v>108</v>
-      </c>
-      <c r="E98">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F98" t="s">
-        <v>234</v>
+        <v>521</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>112</v>
+        <v>352</v>
       </c>
       <c r="B99" t="s">
         <v>266</v>
       </c>
       <c r="C99">
-        <v>3</v>
-      </c>
-      <c r="D99" t="s">
-        <v>108</v>
-      </c>
-      <c r="E99">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F99" t="s">
-        <v>235</v>
+        <v>520</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>113</v>
+        <v>351</v>
       </c>
       <c r="B100" t="s">
         <v>266</v>
       </c>
       <c r="C100">
-        <v>3</v>
-      </c>
-      <c r="D100" t="s">
-        <v>108</v>
-      </c>
-      <c r="E100">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F100" t="s">
-        <v>236</v>
+        <v>519</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>114</v>
+        <v>350</v>
       </c>
       <c r="B101" t="s">
         <v>266</v>
       </c>
       <c r="C101">
-        <v>2</v>
-      </c>
-      <c r="D101" t="s">
-        <v>115</v>
-      </c>
-      <c r="E101">
         <v>1</v>
       </c>
       <c r="F101" t="s">
-        <v>237</v>
+        <v>518</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>116</v>
+        <v>349</v>
       </c>
       <c r="B102" t="s">
         <v>266</v>
       </c>
       <c r="C102">
-        <v>2</v>
-      </c>
-      <c r="D102" t="s">
-        <v>115</v>
-      </c>
-      <c r="E102">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F102" t="s">
-        <v>238</v>
+        <v>517</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>117</v>
+        <v>348</v>
       </c>
       <c r="B103" t="s">
         <v>266</v>
       </c>
       <c r="C103">
-        <v>2</v>
-      </c>
-      <c r="D103" t="s">
-        <v>115</v>
-      </c>
-      <c r="E103">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F103" t="s">
-        <v>239</v>
+        <v>516</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>118</v>
+        <v>347</v>
       </c>
       <c r="B104" t="s">
         <v>266</v>
       </c>
       <c r="C104">
-        <v>2</v>
-      </c>
-      <c r="D104" t="s">
-        <v>115</v>
-      </c>
-      <c r="E104">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F104" t="s">
-        <v>240</v>
+        <v>515</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>119</v>
+        <v>346</v>
       </c>
       <c r="B105" t="s">
         <v>266</v>
       </c>
       <c r="C105">
-        <v>2</v>
-      </c>
-      <c r="D105" t="s">
-        <v>120</v>
-      </c>
-      <c r="E105">
         <v>1</v>
       </c>
       <c r="F105" t="s">
-        <v>241</v>
+        <v>514</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>121</v>
+        <v>345</v>
       </c>
       <c r="B106" t="s">
         <v>266</v>
       </c>
       <c r="C106">
-        <v>2</v>
-      </c>
-      <c r="D106" t="s">
-        <v>120</v>
-      </c>
-      <c r="E106">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F106" t="s">
-        <v>242</v>
+        <v>513</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>122</v>
+        <v>344</v>
       </c>
       <c r="B107" t="s">
         <v>266</v>
       </c>
       <c r="C107">
-        <v>2</v>
-      </c>
-      <c r="D107" t="s">
-        <v>120</v>
-      </c>
-      <c r="E107">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F107" t="s">
-        <v>243</v>
+        <v>512</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>123</v>
+        <v>343</v>
       </c>
       <c r="B108" t="s">
         <v>266</v>
       </c>
       <c r="C108">
-        <v>2</v>
-      </c>
-      <c r="D108" t="s">
-        <v>120</v>
-      </c>
-      <c r="E108">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F108" t="s">
-        <v>244</v>
+        <v>511</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>124</v>
+        <v>342</v>
       </c>
       <c r="B109" t="s">
         <v>266</v>
       </c>
       <c r="C109">
-        <v>2</v>
-      </c>
-      <c r="D109" t="s">
-        <v>120</v>
-      </c>
-      <c r="E109">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F109" t="s">
-        <v>245</v>
+        <v>510</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>125</v>
+        <v>341</v>
       </c>
       <c r="B110" t="s">
         <v>266</v>
       </c>
       <c r="C110">
-        <v>2</v>
-      </c>
-      <c r="D110" t="s">
-        <v>126</v>
-      </c>
-      <c r="E110">
         <v>1</v>
       </c>
       <c r="F110" t="s">
-        <v>246</v>
+        <v>509</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>127</v>
+        <v>340</v>
       </c>
       <c r="B111" t="s">
         <v>266</v>
       </c>
       <c r="C111">
-        <v>2</v>
-      </c>
-      <c r="D111" t="s">
-        <v>126</v>
-      </c>
-      <c r="E111">
         <v>1</v>
       </c>
       <c r="F111" t="s">
-        <v>247</v>
+        <v>508</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>128</v>
+        <v>339</v>
       </c>
       <c r="B112" t="s">
         <v>266</v>
       </c>
       <c r="C112">
-        <v>2</v>
-      </c>
-      <c r="D112" t="s">
-        <v>126</v>
-      </c>
-      <c r="E112">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F112" t="s">
-        <v>248</v>
+        <v>507</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>129</v>
+        <v>338</v>
       </c>
       <c r="B113" t="s">
         <v>266</v>
       </c>
       <c r="C113">
-        <v>2</v>
-      </c>
-      <c r="D113" t="s">
-        <v>126</v>
-      </c>
-      <c r="E113">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F113" t="s">
-        <v>249</v>
+        <v>506</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>130</v>
+        <v>337</v>
       </c>
       <c r="B114" t="s">
         <v>266</v>
       </c>
       <c r="C114">
-        <v>2</v>
-      </c>
-      <c r="D114" t="s">
-        <v>131</v>
-      </c>
-      <c r="E114">
         <v>1</v>
       </c>
       <c r="F114" t="s">
-        <v>250</v>
+        <v>505</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>132</v>
+        <v>336</v>
       </c>
       <c r="B115" t="s">
         <v>266</v>
       </c>
       <c r="C115">
-        <v>2</v>
-      </c>
-      <c r="D115" t="s">
-        <v>131</v>
-      </c>
-      <c r="E115">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F115" t="s">
-        <v>251</v>
+        <v>504</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>133</v>
+        <v>335</v>
       </c>
       <c r="B116" t="s">
         <v>266</v>
       </c>
       <c r="C116">
-        <v>2</v>
-      </c>
-      <c r="D116" t="s">
-        <v>131</v>
-      </c>
-      <c r="E116">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F116" t="s">
-        <v>252</v>
+        <v>503</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>134</v>
+        <v>334</v>
       </c>
       <c r="B117" t="s">
         <v>266</v>
       </c>
       <c r="C117">
-        <v>2</v>
-      </c>
-      <c r="D117" t="s">
-        <v>131</v>
-      </c>
-      <c r="E117">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F117" t="s">
-        <v>253</v>
+        <v>502</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>135</v>
+        <v>333</v>
       </c>
       <c r="B118" t="s">
         <v>266</v>
       </c>
       <c r="C118">
-        <v>2</v>
-      </c>
-      <c r="D118" t="s">
-        <v>136</v>
-      </c>
-      <c r="E118">
         <v>1</v>
       </c>
       <c r="F118" t="s">
-        <v>254</v>
+        <v>501</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>137</v>
+        <v>332</v>
       </c>
       <c r="B119" t="s">
         <v>266</v>
       </c>
       <c r="C119">
-        <v>2</v>
-      </c>
-      <c r="D119" t="s">
-        <v>136</v>
-      </c>
-      <c r="E119">
         <v>1</v>
       </c>
       <c r="F119" t="s">
-        <v>255</v>
+        <v>500</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>138</v>
+        <v>331</v>
       </c>
       <c r="B120" t="s">
         <v>266</v>
       </c>
       <c r="C120">
-        <v>2</v>
-      </c>
-      <c r="D120" t="s">
-        <v>136</v>
-      </c>
-      <c r="E120">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F120" t="s">
-        <v>256</v>
+        <v>499</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>139</v>
+        <v>330</v>
       </c>
       <c r="B121" t="s">
         <v>266</v>
       </c>
       <c r="C121">
-        <v>2</v>
-      </c>
-      <c r="D121" t="s">
-        <v>136</v>
-      </c>
-      <c r="E121">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F121" t="s">
-        <v>257</v>
+        <v>498</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>140</v>
+        <v>329</v>
       </c>
       <c r="B122" t="s">
         <v>266</v>
       </c>
       <c r="C122">
-        <v>2</v>
-      </c>
-      <c r="D122" t="s">
-        <v>136</v>
-      </c>
-      <c r="E122">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F122" t="s">
-        <v>258</v>
+        <v>497</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>141</v>
+        <v>328</v>
       </c>
       <c r="B123" t="s">
         <v>266</v>
       </c>
       <c r="C123">
-        <v>2</v>
-      </c>
-      <c r="D123" t="s">
-        <v>136</v>
-      </c>
-      <c r="E123">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F123" t="s">
-        <v>259</v>
+        <v>496</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>94</v>
+        <v>327</v>
       </c>
       <c r="B124" t="s">
-        <v>94</v>
+        <v>266</v>
       </c>
       <c r="C124">
-        <v>2</v>
-      </c>
-      <c r="D124" t="s">
-        <v>142</v>
-      </c>
-      <c r="E124">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="F124" t="s">
+        <v>495</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>94</v>
+        <v>326</v>
       </c>
       <c r="B125" t="s">
-        <v>94</v>
+        <v>266</v>
       </c>
       <c r="C125">
-        <v>2</v>
-      </c>
-      <c r="D125" t="s">
-        <v>142</v>
-      </c>
-      <c r="E125">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F125" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>94</v>
+        <v>325</v>
       </c>
       <c r="B126" t="s">
-        <v>94</v>
+        <v>266</v>
       </c>
       <c r="C126">
-        <v>2</v>
-      </c>
-      <c r="D126" t="s">
-        <v>142</v>
-      </c>
-      <c r="E126">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="F126" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>94</v>
+        <v>324</v>
       </c>
       <c r="B127" t="s">
-        <v>94</v>
+        <v>266</v>
       </c>
       <c r="C127">
-        <v>2</v>
-      </c>
-      <c r="D127" t="s">
-        <v>143</v>
-      </c>
-      <c r="E127">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="F127" t="s">
+        <v>492</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
+        <v>323</v>
+      </c>
+      <c r="B128" t="s">
+        <v>266</v>
+      </c>
+      <c r="C128">
+        <v>1</v>
+      </c>
+      <c r="F128" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>322</v>
+      </c>
+      <c r="B129" t="s">
+        <v>266</v>
+      </c>
+      <c r="C129">
+        <v>1</v>
+      </c>
+      <c r="F129" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>321</v>
+      </c>
+      <c r="B130" t="s">
+        <v>266</v>
+      </c>
+      <c r="C130">
+        <v>1</v>
+      </c>
+      <c r="F130" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>320</v>
+      </c>
+      <c r="B131" t="s">
+        <v>266</v>
+      </c>
+      <c r="C131">
+        <v>1</v>
+      </c>
+      <c r="F131" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>319</v>
+      </c>
+      <c r="B132" t="s">
+        <v>266</v>
+      </c>
+      <c r="C132">
+        <v>1</v>
+      </c>
+      <c r="F132" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>318</v>
+      </c>
+      <c r="B133" t="s">
+        <v>266</v>
+      </c>
+      <c r="C133">
+        <v>1</v>
+      </c>
+      <c r="F133" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>317</v>
+      </c>
+      <c r="B134" t="s">
+        <v>266</v>
+      </c>
+      <c r="C134">
+        <v>1</v>
+      </c>
+      <c r="F134" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>316</v>
+      </c>
+      <c r="B135" t="s">
+        <v>266</v>
+      </c>
+      <c r="C135">
+        <v>1</v>
+      </c>
+      <c r="F135" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>315</v>
+      </c>
+      <c r="B136" t="s">
+        <v>266</v>
+      </c>
+      <c r="C136">
+        <v>1</v>
+      </c>
+      <c r="F136" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>314</v>
+      </c>
+      <c r="B137" t="s">
+        <v>266</v>
+      </c>
+      <c r="C137">
+        <v>1</v>
+      </c>
+      <c r="F137" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>313</v>
+      </c>
+      <c r="B138" t="s">
+        <v>266</v>
+      </c>
+      <c r="C138">
+        <v>1</v>
+      </c>
+      <c r="F138" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>312</v>
+      </c>
+      <c r="B139" t="s">
+        <v>266</v>
+      </c>
+      <c r="C139">
+        <v>1</v>
+      </c>
+      <c r="F139" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>311</v>
+      </c>
+      <c r="B140" t="s">
+        <v>266</v>
+      </c>
+      <c r="C140">
+        <v>1</v>
+      </c>
+      <c r="F140" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>450</v>
+      </c>
+      <c r="B141" t="s">
+        <v>266</v>
+      </c>
+      <c r="C141">
+        <v>1</v>
+      </c>
+      <c r="F141" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>310</v>
+      </c>
+      <c r="B142" t="s">
+        <v>266</v>
+      </c>
+      <c r="C142">
+        <v>1</v>
+      </c>
+      <c r="F142" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>309</v>
+      </c>
+      <c r="B143" t="s">
+        <v>266</v>
+      </c>
+      <c r="C143">
+        <v>1</v>
+      </c>
+      <c r="F143" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>308</v>
+      </c>
+      <c r="B144" t="s">
+        <v>266</v>
+      </c>
+      <c r="C144">
+        <v>1</v>
+      </c>
+      <c r="F144" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>307</v>
+      </c>
+      <c r="B145" t="s">
+        <v>266</v>
+      </c>
+      <c r="C145">
+        <v>1</v>
+      </c>
+      <c r="F145" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>306</v>
+      </c>
+      <c r="B146" t="s">
+        <v>266</v>
+      </c>
+      <c r="C146">
+        <v>1</v>
+      </c>
+      <c r="F146" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>305</v>
+      </c>
+      <c r="B147" t="s">
+        <v>266</v>
+      </c>
+      <c r="C147">
+        <v>1</v>
+      </c>
+      <c r="F147" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>304</v>
+      </c>
+      <c r="B148" t="s">
+        <v>266</v>
+      </c>
+      <c r="C148">
+        <v>1</v>
+      </c>
+      <c r="F148" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>303</v>
+      </c>
+      <c r="B149" t="s">
+        <v>266</v>
+      </c>
+      <c r="C149">
+        <v>1</v>
+      </c>
+      <c r="F149" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>302</v>
+      </c>
+      <c r="B150" t="s">
+        <v>266</v>
+      </c>
+      <c r="C150">
+        <v>1</v>
+      </c>
+      <c r="F150" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>301</v>
+      </c>
+      <c r="B151" t="s">
+        <v>266</v>
+      </c>
+      <c r="C151">
+        <v>1</v>
+      </c>
+      <c r="F151" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>300</v>
+      </c>
+      <c r="B152" t="s">
+        <v>266</v>
+      </c>
+      <c r="C152">
+        <v>1</v>
+      </c>
+      <c r="F152" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>299</v>
+      </c>
+      <c r="B153" t="s">
+        <v>266</v>
+      </c>
+      <c r="C153">
+        <v>1</v>
+      </c>
+      <c r="F153" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>298</v>
+      </c>
+      <c r="B154" t="s">
+        <v>266</v>
+      </c>
+      <c r="C154">
+        <v>1</v>
+      </c>
+      <c r="F154" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>297</v>
+      </c>
+      <c r="B155" t="s">
+        <v>266</v>
+      </c>
+      <c r="C155">
+        <v>1</v>
+      </c>
+      <c r="F155" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>296</v>
+      </c>
+      <c r="B156" t="s">
+        <v>266</v>
+      </c>
+      <c r="C156">
+        <v>1</v>
+      </c>
+      <c r="F156" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>295</v>
+      </c>
+      <c r="B157" t="s">
+        <v>266</v>
+      </c>
+      <c r="C157">
+        <v>1</v>
+      </c>
+      <c r="F157" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>294</v>
+      </c>
+      <c r="B158" t="s">
+        <v>266</v>
+      </c>
+      <c r="C158">
+        <v>1</v>
+      </c>
+      <c r="F158" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>293</v>
+      </c>
+      <c r="B159" t="s">
+        <v>266</v>
+      </c>
+      <c r="C159">
+        <v>1</v>
+      </c>
+      <c r="F159" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>292</v>
+      </c>
+      <c r="B160" t="s">
+        <v>266</v>
+      </c>
+      <c r="C160">
+        <v>1</v>
+      </c>
+      <c r="F160" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>291</v>
+      </c>
+      <c r="B161" t="s">
+        <v>266</v>
+      </c>
+      <c r="C161">
+        <v>1</v>
+      </c>
+      <c r="F161" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>290</v>
+      </c>
+      <c r="B162" t="s">
+        <v>266</v>
+      </c>
+      <c r="C162">
+        <v>1</v>
+      </c>
+      <c r="F162" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>289</v>
+      </c>
+      <c r="B163" t="s">
+        <v>266</v>
+      </c>
+      <c r="C163">
+        <v>1</v>
+      </c>
+      <c r="F163" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>288</v>
+      </c>
+      <c r="B164" t="s">
+        <v>266</v>
+      </c>
+      <c r="C164">
+        <v>1</v>
+      </c>
+      <c r="F164" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>287</v>
+      </c>
+      <c r="B165" t="s">
+        <v>266</v>
+      </c>
+      <c r="C165">
+        <v>1</v>
+      </c>
+      <c r="F165" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>286</v>
+      </c>
+      <c r="B166" t="s">
+        <v>266</v>
+      </c>
+      <c r="C166">
+        <v>1</v>
+      </c>
+      <c r="F166" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>285</v>
+      </c>
+      <c r="B167" t="s">
+        <v>266</v>
+      </c>
+      <c r="C167">
+        <v>1</v>
+      </c>
+      <c r="F167" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>284</v>
+      </c>
+      <c r="B168" t="s">
+        <v>266</v>
+      </c>
+      <c r="C168">
+        <v>1</v>
+      </c>
+      <c r="F168" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>283</v>
+      </c>
+      <c r="B169" t="s">
+        <v>266</v>
+      </c>
+      <c r="C169">
+        <v>1</v>
+      </c>
+      <c r="F169" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>275</v>
+      </c>
+      <c r="B170" t="s">
+        <v>266</v>
+      </c>
+      <c r="C170">
+        <v>1</v>
+      </c>
+      <c r="F170" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>274</v>
+      </c>
+      <c r="B171" t="s">
+        <v>266</v>
+      </c>
+      <c r="C171">
+        <v>1</v>
+      </c>
+      <c r="F171" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>273</v>
+      </c>
+      <c r="B172" t="s">
+        <v>266</v>
+      </c>
+      <c r="C172">
+        <v>1</v>
+      </c>
+      <c r="F172" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>272</v>
+      </c>
+      <c r="B173" t="s">
+        <v>266</v>
+      </c>
+      <c r="C173">
+        <v>1</v>
+      </c>
+      <c r="F173" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>271</v>
+      </c>
+      <c r="B174" t="s">
+        <v>266</v>
+      </c>
+      <c r="C174">
+        <v>1</v>
+      </c>
+      <c r="F174" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>270</v>
+      </c>
+      <c r="B175" t="s">
+        <v>266</v>
+      </c>
+      <c r="C175">
+        <v>1</v>
+      </c>
+      <c r="F175" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>269</v>
+      </c>
+      <c r="B176" t="s">
+        <v>266</v>
+      </c>
+      <c r="C176">
+        <v>1</v>
+      </c>
+      <c r="F176" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>267</v>
+      </c>
+      <c r="B177" t="s">
+        <v>266</v>
+      </c>
+      <c r="C177">
+        <v>1</v>
+      </c>
+      <c r="F177" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>70</v>
+      </c>
+      <c r="B178" t="s">
+        <v>266</v>
+      </c>
+      <c r="C178">
+        <v>2</v>
+      </c>
+      <c r="D178" t="s">
+        <v>71</v>
+      </c>
+      <c r="E178">
+        <v>1</v>
+      </c>
+      <c r="F178" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>72</v>
+      </c>
+      <c r="B179" t="s">
+        <v>266</v>
+      </c>
+      <c r="C179">
+        <v>2</v>
+      </c>
+      <c r="D179" t="s">
+        <v>71</v>
+      </c>
+      <c r="E179">
+        <v>1</v>
+      </c>
+      <c r="F179" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>73</v>
+      </c>
+      <c r="B180" t="s">
+        <v>266</v>
+      </c>
+      <c r="C180">
+        <v>2</v>
+      </c>
+      <c r="D180" t="s">
+        <v>71</v>
+      </c>
+      <c r="E180">
+        <v>2</v>
+      </c>
+      <c r="F180" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>74</v>
+      </c>
+      <c r="B181" t="s">
+        <v>266</v>
+      </c>
+      <c r="C181">
+        <v>2</v>
+      </c>
+      <c r="D181" t="s">
+        <v>71</v>
+      </c>
+      <c r="E181">
+        <v>3</v>
+      </c>
+      <c r="F181" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>75</v>
+      </c>
+      <c r="B182" t="s">
+        <v>266</v>
+      </c>
+      <c r="C182">
+        <v>2</v>
+      </c>
+      <c r="D182" t="s">
+        <v>71</v>
+      </c>
+      <c r="E182">
+        <v>3</v>
+      </c>
+      <c r="F182" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>76</v>
+      </c>
+      <c r="B183" t="s">
+        <v>266</v>
+      </c>
+      <c r="C183">
+        <v>2</v>
+      </c>
+      <c r="D183" t="s">
+        <v>77</v>
+      </c>
+      <c r="E183">
+        <v>1</v>
+      </c>
+      <c r="F183" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>78</v>
+      </c>
+      <c r="B184" t="s">
+        <v>266</v>
+      </c>
+      <c r="C184">
+        <v>2</v>
+      </c>
+      <c r="D184" t="s">
+        <v>77</v>
+      </c>
+      <c r="E184">
+        <v>2</v>
+      </c>
+      <c r="F184" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>79</v>
+      </c>
+      <c r="B185" t="s">
+        <v>266</v>
+      </c>
+      <c r="C185">
+        <v>2</v>
+      </c>
+      <c r="D185" t="s">
+        <v>77</v>
+      </c>
+      <c r="E185">
+        <v>3</v>
+      </c>
+      <c r="F185" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>80</v>
+      </c>
+      <c r="B186" t="s">
+        <v>266</v>
+      </c>
+      <c r="C186">
+        <v>2</v>
+      </c>
+      <c r="D186" t="s">
+        <v>81</v>
+      </c>
+      <c r="E186">
+        <v>1</v>
+      </c>
+      <c r="F186" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>82</v>
+      </c>
+      <c r="B187" t="s">
+        <v>266</v>
+      </c>
+      <c r="C187">
+        <v>2</v>
+      </c>
+      <c r="D187" t="s">
+        <v>81</v>
+      </c>
+      <c r="E187">
+        <v>1</v>
+      </c>
+      <c r="F187" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>83</v>
+      </c>
+      <c r="B188" t="s">
+        <v>266</v>
+      </c>
+      <c r="C188">
+        <v>2</v>
+      </c>
+      <c r="D188" t="s">
+        <v>81</v>
+      </c>
+      <c r="E188">
+        <v>2</v>
+      </c>
+      <c r="F188" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>84</v>
+      </c>
+      <c r="B189" t="s">
+        <v>266</v>
+      </c>
+      <c r="C189">
+        <v>2</v>
+      </c>
+      <c r="D189" t="s">
+        <v>81</v>
+      </c>
+      <c r="E189">
+        <v>2</v>
+      </c>
+      <c r="F189" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>85</v>
+      </c>
+      <c r="B190" t="s">
+        <v>266</v>
+      </c>
+      <c r="C190">
+        <v>2</v>
+      </c>
+      <c r="D190" t="s">
+        <v>81</v>
+      </c>
+      <c r="E190">
+        <v>3</v>
+      </c>
+      <c r="F190" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>86</v>
+      </c>
+      <c r="B191" t="s">
+        <v>266</v>
+      </c>
+      <c r="C191">
+        <v>2</v>
+      </c>
+      <c r="D191" t="s">
+        <v>81</v>
+      </c>
+      <c r="E191">
+        <v>3</v>
+      </c>
+      <c r="F191" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>87</v>
+      </c>
+      <c r="B192" t="s">
+        <v>266</v>
+      </c>
+      <c r="C192">
+        <v>2</v>
+      </c>
+      <c r="D192" t="s">
+        <v>88</v>
+      </c>
+      <c r="E192">
+        <v>1</v>
+      </c>
+      <c r="F192" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>89</v>
+      </c>
+      <c r="B193" t="s">
+        <v>266</v>
+      </c>
+      <c r="C193">
+        <v>2</v>
+      </c>
+      <c r="D193" t="s">
+        <v>88</v>
+      </c>
+      <c r="E193">
+        <v>1</v>
+      </c>
+      <c r="F193" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>90</v>
+      </c>
+      <c r="B194" t="s">
+        <v>266</v>
+      </c>
+      <c r="C194">
+        <v>2</v>
+      </c>
+      <c r="D194" t="s">
+        <v>88</v>
+      </c>
+      <c r="E194">
+        <v>2</v>
+      </c>
+      <c r="F194" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>91</v>
+      </c>
+      <c r="B195" t="s">
+        <v>266</v>
+      </c>
+      <c r="C195">
+        <v>2</v>
+      </c>
+      <c r="D195" t="s">
+        <v>88</v>
+      </c>
+      <c r="E195">
+        <v>2</v>
+      </c>
+      <c r="F195" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>92</v>
+      </c>
+      <c r="B196" t="s">
+        <v>266</v>
+      </c>
+      <c r="C196">
+        <v>2</v>
+      </c>
+      <c r="D196" t="s">
+        <v>88</v>
+      </c>
+      <c r="E196">
+        <v>3</v>
+      </c>
+      <c r="F196" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>93</v>
+      </c>
+      <c r="B197" t="s">
+        <v>266</v>
+      </c>
+      <c r="C197">
+        <v>2</v>
+      </c>
+      <c r="D197" t="s">
+        <v>88</v>
+      </c>
+      <c r="E197">
+        <v>3</v>
+      </c>
+      <c r="F197" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>114</v>
+      </c>
+      <c r="B198" t="s">
+        <v>266</v>
+      </c>
+      <c r="C198">
+        <v>2</v>
+      </c>
+      <c r="D198" t="s">
+        <v>115</v>
+      </c>
+      <c r="E198">
+        <v>1</v>
+      </c>
+      <c r="F198" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>116</v>
+      </c>
+      <c r="B199" t="s">
+        <v>266</v>
+      </c>
+      <c r="C199">
+        <v>2</v>
+      </c>
+      <c r="D199" t="s">
+        <v>115</v>
+      </c>
+      <c r="E199">
+        <v>2</v>
+      </c>
+      <c r="F199" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>117</v>
+      </c>
+      <c r="B200" t="s">
+        <v>266</v>
+      </c>
+      <c r="C200">
+        <v>2</v>
+      </c>
+      <c r="D200" t="s">
+        <v>115</v>
+      </c>
+      <c r="E200">
+        <v>3</v>
+      </c>
+      <c r="F200" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>118</v>
+      </c>
+      <c r="B201" t="s">
+        <v>266</v>
+      </c>
+      <c r="C201">
+        <v>2</v>
+      </c>
+      <c r="D201" t="s">
+        <v>115</v>
+      </c>
+      <c r="E201">
+        <v>3</v>
+      </c>
+      <c r="F201" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>119</v>
+      </c>
+      <c r="B202" t="s">
+        <v>266</v>
+      </c>
+      <c r="C202">
+        <v>2</v>
+      </c>
+      <c r="D202" t="s">
+        <v>120</v>
+      </c>
+      <c r="E202">
+        <v>1</v>
+      </c>
+      <c r="F202" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>121</v>
+      </c>
+      <c r="B203" t="s">
+        <v>266</v>
+      </c>
+      <c r="C203">
+        <v>2</v>
+      </c>
+      <c r="D203" t="s">
+        <v>120</v>
+      </c>
+      <c r="E203">
+        <v>2</v>
+      </c>
+      <c r="F203" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>122</v>
+      </c>
+      <c r="B204" t="s">
+        <v>266</v>
+      </c>
+      <c r="C204">
+        <v>2</v>
+      </c>
+      <c r="D204" t="s">
+        <v>120</v>
+      </c>
+      <c r="E204">
+        <v>2</v>
+      </c>
+      <c r="F204" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>123</v>
+      </c>
+      <c r="B205" t="s">
+        <v>266</v>
+      </c>
+      <c r="C205">
+        <v>2</v>
+      </c>
+      <c r="D205" t="s">
+        <v>120</v>
+      </c>
+      <c r="E205">
+        <v>3</v>
+      </c>
+      <c r="F205" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>124</v>
+      </c>
+      <c r="B206" t="s">
+        <v>266</v>
+      </c>
+      <c r="C206">
+        <v>2</v>
+      </c>
+      <c r="D206" t="s">
+        <v>120</v>
+      </c>
+      <c r="E206">
+        <v>3</v>
+      </c>
+      <c r="F206" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>125</v>
+      </c>
+      <c r="B207" t="s">
+        <v>266</v>
+      </c>
+      <c r="C207">
+        <v>2</v>
+      </c>
+      <c r="D207" t="s">
+        <v>126</v>
+      </c>
+      <c r="E207">
+        <v>1</v>
+      </c>
+      <c r="F207" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>127</v>
+      </c>
+      <c r="B208" t="s">
+        <v>266</v>
+      </c>
+      <c r="C208">
+        <v>2</v>
+      </c>
+      <c r="D208" t="s">
+        <v>126</v>
+      </c>
+      <c r="E208">
+        <v>1</v>
+      </c>
+      <c r="F208" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>128</v>
+      </c>
+      <c r="B209" t="s">
+        <v>266</v>
+      </c>
+      <c r="C209">
+        <v>2</v>
+      </c>
+      <c r="D209" t="s">
+        <v>126</v>
+      </c>
+      <c r="E209">
+        <v>2</v>
+      </c>
+      <c r="F209" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>129</v>
+      </c>
+      <c r="B210" t="s">
+        <v>266</v>
+      </c>
+      <c r="C210">
+        <v>2</v>
+      </c>
+      <c r="D210" t="s">
+        <v>126</v>
+      </c>
+      <c r="E210">
+        <v>3</v>
+      </c>
+      <c r="F210" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>130</v>
+      </c>
+      <c r="B211" t="s">
+        <v>266</v>
+      </c>
+      <c r="C211">
+        <v>2</v>
+      </c>
+      <c r="D211" t="s">
+        <v>131</v>
+      </c>
+      <c r="E211">
+        <v>1</v>
+      </c>
+      <c r="F211" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>132</v>
+      </c>
+      <c r="B212" t="s">
+        <v>266</v>
+      </c>
+      <c r="C212">
+        <v>2</v>
+      </c>
+      <c r="D212" t="s">
+        <v>131</v>
+      </c>
+      <c r="E212">
+        <v>2</v>
+      </c>
+      <c r="F212" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>133</v>
+      </c>
+      <c r="B213" t="s">
+        <v>266</v>
+      </c>
+      <c r="C213">
+        <v>2</v>
+      </c>
+      <c r="D213" t="s">
+        <v>131</v>
+      </c>
+      <c r="E213">
+        <v>3</v>
+      </c>
+      <c r="F213" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>134</v>
+      </c>
+      <c r="B214" t="s">
+        <v>266</v>
+      </c>
+      <c r="C214">
+        <v>2</v>
+      </c>
+      <c r="D214" t="s">
+        <v>131</v>
+      </c>
+      <c r="E214">
+        <v>3</v>
+      </c>
+      <c r="F214" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>135</v>
+      </c>
+      <c r="B215" t="s">
+        <v>266</v>
+      </c>
+      <c r="C215">
+        <v>2</v>
+      </c>
+      <c r="D215" t="s">
+        <v>136</v>
+      </c>
+      <c r="E215">
+        <v>1</v>
+      </c>
+      <c r="F215" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>137</v>
+      </c>
+      <c r="B216" t="s">
+        <v>266</v>
+      </c>
+      <c r="C216">
+        <v>2</v>
+      </c>
+      <c r="D216" t="s">
+        <v>136</v>
+      </c>
+      <c r="E216">
+        <v>1</v>
+      </c>
+      <c r="F216" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>138</v>
+      </c>
+      <c r="B217" t="s">
+        <v>266</v>
+      </c>
+      <c r="C217">
+        <v>2</v>
+      </c>
+      <c r="D217" t="s">
+        <v>136</v>
+      </c>
+      <c r="E217">
+        <v>2</v>
+      </c>
+      <c r="F217" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>139</v>
+      </c>
+      <c r="B218" t="s">
+        <v>266</v>
+      </c>
+      <c r="C218">
+        <v>2</v>
+      </c>
+      <c r="D218" t="s">
+        <v>136</v>
+      </c>
+      <c r="E218">
+        <v>2</v>
+      </c>
+      <c r="F218" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>140</v>
+      </c>
+      <c r="B219" t="s">
+        <v>266</v>
+      </c>
+      <c r="C219">
+        <v>2</v>
+      </c>
+      <c r="D219" t="s">
+        <v>136</v>
+      </c>
+      <c r="E219">
+        <v>3</v>
+      </c>
+      <c r="F219" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>141</v>
+      </c>
+      <c r="B220" t="s">
+        <v>266</v>
+      </c>
+      <c r="C220">
+        <v>2</v>
+      </c>
+      <c r="D220" t="s">
+        <v>136</v>
+      </c>
+      <c r="E220">
+        <v>3</v>
+      </c>
+      <c r="F220" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
         <v>94</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B221" t="s">
         <v>94</v>
       </c>
-      <c r="C128">
-        <v>2</v>
-      </c>
-      <c r="D128" t="s">
+      <c r="C221">
+        <v>2</v>
+      </c>
+      <c r="D221" t="s">
+        <v>142</v>
+      </c>
+      <c r="E221">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>94</v>
+      </c>
+      <c r="B222" t="s">
+        <v>94</v>
+      </c>
+      <c r="C222">
+        <v>2</v>
+      </c>
+      <c r="D222" t="s">
+        <v>142</v>
+      </c>
+      <c r="E222">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>94</v>
+      </c>
+      <c r="B223" t="s">
+        <v>94</v>
+      </c>
+      <c r="C223">
+        <v>2</v>
+      </c>
+      <c r="D223" t="s">
+        <v>142</v>
+      </c>
+      <c r="E223">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>94</v>
+      </c>
+      <c r="B224" t="s">
+        <v>94</v>
+      </c>
+      <c r="C224">
+        <v>2</v>
+      </c>
+      <c r="D224" t="s">
         <v>143</v>
       </c>
-      <c r="E128">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A129" t="s">
+      <c r="E224">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
         <v>94</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B225" t="s">
         <v>94</v>
       </c>
-      <c r="C129">
-        <v>2</v>
-      </c>
-      <c r="D129" t="s">
+      <c r="C225">
+        <v>2</v>
+      </c>
+      <c r="D225" t="s">
         <v>143</v>
       </c>
-      <c r="E129">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A130" t="s">
+      <c r="E225">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
         <v>94</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B226" t="s">
         <v>94</v>
       </c>
-      <c r="C130">
-        <v>2</v>
-      </c>
-      <c r="D130" t="s">
+      <c r="C226">
+        <v>2</v>
+      </c>
+      <c r="D226" t="s">
+        <v>143</v>
+      </c>
+      <c r="E226">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>94</v>
+      </c>
+      <c r="B227" t="s">
+        <v>94</v>
+      </c>
+      <c r="C227">
+        <v>2</v>
+      </c>
+      <c r="D227" t="s">
         <v>144</v>
       </c>
-      <c r="E130">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A131" t="s">
+      <c r="E227">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
         <v>94</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B228" t="s">
         <v>94</v>
       </c>
-      <c r="C131">
-        <v>2</v>
-      </c>
-      <c r="D131" t="s">
+      <c r="C228">
+        <v>2</v>
+      </c>
+      <c r="D228" t="s">
         <v>144</v>
       </c>
-      <c r="E131">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
+      <c r="E228">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
         <v>94</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B229" t="s">
         <v>94</v>
       </c>
-      <c r="C132">
-        <v>2</v>
-      </c>
-      <c r="D132" t="s">
+      <c r="C229">
+        <v>2</v>
+      </c>
+      <c r="D229" t="s">
         <v>144</v>
       </c>
-      <c r="E132">
-        <v>3</v>
+      <c r="E229">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>0</v>
+      </c>
+      <c r="B230" t="s">
+        <v>266</v>
+      </c>
+      <c r="C230">
+        <v>3</v>
+      </c>
+      <c r="D230" t="s">
+        <v>1</v>
+      </c>
+      <c r="E230">
+        <v>1</v>
+      </c>
+      <c r="F230" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>2</v>
+      </c>
+      <c r="B231" t="s">
+        <v>266</v>
+      </c>
+      <c r="C231">
+        <v>3</v>
+      </c>
+      <c r="D231" t="s">
+        <v>1</v>
+      </c>
+      <c r="E231">
+        <v>1</v>
+      </c>
+      <c r="F231" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>3</v>
+      </c>
+      <c r="B232" t="s">
+        <v>266</v>
+      </c>
+      <c r="C232">
+        <v>3</v>
+      </c>
+      <c r="D232" t="s">
+        <v>1</v>
+      </c>
+      <c r="E232">
+        <v>2</v>
+      </c>
+      <c r="F232" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>4</v>
+      </c>
+      <c r="B233" t="s">
+        <v>266</v>
+      </c>
+      <c r="C233">
+        <v>3</v>
+      </c>
+      <c r="D233" t="s">
+        <v>1</v>
+      </c>
+      <c r="E233">
+        <v>2</v>
+      </c>
+      <c r="F233" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>5</v>
+      </c>
+      <c r="B234" t="s">
+        <v>266</v>
+      </c>
+      <c r="C234">
+        <v>3</v>
+      </c>
+      <c r="D234" t="s">
+        <v>1</v>
+      </c>
+      <c r="E234">
+        <v>3</v>
+      </c>
+      <c r="F234" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>6</v>
+      </c>
+      <c r="B235" t="s">
+        <v>266</v>
+      </c>
+      <c r="C235">
+        <v>3</v>
+      </c>
+      <c r="D235" t="s">
+        <v>1</v>
+      </c>
+      <c r="E235">
+        <v>3</v>
+      </c>
+      <c r="F235" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>7</v>
+      </c>
+      <c r="B236" t="s">
+        <v>266</v>
+      </c>
+      <c r="C236">
+        <v>3</v>
+      </c>
+      <c r="D236" t="s">
+        <v>8</v>
+      </c>
+      <c r="E236">
+        <v>1</v>
+      </c>
+      <c r="F236" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>9</v>
+      </c>
+      <c r="B237" t="s">
+        <v>266</v>
+      </c>
+      <c r="C237">
+        <v>3</v>
+      </c>
+      <c r="D237" t="s">
+        <v>8</v>
+      </c>
+      <c r="E237">
+        <v>1</v>
+      </c>
+      <c r="F237" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>10</v>
+      </c>
+      <c r="B238" t="s">
+        <v>266</v>
+      </c>
+      <c r="C238">
+        <v>3</v>
+      </c>
+      <c r="D238" t="s">
+        <v>8</v>
+      </c>
+      <c r="E238">
+        <v>2</v>
+      </c>
+      <c r="F238" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>11</v>
+      </c>
+      <c r="B239" t="s">
+        <v>266</v>
+      </c>
+      <c r="C239">
+        <v>3</v>
+      </c>
+      <c r="D239" t="s">
+        <v>8</v>
+      </c>
+      <c r="E239">
+        <v>2</v>
+      </c>
+      <c r="F239" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>12</v>
+      </c>
+      <c r="B240" t="s">
+        <v>266</v>
+      </c>
+      <c r="C240">
+        <v>3</v>
+      </c>
+      <c r="D240" t="s">
+        <v>8</v>
+      </c>
+      <c r="E240">
+        <v>3</v>
+      </c>
+      <c r="F240" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>13</v>
+      </c>
+      <c r="B241" t="s">
+        <v>266</v>
+      </c>
+      <c r="C241">
+        <v>3</v>
+      </c>
+      <c r="D241" t="s">
+        <v>8</v>
+      </c>
+      <c r="E241">
+        <v>3</v>
+      </c>
+      <c r="F241" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>14</v>
+      </c>
+      <c r="B242" t="s">
+        <v>266</v>
+      </c>
+      <c r="C242">
+        <v>3</v>
+      </c>
+      <c r="D242" t="s">
+        <v>15</v>
+      </c>
+      <c r="E242">
+        <v>1</v>
+      </c>
+      <c r="F242" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>16</v>
+      </c>
+      <c r="B243" t="s">
+        <v>266</v>
+      </c>
+      <c r="C243">
+        <v>3</v>
+      </c>
+      <c r="D243" t="s">
+        <v>15</v>
+      </c>
+      <c r="E243">
+        <v>1</v>
+      </c>
+      <c r="F243" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>17</v>
+      </c>
+      <c r="B244" t="s">
+        <v>266</v>
+      </c>
+      <c r="C244">
+        <v>3</v>
+      </c>
+      <c r="D244" t="s">
+        <v>15</v>
+      </c>
+      <c r="E244">
+        <v>2</v>
+      </c>
+      <c r="F244" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>18</v>
+      </c>
+      <c r="B245" t="s">
+        <v>266</v>
+      </c>
+      <c r="C245">
+        <v>3</v>
+      </c>
+      <c r="D245" t="s">
+        <v>15</v>
+      </c>
+      <c r="E245">
+        <v>2</v>
+      </c>
+      <c r="F245" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>19</v>
+      </c>
+      <c r="B246" t="s">
+        <v>266</v>
+      </c>
+      <c r="C246">
+        <v>3</v>
+      </c>
+      <c r="D246" t="s">
+        <v>15</v>
+      </c>
+      <c r="E246">
+        <v>3</v>
+      </c>
+      <c r="F246" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>20</v>
+      </c>
+      <c r="B247" t="s">
+        <v>266</v>
+      </c>
+      <c r="C247">
+        <v>3</v>
+      </c>
+      <c r="D247" t="s">
+        <v>15</v>
+      </c>
+      <c r="E247">
+        <v>3</v>
+      </c>
+      <c r="F247" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>21</v>
+      </c>
+      <c r="B248" t="s">
+        <v>266</v>
+      </c>
+      <c r="C248">
+        <v>3</v>
+      </c>
+      <c r="D248" t="s">
+        <v>15</v>
+      </c>
+      <c r="E248">
+        <v>3</v>
+      </c>
+      <c r="F248" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>22</v>
+      </c>
+      <c r="B249" t="s">
+        <v>266</v>
+      </c>
+      <c r="C249">
+        <v>3</v>
+      </c>
+      <c r="D249" t="s">
+        <v>23</v>
+      </c>
+      <c r="E249">
+        <v>1</v>
+      </c>
+      <c r="F249" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>24</v>
+      </c>
+      <c r="B250" t="s">
+        <v>266</v>
+      </c>
+      <c r="C250">
+        <v>3</v>
+      </c>
+      <c r="D250" t="s">
+        <v>23</v>
+      </c>
+      <c r="E250">
+        <v>1</v>
+      </c>
+      <c r="F250" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>25</v>
+      </c>
+      <c r="B251" t="s">
+        <v>266</v>
+      </c>
+      <c r="C251">
+        <v>3</v>
+      </c>
+      <c r="D251" t="s">
+        <v>23</v>
+      </c>
+      <c r="E251">
+        <v>2</v>
+      </c>
+      <c r="F251" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>26</v>
+      </c>
+      <c r="B252" t="s">
+        <v>266</v>
+      </c>
+      <c r="C252">
+        <v>3</v>
+      </c>
+      <c r="D252" t="s">
+        <v>23</v>
+      </c>
+      <c r="E252">
+        <v>2</v>
+      </c>
+      <c r="F252" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>27</v>
+      </c>
+      <c r="B253" t="s">
+        <v>266</v>
+      </c>
+      <c r="C253">
+        <v>3</v>
+      </c>
+      <c r="D253" t="s">
+        <v>23</v>
+      </c>
+      <c r="E253">
+        <v>3</v>
+      </c>
+      <c r="F253" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>28</v>
+      </c>
+      <c r="B254" t="s">
+        <v>266</v>
+      </c>
+      <c r="C254">
+        <v>3</v>
+      </c>
+      <c r="D254" t="s">
+        <v>23</v>
+      </c>
+      <c r="E254">
+        <v>3</v>
+      </c>
+      <c r="F254" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>29</v>
+      </c>
+      <c r="B255" t="s">
+        <v>266</v>
+      </c>
+      <c r="C255">
+        <v>3</v>
+      </c>
+      <c r="D255" t="s">
+        <v>30</v>
+      </c>
+      <c r="E255">
+        <v>1</v>
+      </c>
+      <c r="F255" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>31</v>
+      </c>
+      <c r="B256" t="s">
+        <v>266</v>
+      </c>
+      <c r="C256">
+        <v>3</v>
+      </c>
+      <c r="D256" t="s">
+        <v>30</v>
+      </c>
+      <c r="E256">
+        <v>1</v>
+      </c>
+      <c r="F256" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>32</v>
+      </c>
+      <c r="B257" t="s">
+        <v>266</v>
+      </c>
+      <c r="C257">
+        <v>3</v>
+      </c>
+      <c r="D257" t="s">
+        <v>30</v>
+      </c>
+      <c r="E257">
+        <v>2</v>
+      </c>
+      <c r="F257" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>33</v>
+      </c>
+      <c r="B258" t="s">
+        <v>266</v>
+      </c>
+      <c r="C258">
+        <v>3</v>
+      </c>
+      <c r="D258" t="s">
+        <v>30</v>
+      </c>
+      <c r="E258">
+        <v>2</v>
+      </c>
+      <c r="F258" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>34</v>
+      </c>
+      <c r="B259" t="s">
+        <v>266</v>
+      </c>
+      <c r="C259">
+        <v>3</v>
+      </c>
+      <c r="D259" t="s">
+        <v>30</v>
+      </c>
+      <c r="E259">
+        <v>3</v>
+      </c>
+      <c r="F259" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>35</v>
+      </c>
+      <c r="B260" t="s">
+        <v>266</v>
+      </c>
+      <c r="C260">
+        <v>3</v>
+      </c>
+      <c r="D260" t="s">
+        <v>30</v>
+      </c>
+      <c r="E260">
+        <v>3</v>
+      </c>
+      <c r="F260" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>36</v>
+      </c>
+      <c r="B261" t="s">
+        <v>266</v>
+      </c>
+      <c r="C261">
+        <v>3</v>
+      </c>
+      <c r="D261" t="s">
+        <v>37</v>
+      </c>
+      <c r="E261">
+        <v>1</v>
+      </c>
+      <c r="F261" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>38</v>
+      </c>
+      <c r="B262" t="s">
+        <v>266</v>
+      </c>
+      <c r="C262">
+        <v>3</v>
+      </c>
+      <c r="D262" t="s">
+        <v>37</v>
+      </c>
+      <c r="E262">
+        <v>1</v>
+      </c>
+      <c r="F262" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>39</v>
+      </c>
+      <c r="B263" t="s">
+        <v>266</v>
+      </c>
+      <c r="C263">
+        <v>3</v>
+      </c>
+      <c r="D263" t="s">
+        <v>37</v>
+      </c>
+      <c r="E263">
+        <v>2</v>
+      </c>
+      <c r="F263" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>40</v>
+      </c>
+      <c r="B264" t="s">
+        <v>266</v>
+      </c>
+      <c r="C264">
+        <v>3</v>
+      </c>
+      <c r="D264" t="s">
+        <v>37</v>
+      </c>
+      <c r="E264">
+        <v>2</v>
+      </c>
+      <c r="F264" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>41</v>
+      </c>
+      <c r="B265" t="s">
+        <v>266</v>
+      </c>
+      <c r="C265">
+        <v>3</v>
+      </c>
+      <c r="D265" t="s">
+        <v>37</v>
+      </c>
+      <c r="E265">
+        <v>3</v>
+      </c>
+      <c r="F265" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>42</v>
+      </c>
+      <c r="B266" t="s">
+        <v>266</v>
+      </c>
+      <c r="C266">
+        <v>3</v>
+      </c>
+      <c r="D266" t="s">
+        <v>37</v>
+      </c>
+      <c r="E266">
+        <v>3</v>
+      </c>
+      <c r="F266" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>43</v>
+      </c>
+      <c r="B267" t="s">
+        <v>266</v>
+      </c>
+      <c r="C267">
+        <v>3</v>
+      </c>
+      <c r="D267" t="s">
+        <v>44</v>
+      </c>
+      <c r="E267">
+        <v>1</v>
+      </c>
+      <c r="F267" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>45</v>
+      </c>
+      <c r="B268" t="s">
+        <v>266</v>
+      </c>
+      <c r="C268">
+        <v>3</v>
+      </c>
+      <c r="D268" t="s">
+        <v>44</v>
+      </c>
+      <c r="E268">
+        <v>1</v>
+      </c>
+      <c r="F268" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>46</v>
+      </c>
+      <c r="B269" t="s">
+        <v>266</v>
+      </c>
+      <c r="C269">
+        <v>3</v>
+      </c>
+      <c r="D269" t="s">
+        <v>44</v>
+      </c>
+      <c r="E269">
+        <v>2</v>
+      </c>
+      <c r="F269" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>47</v>
+      </c>
+      <c r="B270" t="s">
+        <v>266</v>
+      </c>
+      <c r="C270">
+        <v>3</v>
+      </c>
+      <c r="D270" t="s">
+        <v>44</v>
+      </c>
+      <c r="E270">
+        <v>3</v>
+      </c>
+      <c r="F270" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>48</v>
+      </c>
+      <c r="B271" t="s">
+        <v>266</v>
+      </c>
+      <c r="C271">
+        <v>3</v>
+      </c>
+      <c r="D271" t="s">
+        <v>44</v>
+      </c>
+      <c r="E271">
+        <v>3</v>
+      </c>
+      <c r="F271" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>49</v>
+      </c>
+      <c r="B272" t="s">
+        <v>266</v>
+      </c>
+      <c r="C272">
+        <v>3</v>
+      </c>
+      <c r="D272" t="s">
+        <v>50</v>
+      </c>
+      <c r="E272">
+        <v>1</v>
+      </c>
+      <c r="F272" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>51</v>
+      </c>
+      <c r="B273" t="s">
+        <v>266</v>
+      </c>
+      <c r="C273">
+        <v>3</v>
+      </c>
+      <c r="D273" t="s">
+        <v>50</v>
+      </c>
+      <c r="E273">
+        <v>1</v>
+      </c>
+      <c r="F273" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>52</v>
+      </c>
+      <c r="B274" t="s">
+        <v>266</v>
+      </c>
+      <c r="C274">
+        <v>3</v>
+      </c>
+      <c r="D274" t="s">
+        <v>50</v>
+      </c>
+      <c r="E274">
+        <v>2</v>
+      </c>
+      <c r="F274" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>53</v>
+      </c>
+      <c r="B275" t="s">
+        <v>266</v>
+      </c>
+      <c r="C275">
+        <v>3</v>
+      </c>
+      <c r="D275" t="s">
+        <v>50</v>
+      </c>
+      <c r="E275">
+        <v>3</v>
+      </c>
+      <c r="F275" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>54</v>
+      </c>
+      <c r="B276" t="s">
+        <v>266</v>
+      </c>
+      <c r="C276">
+        <v>3</v>
+      </c>
+      <c r="D276" t="s">
+        <v>50</v>
+      </c>
+      <c r="E276">
+        <v>3</v>
+      </c>
+      <c r="F276" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>55</v>
+      </c>
+      <c r="B277" t="s">
+        <v>266</v>
+      </c>
+      <c r="C277">
+        <v>3</v>
+      </c>
+      <c r="D277" t="s">
+        <v>56</v>
+      </c>
+      <c r="E277">
+        <v>1</v>
+      </c>
+      <c r="F277" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>57</v>
+      </c>
+      <c r="B278" t="s">
+        <v>266</v>
+      </c>
+      <c r="C278">
+        <v>3</v>
+      </c>
+      <c r="D278" t="s">
+        <v>56</v>
+      </c>
+      <c r="E278">
+        <v>2</v>
+      </c>
+      <c r="F278" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>58</v>
+      </c>
+      <c r="B279" t="s">
+        <v>266</v>
+      </c>
+      <c r="C279">
+        <v>3</v>
+      </c>
+      <c r="D279" t="s">
+        <v>56</v>
+      </c>
+      <c r="E279">
+        <v>3</v>
+      </c>
+      <c r="F279" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>59</v>
+      </c>
+      <c r="B280" t="s">
+        <v>266</v>
+      </c>
+      <c r="C280">
+        <v>3</v>
+      </c>
+      <c r="D280" t="s">
+        <v>60</v>
+      </c>
+      <c r="E280">
+        <v>1</v>
+      </c>
+      <c r="F280" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>61</v>
+      </c>
+      <c r="B281" t="s">
+        <v>266</v>
+      </c>
+      <c r="C281">
+        <v>3</v>
+      </c>
+      <c r="D281" t="s">
+        <v>60</v>
+      </c>
+      <c r="E281">
+        <v>2</v>
+      </c>
+      <c r="F281" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>62</v>
+      </c>
+      <c r="B282" t="s">
+        <v>266</v>
+      </c>
+      <c r="C282">
+        <v>3</v>
+      </c>
+      <c r="D282" t="s">
+        <v>60</v>
+      </c>
+      <c r="E282">
+        <v>3</v>
+      </c>
+      <c r="F282" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>63</v>
+      </c>
+      <c r="B283" t="s">
+        <v>266</v>
+      </c>
+      <c r="C283">
+        <v>3</v>
+      </c>
+      <c r="D283" t="s">
+        <v>60</v>
+      </c>
+      <c r="E283">
+        <v>3</v>
+      </c>
+      <c r="F283" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>64</v>
+      </c>
+      <c r="B284" t="s">
+        <v>266</v>
+      </c>
+      <c r="C284">
+        <v>3</v>
+      </c>
+      <c r="D284" t="s">
+        <v>65</v>
+      </c>
+      <c r="E284">
+        <v>1</v>
+      </c>
+      <c r="F284" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>66</v>
+      </c>
+      <c r="B285" t="s">
+        <v>266</v>
+      </c>
+      <c r="C285">
+        <v>3</v>
+      </c>
+      <c r="D285" t="s">
+        <v>65</v>
+      </c>
+      <c r="E285">
+        <v>1</v>
+      </c>
+      <c r="F285" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>67</v>
+      </c>
+      <c r="B286" t="s">
+        <v>266</v>
+      </c>
+      <c r="C286">
+        <v>3</v>
+      </c>
+      <c r="D286" t="s">
+        <v>65</v>
+      </c>
+      <c r="E286">
+        <v>2</v>
+      </c>
+      <c r="F286" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>68</v>
+      </c>
+      <c r="B287" t="s">
+        <v>68</v>
+      </c>
+      <c r="C287">
+        <v>3</v>
+      </c>
+      <c r="D287" t="s">
+        <v>65</v>
+      </c>
+      <c r="E287">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>68</v>
+      </c>
+      <c r="B288" t="s">
+        <v>68</v>
+      </c>
+      <c r="C288">
+        <v>3</v>
+      </c>
+      <c r="D288" t="s">
+        <v>69</v>
+      </c>
+      <c r="E288">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>68</v>
+      </c>
+      <c r="B289" t="s">
+        <v>68</v>
+      </c>
+      <c r="C289">
+        <v>3</v>
+      </c>
+      <c r="D289" t="s">
+        <v>69</v>
+      </c>
+      <c r="E289">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>68</v>
+      </c>
+      <c r="B290" t="s">
+        <v>68</v>
+      </c>
+      <c r="C290">
+        <v>3</v>
+      </c>
+      <c r="D290" t="s">
+        <v>69</v>
+      </c>
+      <c r="E290">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>94</v>
+      </c>
+      <c r="B291" t="s">
+        <v>94</v>
+      </c>
+      <c r="C291">
+        <v>3</v>
+      </c>
+      <c r="D291" t="s">
+        <v>95</v>
+      </c>
+      <c r="E291">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>94</v>
+      </c>
+      <c r="B292" t="s">
+        <v>94</v>
+      </c>
+      <c r="C292">
+        <v>3</v>
+      </c>
+      <c r="D292" t="s">
+        <v>95</v>
+      </c>
+      <c r="E292">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>94</v>
+      </c>
+      <c r="B293" t="s">
+        <v>94</v>
+      </c>
+      <c r="C293">
+        <v>3</v>
+      </c>
+      <c r="D293" t="s">
+        <v>95</v>
+      </c>
+      <c r="E293">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>96</v>
+      </c>
+      <c r="B294" t="s">
+        <v>266</v>
+      </c>
+      <c r="C294">
+        <v>3</v>
+      </c>
+      <c r="D294" t="s">
+        <v>97</v>
+      </c>
+      <c r="E294">
+        <v>1</v>
+      </c>
+      <c r="F294" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>98</v>
+      </c>
+      <c r="B295" t="s">
+        <v>266</v>
+      </c>
+      <c r="C295">
+        <v>3</v>
+      </c>
+      <c r="D295" t="s">
+        <v>97</v>
+      </c>
+      <c r="E295">
+        <v>2</v>
+      </c>
+      <c r="F295" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>99</v>
+      </c>
+      <c r="B296" t="s">
+        <v>266</v>
+      </c>
+      <c r="C296">
+        <v>3</v>
+      </c>
+      <c r="D296" t="s">
+        <v>97</v>
+      </c>
+      <c r="E296">
+        <v>2</v>
+      </c>
+      <c r="F296" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>100</v>
+      </c>
+      <c r="B297" t="s">
+        <v>266</v>
+      </c>
+      <c r="C297">
+        <v>3</v>
+      </c>
+      <c r="D297" t="s">
+        <v>97</v>
+      </c>
+      <c r="E297">
+        <v>3</v>
+      </c>
+      <c r="F297" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>101</v>
+      </c>
+      <c r="B298" t="s">
+        <v>266</v>
+      </c>
+      <c r="C298">
+        <v>3</v>
+      </c>
+      <c r="D298" t="s">
+        <v>102</v>
+      </c>
+      <c r="E298">
+        <v>1</v>
+      </c>
+      <c r="F298" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>103</v>
+      </c>
+      <c r="B299" t="s">
+        <v>266</v>
+      </c>
+      <c r="C299">
+        <v>3</v>
+      </c>
+      <c r="D299" t="s">
+        <v>102</v>
+      </c>
+      <c r="E299">
+        <v>1</v>
+      </c>
+      <c r="F299" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>104</v>
+      </c>
+      <c r="B300" t="s">
+        <v>266</v>
+      </c>
+      <c r="C300">
+        <v>3</v>
+      </c>
+      <c r="D300" t="s">
+        <v>102</v>
+      </c>
+      <c r="E300">
+        <v>2</v>
+      </c>
+      <c r="F300" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>105</v>
+      </c>
+      <c r="B301" t="s">
+        <v>266</v>
+      </c>
+      <c r="C301">
+        <v>3</v>
+      </c>
+      <c r="D301" t="s">
+        <v>102</v>
+      </c>
+      <c r="E301">
+        <v>2</v>
+      </c>
+      <c r="F301" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>106</v>
+      </c>
+      <c r="B302" t="s">
+        <v>266</v>
+      </c>
+      <c r="C302">
+        <v>3</v>
+      </c>
+      <c r="D302" t="s">
+        <v>102</v>
+      </c>
+      <c r="E302">
+        <v>3</v>
+      </c>
+      <c r="F302" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>107</v>
+      </c>
+      <c r="B303" t="s">
+        <v>266</v>
+      </c>
+      <c r="C303">
+        <v>3</v>
+      </c>
+      <c r="D303" t="s">
+        <v>108</v>
+      </c>
+      <c r="E303">
+        <v>1</v>
+      </c>
+      <c r="F303" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>109</v>
+      </c>
+      <c r="B304" t="s">
+        <v>266</v>
+      </c>
+      <c r="C304">
+        <v>3</v>
+      </c>
+      <c r="D304" t="s">
+        <v>108</v>
+      </c>
+      <c r="E304">
+        <v>1</v>
+      </c>
+      <c r="F304" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>110</v>
+      </c>
+      <c r="B305" t="s">
+        <v>266</v>
+      </c>
+      <c r="C305">
+        <v>3</v>
+      </c>
+      <c r="D305" t="s">
+        <v>108</v>
+      </c>
+      <c r="E305">
+        <v>2</v>
+      </c>
+      <c r="F305" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>111</v>
+      </c>
+      <c r="B306" t="s">
+        <v>266</v>
+      </c>
+      <c r="C306">
+        <v>3</v>
+      </c>
+      <c r="D306" t="s">
+        <v>108</v>
+      </c>
+      <c r="E306">
+        <v>2</v>
+      </c>
+      <c r="F306" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>112</v>
+      </c>
+      <c r="B307" t="s">
+        <v>266</v>
+      </c>
+      <c r="C307">
+        <v>3</v>
+      </c>
+      <c r="D307" t="s">
+        <v>108</v>
+      </c>
+      <c r="E307">
+        <v>3</v>
+      </c>
+      <c r="F307" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>113</v>
+      </c>
+      <c r="B308" t="s">
+        <v>266</v>
+      </c>
+      <c r="C308">
+        <v>3</v>
+      </c>
+      <c r="D308" t="s">
+        <v>108</v>
+      </c>
+      <c r="E308">
+        <v>3</v>
+      </c>
+      <c r="F308" t="s">
+        <v>236</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F308">
+    <sortCondition ref="C2:C308"/>
+    <sortCondition ref="D2:D308"/>
+    <sortCondition ref="E2:E308"/>
+    <sortCondition descending="1" ref="A2:A308"/>
+  </sortState>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/EOAT_data.xlsx
+++ b/data/EOAT_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\procesos.CAZEL\Desktop\Becario Procesos\EOAT Project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{647626B9-F884-4F9C-B616-1ADAAB8F39B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B21A3D01-0935-4603-800B-CAF25F4A4CC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{440E3869-3C3F-4E8C-A8BD-ADEB8E2EA552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1042" uniqueCount="619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="615">
   <si>
     <t>I-1937</t>
   </si>
@@ -125,15 +125,9 @@
     <t>I-1812</t>
   </si>
   <si>
-    <t>I-1804</t>
-  </si>
-  <si>
     <t>C05</t>
   </si>
   <si>
-    <t>I-1803</t>
-  </si>
-  <si>
     <t>I-1802</t>
   </si>
   <si>
@@ -546,12 +540,6 @@
   </si>
   <si>
     <t>I-1812.jpeg</t>
-  </si>
-  <si>
-    <t>I-1804.jpeg</t>
-  </si>
-  <si>
-    <t>I-1803.jpeg</t>
   </si>
   <si>
     <t>I-1802.jpeg</t>
@@ -2270,7 +2258,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B6791C-A8A7-4753-A504-FAA9E3EE8745}">
-  <dimension ref="A1:F308"/>
+  <dimension ref="A1:F306"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -2283,5066 +2271,5026 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C1" t="s">
+        <v>258</v>
+      </c>
+      <c r="D1" t="s">
+        <v>259</v>
+      </c>
+      <c r="E1" t="s">
         <v>260</v>
       </c>
-      <c r="B1" t="s">
+      <c r="F1" t="s">
         <v>261</v>
-      </c>
-      <c r="C1" t="s">
-        <v>262</v>
-      </c>
-      <c r="D1" t="s">
-        <v>263</v>
-      </c>
-      <c r="E1" t="s">
-        <v>264</v>
-      </c>
-      <c r="F1" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>445</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C2">
+        <v>3</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>613</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>444</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>612</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>447</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>615</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>448</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>616</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>443</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
       </c>
       <c r="F6" t="s">
-        <v>611</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>442</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>610</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>446</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C8">
+        <v>3</v>
+      </c>
+      <c r="D8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8">
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>614</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>449</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9">
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>617</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>441</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
       </c>
       <c r="F10" t="s">
-        <v>609</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>440</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C11">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11">
+        <v>2</v>
       </c>
       <c r="F11" t="s">
-        <v>608</v>
+        <v>152</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>439</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C12">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12">
+        <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>607</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>438</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C13">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D13" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13">
+        <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>606</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>437</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C14">
+        <v>3</v>
+      </c>
+      <c r="D14" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14">
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>605</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>436</v>
+        <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C15">
+        <v>3</v>
+      </c>
+      <c r="D15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15">
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>604</v>
+        <v>156</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>435</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D16" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16">
+        <v>2</v>
       </c>
       <c r="F16" t="s">
-        <v>603</v>
+        <v>157</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>434</v>
+        <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C17">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D17" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17">
+        <v>2</v>
       </c>
       <c r="F17" t="s">
-        <v>602</v>
+        <v>158</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>433</v>
+        <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D18" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18">
+        <v>3</v>
       </c>
       <c r="F18" t="s">
-        <v>601</v>
+        <v>159</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>432</v>
+        <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E19">
+        <v>3</v>
       </c>
       <c r="F19" t="s">
-        <v>600</v>
+        <v>160</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>431</v>
+        <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E20">
+        <v>3</v>
       </c>
       <c r="F20" t="s">
-        <v>599</v>
+        <v>161</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>430</v>
+        <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C21">
+        <v>3</v>
+      </c>
+      <c r="D21" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21">
         <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>598</v>
+        <v>162</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>429</v>
+        <v>24</v>
       </c>
       <c r="B22" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C22">
+        <v>3</v>
+      </c>
+      <c r="D22" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22">
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>597</v>
+        <v>163</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>428</v>
+        <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D23" t="s">
+        <v>23</v>
+      </c>
+      <c r="E23">
+        <v>2</v>
       </c>
       <c r="F23" t="s">
-        <v>596</v>
+        <v>164</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>427</v>
+        <v>26</v>
       </c>
       <c r="B24" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D24" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24">
+        <v>2</v>
       </c>
       <c r="F24" t="s">
-        <v>595</v>
+        <v>165</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>426</v>
+        <v>27</v>
       </c>
       <c r="B25" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D25" t="s">
+        <v>23</v>
+      </c>
+      <c r="E25">
+        <v>3</v>
       </c>
       <c r="F25" t="s">
-        <v>594</v>
+        <v>166</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>425</v>
+        <v>28</v>
       </c>
       <c r="B26" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D26" t="s">
+        <v>23</v>
+      </c>
+      <c r="E26">
+        <v>3</v>
       </c>
       <c r="F26" t="s">
-        <v>593</v>
+        <v>167</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>424</v>
+        <v>92</v>
       </c>
       <c r="B27" t="s">
-        <v>266</v>
+        <v>92</v>
       </c>
       <c r="C27">
-        <v>1</v>
-      </c>
-      <c r="F27" t="s">
-        <v>592</v>
+        <v>3</v>
+      </c>
+      <c r="D27" t="s">
+        <v>29</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>423</v>
+        <v>30</v>
       </c>
       <c r="B28" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D28" t="s">
+        <v>29</v>
+      </c>
+      <c r="E28">
+        <v>2</v>
       </c>
       <c r="F28" t="s">
-        <v>591</v>
+        <v>168</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>422</v>
+        <v>31</v>
       </c>
       <c r="B29" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C29">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D29" t="s">
+        <v>29</v>
+      </c>
+      <c r="E29">
+        <v>2</v>
       </c>
       <c r="F29" t="s">
-        <v>590</v>
+        <v>169</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>421</v>
+        <v>32</v>
       </c>
       <c r="B30" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D30" t="s">
+        <v>29</v>
+      </c>
+      <c r="E30">
+        <v>3</v>
       </c>
       <c r="F30" t="s">
-        <v>589</v>
+        <v>170</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>420</v>
+        <v>33</v>
       </c>
       <c r="B31" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D31" t="s">
+        <v>29</v>
+      </c>
+      <c r="E31">
+        <v>3</v>
       </c>
       <c r="F31" t="s">
-        <v>588</v>
+        <v>171</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>419</v>
+        <v>34</v>
       </c>
       <c r="B32" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C32">
+        <v>3</v>
+      </c>
+      <c r="D32" t="s">
+        <v>35</v>
+      </c>
+      <c r="E32">
         <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>587</v>
+        <v>172</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>418</v>
+        <v>36</v>
       </c>
       <c r="B33" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C33">
+        <v>3</v>
+      </c>
+      <c r="D33" t="s">
+        <v>35</v>
+      </c>
+      <c r="E33">
         <v>1</v>
       </c>
       <c r="F33" t="s">
-        <v>586</v>
+        <v>173</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>417</v>
+        <v>37</v>
       </c>
       <c r="B34" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C34">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D34" t="s">
+        <v>35</v>
+      </c>
+      <c r="E34">
+        <v>2</v>
       </c>
       <c r="F34" t="s">
-        <v>585</v>
+        <v>174</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>416</v>
+        <v>38</v>
       </c>
       <c r="B35" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D35" t="s">
+        <v>35</v>
+      </c>
+      <c r="E35">
+        <v>2</v>
       </c>
       <c r="F35" t="s">
-        <v>584</v>
+        <v>175</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>415</v>
+        <v>39</v>
       </c>
       <c r="B36" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C36">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D36" t="s">
+        <v>35</v>
+      </c>
+      <c r="E36">
+        <v>3</v>
       </c>
       <c r="F36" t="s">
-        <v>583</v>
+        <v>176</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>414</v>
+        <v>40</v>
       </c>
       <c r="B37" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D37" t="s">
+        <v>35</v>
+      </c>
+      <c r="E37">
+        <v>3</v>
       </c>
       <c r="F37" t="s">
-        <v>582</v>
+        <v>177</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>413</v>
+        <v>41</v>
       </c>
       <c r="B38" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C38">
+        <v>3</v>
+      </c>
+      <c r="D38" t="s">
+        <v>42</v>
+      </c>
+      <c r="E38">
         <v>1</v>
       </c>
       <c r="F38" t="s">
-        <v>581</v>
+        <v>178</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>412</v>
+        <v>43</v>
       </c>
       <c r="B39" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C39">
+        <v>3</v>
+      </c>
+      <c r="D39" t="s">
+        <v>42</v>
+      </c>
+      <c r="E39">
         <v>1</v>
       </c>
       <c r="F39" t="s">
-        <v>580</v>
+        <v>179</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>411</v>
+        <v>44</v>
       </c>
       <c r="B40" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C40">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D40" t="s">
+        <v>42</v>
+      </c>
+      <c r="E40">
+        <v>2</v>
       </c>
       <c r="F40" t="s">
-        <v>579</v>
+        <v>180</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>410</v>
+        <v>45</v>
       </c>
       <c r="B41" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C41">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D41" t="s">
+        <v>42</v>
+      </c>
+      <c r="E41">
+        <v>3</v>
       </c>
       <c r="F41" t="s">
-        <v>578</v>
+        <v>181</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>409</v>
+        <v>46</v>
       </c>
       <c r="B42" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C42">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D42" t="s">
+        <v>42</v>
+      </c>
+      <c r="E42">
+        <v>3</v>
       </c>
       <c r="F42" t="s">
-        <v>577</v>
+        <v>182</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>408</v>
+        <v>47</v>
       </c>
       <c r="B43" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C43">
+        <v>3</v>
+      </c>
+      <c r="D43" t="s">
+        <v>48</v>
+      </c>
+      <c r="E43">
         <v>1</v>
       </c>
       <c r="F43" t="s">
-        <v>576</v>
+        <v>183</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>407</v>
+        <v>49</v>
       </c>
       <c r="B44" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C44">
+        <v>3</v>
+      </c>
+      <c r="D44" t="s">
+        <v>48</v>
+      </c>
+      <c r="E44">
         <v>1</v>
       </c>
       <c r="F44" t="s">
-        <v>575</v>
+        <v>184</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>406</v>
+        <v>50</v>
       </c>
       <c r="B45" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C45">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D45" t="s">
+        <v>48</v>
+      </c>
+      <c r="E45">
+        <v>2</v>
       </c>
       <c r="F45" t="s">
-        <v>574</v>
+        <v>185</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>405</v>
+        <v>51</v>
       </c>
       <c r="B46" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C46">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D46" t="s">
+        <v>48</v>
+      </c>
+      <c r="E46">
+        <v>3</v>
       </c>
       <c r="F46" t="s">
-        <v>573</v>
+        <v>186</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>404</v>
+        <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C47">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D47" t="s">
+        <v>48</v>
+      </c>
+      <c r="E47">
+        <v>3</v>
       </c>
       <c r="F47" t="s">
-        <v>572</v>
+        <v>187</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>403</v>
+        <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C48">
+        <v>3</v>
+      </c>
+      <c r="D48" t="s">
+        <v>54</v>
+      </c>
+      <c r="E48">
         <v>1</v>
       </c>
       <c r="F48" t="s">
-        <v>571</v>
+        <v>188</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>402</v>
+        <v>55</v>
       </c>
       <c r="B49" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D49" t="s">
+        <v>54</v>
+      </c>
+      <c r="E49">
+        <v>2</v>
       </c>
       <c r="F49" t="s">
-        <v>570</v>
+        <v>189</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>401</v>
+        <v>56</v>
       </c>
       <c r="B50" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C50">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D50" t="s">
+        <v>54</v>
+      </c>
+      <c r="E50">
+        <v>3</v>
       </c>
       <c r="F50" t="s">
-        <v>569</v>
+        <v>190</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>400</v>
+        <v>57</v>
       </c>
       <c r="B51" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C51">
+        <v>3</v>
+      </c>
+      <c r="D51" t="s">
+        <v>58</v>
+      </c>
+      <c r="E51">
         <v>1</v>
       </c>
       <c r="F51" t="s">
-        <v>568</v>
+        <v>191</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>399</v>
+        <v>59</v>
       </c>
       <c r="B52" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C52">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D52" t="s">
+        <v>58</v>
+      </c>
+      <c r="E52">
+        <v>2</v>
       </c>
       <c r="F52" t="s">
-        <v>567</v>
+        <v>192</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>398</v>
+        <v>61</v>
       </c>
       <c r="B53" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C53">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D53" t="s">
+        <v>58</v>
+      </c>
+      <c r="E53">
+        <v>3</v>
       </c>
       <c r="F53" t="s">
-        <v>566</v>
+        <v>194</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>397</v>
+        <v>62</v>
       </c>
       <c r="B54" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C54">
+        <v>3</v>
+      </c>
+      <c r="D54" t="s">
+        <v>63</v>
+      </c>
+      <c r="E54">
         <v>1</v>
       </c>
       <c r="F54" t="s">
-        <v>565</v>
+        <v>195</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>396</v>
+        <v>64</v>
       </c>
       <c r="B55" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C55">
+        <v>3</v>
+      </c>
+      <c r="D55" t="s">
+        <v>63</v>
+      </c>
+      <c r="E55">
         <v>1</v>
       </c>
       <c r="F55" t="s">
-        <v>564</v>
+        <v>196</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>395</v>
+        <v>65</v>
       </c>
       <c r="B56" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C56">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D56" t="s">
+        <v>63</v>
+      </c>
+      <c r="E56">
+        <v>2</v>
       </c>
       <c r="F56" t="s">
-        <v>563</v>
+        <v>197</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>394</v>
+        <v>66</v>
       </c>
       <c r="B57" t="s">
-        <v>266</v>
+        <v>66</v>
       </c>
       <c r="C57">
-        <v>1</v>
-      </c>
-      <c r="F57" t="s">
-        <v>562</v>
+        <v>3</v>
+      </c>
+      <c r="D57" t="s">
+        <v>63</v>
+      </c>
+      <c r="E57">
+        <v>3</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>393</v>
+        <v>66</v>
       </c>
       <c r="B58" t="s">
-        <v>266</v>
+        <v>66</v>
       </c>
       <c r="C58">
-        <v>1</v>
-      </c>
-      <c r="F58" t="s">
-        <v>561</v>
+        <v>3</v>
+      </c>
+      <c r="D58" t="s">
+        <v>67</v>
+      </c>
+      <c r="E58">
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>392</v>
+        <v>66</v>
       </c>
       <c r="B59" t="s">
-        <v>266</v>
+        <v>66</v>
       </c>
       <c r="C59">
-        <v>1</v>
-      </c>
-      <c r="F59" t="s">
-        <v>560</v>
+        <v>3</v>
+      </c>
+      <c r="D59" t="s">
+        <v>67</v>
+      </c>
+      <c r="E59">
+        <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>391</v>
+        <v>66</v>
       </c>
       <c r="B60" t="s">
-        <v>266</v>
+        <v>66</v>
       </c>
       <c r="C60">
-        <v>1</v>
-      </c>
-      <c r="F60" t="s">
-        <v>559</v>
+        <v>3</v>
+      </c>
+      <c r="D60" t="s">
+        <v>67</v>
+      </c>
+      <c r="E60">
+        <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>390</v>
+        <v>92</v>
       </c>
       <c r="B61" t="s">
-        <v>266</v>
+        <v>92</v>
       </c>
       <c r="C61">
-        <v>1</v>
-      </c>
-      <c r="F61" t="s">
-        <v>558</v>
+        <v>3</v>
+      </c>
+      <c r="D61" t="s">
+        <v>93</v>
+      </c>
+      <c r="E61">
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>389</v>
+        <v>92</v>
       </c>
       <c r="B62" t="s">
-        <v>266</v>
+        <v>92</v>
       </c>
       <c r="C62">
-        <v>1</v>
-      </c>
-      <c r="F62" t="s">
-        <v>557</v>
+        <v>3</v>
+      </c>
+      <c r="D62" t="s">
+        <v>93</v>
+      </c>
+      <c r="E62">
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>388</v>
+        <v>60</v>
       </c>
       <c r="B63" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C63">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D63" t="s">
+        <v>93</v>
+      </c>
+      <c r="E63">
+        <v>3</v>
       </c>
       <c r="F63" t="s">
-        <v>556</v>
+        <v>193</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>387</v>
+        <v>94</v>
       </c>
       <c r="B64" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C64">
+        <v>3</v>
+      </c>
+      <c r="D64" t="s">
+        <v>95</v>
+      </c>
+      <c r="E64">
         <v>1</v>
       </c>
       <c r="F64" t="s">
-        <v>555</v>
+        <v>218</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>386</v>
+        <v>96</v>
       </c>
       <c r="B65" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C65">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D65" t="s">
+        <v>95</v>
+      </c>
+      <c r="E65">
+        <v>2</v>
       </c>
       <c r="F65" t="s">
-        <v>554</v>
+        <v>219</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>385</v>
+        <v>97</v>
       </c>
       <c r="B66" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C66">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D66" t="s">
+        <v>95</v>
+      </c>
+      <c r="E66">
+        <v>2</v>
       </c>
       <c r="F66" t="s">
-        <v>553</v>
+        <v>220</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>384</v>
+        <v>98</v>
       </c>
       <c r="B67" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C67">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D67" t="s">
+        <v>95</v>
+      </c>
+      <c r="E67">
+        <v>3</v>
       </c>
       <c r="F67" t="s">
-        <v>552</v>
+        <v>221</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>383</v>
+        <v>99</v>
       </c>
       <c r="B68" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C68">
+        <v>3</v>
+      </c>
+      <c r="D68" t="s">
+        <v>100</v>
+      </c>
+      <c r="E68">
         <v>1</v>
       </c>
       <c r="F68" t="s">
-        <v>551</v>
+        <v>222</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>382</v>
+        <v>101</v>
       </c>
       <c r="B69" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C69">
+        <v>3</v>
+      </c>
+      <c r="D69" t="s">
+        <v>100</v>
+      </c>
+      <c r="E69">
         <v>1</v>
       </c>
       <c r="F69" t="s">
-        <v>550</v>
+        <v>223</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>381</v>
+        <v>102</v>
       </c>
       <c r="B70" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C70">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D70" t="s">
+        <v>100</v>
+      </c>
+      <c r="E70">
+        <v>2</v>
       </c>
       <c r="F70" t="s">
-        <v>549</v>
+        <v>224</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>380</v>
+        <v>103</v>
       </c>
       <c r="B71" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C71">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D71" t="s">
+        <v>100</v>
+      </c>
+      <c r="E71">
+        <v>2</v>
       </c>
       <c r="F71" t="s">
-        <v>548</v>
+        <v>225</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>379</v>
+        <v>104</v>
       </c>
       <c r="B72" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C72">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D72" t="s">
+        <v>100</v>
+      </c>
+      <c r="E72">
+        <v>3</v>
       </c>
       <c r="F72" t="s">
-        <v>547</v>
+        <v>226</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>378</v>
+        <v>105</v>
       </c>
       <c r="B73" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C73">
+        <v>3</v>
+      </c>
+      <c r="D73" t="s">
+        <v>106</v>
+      </c>
+      <c r="E73">
         <v>1</v>
       </c>
       <c r="F73" t="s">
-        <v>546</v>
+        <v>227</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>377</v>
+        <v>107</v>
       </c>
       <c r="B74" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C74">
+        <v>3</v>
+      </c>
+      <c r="D74" t="s">
+        <v>106</v>
+      </c>
+      <c r="E74">
         <v>1</v>
       </c>
       <c r="F74" t="s">
-        <v>545</v>
+        <v>228</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>376</v>
+        <v>108</v>
       </c>
       <c r="B75" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C75">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D75" t="s">
+        <v>106</v>
+      </c>
+      <c r="E75">
+        <v>2</v>
       </c>
       <c r="F75" t="s">
-        <v>544</v>
+        <v>229</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>375</v>
+        <v>109</v>
       </c>
       <c r="B76" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C76">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D76" t="s">
+        <v>106</v>
+      </c>
+      <c r="E76">
+        <v>2</v>
       </c>
       <c r="F76" t="s">
-        <v>543</v>
+        <v>230</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>374</v>
+        <v>110</v>
       </c>
       <c r="B77" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C77">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D77" t="s">
+        <v>106</v>
+      </c>
+      <c r="E77">
+        <v>3</v>
       </c>
       <c r="F77" t="s">
-        <v>542</v>
+        <v>231</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>373</v>
+        <v>111</v>
       </c>
       <c r="B78" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C78">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="D78" t="s">
+        <v>106</v>
+      </c>
+      <c r="E78">
+        <v>3</v>
       </c>
       <c r="F78" t="s">
-        <v>541</v>
+        <v>232</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>372</v>
+        <v>68</v>
       </c>
       <c r="B79" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C79">
+        <v>2</v>
+      </c>
+      <c r="D79" t="s">
+        <v>69</v>
+      </c>
+      <c r="E79">
         <v>1</v>
       </c>
       <c r="F79" t="s">
-        <v>540</v>
+        <v>198</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>371</v>
+        <v>70</v>
       </c>
       <c r="B80" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C80">
+        <v>2</v>
+      </c>
+      <c r="D80" t="s">
+        <v>69</v>
+      </c>
+      <c r="E80">
         <v>1</v>
       </c>
       <c r="F80" t="s">
-        <v>539</v>
+        <v>199</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>370</v>
+        <v>71</v>
       </c>
       <c r="B81" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C81">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D81" t="s">
+        <v>69</v>
+      </c>
+      <c r="E81">
+        <v>2</v>
       </c>
       <c r="F81" t="s">
-        <v>538</v>
+        <v>200</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>369</v>
+        <v>72</v>
       </c>
       <c r="B82" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C82">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D82" t="s">
+        <v>69</v>
+      </c>
+      <c r="E82">
+        <v>3</v>
       </c>
       <c r="F82" t="s">
-        <v>537</v>
+        <v>201</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>368</v>
+        <v>73</v>
       </c>
       <c r="B83" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C83">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D83" t="s">
+        <v>69</v>
+      </c>
+      <c r="E83">
+        <v>3</v>
       </c>
       <c r="F83" t="s">
-        <v>536</v>
+        <v>202</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>367</v>
+        <v>74</v>
       </c>
       <c r="B84" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C84">
+        <v>2</v>
+      </c>
+      <c r="D84" t="s">
+        <v>75</v>
+      </c>
+      <c r="E84">
         <v>1</v>
       </c>
       <c r="F84" t="s">
-        <v>535</v>
+        <v>203</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>366</v>
+        <v>76</v>
       </c>
       <c r="B85" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C85">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D85" t="s">
+        <v>75</v>
+      </c>
+      <c r="E85">
+        <v>2</v>
       </c>
       <c r="F85" t="s">
-        <v>534</v>
+        <v>204</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>365</v>
+        <v>77</v>
       </c>
       <c r="B86" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C86">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D86" t="s">
+        <v>75</v>
+      </c>
+      <c r="E86">
+        <v>3</v>
       </c>
       <c r="F86" t="s">
-        <v>533</v>
+        <v>205</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>364</v>
+        <v>78</v>
       </c>
       <c r="B87" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C87">
+        <v>2</v>
+      </c>
+      <c r="D87" t="s">
+        <v>79</v>
+      </c>
+      <c r="E87">
         <v>1</v>
       </c>
       <c r="F87" t="s">
-        <v>532</v>
+        <v>206</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>363</v>
+        <v>80</v>
       </c>
       <c r="B88" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C88">
+        <v>2</v>
+      </c>
+      <c r="D88" t="s">
+        <v>79</v>
+      </c>
+      <c r="E88">
         <v>1</v>
       </c>
       <c r="F88" t="s">
-        <v>531</v>
+        <v>207</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>362</v>
+        <v>81</v>
       </c>
       <c r="B89" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C89">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D89" t="s">
+        <v>79</v>
+      </c>
+      <c r="E89">
+        <v>2</v>
       </c>
       <c r="F89" t="s">
-        <v>530</v>
+        <v>208</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>361</v>
+        <v>82</v>
       </c>
       <c r="B90" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C90">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D90" t="s">
+        <v>79</v>
+      </c>
+      <c r="E90">
+        <v>2</v>
       </c>
       <c r="F90" t="s">
-        <v>529</v>
+        <v>209</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>360</v>
+        <v>83</v>
       </c>
       <c r="B91" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C91">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D91" t="s">
+        <v>79</v>
+      </c>
+      <c r="E91">
+        <v>3</v>
       </c>
       <c r="F91" t="s">
-        <v>528</v>
+        <v>210</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>359</v>
+        <v>84</v>
       </c>
       <c r="B92" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C92">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D92" t="s">
+        <v>79</v>
+      </c>
+      <c r="E92">
+        <v>3</v>
       </c>
       <c r="F92" t="s">
-        <v>527</v>
+        <v>211</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>358</v>
+        <v>85</v>
       </c>
       <c r="B93" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C93">
+        <v>2</v>
+      </c>
+      <c r="D93" t="s">
+        <v>86</v>
+      </c>
+      <c r="E93">
         <v>1</v>
       </c>
       <c r="F93" t="s">
-        <v>526</v>
+        <v>212</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>357</v>
+        <v>87</v>
       </c>
       <c r="B94" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C94">
+        <v>2</v>
+      </c>
+      <c r="D94" t="s">
+        <v>86</v>
+      </c>
+      <c r="E94">
         <v>1</v>
       </c>
       <c r="F94" t="s">
-        <v>525</v>
+        <v>213</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>356</v>
+        <v>88</v>
       </c>
       <c r="B95" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C95">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D95" t="s">
+        <v>86</v>
+      </c>
+      <c r="E95">
+        <v>2</v>
       </c>
       <c r="F95" t="s">
-        <v>524</v>
+        <v>214</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>355</v>
+        <v>89</v>
       </c>
       <c r="B96" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C96">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D96" t="s">
+        <v>86</v>
+      </c>
+      <c r="E96">
+        <v>2</v>
       </c>
       <c r="F96" t="s">
-        <v>523</v>
+        <v>215</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>354</v>
+        <v>90</v>
       </c>
       <c r="B97" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C97">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D97" t="s">
+        <v>86</v>
+      </c>
+      <c r="E97">
+        <v>3</v>
       </c>
       <c r="F97" t="s">
-        <v>522</v>
+        <v>216</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>353</v>
+        <v>91</v>
       </c>
       <c r="B98" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C98">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D98" t="s">
+        <v>86</v>
+      </c>
+      <c r="E98">
+        <v>3</v>
       </c>
       <c r="F98" t="s">
-        <v>521</v>
+        <v>217</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>352</v>
+        <v>112</v>
       </c>
       <c r="B99" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C99">
+        <v>2</v>
+      </c>
+      <c r="D99" t="s">
+        <v>113</v>
+      </c>
+      <c r="E99">
         <v>1</v>
       </c>
       <c r="F99" t="s">
-        <v>520</v>
+        <v>233</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>351</v>
+        <v>114</v>
       </c>
       <c r="B100" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C100">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D100" t="s">
+        <v>113</v>
+      </c>
+      <c r="E100">
+        <v>2</v>
       </c>
       <c r="F100" t="s">
-        <v>519</v>
+        <v>234</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>350</v>
+        <v>115</v>
       </c>
       <c r="B101" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C101">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D101" t="s">
+        <v>113</v>
+      </c>
+      <c r="E101">
+        <v>3</v>
       </c>
       <c r="F101" t="s">
-        <v>518</v>
+        <v>235</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>349</v>
+        <v>116</v>
       </c>
       <c r="B102" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C102">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D102" t="s">
+        <v>113</v>
+      </c>
+      <c r="E102">
+        <v>3</v>
       </c>
       <c r="F102" t="s">
-        <v>517</v>
+        <v>236</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>348</v>
+        <v>117</v>
       </c>
       <c r="B103" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C103">
+        <v>2</v>
+      </c>
+      <c r="D103" t="s">
+        <v>118</v>
+      </c>
+      <c r="E103">
         <v>1</v>
       </c>
       <c r="F103" t="s">
-        <v>516</v>
+        <v>237</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>347</v>
+        <v>119</v>
       </c>
       <c r="B104" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C104">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D104" t="s">
+        <v>118</v>
+      </c>
+      <c r="E104">
+        <v>2</v>
       </c>
       <c r="F104" t="s">
-        <v>515</v>
+        <v>238</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>346</v>
+        <v>120</v>
       </c>
       <c r="B105" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C105">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D105" t="s">
+        <v>118</v>
+      </c>
+      <c r="E105">
+        <v>2</v>
       </c>
       <c r="F105" t="s">
-        <v>514</v>
+        <v>239</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>345</v>
+        <v>121</v>
       </c>
       <c r="B106" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C106">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D106" t="s">
+        <v>118</v>
+      </c>
+      <c r="E106">
+        <v>3</v>
       </c>
       <c r="F106" t="s">
-        <v>513</v>
+        <v>240</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>344</v>
+        <v>122</v>
       </c>
       <c r="B107" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C107">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D107" t="s">
+        <v>118</v>
+      </c>
+      <c r="E107">
+        <v>3</v>
       </c>
       <c r="F107" t="s">
-        <v>512</v>
+        <v>241</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>343</v>
+        <v>123</v>
       </c>
       <c r="B108" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C108">
+        <v>2</v>
+      </c>
+      <c r="D108" t="s">
+        <v>124</v>
+      </c>
+      <c r="E108">
         <v>1</v>
       </c>
       <c r="F108" t="s">
-        <v>511</v>
+        <v>242</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>342</v>
+        <v>126</v>
       </c>
       <c r="B109" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C109">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D109" t="s">
+        <v>124</v>
+      </c>
+      <c r="E109">
+        <v>2</v>
       </c>
       <c r="F109" t="s">
-        <v>510</v>
+        <v>244</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>341</v>
+        <v>125</v>
       </c>
       <c r="B110" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C110">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D110" t="s">
+        <v>124</v>
+      </c>
+      <c r="E110">
+        <v>3</v>
       </c>
       <c r="F110" t="s">
-        <v>509</v>
+        <v>243</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>340</v>
+        <v>127</v>
       </c>
       <c r="B111" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C111">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D111" t="s">
+        <v>124</v>
+      </c>
+      <c r="E111">
+        <v>3</v>
       </c>
       <c r="F111" t="s">
-        <v>508</v>
+        <v>245</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>339</v>
+        <v>128</v>
       </c>
       <c r="B112" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C112">
+        <v>2</v>
+      </c>
+      <c r="D112" t="s">
+        <v>129</v>
+      </c>
+      <c r="E112">
         <v>1</v>
       </c>
       <c r="F112" t="s">
-        <v>507</v>
+        <v>246</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>338</v>
+        <v>130</v>
       </c>
       <c r="B113" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C113">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D113" t="s">
+        <v>129</v>
+      </c>
+      <c r="E113">
+        <v>2</v>
       </c>
       <c r="F113" t="s">
-        <v>506</v>
+        <v>247</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>337</v>
+        <v>131</v>
       </c>
       <c r="B114" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C114">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D114" t="s">
+        <v>129</v>
+      </c>
+      <c r="E114">
+        <v>3</v>
       </c>
       <c r="F114" t="s">
-        <v>505</v>
+        <v>248</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>336</v>
+        <v>132</v>
       </c>
       <c r="B115" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C115">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D115" t="s">
+        <v>129</v>
+      </c>
+      <c r="E115">
+        <v>3</v>
       </c>
       <c r="F115" t="s">
-        <v>504</v>
+        <v>249</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>335</v>
+        <v>133</v>
       </c>
       <c r="B116" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C116">
+        <v>2</v>
+      </c>
+      <c r="D116" t="s">
+        <v>134</v>
+      </c>
+      <c r="E116">
         <v>1</v>
       </c>
       <c r="F116" t="s">
-        <v>503</v>
+        <v>250</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>334</v>
+        <v>135</v>
       </c>
       <c r="B117" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C117">
+        <v>2</v>
+      </c>
+      <c r="D117" t="s">
+        <v>134</v>
+      </c>
+      <c r="E117">
         <v>1</v>
       </c>
       <c r="F117" t="s">
-        <v>502</v>
+        <v>251</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>333</v>
+        <v>136</v>
       </c>
       <c r="B118" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C118">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D118" t="s">
+        <v>134</v>
+      </c>
+      <c r="E118">
+        <v>2</v>
       </c>
       <c r="F118" t="s">
-        <v>501</v>
+        <v>252</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>332</v>
+        <v>137</v>
       </c>
       <c r="B119" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C119">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D119" t="s">
+        <v>134</v>
+      </c>
+      <c r="E119">
+        <v>2</v>
       </c>
       <c r="F119" t="s">
-        <v>500</v>
+        <v>253</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>331</v>
+        <v>138</v>
       </c>
       <c r="B120" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C120">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D120" t="s">
+        <v>134</v>
+      </c>
+      <c r="E120">
+        <v>3</v>
       </c>
       <c r="F120" t="s">
-        <v>499</v>
+        <v>254</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>330</v>
+        <v>139</v>
       </c>
       <c r="B121" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C121">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="D121" t="s">
+        <v>134</v>
+      </c>
+      <c r="E121">
+        <v>3</v>
       </c>
       <c r="F121" t="s">
-        <v>498</v>
+        <v>255</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>329</v>
+        <v>92</v>
       </c>
       <c r="B122" t="s">
-        <v>266</v>
+        <v>92</v>
       </c>
       <c r="C122">
-        <v>1</v>
-      </c>
-      <c r="F122" t="s">
-        <v>497</v>
+        <v>2</v>
+      </c>
+      <c r="D122" t="s">
+        <v>140</v>
+      </c>
+      <c r="E122">
+        <v>1</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>328</v>
+        <v>92</v>
       </c>
       <c r="B123" t="s">
-        <v>266</v>
+        <v>92</v>
       </c>
       <c r="C123">
-        <v>1</v>
-      </c>
-      <c r="F123" t="s">
-        <v>496</v>
+        <v>2</v>
+      </c>
+      <c r="D123" t="s">
+        <v>140</v>
+      </c>
+      <c r="E123">
+        <v>2</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>327</v>
+        <v>92</v>
       </c>
       <c r="B124" t="s">
-        <v>266</v>
+        <v>92</v>
       </c>
       <c r="C124">
-        <v>1</v>
-      </c>
-      <c r="F124" t="s">
-        <v>495</v>
+        <v>2</v>
+      </c>
+      <c r="D124" t="s">
+        <v>140</v>
+      </c>
+      <c r="E124">
+        <v>3</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>326</v>
+        <v>92</v>
       </c>
       <c r="B125" t="s">
-        <v>266</v>
+        <v>92</v>
       </c>
       <c r="C125">
-        <v>1</v>
-      </c>
-      <c r="F125" t="s">
-        <v>494</v>
+        <v>2</v>
+      </c>
+      <c r="D125" t="s">
+        <v>141</v>
+      </c>
+      <c r="E125">
+        <v>1</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>325</v>
+        <v>92</v>
       </c>
       <c r="B126" t="s">
-        <v>266</v>
+        <v>92</v>
       </c>
       <c r="C126">
-        <v>1</v>
-      </c>
-      <c r="F126" t="s">
-        <v>493</v>
+        <v>2</v>
+      </c>
+      <c r="D126" t="s">
+        <v>141</v>
+      </c>
+      <c r="E126">
+        <v>2</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>324</v>
+        <v>92</v>
       </c>
       <c r="B127" t="s">
-        <v>266</v>
+        <v>92</v>
       </c>
       <c r="C127">
-        <v>1</v>
-      </c>
-      <c r="F127" t="s">
-        <v>492</v>
+        <v>2</v>
+      </c>
+      <c r="D127" t="s">
+        <v>141</v>
+      </c>
+      <c r="E127">
+        <v>3</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>323</v>
+        <v>92</v>
       </c>
       <c r="B128" t="s">
-        <v>266</v>
+        <v>92</v>
       </c>
       <c r="C128">
-        <v>1</v>
-      </c>
-      <c r="F128" t="s">
-        <v>491</v>
+        <v>2</v>
+      </c>
+      <c r="D128" t="s">
+        <v>142</v>
+      </c>
+      <c r="E128">
+        <v>1</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>322</v>
+        <v>92</v>
       </c>
       <c r="B129" t="s">
-        <v>266</v>
+        <v>92</v>
       </c>
       <c r="C129">
-        <v>1</v>
-      </c>
-      <c r="F129" t="s">
-        <v>490</v>
+        <v>2</v>
+      </c>
+      <c r="D129" t="s">
+        <v>142</v>
+      </c>
+      <c r="E129">
+        <v>2</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>321</v>
+        <v>92</v>
       </c>
       <c r="B130" t="s">
-        <v>266</v>
+        <v>92</v>
       </c>
       <c r="C130">
-        <v>1</v>
-      </c>
-      <c r="F130" t="s">
-        <v>489</v>
+        <v>2</v>
+      </c>
+      <c r="D130" t="s">
+        <v>142</v>
+      </c>
+      <c r="E130">
+        <v>3</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>320</v>
+        <v>441</v>
       </c>
       <c r="B131" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C131">
         <v>1</v>
       </c>
       <c r="F131" t="s">
-        <v>488</v>
+        <v>609</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>319</v>
+        <v>440</v>
       </c>
       <c r="B132" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C132">
         <v>1</v>
       </c>
       <c r="F132" t="s">
-        <v>487</v>
+        <v>608</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>318</v>
+        <v>443</v>
       </c>
       <c r="B133" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C133">
         <v>1</v>
       </c>
       <c r="F133" t="s">
-        <v>486</v>
+        <v>611</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>317</v>
+        <v>444</v>
       </c>
       <c r="B134" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C134">
         <v>1</v>
       </c>
       <c r="F134" t="s">
-        <v>485</v>
+        <v>612</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>316</v>
+        <v>439</v>
       </c>
       <c r="B135" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C135">
         <v>1</v>
       </c>
       <c r="F135" t="s">
-        <v>484</v>
+        <v>607</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>315</v>
+        <v>438</v>
       </c>
       <c r="B136" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C136">
         <v>1</v>
       </c>
       <c r="F136" t="s">
-        <v>483</v>
+        <v>606</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>314</v>
+        <v>442</v>
       </c>
       <c r="B137" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C137">
         <v>1</v>
       </c>
       <c r="F137" t="s">
-        <v>482</v>
+        <v>610</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>313</v>
+        <v>445</v>
       </c>
       <c r="B138" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C138">
         <v>1</v>
       </c>
       <c r="F138" t="s">
-        <v>481</v>
+        <v>613</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>312</v>
+        <v>437</v>
       </c>
       <c r="B139" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C139">
         <v>1</v>
       </c>
       <c r="F139" t="s">
-        <v>480</v>
+        <v>605</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>311</v>
+        <v>436</v>
       </c>
       <c r="B140" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C140">
         <v>1</v>
       </c>
       <c r="F140" t="s">
-        <v>479</v>
+        <v>604</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>450</v>
+        <v>435</v>
       </c>
       <c r="B141" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C141">
         <v>1</v>
       </c>
       <c r="F141" t="s">
-        <v>618</v>
+        <v>603</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>310</v>
+        <v>434</v>
       </c>
       <c r="B142" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C142">
         <v>1</v>
       </c>
       <c r="F142" t="s">
-        <v>478</v>
+        <v>602</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>309</v>
+        <v>433</v>
       </c>
       <c r="B143" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C143">
         <v>1</v>
       </c>
       <c r="F143" t="s">
-        <v>477</v>
+        <v>601</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>308</v>
+        <v>432</v>
       </c>
       <c r="B144" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C144">
         <v>1</v>
       </c>
       <c r="F144" t="s">
-        <v>476</v>
+        <v>600</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>307</v>
+        <v>431</v>
       </c>
       <c r="B145" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C145">
         <v>1</v>
       </c>
       <c r="F145" t="s">
-        <v>475</v>
+        <v>599</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>306</v>
+        <v>430</v>
       </c>
       <c r="B146" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C146">
         <v>1</v>
       </c>
       <c r="F146" t="s">
-        <v>474</v>
+        <v>598</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>305</v>
+        <v>429</v>
       </c>
       <c r="B147" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C147">
         <v>1</v>
       </c>
       <c r="F147" t="s">
-        <v>473</v>
+        <v>597</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>304</v>
+        <v>428</v>
       </c>
       <c r="B148" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C148">
         <v>1</v>
       </c>
       <c r="F148" t="s">
-        <v>472</v>
+        <v>596</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>303</v>
+        <v>427</v>
       </c>
       <c r="B149" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C149">
         <v>1</v>
       </c>
       <c r="F149" t="s">
-        <v>471</v>
+        <v>595</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>302</v>
+        <v>426</v>
       </c>
       <c r="B150" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C150">
         <v>1</v>
       </c>
       <c r="F150" t="s">
-        <v>470</v>
+        <v>594</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>301</v>
+        <v>425</v>
       </c>
       <c r="B151" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C151">
         <v>1</v>
       </c>
       <c r="F151" t="s">
-        <v>469</v>
+        <v>593</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>300</v>
+        <v>424</v>
       </c>
       <c r="B152" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C152">
         <v>1</v>
       </c>
       <c r="F152" t="s">
-        <v>468</v>
+        <v>592</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>299</v>
+        <v>423</v>
       </c>
       <c r="B153" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C153">
         <v>1</v>
       </c>
       <c r="F153" t="s">
-        <v>467</v>
+        <v>591</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>298</v>
+        <v>422</v>
       </c>
       <c r="B154" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C154">
         <v>1</v>
       </c>
       <c r="F154" t="s">
-        <v>466</v>
+        <v>590</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>297</v>
+        <v>421</v>
       </c>
       <c r="B155" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C155">
         <v>1</v>
       </c>
       <c r="F155" t="s">
-        <v>465</v>
+        <v>589</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>296</v>
+        <v>420</v>
       </c>
       <c r="B156" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C156">
         <v>1</v>
       </c>
       <c r="F156" t="s">
-        <v>464</v>
+        <v>588</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>295</v>
+        <v>419</v>
       </c>
       <c r="B157" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C157">
         <v>1</v>
       </c>
       <c r="F157" t="s">
-        <v>463</v>
+        <v>587</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>294</v>
+        <v>418</v>
       </c>
       <c r="B158" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C158">
         <v>1</v>
       </c>
       <c r="F158" t="s">
-        <v>462</v>
+        <v>586</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>293</v>
+        <v>417</v>
       </c>
       <c r="B159" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C159">
         <v>1</v>
       </c>
       <c r="F159" t="s">
-        <v>461</v>
+        <v>585</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>292</v>
+        <v>416</v>
       </c>
       <c r="B160" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C160">
         <v>1</v>
       </c>
       <c r="F160" t="s">
-        <v>460</v>
+        <v>584</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>291</v>
+        <v>415</v>
       </c>
       <c r="B161" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C161">
         <v>1</v>
       </c>
       <c r="F161" t="s">
-        <v>459</v>
+        <v>583</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>290</v>
+        <v>414</v>
       </c>
       <c r="B162" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C162">
         <v>1</v>
       </c>
       <c r="F162" t="s">
-        <v>458</v>
+        <v>582</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>289</v>
+        <v>413</v>
       </c>
       <c r="B163" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C163">
         <v>1</v>
       </c>
       <c r="F163" t="s">
-        <v>457</v>
+        <v>581</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>288</v>
+        <v>412</v>
       </c>
       <c r="B164" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C164">
         <v>1</v>
       </c>
       <c r="F164" t="s">
-        <v>456</v>
+        <v>580</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>287</v>
+        <v>411</v>
       </c>
       <c r="B165" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C165">
         <v>1</v>
       </c>
       <c r="F165" t="s">
-        <v>455</v>
+        <v>579</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>286</v>
+        <v>410</v>
       </c>
       <c r="B166" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C166">
         <v>1</v>
       </c>
       <c r="F166" t="s">
-        <v>454</v>
+        <v>578</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>285</v>
+        <v>409</v>
       </c>
       <c r="B167" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C167">
         <v>1</v>
       </c>
       <c r="F167" t="s">
-        <v>453</v>
+        <v>577</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>284</v>
+        <v>408</v>
       </c>
       <c r="B168" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C168">
         <v>1</v>
       </c>
       <c r="F168" t="s">
-        <v>452</v>
+        <v>576</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>283</v>
+        <v>407</v>
       </c>
       <c r="B169" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C169">
         <v>1</v>
       </c>
       <c r="F169" t="s">
-        <v>451</v>
+        <v>575</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>275</v>
+        <v>406</v>
       </c>
       <c r="B170" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C170">
         <v>1</v>
       </c>
       <c r="F170" t="s">
-        <v>282</v>
+        <v>574</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>274</v>
+        <v>405</v>
       </c>
       <c r="B171" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C171">
         <v>1</v>
       </c>
       <c r="F171" t="s">
-        <v>281</v>
+        <v>573</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>273</v>
+        <v>404</v>
       </c>
       <c r="B172" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C172">
         <v>1</v>
       </c>
       <c r="F172" t="s">
-        <v>280</v>
+        <v>572</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>272</v>
+        <v>403</v>
       </c>
       <c r="B173" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C173">
         <v>1</v>
       </c>
       <c r="F173" t="s">
-        <v>279</v>
+        <v>571</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>271</v>
+        <v>402</v>
       </c>
       <c r="B174" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C174">
         <v>1</v>
       </c>
       <c r="F174" t="s">
-        <v>278</v>
+        <v>570</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>270</v>
+        <v>401</v>
       </c>
       <c r="B175" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C175">
         <v>1</v>
       </c>
       <c r="F175" t="s">
-        <v>277</v>
+        <v>569</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>269</v>
+        <v>400</v>
       </c>
       <c r="B176" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C176">
         <v>1</v>
       </c>
       <c r="F176" t="s">
-        <v>276</v>
+        <v>568</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>267</v>
+        <v>399</v>
       </c>
       <c r="B177" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C177">
         <v>1</v>
       </c>
       <c r="F177" t="s">
-        <v>268</v>
+        <v>567</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>70</v>
+        <v>398</v>
       </c>
       <c r="B178" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C178">
-        <v>2</v>
-      </c>
-      <c r="D178" t="s">
-        <v>71</v>
-      </c>
-      <c r="E178">
         <v>1</v>
       </c>
       <c r="F178" t="s">
-        <v>202</v>
+        <v>566</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>72</v>
+        <v>397</v>
       </c>
       <c r="B179" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C179">
-        <v>2</v>
-      </c>
-      <c r="D179" t="s">
-        <v>71</v>
-      </c>
-      <c r="E179">
         <v>1</v>
       </c>
       <c r="F179" t="s">
-        <v>203</v>
+        <v>565</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>73</v>
+        <v>396</v>
       </c>
       <c r="B180" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C180">
-        <v>2</v>
-      </c>
-      <c r="D180" t="s">
-        <v>71</v>
-      </c>
-      <c r="E180">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F180" t="s">
-        <v>204</v>
+        <v>564</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>74</v>
+        <v>395</v>
       </c>
       <c r="B181" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C181">
-        <v>2</v>
-      </c>
-      <c r="D181" t="s">
-        <v>71</v>
-      </c>
-      <c r="E181">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F181" t="s">
-        <v>205</v>
+        <v>563</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>75</v>
+        <v>394</v>
       </c>
       <c r="B182" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C182">
-        <v>2</v>
-      </c>
-      <c r="D182" t="s">
-        <v>71</v>
-      </c>
-      <c r="E182">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F182" t="s">
-        <v>206</v>
+        <v>562</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>76</v>
+        <v>393</v>
       </c>
       <c r="B183" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C183">
-        <v>2</v>
-      </c>
-      <c r="D183" t="s">
-        <v>77</v>
-      </c>
-      <c r="E183">
         <v>1</v>
       </c>
       <c r="F183" t="s">
-        <v>207</v>
+        <v>561</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>78</v>
+        <v>392</v>
       </c>
       <c r="B184" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C184">
-        <v>2</v>
-      </c>
-      <c r="D184" t="s">
-        <v>77</v>
-      </c>
-      <c r="E184">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F184" t="s">
-        <v>208</v>
+        <v>560</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>79</v>
+        <v>391</v>
       </c>
       <c r="B185" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C185">
-        <v>2</v>
-      </c>
-      <c r="D185" t="s">
-        <v>77</v>
-      </c>
-      <c r="E185">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F185" t="s">
-        <v>209</v>
+        <v>559</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>80</v>
+        <v>390</v>
       </c>
       <c r="B186" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C186">
-        <v>2</v>
-      </c>
-      <c r="D186" t="s">
-        <v>81</v>
-      </c>
-      <c r="E186">
         <v>1</v>
       </c>
       <c r="F186" t="s">
-        <v>210</v>
+        <v>558</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>82</v>
+        <v>389</v>
       </c>
       <c r="B187" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C187">
-        <v>2</v>
-      </c>
-      <c r="D187" t="s">
-        <v>81</v>
-      </c>
-      <c r="E187">
         <v>1</v>
       </c>
       <c r="F187" t="s">
-        <v>211</v>
+        <v>557</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>83</v>
+        <v>388</v>
       </c>
       <c r="B188" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C188">
-        <v>2</v>
-      </c>
-      <c r="D188" t="s">
-        <v>81</v>
-      </c>
-      <c r="E188">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F188" t="s">
-        <v>212</v>
+        <v>556</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>84</v>
+        <v>387</v>
       </c>
       <c r="B189" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C189">
-        <v>2</v>
-      </c>
-      <c r="D189" t="s">
-        <v>81</v>
-      </c>
-      <c r="E189">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F189" t="s">
-        <v>213</v>
+        <v>555</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>85</v>
+        <v>386</v>
       </c>
       <c r="B190" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C190">
-        <v>2</v>
-      </c>
-      <c r="D190" t="s">
-        <v>81</v>
-      </c>
-      <c r="E190">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F190" t="s">
-        <v>214</v>
+        <v>554</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>86</v>
+        <v>385</v>
       </c>
       <c r="B191" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C191">
-        <v>2</v>
-      </c>
-      <c r="D191" t="s">
-        <v>81</v>
-      </c>
-      <c r="E191">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F191" t="s">
-        <v>215</v>
+        <v>553</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>87</v>
+        <v>384</v>
       </c>
       <c r="B192" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C192">
-        <v>2</v>
-      </c>
-      <c r="D192" t="s">
-        <v>88</v>
-      </c>
-      <c r="E192">
         <v>1</v>
       </c>
       <c r="F192" t="s">
-        <v>216</v>
+        <v>552</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>89</v>
+        <v>383</v>
       </c>
       <c r="B193" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C193">
-        <v>2</v>
-      </c>
-      <c r="D193" t="s">
-        <v>88</v>
-      </c>
-      <c r="E193">
         <v>1</v>
       </c>
       <c r="F193" t="s">
-        <v>217</v>
+        <v>551</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>90</v>
+        <v>382</v>
       </c>
       <c r="B194" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C194">
-        <v>2</v>
-      </c>
-      <c r="D194" t="s">
-        <v>88</v>
-      </c>
-      <c r="E194">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F194" t="s">
-        <v>218</v>
+        <v>550</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>91</v>
+        <v>381</v>
       </c>
       <c r="B195" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C195">
-        <v>2</v>
-      </c>
-      <c r="D195" t="s">
-        <v>88</v>
-      </c>
-      <c r="E195">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F195" t="s">
-        <v>219</v>
+        <v>549</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>92</v>
+        <v>380</v>
       </c>
       <c r="B196" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C196">
-        <v>2</v>
-      </c>
-      <c r="D196" t="s">
-        <v>88</v>
-      </c>
-      <c r="E196">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F196" t="s">
-        <v>220</v>
+        <v>548</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>93</v>
+        <v>379</v>
       </c>
       <c r="B197" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C197">
-        <v>2</v>
-      </c>
-      <c r="D197" t="s">
-        <v>88</v>
-      </c>
-      <c r="E197">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F197" t="s">
-        <v>221</v>
+        <v>547</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>114</v>
+        <v>378</v>
       </c>
       <c r="B198" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C198">
-        <v>2</v>
-      </c>
-      <c r="D198" t="s">
-        <v>115</v>
-      </c>
-      <c r="E198">
         <v>1</v>
       </c>
       <c r="F198" t="s">
-        <v>237</v>
+        <v>546</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>116</v>
+        <v>377</v>
       </c>
       <c r="B199" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C199">
-        <v>2</v>
-      </c>
-      <c r="D199" t="s">
-        <v>115</v>
-      </c>
-      <c r="E199">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F199" t="s">
-        <v>238</v>
+        <v>545</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>117</v>
+        <v>376</v>
       </c>
       <c r="B200" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C200">
-        <v>2</v>
-      </c>
-      <c r="D200" t="s">
-        <v>115</v>
-      </c>
-      <c r="E200">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F200" t="s">
-        <v>239</v>
+        <v>544</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>118</v>
+        <v>375</v>
       </c>
       <c r="B201" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C201">
-        <v>2</v>
-      </c>
-      <c r="D201" t="s">
-        <v>115</v>
-      </c>
-      <c r="E201">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F201" t="s">
-        <v>240</v>
+        <v>543</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>119</v>
+        <v>374</v>
       </c>
       <c r="B202" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C202">
-        <v>2</v>
-      </c>
-      <c r="D202" t="s">
-        <v>120</v>
-      </c>
-      <c r="E202">
         <v>1</v>
       </c>
       <c r="F202" t="s">
-        <v>241</v>
+        <v>542</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>121</v>
+        <v>373</v>
       </c>
       <c r="B203" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C203">
-        <v>2</v>
-      </c>
-      <c r="D203" t="s">
-        <v>120</v>
-      </c>
-      <c r="E203">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F203" t="s">
-        <v>242</v>
+        <v>541</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>122</v>
+        <v>372</v>
       </c>
       <c r="B204" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C204">
-        <v>2</v>
-      </c>
-      <c r="D204" t="s">
-        <v>120</v>
-      </c>
-      <c r="E204">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F204" t="s">
-        <v>243</v>
+        <v>540</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>123</v>
+        <v>371</v>
       </c>
       <c r="B205" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C205">
-        <v>2</v>
-      </c>
-      <c r="D205" t="s">
-        <v>120</v>
-      </c>
-      <c r="E205">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F205" t="s">
-        <v>244</v>
+        <v>539</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>124</v>
+        <v>370</v>
       </c>
       <c r="B206" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C206">
-        <v>2</v>
-      </c>
-      <c r="D206" t="s">
-        <v>120</v>
-      </c>
-      <c r="E206">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F206" t="s">
-        <v>245</v>
+        <v>538</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>125</v>
+        <v>369</v>
       </c>
       <c r="B207" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C207">
-        <v>2</v>
-      </c>
-      <c r="D207" t="s">
-        <v>126</v>
-      </c>
-      <c r="E207">
         <v>1</v>
       </c>
       <c r="F207" t="s">
-        <v>246</v>
+        <v>537</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>127</v>
+        <v>368</v>
       </c>
       <c r="B208" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C208">
-        <v>2</v>
-      </c>
-      <c r="D208" t="s">
-        <v>126</v>
-      </c>
-      <c r="E208">
         <v>1</v>
       </c>
       <c r="F208" t="s">
-        <v>247</v>
+        <v>536</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>128</v>
+        <v>367</v>
       </c>
       <c r="B209" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C209">
-        <v>2</v>
-      </c>
-      <c r="D209" t="s">
-        <v>126</v>
-      </c>
-      <c r="E209">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F209" t="s">
-        <v>248</v>
+        <v>535</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>129</v>
+        <v>366</v>
       </c>
       <c r="B210" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C210">
-        <v>2</v>
-      </c>
-      <c r="D210" t="s">
-        <v>126</v>
-      </c>
-      <c r="E210">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F210" t="s">
-        <v>249</v>
+        <v>534</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>130</v>
+        <v>365</v>
       </c>
       <c r="B211" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C211">
-        <v>2</v>
-      </c>
-      <c r="D211" t="s">
-        <v>131</v>
-      </c>
-      <c r="E211">
         <v>1</v>
       </c>
       <c r="F211" t="s">
-        <v>250</v>
+        <v>533</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>132</v>
+        <v>364</v>
       </c>
       <c r="B212" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C212">
-        <v>2</v>
-      </c>
-      <c r="D212" t="s">
-        <v>131</v>
-      </c>
-      <c r="E212">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F212" t="s">
-        <v>251</v>
+        <v>532</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>133</v>
+        <v>363</v>
       </c>
       <c r="B213" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C213">
-        <v>2</v>
-      </c>
-      <c r="D213" t="s">
-        <v>131</v>
-      </c>
-      <c r="E213">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F213" t="s">
-        <v>252</v>
+        <v>531</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>134</v>
+        <v>362</v>
       </c>
       <c r="B214" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C214">
-        <v>2</v>
-      </c>
-      <c r="D214" t="s">
-        <v>131</v>
-      </c>
-      <c r="E214">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F214" t="s">
-        <v>253</v>
+        <v>530</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>135</v>
+        <v>361</v>
       </c>
       <c r="B215" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C215">
-        <v>2</v>
-      </c>
-      <c r="D215" t="s">
-        <v>136</v>
-      </c>
-      <c r="E215">
         <v>1</v>
       </c>
       <c r="F215" t="s">
-        <v>254</v>
+        <v>529</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>137</v>
+        <v>360</v>
       </c>
       <c r="B216" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C216">
-        <v>2</v>
-      </c>
-      <c r="D216" t="s">
-        <v>136</v>
-      </c>
-      <c r="E216">
         <v>1</v>
       </c>
       <c r="F216" t="s">
-        <v>255</v>
+        <v>528</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>138</v>
+        <v>359</v>
       </c>
       <c r="B217" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C217">
-        <v>2</v>
-      </c>
-      <c r="D217" t="s">
-        <v>136</v>
-      </c>
-      <c r="E217">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F217" t="s">
-        <v>256</v>
+        <v>527</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>139</v>
+        <v>358</v>
       </c>
       <c r="B218" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C218">
-        <v>2</v>
-      </c>
-      <c r="D218" t="s">
-        <v>136</v>
-      </c>
-      <c r="E218">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F218" t="s">
-        <v>257</v>
+        <v>526</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>140</v>
+        <v>357</v>
       </c>
       <c r="B219" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C219">
-        <v>2</v>
-      </c>
-      <c r="D219" t="s">
-        <v>136</v>
-      </c>
-      <c r="E219">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F219" t="s">
-        <v>258</v>
+        <v>525</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>141</v>
+        <v>356</v>
       </c>
       <c r="B220" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C220">
-        <v>2</v>
-      </c>
-      <c r="D220" t="s">
-        <v>136</v>
-      </c>
-      <c r="E220">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F220" t="s">
-        <v>259</v>
+        <v>524</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>94</v>
+        <v>355</v>
       </c>
       <c r="B221" t="s">
-        <v>94</v>
+        <v>262</v>
       </c>
       <c r="C221">
-        <v>2</v>
-      </c>
-      <c r="D221" t="s">
-        <v>142</v>
-      </c>
-      <c r="E221">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="F221" t="s">
+        <v>523</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>94</v>
+        <v>354</v>
       </c>
       <c r="B222" t="s">
-        <v>94</v>
+        <v>262</v>
       </c>
       <c r="C222">
-        <v>2</v>
-      </c>
-      <c r="D222" t="s">
-        <v>142</v>
-      </c>
-      <c r="E222">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F222" t="s">
+        <v>522</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>94</v>
+        <v>353</v>
       </c>
       <c r="B223" t="s">
-        <v>94</v>
+        <v>262</v>
       </c>
       <c r="C223">
-        <v>2</v>
-      </c>
-      <c r="D223" t="s">
-        <v>142</v>
-      </c>
-      <c r="E223">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="F223" t="s">
+        <v>521</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>94</v>
+        <v>352</v>
       </c>
       <c r="B224" t="s">
-        <v>94</v>
+        <v>262</v>
       </c>
       <c r="C224">
-        <v>2</v>
-      </c>
-      <c r="D224" t="s">
-        <v>143</v>
-      </c>
-      <c r="E224">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="F224" t="s">
+        <v>520</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>94</v>
+        <v>351</v>
       </c>
       <c r="B225" t="s">
-        <v>94</v>
+        <v>262</v>
       </c>
       <c r="C225">
-        <v>2</v>
-      </c>
-      <c r="D225" t="s">
-        <v>143</v>
-      </c>
-      <c r="E225">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F225" t="s">
+        <v>519</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>94</v>
+        <v>350</v>
       </c>
       <c r="B226" t="s">
-        <v>94</v>
+        <v>262</v>
       </c>
       <c r="C226">
-        <v>2</v>
-      </c>
-      <c r="D226" t="s">
-        <v>143</v>
-      </c>
-      <c r="E226">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="F226" t="s">
+        <v>518</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>94</v>
+        <v>349</v>
       </c>
       <c r="B227" t="s">
-        <v>94</v>
+        <v>262</v>
       </c>
       <c r="C227">
-        <v>2</v>
-      </c>
-      <c r="D227" t="s">
-        <v>144</v>
-      </c>
-      <c r="E227">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="F227" t="s">
+        <v>517</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>94</v>
+        <v>348</v>
       </c>
       <c r="B228" t="s">
-        <v>94</v>
+        <v>262</v>
       </c>
       <c r="C228">
-        <v>2</v>
-      </c>
-      <c r="D228" t="s">
-        <v>144</v>
-      </c>
-      <c r="E228">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F228" t="s">
+        <v>516</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>94</v>
+        <v>347</v>
       </c>
       <c r="B229" t="s">
-        <v>94</v>
+        <v>262</v>
       </c>
       <c r="C229">
-        <v>2</v>
-      </c>
-      <c r="D229" t="s">
-        <v>144</v>
-      </c>
-      <c r="E229">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="F229" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>0</v>
+        <v>346</v>
       </c>
       <c r="B230" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C230">
-        <v>3</v>
-      </c>
-      <c r="D230" t="s">
-        <v>1</v>
-      </c>
-      <c r="E230">
         <v>1</v>
       </c>
       <c r="F230" t="s">
-        <v>145</v>
+        <v>514</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>2</v>
+        <v>345</v>
       </c>
       <c r="B231" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C231">
-        <v>3</v>
-      </c>
-      <c r="D231" t="s">
-        <v>1</v>
-      </c>
-      <c r="E231">
         <v>1</v>
       </c>
       <c r="F231" t="s">
-        <v>146</v>
+        <v>513</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>3</v>
+        <v>344</v>
       </c>
       <c r="B232" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C232">
-        <v>3</v>
-      </c>
-      <c r="D232" t="s">
-        <v>1</v>
-      </c>
-      <c r="E232">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F232" t="s">
-        <v>147</v>
+        <v>512</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>4</v>
+        <v>343</v>
       </c>
       <c r="B233" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C233">
-        <v>3</v>
-      </c>
-      <c r="D233" t="s">
-        <v>1</v>
-      </c>
-      <c r="E233">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F233" t="s">
-        <v>148</v>
+        <v>511</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>5</v>
+        <v>342</v>
       </c>
       <c r="B234" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C234">
-        <v>3</v>
-      </c>
-      <c r="D234" t="s">
-        <v>1</v>
-      </c>
-      <c r="E234">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F234" t="s">
-        <v>149</v>
+        <v>510</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>6</v>
+        <v>341</v>
       </c>
       <c r="B235" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C235">
-        <v>3</v>
-      </c>
-      <c r="D235" t="s">
-        <v>1</v>
-      </c>
-      <c r="E235">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F235" t="s">
-        <v>150</v>
+        <v>509</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>7</v>
+        <v>340</v>
       </c>
       <c r="B236" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C236">
-        <v>3</v>
-      </c>
-      <c r="D236" t="s">
-        <v>8</v>
-      </c>
-      <c r="E236">
         <v>1</v>
       </c>
       <c r="F236" t="s">
-        <v>151</v>
+        <v>508</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>9</v>
+        <v>339</v>
       </c>
       <c r="B237" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C237">
-        <v>3</v>
-      </c>
-      <c r="D237" t="s">
-        <v>8</v>
-      </c>
-      <c r="E237">
         <v>1</v>
       </c>
       <c r="F237" t="s">
-        <v>152</v>
+        <v>507</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>10</v>
+        <v>338</v>
       </c>
       <c r="B238" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C238">
-        <v>3</v>
-      </c>
-      <c r="D238" t="s">
-        <v>8</v>
-      </c>
-      <c r="E238">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F238" t="s">
-        <v>153</v>
+        <v>506</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>11</v>
+        <v>337</v>
       </c>
       <c r="B239" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C239">
-        <v>3</v>
-      </c>
-      <c r="D239" t="s">
-        <v>8</v>
-      </c>
-      <c r="E239">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F239" t="s">
-        <v>154</v>
+        <v>505</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>12</v>
+        <v>336</v>
       </c>
       <c r="B240" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C240">
-        <v>3</v>
-      </c>
-      <c r="D240" t="s">
-        <v>8</v>
-      </c>
-      <c r="E240">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F240" t="s">
-        <v>155</v>
+        <v>504</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>13</v>
+        <v>335</v>
       </c>
       <c r="B241" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C241">
-        <v>3</v>
-      </c>
-      <c r="D241" t="s">
-        <v>8</v>
-      </c>
-      <c r="E241">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F241" t="s">
-        <v>156</v>
+        <v>503</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>14</v>
+        <v>334</v>
       </c>
       <c r="B242" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C242">
-        <v>3</v>
-      </c>
-      <c r="D242" t="s">
-        <v>15</v>
-      </c>
-      <c r="E242">
         <v>1</v>
       </c>
       <c r="F242" t="s">
-        <v>157</v>
+        <v>502</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>16</v>
+        <v>333</v>
       </c>
       <c r="B243" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C243">
-        <v>3</v>
-      </c>
-      <c r="D243" t="s">
-        <v>15</v>
-      </c>
-      <c r="E243">
         <v>1</v>
       </c>
       <c r="F243" t="s">
-        <v>158</v>
+        <v>501</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>17</v>
+        <v>332</v>
       </c>
       <c r="B244" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C244">
-        <v>3</v>
-      </c>
-      <c r="D244" t="s">
-        <v>15</v>
-      </c>
-      <c r="E244">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F244" t="s">
-        <v>159</v>
+        <v>500</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>18</v>
+        <v>331</v>
       </c>
       <c r="B245" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C245">
-        <v>3</v>
-      </c>
-      <c r="D245" t="s">
-        <v>15</v>
-      </c>
-      <c r="E245">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F245" t="s">
-        <v>160</v>
+        <v>499</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>19</v>
+        <v>330</v>
       </c>
       <c r="B246" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C246">
-        <v>3</v>
-      </c>
-      <c r="D246" t="s">
-        <v>15</v>
-      </c>
-      <c r="E246">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F246" t="s">
-        <v>161</v>
+        <v>498</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>20</v>
+        <v>329</v>
       </c>
       <c r="B247" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C247">
-        <v>3</v>
-      </c>
-      <c r="D247" t="s">
-        <v>15</v>
-      </c>
-      <c r="E247">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F247" t="s">
-        <v>162</v>
+        <v>497</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>21</v>
+        <v>328</v>
       </c>
       <c r="B248" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C248">
-        <v>3</v>
-      </c>
-      <c r="D248" t="s">
-        <v>15</v>
-      </c>
-      <c r="E248">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F248" t="s">
-        <v>163</v>
+        <v>496</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>22</v>
+        <v>327</v>
       </c>
       <c r="B249" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C249">
-        <v>3</v>
-      </c>
-      <c r="D249" t="s">
-        <v>23</v>
-      </c>
-      <c r="E249">
         <v>1</v>
       </c>
       <c r="F249" t="s">
-        <v>164</v>
+        <v>495</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>24</v>
+        <v>326</v>
       </c>
       <c r="B250" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C250">
-        <v>3</v>
-      </c>
-      <c r="D250" t="s">
-        <v>23</v>
-      </c>
-      <c r="E250">
         <v>1</v>
       </c>
       <c r="F250" t="s">
-        <v>165</v>
+        <v>494</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>25</v>
+        <v>325</v>
       </c>
       <c r="B251" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C251">
-        <v>3</v>
-      </c>
-      <c r="D251" t="s">
-        <v>23</v>
-      </c>
-      <c r="E251">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F251" t="s">
-        <v>166</v>
+        <v>493</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>26</v>
+        <v>324</v>
       </c>
       <c r="B252" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C252">
-        <v>3</v>
-      </c>
-      <c r="D252" t="s">
-        <v>23</v>
-      </c>
-      <c r="E252">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F252" t="s">
-        <v>167</v>
+        <v>492</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>27</v>
+        <v>323</v>
       </c>
       <c r="B253" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C253">
-        <v>3</v>
-      </c>
-      <c r="D253" t="s">
-        <v>23</v>
-      </c>
-      <c r="E253">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F253" t="s">
-        <v>168</v>
+        <v>491</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>28</v>
+        <v>322</v>
       </c>
       <c r="B254" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C254">
-        <v>3</v>
-      </c>
-      <c r="D254" t="s">
-        <v>23</v>
-      </c>
-      <c r="E254">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F254" t="s">
-        <v>169</v>
+        <v>490</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>29</v>
+        <v>321</v>
       </c>
       <c r="B255" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C255">
-        <v>3</v>
-      </c>
-      <c r="D255" t="s">
-        <v>30</v>
-      </c>
-      <c r="E255">
         <v>1</v>
       </c>
       <c r="F255" t="s">
-        <v>170</v>
+        <v>489</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>31</v>
+        <v>320</v>
       </c>
       <c r="B256" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C256">
-        <v>3</v>
-      </c>
-      <c r="D256" t="s">
-        <v>30</v>
-      </c>
-      <c r="E256">
         <v>1</v>
       </c>
       <c r="F256" t="s">
-        <v>171</v>
+        <v>488</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>32</v>
+        <v>319</v>
       </c>
       <c r="B257" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C257">
-        <v>3</v>
-      </c>
-      <c r="D257" t="s">
-        <v>30</v>
-      </c>
-      <c r="E257">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F257" t="s">
-        <v>172</v>
+        <v>487</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>33</v>
+        <v>318</v>
       </c>
       <c r="B258" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C258">
-        <v>3</v>
-      </c>
-      <c r="D258" t="s">
-        <v>30</v>
-      </c>
-      <c r="E258">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F258" t="s">
-        <v>173</v>
+        <v>486</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>34</v>
+        <v>317</v>
       </c>
       <c r="B259" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C259">
-        <v>3</v>
-      </c>
-      <c r="D259" t="s">
-        <v>30</v>
-      </c>
-      <c r="E259">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F259" t="s">
-        <v>174</v>
+        <v>485</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>35</v>
+        <v>316</v>
       </c>
       <c r="B260" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C260">
-        <v>3</v>
-      </c>
-      <c r="D260" t="s">
-        <v>30</v>
-      </c>
-      <c r="E260">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F260" t="s">
-        <v>175</v>
+        <v>484</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>36</v>
+        <v>315</v>
       </c>
       <c r="B261" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C261">
-        <v>3</v>
-      </c>
-      <c r="D261" t="s">
-        <v>37</v>
-      </c>
-      <c r="E261">
         <v>1</v>
       </c>
       <c r="F261" t="s">
-        <v>176</v>
+        <v>483</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>38</v>
+        <v>314</v>
       </c>
       <c r="B262" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C262">
-        <v>3</v>
-      </c>
-      <c r="D262" t="s">
-        <v>37</v>
-      </c>
-      <c r="E262">
         <v>1</v>
       </c>
       <c r="F262" t="s">
-        <v>177</v>
+        <v>482</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>39</v>
+        <v>313</v>
       </c>
       <c r="B263" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C263">
-        <v>3</v>
-      </c>
-      <c r="D263" t="s">
-        <v>37</v>
-      </c>
-      <c r="E263">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F263" t="s">
-        <v>178</v>
+        <v>481</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>40</v>
+        <v>312</v>
       </c>
       <c r="B264" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C264">
-        <v>3</v>
-      </c>
-      <c r="D264" t="s">
-        <v>37</v>
-      </c>
-      <c r="E264">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F264" t="s">
-        <v>179</v>
+        <v>480</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>41</v>
+        <v>311</v>
       </c>
       <c r="B265" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C265">
-        <v>3</v>
-      </c>
-      <c r="D265" t="s">
-        <v>37</v>
-      </c>
-      <c r="E265">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F265" t="s">
-        <v>180</v>
+        <v>479</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>42</v>
+        <v>310</v>
       </c>
       <c r="B266" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C266">
-        <v>3</v>
-      </c>
-      <c r="D266" t="s">
-        <v>37</v>
-      </c>
-      <c r="E266">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F266" t="s">
-        <v>181</v>
+        <v>478</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>43</v>
+        <v>309</v>
       </c>
       <c r="B267" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C267">
-        <v>3</v>
-      </c>
-      <c r="D267" t="s">
-        <v>44</v>
-      </c>
-      <c r="E267">
         <v>1</v>
       </c>
       <c r="F267" t="s">
-        <v>182</v>
+        <v>477</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>45</v>
+        <v>308</v>
       </c>
       <c r="B268" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C268">
-        <v>3</v>
-      </c>
-      <c r="D268" t="s">
-        <v>44</v>
-      </c>
-      <c r="E268">
         <v>1</v>
       </c>
       <c r="F268" t="s">
-        <v>183</v>
+        <v>476</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>46</v>
+        <v>307</v>
       </c>
       <c r="B269" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C269">
-        <v>3</v>
-      </c>
-      <c r="D269" t="s">
-        <v>44</v>
-      </c>
-      <c r="E269">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F269" t="s">
-        <v>184</v>
+        <v>475</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>47</v>
+        <v>446</v>
       </c>
       <c r="B270" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C270">
-        <v>3</v>
-      </c>
-      <c r="D270" t="s">
-        <v>44</v>
-      </c>
-      <c r="E270">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F270" t="s">
-        <v>185</v>
+        <v>614</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>48</v>
+        <v>306</v>
       </c>
       <c r="B271" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C271">
-        <v>3</v>
-      </c>
-      <c r="D271" t="s">
-        <v>44</v>
-      </c>
-      <c r="E271">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F271" t="s">
-        <v>186</v>
+        <v>474</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>49</v>
+        <v>305</v>
       </c>
       <c r="B272" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C272">
-        <v>3</v>
-      </c>
-      <c r="D272" t="s">
-        <v>50</v>
-      </c>
-      <c r="E272">
         <v>1</v>
       </c>
       <c r="F272" t="s">
-        <v>187</v>
+        <v>473</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>51</v>
+        <v>304</v>
       </c>
       <c r="B273" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C273">
-        <v>3</v>
-      </c>
-      <c r="D273" t="s">
-        <v>50</v>
-      </c>
-      <c r="E273">
         <v>1</v>
       </c>
       <c r="F273" t="s">
-        <v>188</v>
+        <v>472</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>52</v>
+        <v>303</v>
       </c>
       <c r="B274" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C274">
-        <v>3</v>
-      </c>
-      <c r="D274" t="s">
-        <v>50</v>
-      </c>
-      <c r="E274">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F274" t="s">
-        <v>189</v>
+        <v>471</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>53</v>
+        <v>302</v>
       </c>
       <c r="B275" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C275">
-        <v>3</v>
-      </c>
-      <c r="D275" t="s">
-        <v>50</v>
-      </c>
-      <c r="E275">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F275" t="s">
-        <v>190</v>
+        <v>470</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>54</v>
+        <v>301</v>
       </c>
       <c r="B276" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C276">
-        <v>3</v>
-      </c>
-      <c r="D276" t="s">
-        <v>50</v>
-      </c>
-      <c r="E276">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F276" t="s">
-        <v>191</v>
+        <v>469</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>55</v>
+        <v>300</v>
       </c>
       <c r="B277" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C277">
-        <v>3</v>
-      </c>
-      <c r="D277" t="s">
-        <v>56</v>
-      </c>
-      <c r="E277">
         <v>1</v>
       </c>
       <c r="F277" t="s">
-        <v>192</v>
+        <v>468</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>57</v>
+        <v>299</v>
       </c>
       <c r="B278" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C278">
-        <v>3</v>
-      </c>
-      <c r="D278" t="s">
-        <v>56</v>
-      </c>
-      <c r="E278">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F278" t="s">
-        <v>193</v>
+        <v>467</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>58</v>
+        <v>298</v>
       </c>
       <c r="B279" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C279">
-        <v>3</v>
-      </c>
-      <c r="D279" t="s">
-        <v>56</v>
-      </c>
-      <c r="E279">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F279" t="s">
-        <v>194</v>
+        <v>466</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>59</v>
+        <v>297</v>
       </c>
       <c r="B280" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C280">
-        <v>3</v>
-      </c>
-      <c r="D280" t="s">
-        <v>60</v>
-      </c>
-      <c r="E280">
         <v>1</v>
       </c>
       <c r="F280" t="s">
-        <v>195</v>
+        <v>465</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>61</v>
+        <v>296</v>
       </c>
       <c r="B281" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C281">
-        <v>3</v>
-      </c>
-      <c r="D281" t="s">
-        <v>60</v>
-      </c>
-      <c r="E281">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F281" t="s">
-        <v>196</v>
+        <v>464</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>62</v>
+        <v>295</v>
       </c>
       <c r="B282" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C282">
-        <v>3</v>
-      </c>
-      <c r="D282" t="s">
-        <v>60</v>
-      </c>
-      <c r="E282">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F282" t="s">
-        <v>197</v>
+        <v>463</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>63</v>
+        <v>294</v>
       </c>
       <c r="B283" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C283">
-        <v>3</v>
-      </c>
-      <c r="D283" t="s">
-        <v>60</v>
-      </c>
-      <c r="E283">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F283" t="s">
-        <v>198</v>
+        <v>462</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>64</v>
+        <v>293</v>
       </c>
       <c r="B284" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C284">
-        <v>3</v>
-      </c>
-      <c r="D284" t="s">
-        <v>65</v>
-      </c>
-      <c r="E284">
         <v>1</v>
       </c>
       <c r="F284" t="s">
-        <v>199</v>
+        <v>461</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>66</v>
+        <v>292</v>
       </c>
       <c r="B285" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C285">
-        <v>3</v>
-      </c>
-      <c r="D285" t="s">
-        <v>65</v>
-      </c>
-      <c r="E285">
         <v>1</v>
       </c>
       <c r="F285" t="s">
-        <v>200</v>
+        <v>460</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>67</v>
+        <v>291</v>
       </c>
       <c r="B286" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C286">
-        <v>3</v>
-      </c>
-      <c r="D286" t="s">
-        <v>65</v>
-      </c>
-      <c r="E286">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F286" t="s">
-        <v>201</v>
+        <v>459</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>68</v>
+        <v>290</v>
       </c>
       <c r="B287" t="s">
-        <v>68</v>
+        <v>262</v>
       </c>
       <c r="C287">
-        <v>3</v>
-      </c>
-      <c r="D287" t="s">
-        <v>65</v>
-      </c>
-      <c r="E287">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="F287" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>68</v>
+        <v>289</v>
       </c>
       <c r="B288" t="s">
-        <v>68</v>
+        <v>262</v>
       </c>
       <c r="C288">
-        <v>3</v>
-      </c>
-      <c r="D288" t="s">
-        <v>69</v>
-      </c>
-      <c r="E288">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="F288" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>68</v>
+        <v>288</v>
       </c>
       <c r="B289" t="s">
-        <v>68</v>
+        <v>262</v>
       </c>
       <c r="C289">
-        <v>3</v>
-      </c>
-      <c r="D289" t="s">
-        <v>69</v>
-      </c>
-      <c r="E289">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F289" t="s">
+        <v>456</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>68</v>
+        <v>287</v>
       </c>
       <c r="B290" t="s">
-        <v>68</v>
+        <v>262</v>
       </c>
       <c r="C290">
-        <v>3</v>
-      </c>
-      <c r="D290" t="s">
-        <v>69</v>
-      </c>
-      <c r="E290">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="F290" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>94</v>
+        <v>286</v>
       </c>
       <c r="B291" t="s">
-        <v>94</v>
+        <v>262</v>
       </c>
       <c r="C291">
-        <v>3</v>
-      </c>
-      <c r="D291" t="s">
-        <v>95</v>
-      </c>
-      <c r="E291">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="F291" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>94</v>
+        <v>285</v>
       </c>
       <c r="B292" t="s">
-        <v>94</v>
+        <v>262</v>
       </c>
       <c r="C292">
-        <v>3</v>
-      </c>
-      <c r="D292" t="s">
-        <v>95</v>
-      </c>
-      <c r="E292">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F292" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>94</v>
+        <v>284</v>
       </c>
       <c r="B293" t="s">
-        <v>94</v>
+        <v>262</v>
       </c>
       <c r="C293">
-        <v>3</v>
-      </c>
-      <c r="D293" t="s">
-        <v>95</v>
-      </c>
-      <c r="E293">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="F293" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>96</v>
+        <v>283</v>
       </c>
       <c r="B294" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C294">
-        <v>3</v>
-      </c>
-      <c r="D294" t="s">
-        <v>97</v>
-      </c>
-      <c r="E294">
         <v>1</v>
       </c>
       <c r="F294" t="s">
-        <v>222</v>
+        <v>451</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>98</v>
+        <v>282</v>
       </c>
       <c r="B295" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C295">
-        <v>3</v>
-      </c>
-      <c r="D295" t="s">
-        <v>97</v>
-      </c>
-      <c r="E295">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F295" t="s">
-        <v>223</v>
+        <v>450</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>99</v>
+        <v>281</v>
       </c>
       <c r="B296" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C296">
-        <v>3</v>
-      </c>
-      <c r="D296" t="s">
-        <v>97</v>
-      </c>
-      <c r="E296">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F296" t="s">
-        <v>224</v>
+        <v>449</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>100</v>
+        <v>280</v>
       </c>
       <c r="B297" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C297">
-        <v>3</v>
-      </c>
-      <c r="D297" t="s">
-        <v>97</v>
-      </c>
-      <c r="E297">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F297" t="s">
-        <v>225</v>
+        <v>448</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>101</v>
+        <v>279</v>
       </c>
       <c r="B298" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C298">
-        <v>3</v>
-      </c>
-      <c r="D298" t="s">
-        <v>102</v>
-      </c>
-      <c r="E298">
         <v>1</v>
       </c>
       <c r="F298" t="s">
-        <v>226</v>
+        <v>447</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>103</v>
+        <v>271</v>
       </c>
       <c r="B299" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C299">
-        <v>3</v>
-      </c>
-      <c r="D299" t="s">
-        <v>102</v>
-      </c>
-      <c r="E299">
         <v>1</v>
       </c>
       <c r="F299" t="s">
-        <v>227</v>
+        <v>278</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>104</v>
+        <v>270</v>
       </c>
       <c r="B300" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C300">
-        <v>3</v>
-      </c>
-      <c r="D300" t="s">
-        <v>102</v>
-      </c>
-      <c r="E300">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F300" t="s">
-        <v>228</v>
+        <v>277</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>105</v>
+        <v>269</v>
       </c>
       <c r="B301" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C301">
-        <v>3</v>
-      </c>
-      <c r="D301" t="s">
-        <v>102</v>
-      </c>
-      <c r="E301">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F301" t="s">
-        <v>229</v>
+        <v>276</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>106</v>
+        <v>268</v>
       </c>
       <c r="B302" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C302">
-        <v>3</v>
-      </c>
-      <c r="D302" t="s">
-        <v>102</v>
-      </c>
-      <c r="E302">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F302" t="s">
-        <v>230</v>
+        <v>275</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>107</v>
+        <v>267</v>
       </c>
       <c r="B303" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C303">
-        <v>3</v>
-      </c>
-      <c r="D303" t="s">
-        <v>108</v>
-      </c>
-      <c r="E303">
         <v>1</v>
       </c>
       <c r="F303" t="s">
-        <v>231</v>
+        <v>274</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>109</v>
+        <v>266</v>
       </c>
       <c r="B304" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C304">
-        <v>3</v>
-      </c>
-      <c r="D304" t="s">
-        <v>108</v>
-      </c>
-      <c r="E304">
         <v>1</v>
       </c>
       <c r="F304" t="s">
-        <v>232</v>
+        <v>273</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>110</v>
+        <v>265</v>
       </c>
       <c r="B305" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C305">
-        <v>3</v>
-      </c>
-      <c r="D305" t="s">
-        <v>108</v>
-      </c>
-      <c r="E305">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F305" t="s">
-        <v>233</v>
+        <v>272</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>111</v>
+        <v>263</v>
       </c>
       <c r="B306" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C306">
-        <v>3</v>
-      </c>
-      <c r="D306" t="s">
-        <v>108</v>
-      </c>
-      <c r="E306">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F306" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A307" t="s">
-        <v>112</v>
-      </c>
-      <c r="B307" t="s">
-        <v>266</v>
-      </c>
-      <c r="C307">
-        <v>3</v>
-      </c>
-      <c r="D307" t="s">
-        <v>108</v>
-      </c>
-      <c r="E307">
-        <v>3</v>
-      </c>
-      <c r="F307" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A308" t="s">
-        <v>113</v>
-      </c>
-      <c r="B308" t="s">
-        <v>266</v>
-      </c>
-      <c r="C308">
-        <v>3</v>
-      </c>
-      <c r="D308" t="s">
-        <v>108</v>
-      </c>
-      <c r="E308">
-        <v>3</v>
-      </c>
-      <c r="F308" t="s">
-        <v>236</v>
+        <v>264</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F308">
-    <sortCondition ref="C2:C308"/>
-    <sortCondition ref="D2:D308"/>
-    <sortCondition ref="E2:E308"/>
-    <sortCondition descending="1" ref="A2:A308"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F306">
+    <sortCondition descending="1" ref="C2:C306"/>
+    <sortCondition ref="D2:D306"/>
+    <sortCondition ref="E2:E306"/>
+    <sortCondition descending="1" ref="A2:A306"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/EOAT_data.xlsx
+++ b/data/EOAT_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\procesos.CAZEL\Desktop\Becario Procesos\EOAT Project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B21A3D01-0935-4603-800B-CAF25F4A4CC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3874C80C-BE0C-4CDD-9B6A-FDE6ADEFAE14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{440E3869-3C3F-4E8C-A8BD-ADEB8E2EA552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1037" uniqueCount="617">
   <si>
     <t>I-1937</t>
   </si>
@@ -1881,6 +1881,12 @@
   </si>
   <si>
     <t>I-1614.jpeg</t>
+  </si>
+  <si>
+    <t>I-1612</t>
+  </si>
+  <si>
+    <t>I-1612.jpeg</t>
   </si>
 </sst>
 </file>
@@ -2258,7 +2264,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B6791C-A8A7-4753-A504-FAA9E3EE8745}">
-  <dimension ref="A1:F306"/>
+  <dimension ref="A1:F307"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -6783,7 +6789,7 @@
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>306</v>
+        <v>615</v>
       </c>
       <c r="B271" t="s">
         <v>262</v>
@@ -6792,12 +6798,12 @@
         <v>1</v>
       </c>
       <c r="F271" t="s">
-        <v>474</v>
+        <v>616</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B272" t="s">
         <v>262</v>
@@ -6806,12 +6812,12 @@
         <v>1</v>
       </c>
       <c r="F272" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B273" t="s">
         <v>262</v>
@@ -6820,12 +6826,12 @@
         <v>1</v>
       </c>
       <c r="F273" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B274" t="s">
         <v>262</v>
@@ -6834,12 +6840,12 @@
         <v>1</v>
       </c>
       <c r="F274" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B275" t="s">
         <v>262</v>
@@ -6848,12 +6854,12 @@
         <v>1</v>
       </c>
       <c r="F275" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B276" t="s">
         <v>262</v>
@@ -6862,12 +6868,12 @@
         <v>1</v>
       </c>
       <c r="F276" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B277" t="s">
         <v>262</v>
@@ -6876,12 +6882,12 @@
         <v>1</v>
       </c>
       <c r="F277" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B278" t="s">
         <v>262</v>
@@ -6890,12 +6896,12 @@
         <v>1</v>
       </c>
       <c r="F278" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B279" t="s">
         <v>262</v>
@@ -6904,12 +6910,12 @@
         <v>1</v>
       </c>
       <c r="F279" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B280" t="s">
         <v>262</v>
@@ -6918,12 +6924,12 @@
         <v>1</v>
       </c>
       <c r="F280" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B281" t="s">
         <v>262</v>
@@ -6932,12 +6938,12 @@
         <v>1</v>
       </c>
       <c r="F281" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B282" t="s">
         <v>262</v>
@@ -6946,12 +6952,12 @@
         <v>1</v>
       </c>
       <c r="F282" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B283" t="s">
         <v>262</v>
@@ -6960,12 +6966,12 @@
         <v>1</v>
       </c>
       <c r="F283" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B284" t="s">
         <v>262</v>
@@ -6974,12 +6980,12 @@
         <v>1</v>
       </c>
       <c r="F284" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B285" t="s">
         <v>262</v>
@@ -6988,12 +6994,12 @@
         <v>1</v>
       </c>
       <c r="F285" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B286" t="s">
         <v>262</v>
@@ -7002,12 +7008,12 @@
         <v>1</v>
       </c>
       <c r="F286" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B287" t="s">
         <v>262</v>
@@ -7016,12 +7022,12 @@
         <v>1</v>
       </c>
       <c r="F287" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B288" t="s">
         <v>262</v>
@@ -7030,12 +7036,12 @@
         <v>1</v>
       </c>
       <c r="F288" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B289" t="s">
         <v>262</v>
@@ -7044,12 +7050,12 @@
         <v>1</v>
       </c>
       <c r="F289" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B290" t="s">
         <v>262</v>
@@ -7058,12 +7064,12 @@
         <v>1</v>
       </c>
       <c r="F290" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B291" t="s">
         <v>262</v>
@@ -7072,12 +7078,12 @@
         <v>1</v>
       </c>
       <c r="F291" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B292" t="s">
         <v>262</v>
@@ -7086,12 +7092,12 @@
         <v>1</v>
       </c>
       <c r="F292" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B293" t="s">
         <v>262</v>
@@ -7100,12 +7106,12 @@
         <v>1</v>
       </c>
       <c r="F293" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B294" t="s">
         <v>262</v>
@@ -7114,12 +7120,12 @@
         <v>1</v>
       </c>
       <c r="F294" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B295" t="s">
         <v>262</v>
@@ -7128,12 +7134,12 @@
         <v>1</v>
       </c>
       <c r="F295" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B296" t="s">
         <v>262</v>
@@ -7142,12 +7148,12 @@
         <v>1</v>
       </c>
       <c r="F296" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B297" t="s">
         <v>262</v>
@@ -7156,12 +7162,12 @@
         <v>1</v>
       </c>
       <c r="F297" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B298" t="s">
         <v>262</v>
@@ -7170,12 +7176,12 @@
         <v>1</v>
       </c>
       <c r="F298" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="B299" t="s">
         <v>262</v>
@@ -7184,12 +7190,12 @@
         <v>1</v>
       </c>
       <c r="F299" t="s">
-        <v>278</v>
+        <v>447</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B300" t="s">
         <v>262</v>
@@ -7198,12 +7204,12 @@
         <v>1</v>
       </c>
       <c r="F300" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B301" t="s">
         <v>262</v>
@@ -7212,12 +7218,12 @@
         <v>1</v>
       </c>
       <c r="F301" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B302" t="s">
         <v>262</v>
@@ -7226,12 +7232,12 @@
         <v>1</v>
       </c>
       <c r="F302" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B303" t="s">
         <v>262</v>
@@ -7240,12 +7246,12 @@
         <v>1</v>
       </c>
       <c r="F303" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B304" t="s">
         <v>262</v>
@@ -7254,12 +7260,12 @@
         <v>1</v>
       </c>
       <c r="F304" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B305" t="s">
         <v>262</v>
@@ -7268,29 +7274,43 @@
         <v>1</v>
       </c>
       <c r="F305" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
+        <v>265</v>
+      </c>
+      <c r="B306" t="s">
+        <v>262</v>
+      </c>
+      <c r="C306">
+        <v>1</v>
+      </c>
+      <c r="F306" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
         <v>263</v>
       </c>
-      <c r="B306" t="s">
-        <v>262</v>
-      </c>
-      <c r="C306">
-        <v>1</v>
-      </c>
-      <c r="F306" t="s">
+      <c r="B307" t="s">
+        <v>262</v>
+      </c>
+      <c r="C307">
+        <v>1</v>
+      </c>
+      <c r="F307" t="s">
         <v>264</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F306">
-    <sortCondition descending="1" ref="C2:C306"/>
-    <sortCondition ref="D2:D306"/>
-    <sortCondition ref="E2:E306"/>
-    <sortCondition descending="1" ref="A2:A306"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F307">
+    <sortCondition descending="1" ref="C2:C307"/>
+    <sortCondition ref="D2:D307"/>
+    <sortCondition ref="E2:E307"/>
+    <sortCondition descending="1" ref="A2:A307"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/EOAT_data.xlsx
+++ b/data/EOAT_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\procesos.CAZEL\Desktop\Becario Procesos\EOAT Project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3874C80C-BE0C-4CDD-9B6A-FDE6ADEFAE14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DF654F5-B9E7-4D81-B375-F2575B9333BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{440E3869-3C3F-4E8C-A8BD-ADEB8E2EA552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1037" uniqueCount="617">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1042" uniqueCount="621">
   <si>
     <t>I-1937</t>
   </si>
@@ -1887,6 +1887,18 @@
   </si>
   <si>
     <t>I-1612.jpeg</t>
+  </si>
+  <si>
+    <t>I-1565</t>
+  </si>
+  <si>
+    <t>I-1699</t>
+  </si>
+  <si>
+    <t>I-1565.jpeg</t>
+  </si>
+  <si>
+    <t>I-1699.jpeg</t>
   </si>
 </sst>
 </file>
@@ -2264,7 +2276,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B6791C-A8A7-4753-A504-FAA9E3EE8745}">
-  <dimension ref="A1:F307"/>
+  <dimension ref="A1:F308"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -2797,10 +2809,10 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>92</v>
+        <v>618</v>
       </c>
       <c r="B27" t="s">
-        <v>92</v>
+        <v>262</v>
       </c>
       <c r="C27">
         <v>3</v>
@@ -2811,10 +2823,13 @@
       <c r="E27">
         <v>1</v>
       </c>
+      <c r="F27" t="s">
+        <v>620</v>
+      </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>30</v>
+        <v>617</v>
       </c>
       <c r="B28" t="s">
         <v>262</v>
@@ -2826,15 +2841,15 @@
         <v>29</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>168</v>
+        <v>619</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B29" t="s">
         <v>262</v>
@@ -2849,12 +2864,12 @@
         <v>2</v>
       </c>
       <c r="F29" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B30" t="s">
         <v>262</v>
@@ -2866,15 +2881,15 @@
         <v>29</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F30" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B31" t="s">
         <v>262</v>
@@ -2889,12 +2904,12 @@
         <v>3</v>
       </c>
       <c r="F31" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B32" t="s">
         <v>262</v>
@@ -2903,18 +2918,18 @@
         <v>3</v>
       </c>
       <c r="D32" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F32" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B33" t="s">
         <v>262</v>
@@ -2929,12 +2944,12 @@
         <v>1</v>
       </c>
       <c r="F33" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B34" t="s">
         <v>262</v>
@@ -2946,15 +2961,15 @@
         <v>35</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B35" t="s">
         <v>262</v>
@@ -2969,12 +2984,12 @@
         <v>2</v>
       </c>
       <c r="F35" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B36" t="s">
         <v>262</v>
@@ -2986,15 +3001,15 @@
         <v>35</v>
       </c>
       <c r="E36">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F36" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B37" t="s">
         <v>262</v>
@@ -3009,12 +3024,12 @@
         <v>3</v>
       </c>
       <c r="F37" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" t="s">
         <v>262</v>
@@ -3023,18 +3038,18 @@
         <v>3</v>
       </c>
       <c r="D38" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E38">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F38" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B39" t="s">
         <v>262</v>
@@ -3049,12 +3064,12 @@
         <v>1</v>
       </c>
       <c r="F39" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B40" t="s">
         <v>262</v>
@@ -3066,15 +3081,15 @@
         <v>42</v>
       </c>
       <c r="E40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F40" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B41" t="s">
         <v>262</v>
@@ -3086,15 +3101,15 @@
         <v>42</v>
       </c>
       <c r="E41">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F41" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B42" t="s">
         <v>262</v>
@@ -3109,12 +3124,12 @@
         <v>3</v>
       </c>
       <c r="F42" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B43" t="s">
         <v>262</v>
@@ -3123,18 +3138,18 @@
         <v>3</v>
       </c>
       <c r="D43" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="E43">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F43" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B44" t="s">
         <v>262</v>
@@ -3149,12 +3164,12 @@
         <v>1</v>
       </c>
       <c r="F44" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B45" t="s">
         <v>262</v>
@@ -3166,15 +3181,15 @@
         <v>48</v>
       </c>
       <c r="E45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F45" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B46" t="s">
         <v>262</v>
@@ -3186,15 +3201,15 @@
         <v>48</v>
       </c>
       <c r="E46">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F46" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B47" t="s">
         <v>262</v>
@@ -3209,12 +3224,12 @@
         <v>3</v>
       </c>
       <c r="F47" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B48" t="s">
         <v>262</v>
@@ -3223,18 +3238,18 @@
         <v>3</v>
       </c>
       <c r="D48" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="E48">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F48" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B49" t="s">
         <v>262</v>
@@ -3246,15 +3261,15 @@
         <v>54</v>
       </c>
       <c r="E49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F49" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B50" t="s">
         <v>262</v>
@@ -3266,15 +3281,15 @@
         <v>54</v>
       </c>
       <c r="E50">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F50" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B51" t="s">
         <v>262</v>
@@ -3283,18 +3298,18 @@
         <v>3</v>
       </c>
       <c r="D51" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="E51">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F51" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B52" t="s">
         <v>262</v>
@@ -3306,15 +3321,15 @@
         <v>58</v>
       </c>
       <c r="E52">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F52" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B53" t="s">
         <v>262</v>
@@ -3326,15 +3341,15 @@
         <v>58</v>
       </c>
       <c r="E53">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F53" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B54" t="s">
         <v>262</v>
@@ -3343,18 +3358,18 @@
         <v>3</v>
       </c>
       <c r="D54" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E54">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F54" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B55" t="s">
         <v>262</v>
@@ -3369,12 +3384,12 @@
         <v>1</v>
       </c>
       <c r="F55" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B56" t="s">
         <v>262</v>
@@ -3386,18 +3401,18 @@
         <v>63</v>
       </c>
       <c r="E56">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F56" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B57" t="s">
-        <v>66</v>
+        <v>262</v>
       </c>
       <c r="C57">
         <v>3</v>
@@ -3406,7 +3421,10 @@
         <v>63</v>
       </c>
       <c r="E57">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="F57" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -3420,10 +3438,10 @@
         <v>3</v>
       </c>
       <c r="D58" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E58">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -3440,7 +3458,7 @@
         <v>67</v>
       </c>
       <c r="E59">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -3457,24 +3475,24 @@
         <v>67</v>
       </c>
       <c r="E60">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="B61" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="C61">
         <v>3</v>
       </c>
       <c r="D61" t="s">
-        <v>93</v>
+        <v>67</v>
       </c>
       <c r="E61">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -3491,15 +3509,15 @@
         <v>93</v>
       </c>
       <c r="E62">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>60</v>
+        <v>92</v>
       </c>
       <c r="B63" t="s">
-        <v>262</v>
+        <v>92</v>
       </c>
       <c r="C63">
         <v>3</v>
@@ -3508,15 +3526,12 @@
         <v>93</v>
       </c>
       <c r="E63">
-        <v>3</v>
-      </c>
-      <c r="F63" t="s">
-        <v>193</v>
+        <v>2</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>94</v>
+        <v>60</v>
       </c>
       <c r="B64" t="s">
         <v>262</v>
@@ -3525,18 +3540,18 @@
         <v>3</v>
       </c>
       <c r="D64" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E64">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F64" t="s">
-        <v>218</v>
+        <v>193</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B65" t="s">
         <v>262</v>
@@ -3548,15 +3563,15 @@
         <v>95</v>
       </c>
       <c r="E65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F65" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B66" t="s">
         <v>262</v>
@@ -3571,12 +3586,12 @@
         <v>2</v>
       </c>
       <c r="F66" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B67" t="s">
         <v>262</v>
@@ -3588,15 +3603,15 @@
         <v>95</v>
       </c>
       <c r="E67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F67" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B68" t="s">
         <v>262</v>
@@ -3605,18 +3620,18 @@
         <v>3</v>
       </c>
       <c r="D68" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E68">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F68" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B69" t="s">
         <v>262</v>
@@ -3631,12 +3646,12 @@
         <v>1</v>
       </c>
       <c r="F69" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B70" t="s">
         <v>262</v>
@@ -3648,15 +3663,15 @@
         <v>100</v>
       </c>
       <c r="E70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F70" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B71" t="s">
         <v>262</v>
@@ -3671,12 +3686,12 @@
         <v>2</v>
       </c>
       <c r="F71" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B72" t="s">
         <v>262</v>
@@ -3688,15 +3703,15 @@
         <v>100</v>
       </c>
       <c r="E72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F72" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B73" t="s">
         <v>262</v>
@@ -3705,18 +3720,18 @@
         <v>3</v>
       </c>
       <c r="D73" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E73">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F73" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B74" t="s">
         <v>262</v>
@@ -3731,12 +3746,12 @@
         <v>1</v>
       </c>
       <c r="F74" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B75" t="s">
         <v>262</v>
@@ -3748,15 +3763,15 @@
         <v>106</v>
       </c>
       <c r="E75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F75" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B76" t="s">
         <v>262</v>
@@ -3771,12 +3786,12 @@
         <v>2</v>
       </c>
       <c r="F76" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B77" t="s">
         <v>262</v>
@@ -3788,15 +3803,15 @@
         <v>106</v>
       </c>
       <c r="E77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F77" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B78" t="s">
         <v>262</v>
@@ -3811,32 +3826,32 @@
         <v>3</v>
       </c>
       <c r="F78" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>68</v>
+        <v>111</v>
       </c>
       <c r="B79" t="s">
         <v>262</v>
       </c>
       <c r="C79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D79" t="s">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="E79">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F79" t="s">
-        <v>198</v>
+        <v>232</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B80" t="s">
         <v>262</v>
@@ -3851,12 +3866,12 @@
         <v>1</v>
       </c>
       <c r="F80" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B81" t="s">
         <v>262</v>
@@ -3868,15 +3883,15 @@
         <v>69</v>
       </c>
       <c r="E81">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F81" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B82" t="s">
         <v>262</v>
@@ -3888,15 +3903,15 @@
         <v>69</v>
       </c>
       <c r="E82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F82" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B83" t="s">
         <v>262</v>
@@ -3911,12 +3926,12 @@
         <v>3</v>
       </c>
       <c r="F83" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B84" t="s">
         <v>262</v>
@@ -3925,18 +3940,18 @@
         <v>2</v>
       </c>
       <c r="D84" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E84">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F84" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B85" t="s">
         <v>262</v>
@@ -3948,15 +3963,15 @@
         <v>75</v>
       </c>
       <c r="E85">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F85" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B86" t="s">
         <v>262</v>
@@ -3968,15 +3983,15 @@
         <v>75</v>
       </c>
       <c r="E86">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F86" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B87" t="s">
         <v>262</v>
@@ -3985,18 +4000,18 @@
         <v>2</v>
       </c>
       <c r="D87" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E87">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F87" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B88" t="s">
         <v>262</v>
@@ -4011,12 +4026,12 @@
         <v>1</v>
       </c>
       <c r="F88" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B89" t="s">
         <v>262</v>
@@ -4028,15 +4043,15 @@
         <v>79</v>
       </c>
       <c r="E89">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F89" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B90" t="s">
         <v>262</v>
@@ -4051,12 +4066,12 @@
         <v>2</v>
       </c>
       <c r="F90" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B91" t="s">
         <v>262</v>
@@ -4068,15 +4083,15 @@
         <v>79</v>
       </c>
       <c r="E91">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F91" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B92" t="s">
         <v>262</v>
@@ -4091,12 +4106,12 @@
         <v>3</v>
       </c>
       <c r="F92" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B93" t="s">
         <v>262</v>
@@ -4105,18 +4120,18 @@
         <v>2</v>
       </c>
       <c r="D93" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="E93">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F93" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B94" t="s">
         <v>262</v>
@@ -4131,12 +4146,12 @@
         <v>1</v>
       </c>
       <c r="F94" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B95" t="s">
         <v>262</v>
@@ -4148,15 +4163,15 @@
         <v>86</v>
       </c>
       <c r="E95">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F95" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B96" t="s">
         <v>262</v>
@@ -4171,12 +4186,12 @@
         <v>2</v>
       </c>
       <c r="F96" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B97" t="s">
         <v>262</v>
@@ -4188,15 +4203,15 @@
         <v>86</v>
       </c>
       <c r="E97">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F97" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B98" t="s">
         <v>262</v>
@@ -4211,12 +4226,12 @@
         <v>3</v>
       </c>
       <c r="F98" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B99" t="s">
         <v>262</v>
@@ -4225,18 +4240,18 @@
         <v>2</v>
       </c>
       <c r="D99" t="s">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="E99">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F99" t="s">
-        <v>233</v>
+        <v>217</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B100" t="s">
         <v>262</v>
@@ -4248,15 +4263,15 @@
         <v>113</v>
       </c>
       <c r="E100">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F100" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B101" t="s">
         <v>262</v>
@@ -4268,15 +4283,15 @@
         <v>113</v>
       </c>
       <c r="E101">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F101" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B102" t="s">
         <v>262</v>
@@ -4291,12 +4306,12 @@
         <v>3</v>
       </c>
       <c r="F102" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B103" t="s">
         <v>262</v>
@@ -4305,18 +4320,18 @@
         <v>2</v>
       </c>
       <c r="D103" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="E103">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F103" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B104" t="s">
         <v>262</v>
@@ -4328,15 +4343,15 @@
         <v>118</v>
       </c>
       <c r="E104">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F104" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B105" t="s">
         <v>262</v>
@@ -4351,12 +4366,12 @@
         <v>2</v>
       </c>
       <c r="F105" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B106" t="s">
         <v>262</v>
@@ -4368,15 +4383,15 @@
         <v>118</v>
       </c>
       <c r="E106">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F106" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B107" t="s">
         <v>262</v>
@@ -4391,12 +4406,12 @@
         <v>3</v>
       </c>
       <c r="F107" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B108" t="s">
         <v>262</v>
@@ -4405,18 +4420,18 @@
         <v>2</v>
       </c>
       <c r="D108" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E108">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F108" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B109" t="s">
         <v>262</v>
@@ -4428,15 +4443,15 @@
         <v>124</v>
       </c>
       <c r="E109">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F109" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B110" t="s">
         <v>262</v>
@@ -4448,15 +4463,15 @@
         <v>124</v>
       </c>
       <c r="E110">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F110" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="B111" t="s">
         <v>262</v>
@@ -4471,12 +4486,12 @@
         <v>3</v>
       </c>
       <c r="F111" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B112" t="s">
         <v>262</v>
@@ -4485,18 +4500,18 @@
         <v>2</v>
       </c>
       <c r="D112" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="E112">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F112" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B113" t="s">
         <v>262</v>
@@ -4508,15 +4523,15 @@
         <v>129</v>
       </c>
       <c r="E113">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F113" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B114" t="s">
         <v>262</v>
@@ -4528,15 +4543,15 @@
         <v>129</v>
       </c>
       <c r="E114">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F114" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B115" t="s">
         <v>262</v>
@@ -4551,12 +4566,12 @@
         <v>3</v>
       </c>
       <c r="F115" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B116" t="s">
         <v>262</v>
@@ -4565,18 +4580,18 @@
         <v>2</v>
       </c>
       <c r="D116" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="E116">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F116" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B117" t="s">
         <v>262</v>
@@ -4591,12 +4606,12 @@
         <v>1</v>
       </c>
       <c r="F117" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B118" t="s">
         <v>262</v>
@@ -4608,15 +4623,15 @@
         <v>134</v>
       </c>
       <c r="E118">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F118" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B119" t="s">
         <v>262</v>
@@ -4631,12 +4646,12 @@
         <v>2</v>
       </c>
       <c r="F119" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B120" t="s">
         <v>262</v>
@@ -4648,15 +4663,15 @@
         <v>134</v>
       </c>
       <c r="E120">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F120" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B121" t="s">
         <v>262</v>
@@ -4671,24 +4686,27 @@
         <v>3</v>
       </c>
       <c r="F121" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>92</v>
+        <v>139</v>
       </c>
       <c r="B122" t="s">
-        <v>92</v>
+        <v>262</v>
       </c>
       <c r="C122">
         <v>2</v>
       </c>
       <c r="D122" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="E122">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="F122" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
@@ -4705,7 +4723,7 @@
         <v>140</v>
       </c>
       <c r="E123">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -4722,7 +4740,7 @@
         <v>140</v>
       </c>
       <c r="E124">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -4736,10 +4754,10 @@
         <v>2</v>
       </c>
       <c r="D125" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E125">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -4756,7 +4774,7 @@
         <v>141</v>
       </c>
       <c r="E126">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -4773,7 +4791,7 @@
         <v>141</v>
       </c>
       <c r="E127">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
@@ -4787,10 +4805,10 @@
         <v>2</v>
       </c>
       <c r="D128" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E128">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
@@ -4807,7 +4825,7 @@
         <v>142</v>
       </c>
       <c r="E129">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -4824,26 +4842,29 @@
         <v>142</v>
       </c>
       <c r="E130">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>441</v>
+        <v>92</v>
       </c>
       <c r="B131" t="s">
-        <v>262</v>
+        <v>92</v>
       </c>
       <c r="C131">
-        <v>1</v>
-      </c>
-      <c r="F131" t="s">
-        <v>609</v>
+        <v>2</v>
+      </c>
+      <c r="D131" t="s">
+        <v>142</v>
+      </c>
+      <c r="E131">
+        <v>3</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B132" t="s">
         <v>262</v>
@@ -4852,12 +4873,12 @@
         <v>1</v>
       </c>
       <c r="F132" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="B133" t="s">
         <v>262</v>
@@ -4866,12 +4887,12 @@
         <v>1</v>
       </c>
       <c r="F133" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B134" t="s">
         <v>262</v>
@@ -4880,12 +4901,12 @@
         <v>1</v>
       </c>
       <c r="F134" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="B135" t="s">
         <v>262</v>
@@ -4894,12 +4915,12 @@
         <v>1</v>
       </c>
       <c r="F135" t="s">
-        <v>607</v>
+        <v>612</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B136" t="s">
         <v>262</v>
@@ -4908,12 +4929,12 @@
         <v>1</v>
       </c>
       <c r="F136" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="B137" t="s">
         <v>262</v>
@@ -4922,12 +4943,12 @@
         <v>1</v>
       </c>
       <c r="F137" t="s">
-        <v>610</v>
+        <v>606</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="B138" t="s">
         <v>262</v>
@@ -4936,12 +4957,12 @@
         <v>1</v>
       </c>
       <c r="F138" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="B139" t="s">
         <v>262</v>
@@ -4950,12 +4971,12 @@
         <v>1</v>
       </c>
       <c r="F139" t="s">
-        <v>605</v>
+        <v>613</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B140" t="s">
         <v>262</v>
@@ -4964,12 +4985,12 @@
         <v>1</v>
       </c>
       <c r="F140" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B141" t="s">
         <v>262</v>
@@ -4978,12 +4999,12 @@
         <v>1</v>
       </c>
       <c r="F141" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B142" t="s">
         <v>262</v>
@@ -4992,12 +5013,12 @@
         <v>1</v>
       </c>
       <c r="F142" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B143" t="s">
         <v>262</v>
@@ -5006,12 +5027,12 @@
         <v>1</v>
       </c>
       <c r="F143" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B144" t="s">
         <v>262</v>
@@ -5020,12 +5041,12 @@
         <v>1</v>
       </c>
       <c r="F144" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B145" t="s">
         <v>262</v>
@@ -5034,12 +5055,12 @@
         <v>1</v>
       </c>
       <c r="F145" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B146" t="s">
         <v>262</v>
@@ -5048,12 +5069,12 @@
         <v>1</v>
       </c>
       <c r="F146" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B147" t="s">
         <v>262</v>
@@ -5062,12 +5083,12 @@
         <v>1</v>
       </c>
       <c r="F147" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B148" t="s">
         <v>262</v>
@@ -5076,12 +5097,12 @@
         <v>1</v>
       </c>
       <c r="F148" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B149" t="s">
         <v>262</v>
@@ -5090,12 +5111,12 @@
         <v>1</v>
       </c>
       <c r="F149" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B150" t="s">
         <v>262</v>
@@ -5104,12 +5125,12 @@
         <v>1</v>
       </c>
       <c r="F150" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B151" t="s">
         <v>262</v>
@@ -5118,12 +5139,12 @@
         <v>1</v>
       </c>
       <c r="F151" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B152" t="s">
         <v>262</v>
@@ -5132,12 +5153,12 @@
         <v>1</v>
       </c>
       <c r="F152" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B153" t="s">
         <v>262</v>
@@ -5146,12 +5167,12 @@
         <v>1</v>
       </c>
       <c r="F153" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B154" t="s">
         <v>262</v>
@@ -5160,12 +5181,12 @@
         <v>1</v>
       </c>
       <c r="F154" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B155" t="s">
         <v>262</v>
@@ -5174,12 +5195,12 @@
         <v>1</v>
       </c>
       <c r="F155" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B156" t="s">
         <v>262</v>
@@ -5188,12 +5209,12 @@
         <v>1</v>
       </c>
       <c r="F156" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B157" t="s">
         <v>262</v>
@@ -5202,12 +5223,12 @@
         <v>1</v>
       </c>
       <c r="F157" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B158" t="s">
         <v>262</v>
@@ -5216,12 +5237,12 @@
         <v>1</v>
       </c>
       <c r="F158" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B159" t="s">
         <v>262</v>
@@ -5230,12 +5251,12 @@
         <v>1</v>
       </c>
       <c r="F159" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B160" t="s">
         <v>262</v>
@@ -5244,12 +5265,12 @@
         <v>1</v>
       </c>
       <c r="F160" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B161" t="s">
         <v>262</v>
@@ -5258,12 +5279,12 @@
         <v>1</v>
       </c>
       <c r="F161" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B162" t="s">
         <v>262</v>
@@ -5272,12 +5293,12 @@
         <v>1</v>
       </c>
       <c r="F162" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B163" t="s">
         <v>262</v>
@@ -5286,12 +5307,12 @@
         <v>1</v>
       </c>
       <c r="F163" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B164" t="s">
         <v>262</v>
@@ -5300,12 +5321,12 @@
         <v>1</v>
       </c>
       <c r="F164" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B165" t="s">
         <v>262</v>
@@ -5314,12 +5335,12 @@
         <v>1</v>
       </c>
       <c r="F165" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B166" t="s">
         <v>262</v>
@@ -5328,12 +5349,12 @@
         <v>1</v>
       </c>
       <c r="F166" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B167" t="s">
         <v>262</v>
@@ -5342,12 +5363,12 @@
         <v>1</v>
       </c>
       <c r="F167" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B168" t="s">
         <v>262</v>
@@ -5356,12 +5377,12 @@
         <v>1</v>
       </c>
       <c r="F168" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B169" t="s">
         <v>262</v>
@@ -5370,12 +5391,12 @@
         <v>1</v>
       </c>
       <c r="F169" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B170" t="s">
         <v>262</v>
@@ -5384,12 +5405,12 @@
         <v>1</v>
       </c>
       <c r="F170" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B171" t="s">
         <v>262</v>
@@ -5398,12 +5419,12 @@
         <v>1</v>
       </c>
       <c r="F171" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B172" t="s">
         <v>262</v>
@@ -5412,12 +5433,12 @@
         <v>1</v>
       </c>
       <c r="F172" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B173" t="s">
         <v>262</v>
@@ -5426,12 +5447,12 @@
         <v>1</v>
       </c>
       <c r="F173" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B174" t="s">
         <v>262</v>
@@ -5440,12 +5461,12 @@
         <v>1</v>
       </c>
       <c r="F174" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B175" t="s">
         <v>262</v>
@@ -5454,12 +5475,12 @@
         <v>1</v>
       </c>
       <c r="F175" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B176" t="s">
         <v>262</v>
@@ -5468,12 +5489,12 @@
         <v>1</v>
       </c>
       <c r="F176" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B177" t="s">
         <v>262</v>
@@ -5482,12 +5503,12 @@
         <v>1</v>
       </c>
       <c r="F177" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B178" t="s">
         <v>262</v>
@@ -5496,12 +5517,12 @@
         <v>1</v>
       </c>
       <c r="F178" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B179" t="s">
         <v>262</v>
@@ -5510,12 +5531,12 @@
         <v>1</v>
       </c>
       <c r="F179" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B180" t="s">
         <v>262</v>
@@ -5524,12 +5545,12 @@
         <v>1</v>
       </c>
       <c r="F180" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B181" t="s">
         <v>262</v>
@@ -5538,12 +5559,12 @@
         <v>1</v>
       </c>
       <c r="F181" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B182" t="s">
         <v>262</v>
@@ -5552,12 +5573,12 @@
         <v>1</v>
       </c>
       <c r="F182" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B183" t="s">
         <v>262</v>
@@ -5566,12 +5587,12 @@
         <v>1</v>
       </c>
       <c r="F183" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B184" t="s">
         <v>262</v>
@@ -5580,12 +5601,12 @@
         <v>1</v>
       </c>
       <c r="F184" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B185" t="s">
         <v>262</v>
@@ -5594,12 +5615,12 @@
         <v>1</v>
       </c>
       <c r="F185" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B186" t="s">
         <v>262</v>
@@ -5608,12 +5629,12 @@
         <v>1</v>
       </c>
       <c r="F186" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B187" t="s">
         <v>262</v>
@@ -5622,12 +5643,12 @@
         <v>1</v>
       </c>
       <c r="F187" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B188" t="s">
         <v>262</v>
@@ -5636,12 +5657,12 @@
         <v>1</v>
       </c>
       <c r="F188" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B189" t="s">
         <v>262</v>
@@ -5650,12 +5671,12 @@
         <v>1</v>
       </c>
       <c r="F189" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B190" t="s">
         <v>262</v>
@@ -5664,12 +5685,12 @@
         <v>1</v>
       </c>
       <c r="F190" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B191" t="s">
         <v>262</v>
@@ -5678,12 +5699,12 @@
         <v>1</v>
       </c>
       <c r="F191" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B192" t="s">
         <v>262</v>
@@ -5692,12 +5713,12 @@
         <v>1</v>
       </c>
       <c r="F192" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B193" t="s">
         <v>262</v>
@@ -5706,12 +5727,12 @@
         <v>1</v>
       </c>
       <c r="F193" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B194" t="s">
         <v>262</v>
@@ -5720,12 +5741,12 @@
         <v>1</v>
       </c>
       <c r="F194" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B195" t="s">
         <v>262</v>
@@ -5734,12 +5755,12 @@
         <v>1</v>
       </c>
       <c r="F195" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B196" t="s">
         <v>262</v>
@@ -5748,12 +5769,12 @@
         <v>1</v>
       </c>
       <c r="F196" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B197" t="s">
         <v>262</v>
@@ -5762,12 +5783,12 @@
         <v>1</v>
       </c>
       <c r="F197" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B198" t="s">
         <v>262</v>
@@ -5776,12 +5797,12 @@
         <v>1</v>
       </c>
       <c r="F198" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B199" t="s">
         <v>262</v>
@@ -5790,12 +5811,12 @@
         <v>1</v>
       </c>
       <c r="F199" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B200" t="s">
         <v>262</v>
@@ -5804,12 +5825,12 @@
         <v>1</v>
       </c>
       <c r="F200" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B201" t="s">
         <v>262</v>
@@ -5818,12 +5839,12 @@
         <v>1</v>
       </c>
       <c r="F201" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B202" t="s">
         <v>262</v>
@@ -5832,12 +5853,12 @@
         <v>1</v>
       </c>
       <c r="F202" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B203" t="s">
         <v>262</v>
@@ -5846,12 +5867,12 @@
         <v>1</v>
       </c>
       <c r="F203" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B204" t="s">
         <v>262</v>
@@ -5860,12 +5881,12 @@
         <v>1</v>
       </c>
       <c r="F204" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B205" t="s">
         <v>262</v>
@@ -5874,12 +5895,12 @@
         <v>1</v>
       </c>
       <c r="F205" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B206" t="s">
         <v>262</v>
@@ -5888,12 +5909,12 @@
         <v>1</v>
       </c>
       <c r="F206" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B207" t="s">
         <v>262</v>
@@ -5902,12 +5923,12 @@
         <v>1</v>
       </c>
       <c r="F207" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B208" t="s">
         <v>262</v>
@@ -5916,12 +5937,12 @@
         <v>1</v>
       </c>
       <c r="F208" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B209" t="s">
         <v>262</v>
@@ -5930,12 +5951,12 @@
         <v>1</v>
       </c>
       <c r="F209" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B210" t="s">
         <v>262</v>
@@ -5944,12 +5965,12 @@
         <v>1</v>
       </c>
       <c r="F210" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B211" t="s">
         <v>262</v>
@@ -5958,12 +5979,12 @@
         <v>1</v>
       </c>
       <c r="F211" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B212" t="s">
         <v>262</v>
@@ -5972,12 +5993,12 @@
         <v>1</v>
       </c>
       <c r="F212" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B213" t="s">
         <v>262</v>
@@ -5986,12 +6007,12 @@
         <v>1</v>
       </c>
       <c r="F213" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B214" t="s">
         <v>262</v>
@@ -6000,12 +6021,12 @@
         <v>1</v>
       </c>
       <c r="F214" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B215" t="s">
         <v>262</v>
@@ -6014,12 +6035,12 @@
         <v>1</v>
       </c>
       <c r="F215" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B216" t="s">
         <v>262</v>
@@ -6028,12 +6049,12 @@
         <v>1</v>
       </c>
       <c r="F216" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B217" t="s">
         <v>262</v>
@@ -6042,12 +6063,12 @@
         <v>1</v>
       </c>
       <c r="F217" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B218" t="s">
         <v>262</v>
@@ -6056,12 +6077,12 @@
         <v>1</v>
       </c>
       <c r="F218" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B219" t="s">
         <v>262</v>
@@ -6070,12 +6091,12 @@
         <v>1</v>
       </c>
       <c r="F219" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B220" t="s">
         <v>262</v>
@@ -6084,12 +6105,12 @@
         <v>1</v>
       </c>
       <c r="F220" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B221" t="s">
         <v>262</v>
@@ -6098,12 +6119,12 @@
         <v>1</v>
       </c>
       <c r="F221" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B222" t="s">
         <v>262</v>
@@ -6112,12 +6133,12 @@
         <v>1</v>
       </c>
       <c r="F222" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B223" t="s">
         <v>262</v>
@@ -6126,12 +6147,12 @@
         <v>1</v>
       </c>
       <c r="F223" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B224" t="s">
         <v>262</v>
@@ -6140,12 +6161,12 @@
         <v>1</v>
       </c>
       <c r="F224" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B225" t="s">
         <v>262</v>
@@ -6154,12 +6175,12 @@
         <v>1</v>
       </c>
       <c r="F225" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B226" t="s">
         <v>262</v>
@@ -6168,12 +6189,12 @@
         <v>1</v>
       </c>
       <c r="F226" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B227" t="s">
         <v>262</v>
@@ -6182,12 +6203,12 @@
         <v>1</v>
       </c>
       <c r="F227" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B228" t="s">
         <v>262</v>
@@ -6196,12 +6217,12 @@
         <v>1</v>
       </c>
       <c r="F228" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B229" t="s">
         <v>262</v>
@@ -6210,12 +6231,12 @@
         <v>1</v>
       </c>
       <c r="F229" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B230" t="s">
         <v>262</v>
@@ -6224,12 +6245,12 @@
         <v>1</v>
       </c>
       <c r="F230" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B231" t="s">
         <v>262</v>
@@ -6238,12 +6259,12 @@
         <v>1</v>
       </c>
       <c r="F231" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B232" t="s">
         <v>262</v>
@@ -6252,12 +6273,12 @@
         <v>1</v>
       </c>
       <c r="F232" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B233" t="s">
         <v>262</v>
@@ -6266,12 +6287,12 @@
         <v>1</v>
       </c>
       <c r="F233" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B234" t="s">
         <v>262</v>
@@ -6280,12 +6301,12 @@
         <v>1</v>
       </c>
       <c r="F234" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B235" t="s">
         <v>262</v>
@@ -6294,12 +6315,12 @@
         <v>1</v>
       </c>
       <c r="F235" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B236" t="s">
         <v>262</v>
@@ -6308,12 +6329,12 @@
         <v>1</v>
       </c>
       <c r="F236" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B237" t="s">
         <v>262</v>
@@ -6322,12 +6343,12 @@
         <v>1</v>
       </c>
       <c r="F237" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B238" t="s">
         <v>262</v>
@@ -6336,12 +6357,12 @@
         <v>1</v>
       </c>
       <c r="F238" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B239" t="s">
         <v>262</v>
@@ -6350,12 +6371,12 @@
         <v>1</v>
       </c>
       <c r="F239" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B240" t="s">
         <v>262</v>
@@ -6364,12 +6385,12 @@
         <v>1</v>
       </c>
       <c r="F240" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B241" t="s">
         <v>262</v>
@@ -6378,12 +6399,12 @@
         <v>1</v>
       </c>
       <c r="F241" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B242" t="s">
         <v>262</v>
@@ -6392,12 +6413,12 @@
         <v>1</v>
       </c>
       <c r="F242" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B243" t="s">
         <v>262</v>
@@ -6406,12 +6427,12 @@
         <v>1</v>
       </c>
       <c r="F243" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B244" t="s">
         <v>262</v>
@@ -6420,12 +6441,12 @@
         <v>1</v>
       </c>
       <c r="F244" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B245" t="s">
         <v>262</v>
@@ -6434,12 +6455,12 @@
         <v>1</v>
       </c>
       <c r="F245" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B246" t="s">
         <v>262</v>
@@ -6448,12 +6469,12 @@
         <v>1</v>
       </c>
       <c r="F246" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B247" t="s">
         <v>262</v>
@@ -6462,12 +6483,12 @@
         <v>1</v>
       </c>
       <c r="F247" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B248" t="s">
         <v>262</v>
@@ -6476,12 +6497,12 @@
         <v>1</v>
       </c>
       <c r="F248" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B249" t="s">
         <v>262</v>
@@ -6490,12 +6511,12 @@
         <v>1</v>
       </c>
       <c r="F249" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B250" t="s">
         <v>262</v>
@@ -6504,12 +6525,12 @@
         <v>1</v>
       </c>
       <c r="F250" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B251" t="s">
         <v>262</v>
@@ -6518,12 +6539,12 @@
         <v>1</v>
       </c>
       <c r="F251" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B252" t="s">
         <v>262</v>
@@ -6532,12 +6553,12 @@
         <v>1</v>
       </c>
       <c r="F252" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B253" t="s">
         <v>262</v>
@@ -6546,12 +6567,12 @@
         <v>1</v>
       </c>
       <c r="F253" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B254" t="s">
         <v>262</v>
@@ -6560,12 +6581,12 @@
         <v>1</v>
       </c>
       <c r="F254" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B255" t="s">
         <v>262</v>
@@ -6574,12 +6595,12 @@
         <v>1</v>
       </c>
       <c r="F255" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B256" t="s">
         <v>262</v>
@@ -6588,12 +6609,12 @@
         <v>1</v>
       </c>
       <c r="F256" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B257" t="s">
         <v>262</v>
@@ -6602,12 +6623,12 @@
         <v>1</v>
       </c>
       <c r="F257" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B258" t="s">
         <v>262</v>
@@ -6616,12 +6637,12 @@
         <v>1</v>
       </c>
       <c r="F258" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B259" t="s">
         <v>262</v>
@@ -6630,12 +6651,12 @@
         <v>1</v>
       </c>
       <c r="F259" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B260" t="s">
         <v>262</v>
@@ -6644,12 +6665,12 @@
         <v>1</v>
       </c>
       <c r="F260" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B261" t="s">
         <v>262</v>
@@ -6658,12 +6679,12 @@
         <v>1</v>
       </c>
       <c r="F261" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B262" t="s">
         <v>262</v>
@@ -6672,12 +6693,12 @@
         <v>1</v>
       </c>
       <c r="F262" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B263" t="s">
         <v>262</v>
@@ -6686,12 +6707,12 @@
         <v>1</v>
       </c>
       <c r="F263" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B264" t="s">
         <v>262</v>
@@ -6700,12 +6721,12 @@
         <v>1</v>
       </c>
       <c r="F264" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B265" t="s">
         <v>262</v>
@@ -6714,12 +6735,12 @@
         <v>1</v>
       </c>
       <c r="F265" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B266" t="s">
         <v>262</v>
@@ -6728,12 +6749,12 @@
         <v>1</v>
       </c>
       <c r="F266" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B267" t="s">
         <v>262</v>
@@ -6742,12 +6763,12 @@
         <v>1</v>
       </c>
       <c r="F267" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B268" t="s">
         <v>262</v>
@@ -6756,12 +6777,12 @@
         <v>1</v>
       </c>
       <c r="F268" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B269" t="s">
         <v>262</v>
@@ -6770,12 +6791,12 @@
         <v>1</v>
       </c>
       <c r="F269" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>446</v>
+        <v>307</v>
       </c>
       <c r="B270" t="s">
         <v>262</v>
@@ -6784,12 +6805,12 @@
         <v>1</v>
       </c>
       <c r="F270" t="s">
-        <v>614</v>
+        <v>475</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>615</v>
+        <v>446</v>
       </c>
       <c r="B271" t="s">
         <v>262</v>
@@ -6798,12 +6819,12 @@
         <v>1</v>
       </c>
       <c r="F271" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>306</v>
+        <v>615</v>
       </c>
       <c r="B272" t="s">
         <v>262</v>
@@ -6812,12 +6833,12 @@
         <v>1</v>
       </c>
       <c r="F272" t="s">
-        <v>474</v>
+        <v>616</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B273" t="s">
         <v>262</v>
@@ -6826,12 +6847,12 @@
         <v>1</v>
       </c>
       <c r="F273" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B274" t="s">
         <v>262</v>
@@ -6840,12 +6861,12 @@
         <v>1</v>
       </c>
       <c r="F274" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B275" t="s">
         <v>262</v>
@@ -6854,12 +6875,12 @@
         <v>1</v>
       </c>
       <c r="F275" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B276" t="s">
         <v>262</v>
@@ -6868,12 +6889,12 @@
         <v>1</v>
       </c>
       <c r="F276" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B277" t="s">
         <v>262</v>
@@ -6882,12 +6903,12 @@
         <v>1</v>
       </c>
       <c r="F277" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B278" t="s">
         <v>262</v>
@@ -6896,12 +6917,12 @@
         <v>1</v>
       </c>
       <c r="F278" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B279" t="s">
         <v>262</v>
@@ -6910,12 +6931,12 @@
         <v>1</v>
       </c>
       <c r="F279" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B280" t="s">
         <v>262</v>
@@ -6924,12 +6945,12 @@
         <v>1</v>
       </c>
       <c r="F280" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B281" t="s">
         <v>262</v>
@@ -6938,12 +6959,12 @@
         <v>1</v>
       </c>
       <c r="F281" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B282" t="s">
         <v>262</v>
@@ -6952,12 +6973,12 @@
         <v>1</v>
       </c>
       <c r="F282" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B283" t="s">
         <v>262</v>
@@ -6966,12 +6987,12 @@
         <v>1</v>
       </c>
       <c r="F283" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B284" t="s">
         <v>262</v>
@@ -6980,12 +7001,12 @@
         <v>1</v>
       </c>
       <c r="F284" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B285" t="s">
         <v>262</v>
@@ -6994,12 +7015,12 @@
         <v>1</v>
       </c>
       <c r="F285" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B286" t="s">
         <v>262</v>
@@ -7008,12 +7029,12 @@
         <v>1</v>
       </c>
       <c r="F286" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B287" t="s">
         <v>262</v>
@@ -7022,12 +7043,12 @@
         <v>1</v>
       </c>
       <c r="F287" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B288" t="s">
         <v>262</v>
@@ -7036,12 +7057,12 @@
         <v>1</v>
       </c>
       <c r="F288" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B289" t="s">
         <v>262</v>
@@ -7050,12 +7071,12 @@
         <v>1</v>
       </c>
       <c r="F289" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B290" t="s">
         <v>262</v>
@@ -7064,12 +7085,12 @@
         <v>1</v>
       </c>
       <c r="F290" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B291" t="s">
         <v>262</v>
@@ -7078,12 +7099,12 @@
         <v>1</v>
       </c>
       <c r="F291" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B292" t="s">
         <v>262</v>
@@ -7092,12 +7113,12 @@
         <v>1</v>
       </c>
       <c r="F292" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B293" t="s">
         <v>262</v>
@@ -7106,12 +7127,12 @@
         <v>1</v>
       </c>
       <c r="F293" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B294" t="s">
         <v>262</v>
@@ -7120,12 +7141,12 @@
         <v>1</v>
       </c>
       <c r="F294" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B295" t="s">
         <v>262</v>
@@ -7134,12 +7155,12 @@
         <v>1</v>
       </c>
       <c r="F295" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B296" t="s">
         <v>262</v>
@@ -7148,12 +7169,12 @@
         <v>1</v>
       </c>
       <c r="F296" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B297" t="s">
         <v>262</v>
@@ -7162,12 +7183,12 @@
         <v>1</v>
       </c>
       <c r="F297" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B298" t="s">
         <v>262</v>
@@ -7176,12 +7197,12 @@
         <v>1</v>
       </c>
       <c r="F298" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B299" t="s">
         <v>262</v>
@@ -7190,12 +7211,12 @@
         <v>1</v>
       </c>
       <c r="F299" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="B300" t="s">
         <v>262</v>
@@ -7204,12 +7225,12 @@
         <v>1</v>
       </c>
       <c r="F300" t="s">
-        <v>278</v>
+        <v>447</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B301" t="s">
         <v>262</v>
@@ -7218,12 +7239,12 @@
         <v>1</v>
       </c>
       <c r="F301" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B302" t="s">
         <v>262</v>
@@ -7232,12 +7253,12 @@
         <v>1</v>
       </c>
       <c r="F302" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B303" t="s">
         <v>262</v>
@@ -7246,12 +7267,12 @@
         <v>1</v>
       </c>
       <c r="F303" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B304" t="s">
         <v>262</v>
@@ -7260,12 +7281,12 @@
         <v>1</v>
       </c>
       <c r="F304" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B305" t="s">
         <v>262</v>
@@ -7274,12 +7295,12 @@
         <v>1</v>
       </c>
       <c r="F305" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B306" t="s">
         <v>262</v>
@@ -7288,29 +7309,43 @@
         <v>1</v>
       </c>
       <c r="F306" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
+        <v>265</v>
+      </c>
+      <c r="B307" t="s">
+        <v>262</v>
+      </c>
+      <c r="C307">
+        <v>1</v>
+      </c>
+      <c r="F307" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
         <v>263</v>
       </c>
-      <c r="B307" t="s">
-        <v>262</v>
-      </c>
-      <c r="C307">
-        <v>1</v>
-      </c>
-      <c r="F307" t="s">
+      <c r="B308" t="s">
+        <v>262</v>
+      </c>
+      <c r="C308">
+        <v>1</v>
+      </c>
+      <c r="F308" t="s">
         <v>264</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F307">
-    <sortCondition descending="1" ref="C2:C307"/>
-    <sortCondition ref="D2:D307"/>
-    <sortCondition ref="E2:E307"/>
-    <sortCondition descending="1" ref="A2:A307"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F308">
+    <sortCondition descending="1" ref="C2:C308"/>
+    <sortCondition ref="D2:D308"/>
+    <sortCondition ref="E2:E308"/>
+    <sortCondition descending="1" ref="A2:A308"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/EOAT_data.xlsx
+++ b/data/EOAT_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\procesos.CAZEL\Desktop\Becario Procesos\EOAT Project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DF654F5-B9E7-4D81-B375-F2575B9333BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8461260A-E646-4DCA-BC8E-BCD9A213AF62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{440E3869-3C3F-4E8C-A8BD-ADEB8E2EA552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1042" uniqueCount="621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1256" uniqueCount="636">
   <si>
     <t>I-1937</t>
   </si>
@@ -899,9 +899,6 @@
     <t>I-1545</t>
   </si>
   <si>
-    <t>I-1556</t>
-  </si>
-  <si>
     <t>I-1557</t>
   </si>
   <si>
@@ -1403,9 +1400,6 @@
     <t>I-1545.jpeg</t>
   </si>
   <si>
-    <t>I-1556.jpeg</t>
-  </si>
-  <si>
     <t>I-1557.jpeg</t>
   </si>
   <si>
@@ -1899,6 +1893,57 @@
   </si>
   <si>
     <t>I-1699.jpeg</t>
+  </si>
+  <si>
+    <t>I-1898</t>
+  </si>
+  <si>
+    <t>I-1866</t>
+  </si>
+  <si>
+    <t>I-1515</t>
+  </si>
+  <si>
+    <t>I-1582</t>
+  </si>
+  <si>
+    <t>I-1583</t>
+  </si>
+  <si>
+    <t>I-1585</t>
+  </si>
+  <si>
+    <t>I-1463</t>
+  </si>
+  <si>
+    <t>I-1628</t>
+  </si>
+  <si>
+    <t>I-1898.jpeg</t>
+  </si>
+  <si>
+    <t>I-1866.jpeg</t>
+  </si>
+  <si>
+    <t>I-1515.jpeg</t>
+  </si>
+  <si>
+    <t>I-1582.jpeg</t>
+  </si>
+  <si>
+    <t>I-1583.jpeg</t>
+  </si>
+  <si>
+    <t>I-1585.jpeg</t>
+  </si>
+  <si>
+    <t>I-1463.jpeg</t>
+  </si>
+  <si>
+    <t>I-1628.jpeg</t>
+  </si>
+  <si>
+    <t>3 y 4</t>
   </si>
 </sst>
 </file>
@@ -2276,14 +2321,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B6791C-A8A7-4753-A504-FAA9E3EE8745}">
-  <dimension ref="A1:F308"/>
+  <dimension ref="A1:F317"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2809,7 +2854,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="B27" t="s">
         <v>262</v>
@@ -2824,12 +2869,12 @@
         <v>1</v>
       </c>
       <c r="F27" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B28" t="s">
         <v>262</v>
@@ -2844,7 +2889,7 @@
         <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -4864,7 +4909,7 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="B132" t="s">
         <v>262</v>
@@ -4872,13 +4917,19 @@
       <c r="C132">
         <v>1</v>
       </c>
+      <c r="D132" t="s">
+        <v>1</v>
+      </c>
+      <c r="E132">
+        <v>1</v>
+      </c>
       <c r="F132" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="B133" t="s">
         <v>262</v>
@@ -4886,13 +4937,19 @@
       <c r="C133">
         <v>1</v>
       </c>
+      <c r="D133" t="s">
+        <v>1</v>
+      </c>
+      <c r="E133">
+        <v>1</v>
+      </c>
       <c r="F133" t="s">
-        <v>608</v>
+        <v>601</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
       <c r="B134" t="s">
         <v>262</v>
@@ -4900,13 +4957,19 @@
       <c r="C134">
         <v>1</v>
       </c>
+      <c r="D134" t="s">
+        <v>1</v>
+      </c>
+      <c r="E134">
+        <v>2</v>
+      </c>
       <c r="F134" t="s">
-        <v>611</v>
+        <v>604</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="B135" t="s">
         <v>262</v>
@@ -4914,13 +4977,19 @@
       <c r="C135">
         <v>1</v>
       </c>
+      <c r="D135" t="s">
+        <v>1</v>
+      </c>
+      <c r="E135">
+        <v>2</v>
+      </c>
       <c r="F135" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="B136" t="s">
         <v>262</v>
@@ -4928,13 +4997,19 @@
       <c r="C136">
         <v>1</v>
       </c>
+      <c r="D136" t="s">
+        <v>1</v>
+      </c>
+      <c r="E136">
+        <v>2</v>
+      </c>
       <c r="F136" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="B137" t="s">
         <v>262</v>
@@ -4942,13 +5017,19 @@
       <c r="C137">
         <v>1</v>
       </c>
+      <c r="D137" t="s">
+        <v>1</v>
+      </c>
+      <c r="E137">
+        <v>3</v>
+      </c>
       <c r="F137" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="B138" t="s">
         <v>262</v>
@@ -4956,13 +5037,19 @@
       <c r="C138">
         <v>1</v>
       </c>
+      <c r="D138" t="s">
+        <v>1</v>
+      </c>
+      <c r="E138">
+        <v>3</v>
+      </c>
       <c r="F138" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="B139" t="s">
         <v>262</v>
@@ -4970,13 +5057,19 @@
       <c r="C139">
         <v>1</v>
       </c>
+      <c r="D139" t="s">
+        <v>1</v>
+      </c>
+      <c r="E139">
+        <v>4</v>
+      </c>
       <c r="F139" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B140" t="s">
         <v>262</v>
@@ -4984,13 +5077,19 @@
       <c r="C140">
         <v>1</v>
       </c>
+      <c r="D140" t="s">
+        <v>1</v>
+      </c>
+      <c r="E140">
+        <v>4</v>
+      </c>
       <c r="F140" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="B141" t="s">
         <v>262</v>
@@ -4998,13 +5097,19 @@
       <c r="C141">
         <v>1</v>
       </c>
+      <c r="D141" t="s">
+        <v>1</v>
+      </c>
+      <c r="E141">
+        <v>4</v>
+      </c>
       <c r="F141" t="s">
-        <v>604</v>
+        <v>609</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>435</v>
+        <v>619</v>
       </c>
       <c r="B142" t="s">
         <v>262</v>
@@ -5012,13 +5117,19 @@
       <c r="C142">
         <v>1</v>
       </c>
+      <c r="D142" t="s">
+        <v>1</v>
+      </c>
+      <c r="E142">
+        <v>4</v>
+      </c>
       <c r="F142" t="s">
-        <v>603</v>
+        <v>627</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>434</v>
+        <v>427</v>
       </c>
       <c r="B143" t="s">
         <v>262</v>
@@ -5026,13 +5137,19 @@
       <c r="C143">
         <v>1</v>
       </c>
+      <c r="D143" t="s">
+        <v>8</v>
+      </c>
+      <c r="E143">
+        <v>1</v>
+      </c>
       <c r="F143" t="s">
-        <v>602</v>
+        <v>594</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="B144" t="s">
         <v>262</v>
@@ -5040,13 +5157,19 @@
       <c r="C144">
         <v>1</v>
       </c>
+      <c r="D144" t="s">
+        <v>8</v>
+      </c>
+      <c r="E144">
+        <v>1</v>
+      </c>
       <c r="F144" t="s">
-        <v>601</v>
+        <v>593</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>432</v>
+        <v>425</v>
       </c>
       <c r="B145" t="s">
         <v>262</v>
@@ -5054,13 +5177,19 @@
       <c r="C145">
         <v>1</v>
       </c>
+      <c r="D145" t="s">
+        <v>8</v>
+      </c>
+      <c r="E145">
+        <v>1</v>
+      </c>
       <c r="F145" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="B146" t="s">
         <v>262</v>
@@ -5068,13 +5197,19 @@
       <c r="C146">
         <v>1</v>
       </c>
+      <c r="D146" t="s">
+        <v>8</v>
+      </c>
+      <c r="E146">
+        <v>2</v>
+      </c>
       <c r="F146" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B147" t="s">
         <v>262</v>
@@ -5082,13 +5217,19 @@
       <c r="C147">
         <v>1</v>
       </c>
+      <c r="D147" t="s">
+        <v>8</v>
+      </c>
+      <c r="E147">
+        <v>2</v>
+      </c>
       <c r="F147" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B148" t="s">
         <v>262</v>
@@ -5096,13 +5237,19 @@
       <c r="C148">
         <v>1</v>
       </c>
+      <c r="D148" t="s">
+        <v>8</v>
+      </c>
+      <c r="E148">
+        <v>3</v>
+      </c>
       <c r="F148" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B149" t="s">
         <v>262</v>
@@ -5110,13 +5257,19 @@
       <c r="C149">
         <v>1</v>
       </c>
+      <c r="D149" t="s">
+        <v>8</v>
+      </c>
+      <c r="E149">
+        <v>3</v>
+      </c>
       <c r="F149" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="B150" t="s">
         <v>262</v>
@@ -5124,13 +5277,19 @@
       <c r="C150">
         <v>1</v>
       </c>
+      <c r="D150" t="s">
+        <v>8</v>
+      </c>
+      <c r="E150">
+        <v>4</v>
+      </c>
       <c r="F150" t="s">
-        <v>595</v>
+        <v>602</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>426</v>
+        <v>433</v>
       </c>
       <c r="B151" t="s">
         <v>262</v>
@@ -5138,13 +5297,19 @@
       <c r="C151">
         <v>1</v>
       </c>
+      <c r="D151" t="s">
+        <v>8</v>
+      </c>
+      <c r="E151">
+        <v>4</v>
+      </c>
       <c r="F151" t="s">
-        <v>594</v>
+        <v>600</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="B152" t="s">
         <v>262</v>
@@ -5152,13 +5317,19 @@
       <c r="C152">
         <v>1</v>
       </c>
+      <c r="D152" t="s">
+        <v>8</v>
+      </c>
+      <c r="E152">
+        <v>4</v>
+      </c>
       <c r="F152" t="s">
-        <v>593</v>
+        <v>599</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="B153" t="s">
         <v>262</v>
@@ -5166,13 +5337,19 @@
       <c r="C153">
         <v>1</v>
       </c>
+      <c r="D153" t="s">
+        <v>15</v>
+      </c>
+      <c r="E153">
+        <v>1</v>
+      </c>
       <c r="F153" t="s">
-        <v>592</v>
+        <v>582</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="B154" t="s">
         <v>262</v>
@@ -5180,13 +5357,19 @@
       <c r="C154">
         <v>1</v>
       </c>
+      <c r="D154" t="s">
+        <v>15</v>
+      </c>
+      <c r="E154">
+        <v>2</v>
+      </c>
       <c r="F154" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="B155" t="s">
         <v>262</v>
@@ -5194,13 +5377,19 @@
       <c r="C155">
         <v>1</v>
       </c>
+      <c r="D155" t="s">
+        <v>15</v>
+      </c>
+      <c r="E155">
+        <v>2</v>
+      </c>
       <c r="F155" t="s">
-        <v>590</v>
+        <v>583</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>421</v>
+        <v>620</v>
       </c>
       <c r="B156" t="s">
         <v>262</v>
@@ -5208,8 +5397,14 @@
       <c r="C156">
         <v>1</v>
       </c>
+      <c r="D156" t="s">
+        <v>15</v>
+      </c>
+      <c r="E156">
+        <v>2</v>
+      </c>
       <c r="F156" t="s">
-        <v>589</v>
+        <v>628</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -5222,8 +5417,14 @@
       <c r="C157">
         <v>1</v>
       </c>
+      <c r="D157" t="s">
+        <v>15</v>
+      </c>
+      <c r="E157">
+        <v>3</v>
+      </c>
       <c r="F157" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
@@ -5236,8 +5437,14 @@
       <c r="C158">
         <v>1</v>
       </c>
+      <c r="D158" t="s">
+        <v>15</v>
+      </c>
+      <c r="E158">
+        <v>3</v>
+      </c>
       <c r="F158" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -5250,13 +5457,19 @@
       <c r="C159">
         <v>1</v>
       </c>
+      <c r="D159" t="s">
+        <v>15</v>
+      </c>
+      <c r="E159">
+        <v>3</v>
+      </c>
       <c r="F159" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="B160" t="s">
         <v>262</v>
@@ -5264,13 +5477,19 @@
       <c r="C160">
         <v>1</v>
       </c>
+      <c r="D160" t="s">
+        <v>15</v>
+      </c>
+      <c r="E160">
+        <v>4</v>
+      </c>
       <c r="F160" t="s">
-        <v>585</v>
+        <v>591</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="B161" t="s">
         <v>262</v>
@@ -5278,13 +5497,19 @@
       <c r="C161">
         <v>1</v>
       </c>
+      <c r="D161" t="s">
+        <v>15</v>
+      </c>
+      <c r="E161">
+        <v>4</v>
+      </c>
       <c r="F161" t="s">
-        <v>584</v>
+        <v>590</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="B162" t="s">
         <v>262</v>
@@ -5292,13 +5517,19 @@
       <c r="C162">
         <v>1</v>
       </c>
+      <c r="D162" t="s">
+        <v>15</v>
+      </c>
+      <c r="E162">
+        <v>4</v>
+      </c>
       <c r="F162" t="s">
-        <v>583</v>
+        <v>589</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="B163" t="s">
         <v>262</v>
@@ -5306,13 +5537,19 @@
       <c r="C163">
         <v>1</v>
       </c>
+      <c r="D163" t="s">
+        <v>15</v>
+      </c>
+      <c r="E163">
+        <v>4</v>
+      </c>
       <c r="F163" t="s">
-        <v>582</v>
+        <v>588</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="B164" t="s">
         <v>262</v>
@@ -5320,13 +5557,19 @@
       <c r="C164">
         <v>1</v>
       </c>
+      <c r="D164" t="s">
+        <v>23</v>
+      </c>
+      <c r="E164">
+        <v>1</v>
+      </c>
       <c r="F164" t="s">
-        <v>581</v>
+        <v>572</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="B165" t="s">
         <v>262</v>
@@ -5334,13 +5577,19 @@
       <c r="C165">
         <v>1</v>
       </c>
+      <c r="D165" t="s">
+        <v>23</v>
+      </c>
+      <c r="E165">
+        <v>1</v>
+      </c>
       <c r="F165" t="s">
-        <v>580</v>
+        <v>571</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="B166" t="s">
         <v>262</v>
@@ -5348,13 +5597,19 @@
       <c r="C166">
         <v>1</v>
       </c>
+      <c r="D166" t="s">
+        <v>23</v>
+      </c>
+      <c r="E166">
+        <v>1</v>
+      </c>
       <c r="F166" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="B167" t="s">
         <v>262</v>
@@ -5362,13 +5617,19 @@
       <c r="C167">
         <v>1</v>
       </c>
+      <c r="D167" t="s">
+        <v>23</v>
+      </c>
+      <c r="E167">
+        <v>1</v>
+      </c>
       <c r="F167" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B168" t="s">
         <v>262</v>
@@ -5376,13 +5637,19 @@
       <c r="C168">
         <v>1</v>
       </c>
+      <c r="D168" t="s">
+        <v>23</v>
+      </c>
+      <c r="E168">
+        <v>2</v>
+      </c>
       <c r="F168" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B169" t="s">
         <v>262</v>
@@ -5390,13 +5657,19 @@
       <c r="C169">
         <v>1</v>
       </c>
+      <c r="D169" t="s">
+        <v>23</v>
+      </c>
+      <c r="E169">
+        <v>2</v>
+      </c>
       <c r="F169" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B170" t="s">
         <v>262</v>
@@ -5404,13 +5677,19 @@
       <c r="C170">
         <v>1</v>
       </c>
+      <c r="D170" t="s">
+        <v>23</v>
+      </c>
+      <c r="E170">
+        <v>3</v>
+      </c>
       <c r="F170" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B171" t="s">
         <v>262</v>
@@ -5418,19 +5697,31 @@
       <c r="C171">
         <v>1</v>
       </c>
+      <c r="D171" t="s">
+        <v>23</v>
+      </c>
+      <c r="E171">
+        <v>3</v>
+      </c>
       <c r="F171" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B172" t="s">
         <v>262</v>
       </c>
       <c r="C172">
         <v>1</v>
+      </c>
+      <c r="D172" t="s">
+        <v>23</v>
+      </c>
+      <c r="E172">
+        <v>3</v>
       </c>
       <c r="F172" t="s">
         <v>573</v>
@@ -5438,7 +5729,7 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="B173" t="s">
         <v>262</v>
@@ -5446,13 +5737,19 @@
       <c r="C173">
         <v>1</v>
       </c>
+      <c r="D173" t="s">
+        <v>23</v>
+      </c>
+      <c r="E173">
+        <v>4</v>
+      </c>
       <c r="F173" t="s">
-        <v>572</v>
+        <v>581</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="B174" t="s">
         <v>262</v>
@@ -5460,13 +5757,19 @@
       <c r="C174">
         <v>1</v>
       </c>
+      <c r="D174" t="s">
+        <v>23</v>
+      </c>
+      <c r="E174">
+        <v>4</v>
+      </c>
       <c r="F174" t="s">
-        <v>571</v>
+        <v>580</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="B175" t="s">
         <v>262</v>
@@ -5474,13 +5777,19 @@
       <c r="C175">
         <v>1</v>
       </c>
+      <c r="D175" t="s">
+        <v>23</v>
+      </c>
+      <c r="E175">
+        <v>4</v>
+      </c>
       <c r="F175" t="s">
-        <v>570</v>
+        <v>579</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="B176" t="s">
         <v>262</v>
@@ -5488,13 +5797,19 @@
       <c r="C176">
         <v>1</v>
       </c>
+      <c r="D176" t="s">
+        <v>23</v>
+      </c>
+      <c r="E176">
+        <v>4</v>
+      </c>
       <c r="F176" t="s">
-        <v>569</v>
+        <v>578</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="B177" t="s">
         <v>262</v>
@@ -5502,13 +5817,19 @@
       <c r="C177">
         <v>1</v>
       </c>
+      <c r="D177" t="s">
+        <v>29</v>
+      </c>
+      <c r="E177">
+        <v>1</v>
+      </c>
       <c r="F177" t="s">
-        <v>568</v>
+        <v>558</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="B178" t="s">
         <v>262</v>
@@ -5516,13 +5837,19 @@
       <c r="C178">
         <v>1</v>
       </c>
+      <c r="D178" t="s">
+        <v>29</v>
+      </c>
+      <c r="E178">
+        <v>1</v>
+      </c>
       <c r="F178" t="s">
-        <v>567</v>
+        <v>557</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B179" t="s">
         <v>262</v>
@@ -5530,13 +5857,19 @@
       <c r="C179">
         <v>1</v>
       </c>
+      <c r="D179" t="s">
+        <v>29</v>
+      </c>
+      <c r="E179">
+        <v>2</v>
+      </c>
       <c r="F179" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="B180" t="s">
         <v>262</v>
@@ -5544,13 +5877,19 @@
       <c r="C180">
         <v>1</v>
       </c>
+      <c r="D180" t="s">
+        <v>29</v>
+      </c>
+      <c r="E180">
+        <v>2</v>
+      </c>
       <c r="F180" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="B181" t="s">
         <v>262</v>
@@ -5558,13 +5897,19 @@
       <c r="C181">
         <v>1</v>
       </c>
+      <c r="D181" t="s">
+        <v>29</v>
+      </c>
+      <c r="E181">
+        <v>2</v>
+      </c>
       <c r="F181" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B182" t="s">
         <v>262</v>
@@ -5572,13 +5917,19 @@
       <c r="C182">
         <v>1</v>
       </c>
+      <c r="D182" t="s">
+        <v>29</v>
+      </c>
+      <c r="E182">
+        <v>3</v>
+      </c>
       <c r="F182" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B183" t="s">
         <v>262</v>
@@ -5586,13 +5937,19 @@
       <c r="C183">
         <v>1</v>
       </c>
+      <c r="D183" t="s">
+        <v>29</v>
+      </c>
+      <c r="E183">
+        <v>3</v>
+      </c>
       <c r="F183" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B184" t="s">
         <v>262</v>
@@ -5600,13 +5957,19 @@
       <c r="C184">
         <v>1</v>
       </c>
+      <c r="D184" t="s">
+        <v>29</v>
+      </c>
+      <c r="E184">
+        <v>3</v>
+      </c>
       <c r="F184" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B185" t="s">
         <v>262</v>
@@ -5614,13 +5977,19 @@
       <c r="C185">
         <v>1</v>
       </c>
+      <c r="D185" t="s">
+        <v>29</v>
+      </c>
+      <c r="E185">
+        <v>3</v>
+      </c>
       <c r="F185" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="B186" t="s">
         <v>262</v>
@@ -5628,13 +5997,19 @@
       <c r="C186">
         <v>1</v>
       </c>
+      <c r="D186" t="s">
+        <v>29</v>
+      </c>
+      <c r="E186">
+        <v>4</v>
+      </c>
       <c r="F186" t="s">
-        <v>559</v>
+        <v>568</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="B187" t="s">
         <v>262</v>
@@ -5642,13 +6017,19 @@
       <c r="C187">
         <v>1</v>
       </c>
+      <c r="D187" t="s">
+        <v>29</v>
+      </c>
+      <c r="E187">
+        <v>4</v>
+      </c>
       <c r="F187" t="s">
-        <v>558</v>
+        <v>567</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="B188" t="s">
         <v>262</v>
@@ -5656,13 +6037,19 @@
       <c r="C188">
         <v>1</v>
       </c>
+      <c r="D188" t="s">
+        <v>29</v>
+      </c>
+      <c r="E188">
+        <v>4</v>
+      </c>
       <c r="F188" t="s">
-        <v>557</v>
+        <v>566</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="B189" t="s">
         <v>262</v>
@@ -5670,13 +6057,19 @@
       <c r="C189">
         <v>1</v>
       </c>
+      <c r="D189" t="s">
+        <v>35</v>
+      </c>
+      <c r="E189">
+        <v>1</v>
+      </c>
       <c r="F189" t="s">
-        <v>556</v>
+        <v>549</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="B190" t="s">
         <v>262</v>
@@ -5684,13 +6077,19 @@
       <c r="C190">
         <v>1</v>
       </c>
+      <c r="D190" t="s">
+        <v>35</v>
+      </c>
+      <c r="E190">
+        <v>1</v>
+      </c>
       <c r="F190" t="s">
-        <v>555</v>
+        <v>548</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="B191" t="s">
         <v>262</v>
@@ -5698,13 +6097,19 @@
       <c r="C191">
         <v>1</v>
       </c>
+      <c r="D191" t="s">
+        <v>35</v>
+      </c>
+      <c r="E191">
+        <v>1</v>
+      </c>
       <c r="F191" t="s">
-        <v>554</v>
+        <v>547</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B192" t="s">
         <v>262</v>
@@ -5712,13 +6117,19 @@
       <c r="C192">
         <v>1</v>
       </c>
+      <c r="D192" t="s">
+        <v>35</v>
+      </c>
+      <c r="E192">
+        <v>2</v>
+      </c>
       <c r="F192" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B193" t="s">
         <v>262</v>
@@ -5726,13 +6137,19 @@
       <c r="C193">
         <v>1</v>
       </c>
+      <c r="D193" t="s">
+        <v>35</v>
+      </c>
+      <c r="E193">
+        <v>2</v>
+      </c>
       <c r="F193" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B194" t="s">
         <v>262</v>
@@ -5740,13 +6157,19 @@
       <c r="C194">
         <v>1</v>
       </c>
+      <c r="D194" t="s">
+        <v>35</v>
+      </c>
+      <c r="E194">
+        <v>3</v>
+      </c>
       <c r="F194" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B195" t="s">
         <v>262</v>
@@ -5754,13 +6177,19 @@
       <c r="C195">
         <v>1</v>
       </c>
+      <c r="D195" t="s">
+        <v>35</v>
+      </c>
+      <c r="E195">
+        <v>3</v>
+      </c>
       <c r="F195" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="B196" t="s">
         <v>262</v>
@@ -5768,13 +6197,19 @@
       <c r="C196">
         <v>1</v>
       </c>
+      <c r="D196" t="s">
+        <v>35</v>
+      </c>
+      <c r="E196">
+        <v>4</v>
+      </c>
       <c r="F196" t="s">
-        <v>549</v>
+        <v>556</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="B197" t="s">
         <v>262</v>
@@ -5782,13 +6217,19 @@
       <c r="C197">
         <v>1</v>
       </c>
+      <c r="D197" t="s">
+        <v>35</v>
+      </c>
+      <c r="E197">
+        <v>4</v>
+      </c>
       <c r="F197" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="B198" t="s">
         <v>262</v>
@@ -5796,13 +6237,19 @@
       <c r="C198">
         <v>1</v>
       </c>
+      <c r="D198" t="s">
+        <v>35</v>
+      </c>
+      <c r="E198">
+        <v>4</v>
+      </c>
       <c r="F198" t="s">
-        <v>547</v>
+        <v>554</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="B199" t="s">
         <v>262</v>
@@ -5810,13 +6257,19 @@
       <c r="C199">
         <v>1</v>
       </c>
+      <c r="D199" t="s">
+        <v>42</v>
+      </c>
+      <c r="E199">
+        <v>1</v>
+      </c>
       <c r="F199" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="B200" t="s">
         <v>262</v>
@@ -5824,13 +6277,19 @@
       <c r="C200">
         <v>1</v>
       </c>
+      <c r="D200" t="s">
+        <v>42</v>
+      </c>
+      <c r="E200">
+        <v>1</v>
+      </c>
       <c r="F200" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="B201" t="s">
         <v>262</v>
@@ -5838,19 +6297,31 @@
       <c r="C201">
         <v>1</v>
       </c>
+      <c r="D201" t="s">
+        <v>42</v>
+      </c>
+      <c r="E201">
+        <v>1</v>
+      </c>
       <c r="F201" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B202" t="s">
         <v>262</v>
       </c>
       <c r="C202">
         <v>1</v>
+      </c>
+      <c r="D202" t="s">
+        <v>42</v>
+      </c>
+      <c r="E202">
+        <v>2</v>
       </c>
       <c r="F202" t="s">
         <v>543</v>
@@ -5858,13 +6329,19 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B203" t="s">
         <v>262</v>
       </c>
       <c r="C203">
         <v>1</v>
+      </c>
+      <c r="D203" t="s">
+        <v>42</v>
+      </c>
+      <c r="E203">
+        <v>2</v>
       </c>
       <c r="F203" t="s">
         <v>542</v>
@@ -5872,13 +6349,19 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B204" t="s">
         <v>262</v>
       </c>
       <c r="C204">
         <v>1</v>
+      </c>
+      <c r="D204" t="s">
+        <v>42</v>
+      </c>
+      <c r="E204">
+        <v>2</v>
       </c>
       <c r="F204" t="s">
         <v>541</v>
@@ -5886,7 +6369,7 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B205" t="s">
         <v>262</v>
@@ -5894,13 +6377,19 @@
       <c r="C205">
         <v>1</v>
       </c>
+      <c r="D205" t="s">
+        <v>42</v>
+      </c>
+      <c r="E205" t="s">
+        <v>635</v>
+      </c>
       <c r="F205" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="B206" t="s">
         <v>262</v>
@@ -5908,13 +6397,19 @@
       <c r="C206">
         <v>1</v>
       </c>
+      <c r="D206" t="s">
+        <v>42</v>
+      </c>
+      <c r="E206" t="s">
+        <v>635</v>
+      </c>
       <c r="F206" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="B207" t="s">
         <v>262</v>
@@ -5922,13 +6417,19 @@
       <c r="C207">
         <v>1</v>
       </c>
+      <c r="D207" t="s">
+        <v>42</v>
+      </c>
+      <c r="E207" t="s">
+        <v>635</v>
+      </c>
       <c r="F207" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="B208" t="s">
         <v>262</v>
@@ -5936,13 +6437,19 @@
       <c r="C208">
         <v>1</v>
       </c>
+      <c r="D208" t="s">
+        <v>48</v>
+      </c>
+      <c r="E208">
+        <v>1</v>
+      </c>
       <c r="F208" t="s">
-        <v>537</v>
+        <v>528</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="B209" t="s">
         <v>262</v>
@@ -5950,13 +6457,19 @@
       <c r="C209">
         <v>1</v>
       </c>
+      <c r="D209" t="s">
+        <v>48</v>
+      </c>
+      <c r="E209">
+        <v>1</v>
+      </c>
       <c r="F209" t="s">
-        <v>536</v>
+        <v>527</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="B210" t="s">
         <v>262</v>
@@ -5964,13 +6477,19 @@
       <c r="C210">
         <v>1</v>
       </c>
+      <c r="D210" t="s">
+        <v>48</v>
+      </c>
+      <c r="E210">
+        <v>1</v>
+      </c>
       <c r="F210" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B211" t="s">
         <v>262</v>
@@ -5978,13 +6497,19 @@
       <c r="C211">
         <v>1</v>
       </c>
+      <c r="D211" t="s">
+        <v>48</v>
+      </c>
+      <c r="E211">
+        <v>2</v>
+      </c>
       <c r="F211" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B212" t="s">
         <v>262</v>
@@ -5992,13 +6517,19 @@
       <c r="C212">
         <v>1</v>
       </c>
+      <c r="D212" t="s">
+        <v>48</v>
+      </c>
+      <c r="E212">
+        <v>2</v>
+      </c>
       <c r="F212" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B213" t="s">
         <v>262</v>
@@ -6006,13 +6537,19 @@
       <c r="C213">
         <v>1</v>
       </c>
+      <c r="D213" t="s">
+        <v>48</v>
+      </c>
+      <c r="E213">
+        <v>2</v>
+      </c>
       <c r="F213" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B214" t="s">
         <v>262</v>
@@ -6020,13 +6557,19 @@
       <c r="C214">
         <v>1</v>
       </c>
+      <c r="D214" t="s">
+        <v>48</v>
+      </c>
+      <c r="E214">
+        <v>3</v>
+      </c>
       <c r="F214" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B215" t="s">
         <v>262</v>
@@ -6034,13 +6577,19 @@
       <c r="C215">
         <v>1</v>
       </c>
+      <c r="D215" t="s">
+        <v>48</v>
+      </c>
+      <c r="E215">
+        <v>3</v>
+      </c>
       <c r="F215" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B216" t="s">
         <v>262</v>
@@ -6048,13 +6597,19 @@
       <c r="C216">
         <v>1</v>
       </c>
+      <c r="D216" t="s">
+        <v>48</v>
+      </c>
+      <c r="E216">
+        <v>3</v>
+      </c>
       <c r="F216" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="B217" t="s">
         <v>262</v>
@@ -6062,13 +6617,19 @@
       <c r="C217">
         <v>1</v>
       </c>
+      <c r="D217" t="s">
+        <v>48</v>
+      </c>
+      <c r="E217">
+        <v>4</v>
+      </c>
       <c r="F217" t="s">
-        <v>528</v>
+        <v>537</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="B218" t="s">
         <v>262</v>
@@ -6076,13 +6637,19 @@
       <c r="C218">
         <v>1</v>
       </c>
+      <c r="D218" t="s">
+        <v>48</v>
+      </c>
+      <c r="E218">
+        <v>4</v>
+      </c>
       <c r="F218" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="B219" t="s">
         <v>262</v>
@@ -6090,13 +6657,19 @@
       <c r="C219">
         <v>1</v>
       </c>
+      <c r="D219" t="s">
+        <v>48</v>
+      </c>
+      <c r="E219">
+        <v>4</v>
+      </c>
       <c r="F219" t="s">
-        <v>526</v>
+        <v>535</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="B220" t="s">
         <v>262</v>
@@ -6104,13 +6677,19 @@
       <c r="C220">
         <v>1</v>
       </c>
+      <c r="D220" t="s">
+        <v>54</v>
+      </c>
+      <c r="E220">
+        <v>1</v>
+      </c>
       <c r="F220" t="s">
-        <v>525</v>
+        <v>517</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="B221" t="s">
         <v>262</v>
@@ -6118,13 +6697,19 @@
       <c r="C221">
         <v>1</v>
       </c>
+      <c r="D221" t="s">
+        <v>54</v>
+      </c>
+      <c r="E221">
+        <v>1</v>
+      </c>
       <c r="F221" t="s">
-        <v>524</v>
+        <v>516</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="B222" t="s">
         <v>262</v>
@@ -6132,13 +6717,19 @@
       <c r="C222">
         <v>1</v>
       </c>
+      <c r="D222" t="s">
+        <v>54</v>
+      </c>
+      <c r="E222">
+        <v>1</v>
+      </c>
       <c r="F222" t="s">
-        <v>523</v>
+        <v>515</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="B223" t="s">
         <v>262</v>
@@ -6146,8 +6737,14 @@
       <c r="C223">
         <v>1</v>
       </c>
+      <c r="D223" t="s">
+        <v>54</v>
+      </c>
+      <c r="E223">
+        <v>1</v>
+      </c>
       <c r="F223" t="s">
-        <v>522</v>
+        <v>514</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -6160,8 +6757,14 @@
       <c r="C224">
         <v>1</v>
       </c>
+      <c r="D224" t="s">
+        <v>54</v>
+      </c>
+      <c r="E224">
+        <v>2</v>
+      </c>
       <c r="F224" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
@@ -6174,8 +6777,14 @@
       <c r="C225">
         <v>1</v>
       </c>
+      <c r="D225" t="s">
+        <v>54</v>
+      </c>
+      <c r="E225">
+        <v>2</v>
+      </c>
       <c r="F225" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -6188,13 +6797,19 @@
       <c r="C226">
         <v>1</v>
       </c>
+      <c r="D226" t="s">
+        <v>54</v>
+      </c>
+      <c r="E226">
+        <v>2</v>
+      </c>
       <c r="F226" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="B227" t="s">
         <v>262</v>
@@ -6202,13 +6817,19 @@
       <c r="C227">
         <v>1</v>
       </c>
+      <c r="D227" t="s">
+        <v>54</v>
+      </c>
+      <c r="E227">
+        <v>3</v>
+      </c>
       <c r="F227" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B228" t="s">
         <v>262</v>
@@ -6216,13 +6837,19 @@
       <c r="C228">
         <v>1</v>
       </c>
+      <c r="D228" t="s">
+        <v>54</v>
+      </c>
+      <c r="E228">
+        <v>3</v>
+      </c>
       <c r="F228" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="B229" t="s">
         <v>262</v>
@@ -6230,13 +6857,19 @@
       <c r="C229">
         <v>1</v>
       </c>
+      <c r="D229" t="s">
+        <v>54</v>
+      </c>
+      <c r="E229">
+        <v>4</v>
+      </c>
       <c r="F229" t="s">
-        <v>516</v>
+        <v>525</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="B230" t="s">
         <v>262</v>
@@ -6244,13 +6877,19 @@
       <c r="C230">
         <v>1</v>
       </c>
+      <c r="D230" t="s">
+        <v>54</v>
+      </c>
+      <c r="E230">
+        <v>4</v>
+      </c>
       <c r="F230" t="s">
-        <v>515</v>
+        <v>524</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="B231" t="s">
         <v>262</v>
@@ -6258,13 +6897,19 @@
       <c r="C231">
         <v>1</v>
       </c>
+      <c r="D231" t="s">
+        <v>54</v>
+      </c>
+      <c r="E231">
+        <v>4</v>
+      </c>
       <c r="F231" t="s">
-        <v>514</v>
+        <v>523</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>345</v>
+        <v>334</v>
       </c>
       <c r="B232" t="s">
         <v>262</v>
@@ -6272,13 +6917,19 @@
       <c r="C232">
         <v>1</v>
       </c>
+      <c r="D232" t="s">
+        <v>58</v>
+      </c>
+      <c r="E232">
+        <v>1</v>
+      </c>
       <c r="F232" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="B233" t="s">
         <v>262</v>
@@ -6286,13 +6937,19 @@
       <c r="C233">
         <v>1</v>
       </c>
+      <c r="D233" t="s">
+        <v>58</v>
+      </c>
+      <c r="E233">
+        <v>1</v>
+      </c>
       <c r="F233" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>343</v>
+        <v>332</v>
       </c>
       <c r="B234" t="s">
         <v>262</v>
@@ -6300,13 +6957,19 @@
       <c r="C234">
         <v>1</v>
       </c>
+      <c r="D234" t="s">
+        <v>58</v>
+      </c>
+      <c r="E234">
+        <v>1</v>
+      </c>
       <c r="F234" t="s">
-        <v>511</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>342</v>
+        <v>331</v>
       </c>
       <c r="B235" t="s">
         <v>262</v>
@@ -6314,13 +6977,19 @@
       <c r="C235">
         <v>1</v>
       </c>
+      <c r="D235" t="s">
+        <v>58</v>
+      </c>
+      <c r="E235">
+        <v>1</v>
+      </c>
       <c r="F235" t="s">
-        <v>510</v>
+        <v>498</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="B236" t="s">
         <v>262</v>
@@ -6328,13 +6997,19 @@
       <c r="C236">
         <v>1</v>
       </c>
+      <c r="D236" t="s">
+        <v>58</v>
+      </c>
+      <c r="E236">
+        <v>2</v>
+      </c>
       <c r="F236" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="B237" t="s">
         <v>262</v>
@@ -6342,13 +7017,19 @@
       <c r="C237">
         <v>1</v>
       </c>
+      <c r="D237" t="s">
+        <v>58</v>
+      </c>
+      <c r="E237">
+        <v>2</v>
+      </c>
       <c r="F237" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B238" t="s">
         <v>262</v>
@@ -6356,13 +7037,19 @@
       <c r="C238">
         <v>1</v>
       </c>
+      <c r="D238" t="s">
+        <v>58</v>
+      </c>
+      <c r="E238">
+        <v>2</v>
+      </c>
       <c r="F238" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="B239" t="s">
         <v>262</v>
@@ -6370,13 +7057,19 @@
       <c r="C239">
         <v>1</v>
       </c>
+      <c r="D239" t="s">
+        <v>58</v>
+      </c>
+      <c r="E239">
+        <v>2</v>
+      </c>
       <c r="F239" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="B240" t="s">
         <v>262</v>
@@ -6384,13 +7077,19 @@
       <c r="C240">
         <v>1</v>
       </c>
+      <c r="D240" t="s">
+        <v>58</v>
+      </c>
+      <c r="E240">
+        <v>3</v>
+      </c>
       <c r="F240" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="B241" t="s">
         <v>262</v>
@@ -6398,13 +7097,19 @@
       <c r="C241">
         <v>1</v>
       </c>
+      <c r="D241" t="s">
+        <v>58</v>
+      </c>
+      <c r="E241">
+        <v>3</v>
+      </c>
       <c r="F241" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="B242" t="s">
         <v>262</v>
@@ -6412,13 +7117,19 @@
       <c r="C242">
         <v>1</v>
       </c>
+      <c r="D242" t="s">
+        <v>58</v>
+      </c>
+      <c r="E242">
+        <v>3</v>
+      </c>
       <c r="F242" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="B243" t="s">
         <v>262</v>
@@ -6426,13 +7137,19 @@
       <c r="C243">
         <v>1</v>
       </c>
+      <c r="D243" t="s">
+        <v>58</v>
+      </c>
+      <c r="E243">
+        <v>3</v>
+      </c>
       <c r="F243" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="B244" t="s">
         <v>262</v>
@@ -6440,13 +7157,19 @@
       <c r="C244">
         <v>1</v>
       </c>
+      <c r="D244" t="s">
+        <v>58</v>
+      </c>
+      <c r="E244">
+        <v>3</v>
+      </c>
       <c r="F244" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="B245" t="s">
         <v>262</v>
@@ -6454,13 +7177,19 @@
       <c r="C245">
         <v>1</v>
       </c>
+      <c r="D245" t="s">
+        <v>58</v>
+      </c>
+      <c r="E245">
+        <v>3</v>
+      </c>
       <c r="F245" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="B246" t="s">
         <v>262</v>
@@ -6468,13 +7197,19 @@
       <c r="C246">
         <v>1</v>
       </c>
+      <c r="D246" t="s">
+        <v>58</v>
+      </c>
+      <c r="E246">
+        <v>4</v>
+      </c>
       <c r="F246" t="s">
-        <v>499</v>
+        <v>513</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="B247" t="s">
         <v>262</v>
@@ -6482,13 +7217,19 @@
       <c r="C247">
         <v>1</v>
       </c>
+      <c r="D247" t="s">
+        <v>58</v>
+      </c>
+      <c r="E247">
+        <v>4</v>
+      </c>
       <c r="F247" t="s">
-        <v>498</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>329</v>
+        <v>318</v>
       </c>
       <c r="B248" t="s">
         <v>262</v>
@@ -6496,13 +7237,19 @@
       <c r="C248">
         <v>1</v>
       </c>
+      <c r="D248" t="s">
+        <v>63</v>
+      </c>
+      <c r="E248">
+        <v>1</v>
+      </c>
       <c r="F248" t="s">
-        <v>497</v>
+        <v>485</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>328</v>
+        <v>317</v>
       </c>
       <c r="B249" t="s">
         <v>262</v>
@@ -6510,13 +7257,19 @@
       <c r="C249">
         <v>1</v>
       </c>
+      <c r="D249" t="s">
+        <v>63</v>
+      </c>
+      <c r="E249">
+        <v>1</v>
+      </c>
       <c r="F249" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="B250" t="s">
         <v>262</v>
@@ -6524,13 +7277,19 @@
       <c r="C250">
         <v>1</v>
       </c>
+      <c r="D250" t="s">
+        <v>63</v>
+      </c>
+      <c r="E250">
+        <v>1</v>
+      </c>
       <c r="F250" t="s">
-        <v>495</v>
+        <v>483</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B251" t="s">
         <v>262</v>
@@ -6538,13 +7297,19 @@
       <c r="C251">
         <v>1</v>
       </c>
+      <c r="D251" t="s">
+        <v>63</v>
+      </c>
+      <c r="E251">
+        <v>2</v>
+      </c>
       <c r="F251" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B252" t="s">
         <v>262</v>
@@ -6552,13 +7317,19 @@
       <c r="C252">
         <v>1</v>
       </c>
+      <c r="D252" t="s">
+        <v>63</v>
+      </c>
+      <c r="E252">
+        <v>2</v>
+      </c>
       <c r="F252" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="B253" t="s">
         <v>262</v>
@@ -6566,13 +7337,19 @@
       <c r="C253">
         <v>1</v>
       </c>
+      <c r="D253" t="s">
+        <v>63</v>
+      </c>
+      <c r="E253">
+        <v>2</v>
+      </c>
       <c r="F253" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="B254" t="s">
         <v>262</v>
@@ -6580,13 +7357,19 @@
       <c r="C254">
         <v>1</v>
       </c>
+      <c r="D254" t="s">
+        <v>63</v>
+      </c>
+      <c r="E254">
+        <v>2</v>
+      </c>
       <c r="F254" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="B255" t="s">
         <v>262</v>
@@ -6594,13 +7377,19 @@
       <c r="C255">
         <v>1</v>
       </c>
+      <c r="D255" t="s">
+        <v>63</v>
+      </c>
+      <c r="E255">
+        <v>3</v>
+      </c>
       <c r="F255" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B256" t="s">
         <v>262</v>
@@ -6608,13 +7397,19 @@
       <c r="C256">
         <v>1</v>
       </c>
+      <c r="D256" t="s">
+        <v>63</v>
+      </c>
+      <c r="E256">
+        <v>3</v>
+      </c>
       <c r="F256" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="B257" t="s">
         <v>262</v>
@@ -6622,13 +7417,19 @@
       <c r="C257">
         <v>1</v>
       </c>
+      <c r="D257" t="s">
+        <v>63</v>
+      </c>
+      <c r="E257">
+        <v>3</v>
+      </c>
       <c r="F257" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B258" t="s">
         <v>262</v>
@@ -6636,13 +7437,19 @@
       <c r="C258">
         <v>1</v>
       </c>
+      <c r="D258" t="s">
+        <v>63</v>
+      </c>
+      <c r="E258">
+        <v>3</v>
+      </c>
       <c r="F258" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="B259" t="s">
         <v>262</v>
@@ -6650,13 +7457,19 @@
       <c r="C259">
         <v>1</v>
       </c>
+      <c r="D259" t="s">
+        <v>63</v>
+      </c>
+      <c r="E259">
+        <v>4</v>
+      </c>
       <c r="F259" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="B260" t="s">
         <v>262</v>
@@ -6664,13 +7477,19 @@
       <c r="C260">
         <v>1</v>
       </c>
+      <c r="D260" t="s">
+        <v>63</v>
+      </c>
+      <c r="E260">
+        <v>4</v>
+      </c>
       <c r="F260" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="B261" t="s">
         <v>262</v>
@@ -6678,13 +7497,19 @@
       <c r="C261">
         <v>1</v>
       </c>
+      <c r="D261" t="s">
+        <v>63</v>
+      </c>
+      <c r="E261">
+        <v>4</v>
+      </c>
       <c r="F261" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="B262" t="s">
         <v>262</v>
@@ -6692,13 +7517,19 @@
       <c r="C262">
         <v>1</v>
       </c>
+      <c r="D262" t="s">
+        <v>63</v>
+      </c>
+      <c r="E262">
+        <v>4</v>
+      </c>
       <c r="F262" t="s">
-        <v>483</v>
+        <v>494</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="B263" t="s">
         <v>262</v>
@@ -6706,13 +7537,19 @@
       <c r="C263">
         <v>1</v>
       </c>
+      <c r="D263" t="s">
+        <v>67</v>
+      </c>
+      <c r="E263">
+        <v>1</v>
+      </c>
       <c r="F263" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="B264" t="s">
         <v>262</v>
@@ -6720,13 +7557,19 @@
       <c r="C264">
         <v>1</v>
       </c>
+      <c r="D264" t="s">
+        <v>67</v>
+      </c>
+      <c r="E264">
+        <v>1</v>
+      </c>
       <c r="F264" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="B265" t="s">
         <v>262</v>
@@ -6734,8 +7577,14 @@
       <c r="C265">
         <v>1</v>
       </c>
+      <c r="D265" t="s">
+        <v>67</v>
+      </c>
+      <c r="E265">
+        <v>1</v>
+      </c>
       <c r="F265" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
@@ -6748,8 +7597,14 @@
       <c r="C266">
         <v>1</v>
       </c>
+      <c r="D266" t="s">
+        <v>67</v>
+      </c>
+      <c r="E266">
+        <v>2</v>
+      </c>
       <c r="F266" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
@@ -6762,8 +7617,14 @@
       <c r="C267">
         <v>1</v>
       </c>
+      <c r="D267" t="s">
+        <v>67</v>
+      </c>
+      <c r="E267">
+        <v>2</v>
+      </c>
       <c r="F267" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
@@ -6776,13 +7637,19 @@
       <c r="C268">
         <v>1</v>
       </c>
+      <c r="D268" t="s">
+        <v>67</v>
+      </c>
+      <c r="E268">
+        <v>2</v>
+      </c>
       <c r="F268" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>308</v>
+        <v>626</v>
       </c>
       <c r="B269" t="s">
         <v>262</v>
@@ -6790,13 +7657,19 @@
       <c r="C269">
         <v>1</v>
       </c>
+      <c r="D269" t="s">
+        <v>67</v>
+      </c>
+      <c r="E269">
+        <v>3</v>
+      </c>
       <c r="F269" t="s">
-        <v>476</v>
+        <v>634</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="B270" t="s">
         <v>262</v>
@@ -6804,13 +7677,19 @@
       <c r="C270">
         <v>1</v>
       </c>
+      <c r="D270" t="s">
+        <v>67</v>
+      </c>
+      <c r="E270">
+        <v>3</v>
+      </c>
       <c r="F270" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>446</v>
+        <v>312</v>
       </c>
       <c r="B271" t="s">
         <v>262</v>
@@ -6818,13 +7697,19 @@
       <c r="C271">
         <v>1</v>
       </c>
+      <c r="D271" t="s">
+        <v>67</v>
+      </c>
+      <c r="E271">
+        <v>3</v>
+      </c>
       <c r="F271" t="s">
-        <v>614</v>
+        <v>479</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>615</v>
+        <v>315</v>
       </c>
       <c r="B272" t="s">
         <v>262</v>
@@ -6832,13 +7717,19 @@
       <c r="C272">
         <v>1</v>
       </c>
+      <c r="D272" t="s">
+        <v>67</v>
+      </c>
+      <c r="E272">
+        <v>4</v>
+      </c>
       <c r="F272" t="s">
-        <v>616</v>
+        <v>482</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="B273" t="s">
         <v>262</v>
@@ -6846,13 +7737,19 @@
       <c r="C273">
         <v>1</v>
       </c>
+      <c r="D273" t="s">
+        <v>67</v>
+      </c>
+      <c r="E273">
+        <v>4</v>
+      </c>
       <c r="F273" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="B274" t="s">
         <v>262</v>
@@ -6860,22 +7757,31 @@
       <c r="C274">
         <v>1</v>
       </c>
+      <c r="D274" t="s">
+        <v>69</v>
+      </c>
+      <c r="E274">
+        <v>1</v>
+      </c>
       <c r="F274" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>304</v>
+        <v>92</v>
       </c>
       <c r="B275" t="s">
-        <v>262</v>
+        <v>92</v>
       </c>
       <c r="C275">
         <v>1</v>
       </c>
-      <c r="F275" t="s">
-        <v>472</v>
+      <c r="D275" t="s">
+        <v>69</v>
+      </c>
+      <c r="E275">
+        <v>2</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
@@ -6888,8 +7794,14 @@
       <c r="C276">
         <v>1</v>
       </c>
+      <c r="D276" t="s">
+        <v>69</v>
+      </c>
+      <c r="E276">
+        <v>3</v>
+      </c>
       <c r="F276" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
@@ -6902,8 +7814,14 @@
       <c r="C277">
         <v>1</v>
       </c>
+      <c r="D277" t="s">
+        <v>69</v>
+      </c>
+      <c r="E277">
+        <v>3</v>
+      </c>
       <c r="F277" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
@@ -6916,13 +7834,19 @@
       <c r="C278">
         <v>1</v>
       </c>
+      <c r="D278" t="s">
+        <v>69</v>
+      </c>
+      <c r="E278">
+        <v>3</v>
+      </c>
       <c r="F278" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>300</v>
+        <v>445</v>
       </c>
       <c r="B279" t="s">
         <v>262</v>
@@ -6930,13 +7854,19 @@
       <c r="C279">
         <v>1</v>
       </c>
+      <c r="D279" t="s">
+        <v>69</v>
+      </c>
+      <c r="E279">
+        <v>4</v>
+      </c>
       <c r="F279" t="s">
-        <v>468</v>
+        <v>612</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>299</v>
+        <v>613</v>
       </c>
       <c r="B280" t="s">
         <v>262</v>
@@ -6944,13 +7874,19 @@
       <c r="C280">
         <v>1</v>
       </c>
+      <c r="D280" t="s">
+        <v>69</v>
+      </c>
+      <c r="E280">
+        <v>4</v>
+      </c>
       <c r="F280" t="s">
-        <v>467</v>
+        <v>614</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="B281" t="s">
         <v>262</v>
@@ -6958,13 +7894,19 @@
       <c r="C281">
         <v>1</v>
       </c>
+      <c r="D281" t="s">
+        <v>69</v>
+      </c>
+      <c r="E281">
+        <v>4</v>
+      </c>
       <c r="F281" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="B282" t="s">
         <v>262</v>
@@ -6972,13 +7914,19 @@
       <c r="C282">
         <v>1</v>
       </c>
+      <c r="D282" t="s">
+        <v>69</v>
+      </c>
+      <c r="E282">
+        <v>4</v>
+      </c>
       <c r="F282" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B283" t="s">
         <v>262</v>
@@ -6986,13 +7934,19 @@
       <c r="C283">
         <v>1</v>
       </c>
+      <c r="D283" t="s">
+        <v>75</v>
+      </c>
+      <c r="E283">
+        <v>1</v>
+      </c>
       <c r="F283" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B284" t="s">
         <v>262</v>
@@ -7000,13 +7954,19 @@
       <c r="C284">
         <v>1</v>
       </c>
+      <c r="D284" t="s">
+        <v>75</v>
+      </c>
+      <c r="E284">
+        <v>1</v>
+      </c>
       <c r="F284" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B285" t="s">
         <v>262</v>
@@ -7014,13 +7974,19 @@
       <c r="C285">
         <v>1</v>
       </c>
+      <c r="D285" t="s">
+        <v>75</v>
+      </c>
+      <c r="E285">
+        <v>1</v>
+      </c>
       <c r="F285" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B286" t="s">
         <v>262</v>
@@ -7028,13 +7994,19 @@
       <c r="C286">
         <v>1</v>
       </c>
+      <c r="D286" t="s">
+        <v>75</v>
+      </c>
+      <c r="E286">
+        <v>2</v>
+      </c>
       <c r="F286" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B287" t="s">
         <v>262</v>
@@ -7042,13 +8014,19 @@
       <c r="C287">
         <v>1</v>
       </c>
+      <c r="D287" t="s">
+        <v>75</v>
+      </c>
+      <c r="E287">
+        <v>2</v>
+      </c>
       <c r="F287" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>291</v>
+        <v>623</v>
       </c>
       <c r="B288" t="s">
         <v>262</v>
@@ -7056,13 +8034,19 @@
       <c r="C288">
         <v>1</v>
       </c>
+      <c r="D288" t="s">
+        <v>75</v>
+      </c>
+      <c r="E288">
+        <v>2</v>
+      </c>
       <c r="F288" t="s">
-        <v>459</v>
+        <v>631</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>290</v>
+        <v>622</v>
       </c>
       <c r="B289" t="s">
         <v>262</v>
@@ -7070,13 +8054,19 @@
       <c r="C289">
         <v>1</v>
       </c>
+      <c r="D289" t="s">
+        <v>75</v>
+      </c>
+      <c r="E289">
+        <v>2</v>
+      </c>
       <c r="F289" t="s">
-        <v>458</v>
+        <v>630</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="B290" t="s">
         <v>262</v>
@@ -7084,13 +8074,19 @@
       <c r="C290">
         <v>1</v>
       </c>
+      <c r="D290" t="s">
+        <v>75</v>
+      </c>
+      <c r="E290">
+        <v>3</v>
+      </c>
       <c r="F290" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="B291" t="s">
         <v>262</v>
@@ -7098,13 +8094,19 @@
       <c r="C291">
         <v>1</v>
       </c>
+      <c r="D291" t="s">
+        <v>75</v>
+      </c>
+      <c r="E291">
+        <v>3</v>
+      </c>
       <c r="F291" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>287</v>
+        <v>624</v>
       </c>
       <c r="B292" t="s">
         <v>262</v>
@@ -7112,13 +8114,19 @@
       <c r="C292">
         <v>1</v>
       </c>
+      <c r="D292" t="s">
+        <v>75</v>
+      </c>
+      <c r="E292">
+        <v>3</v>
+      </c>
       <c r="F292" t="s">
-        <v>455</v>
+        <v>632</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>286</v>
+        <v>299</v>
       </c>
       <c r="B293" t="s">
         <v>262</v>
@@ -7126,13 +8134,19 @@
       <c r="C293">
         <v>1</v>
       </c>
+      <c r="D293" t="s">
+        <v>75</v>
+      </c>
+      <c r="E293">
+        <v>4</v>
+      </c>
       <c r="F293" t="s">
-        <v>454</v>
+        <v>466</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="B294" t="s">
         <v>262</v>
@@ -7140,8 +8154,14 @@
       <c r="C294">
         <v>1</v>
       </c>
+      <c r="D294" t="s">
+        <v>75</v>
+      </c>
+      <c r="E294">
+        <v>4</v>
+      </c>
       <c r="F294" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
@@ -7154,13 +8174,19 @@
       <c r="C295">
         <v>1</v>
       </c>
+      <c r="D295" t="s">
+        <v>79</v>
+      </c>
+      <c r="E295">
+        <v>1</v>
+      </c>
       <c r="F295" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>283</v>
+        <v>621</v>
       </c>
       <c r="B296" t="s">
         <v>262</v>
@@ -7168,18 +8194,30 @@
       <c r="C296">
         <v>1</v>
       </c>
+      <c r="D296" t="s">
+        <v>79</v>
+      </c>
+      <c r="E296">
+        <v>1</v>
+      </c>
       <c r="F296" t="s">
-        <v>451</v>
+        <v>629</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B297" t="s">
         <v>262</v>
       </c>
       <c r="C297">
+        <v>1</v>
+      </c>
+      <c r="D297" t="s">
+        <v>79</v>
+      </c>
+      <c r="E297">
         <v>1</v>
       </c>
       <c r="F297" t="s">
@@ -7188,7 +8226,7 @@
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="B298" t="s">
         <v>262</v>
@@ -7196,13 +8234,19 @@
       <c r="C298">
         <v>1</v>
       </c>
+      <c r="D298" t="s">
+        <v>79</v>
+      </c>
+      <c r="E298">
+        <v>2</v>
+      </c>
       <c r="F298" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B299" t="s">
         <v>262</v>
@@ -7210,13 +8254,19 @@
       <c r="C299">
         <v>1</v>
       </c>
+      <c r="D299" t="s">
+        <v>79</v>
+      </c>
+      <c r="E299">
+        <v>2</v>
+      </c>
       <c r="F299" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B300" t="s">
         <v>262</v>
@@ -7224,13 +8274,19 @@
       <c r="C300">
         <v>1</v>
       </c>
+      <c r="D300" t="s">
+        <v>79</v>
+      </c>
+      <c r="E300">
+        <v>2</v>
+      </c>
       <c r="F300" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>271</v>
+        <v>290</v>
       </c>
       <c r="B301" t="s">
         <v>262</v>
@@ -7238,13 +8294,19 @@
       <c r="C301">
         <v>1</v>
       </c>
+      <c r="D301" t="s">
+        <v>79</v>
+      </c>
+      <c r="E301">
+        <v>3</v>
+      </c>
       <c r="F301" t="s">
-        <v>278</v>
+        <v>457</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>270</v>
+        <v>289</v>
       </c>
       <c r="B302" t="s">
         <v>262</v>
@@ -7252,13 +8314,19 @@
       <c r="C302">
         <v>1</v>
       </c>
+      <c r="D302" t="s">
+        <v>79</v>
+      </c>
+      <c r="E302">
+        <v>3</v>
+      </c>
       <c r="F302" t="s">
-        <v>277</v>
+        <v>456</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>269</v>
+        <v>288</v>
       </c>
       <c r="B303" t="s">
         <v>262</v>
@@ -7266,27 +8334,36 @@
       <c r="C303">
         <v>1</v>
       </c>
+      <c r="D303" t="s">
+        <v>79</v>
+      </c>
+      <c r="E303">
+        <v>3</v>
+      </c>
       <c r="F303" t="s">
-        <v>276</v>
+        <v>455</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>268</v>
+        <v>92</v>
       </c>
       <c r="B304" t="s">
-        <v>262</v>
+        <v>92</v>
       </c>
       <c r="C304">
         <v>1</v>
       </c>
-      <c r="F304" t="s">
-        <v>275</v>
+      <c r="D304" t="s">
+        <v>79</v>
+      </c>
+      <c r="E304">
+        <v>4</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B305" t="s">
         <v>262</v>
@@ -7294,13 +8371,19 @@
       <c r="C305">
         <v>1</v>
       </c>
+      <c r="D305" t="s">
+        <v>86</v>
+      </c>
+      <c r="E305">
+        <v>1</v>
+      </c>
       <c r="F305" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B306" t="s">
         <v>262</v>
@@ -7308,13 +8391,19 @@
       <c r="C306">
         <v>1</v>
       </c>
+      <c r="D306" t="s">
+        <v>86</v>
+      </c>
+      <c r="E306">
+        <v>1</v>
+      </c>
       <c r="F306" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B307" t="s">
         <v>262</v>
@@ -7322,13 +8411,19 @@
       <c r="C307">
         <v>1</v>
       </c>
+      <c r="D307" t="s">
+        <v>86</v>
+      </c>
+      <c r="E307">
+        <v>1</v>
+      </c>
       <c r="F307" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="B308" t="s">
         <v>262</v>
@@ -7336,16 +8431,202 @@
       <c r="C308">
         <v>1</v>
       </c>
+      <c r="D308" t="s">
+        <v>86</v>
+      </c>
+      <c r="E308">
+        <v>2</v>
+      </c>
       <c r="F308" t="s">
-        <v>264</v>
+        <v>276</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>268</v>
+      </c>
+      <c r="B309" t="s">
+        <v>262</v>
+      </c>
+      <c r="C309">
+        <v>1</v>
+      </c>
+      <c r="D309" t="s">
+        <v>86</v>
+      </c>
+      <c r="E309">
+        <v>2</v>
+      </c>
+      <c r="F309" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>267</v>
+      </c>
+      <c r="B310" t="s">
+        <v>262</v>
+      </c>
+      <c r="C310">
+        <v>1</v>
+      </c>
+      <c r="D310" t="s">
+        <v>86</v>
+      </c>
+      <c r="E310">
+        <v>2</v>
+      </c>
+      <c r="F310" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>279</v>
+      </c>
+      <c r="B311" t="s">
+        <v>262</v>
+      </c>
+      <c r="C311">
+        <v>1</v>
+      </c>
+      <c r="D311" t="s">
+        <v>86</v>
+      </c>
+      <c r="E311">
+        <v>3</v>
+      </c>
+      <c r="F311" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
+        <v>625</v>
+      </c>
+      <c r="B312" t="s">
+        <v>262</v>
+      </c>
+      <c r="C312">
+        <v>1</v>
+      </c>
+      <c r="D312" t="s">
+        <v>86</v>
+      </c>
+      <c r="E312">
+        <v>3</v>
+      </c>
+      <c r="F312" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>271</v>
+      </c>
+      <c r="B313" t="s">
+        <v>262</v>
+      </c>
+      <c r="C313">
+        <v>1</v>
+      </c>
+      <c r="D313" t="s">
+        <v>86</v>
+      </c>
+      <c r="E313">
+        <v>3</v>
+      </c>
+      <c r="F313" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>270</v>
+      </c>
+      <c r="B314" t="s">
+        <v>262</v>
+      </c>
+      <c r="C314">
+        <v>1</v>
+      </c>
+      <c r="D314" t="s">
+        <v>86</v>
+      </c>
+      <c r="E314">
+        <v>3</v>
+      </c>
+      <c r="F314" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>282</v>
+      </c>
+      <c r="B315" t="s">
+        <v>262</v>
+      </c>
+      <c r="C315">
+        <v>1</v>
+      </c>
+      <c r="D315" t="s">
+        <v>86</v>
+      </c>
+      <c r="E315">
+        <v>4</v>
+      </c>
+      <c r="F315" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>281</v>
+      </c>
+      <c r="B316" t="s">
+        <v>262</v>
+      </c>
+      <c r="C316">
+        <v>1</v>
+      </c>
+      <c r="D316" t="s">
+        <v>86</v>
+      </c>
+      <c r="E316">
+        <v>4</v>
+      </c>
+      <c r="F316" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>280</v>
+      </c>
+      <c r="B317" t="s">
+        <v>262</v>
+      </c>
+      <c r="C317">
+        <v>1</v>
+      </c>
+      <c r="D317" t="s">
+        <v>86</v>
+      </c>
+      <c r="E317">
+        <v>4</v>
+      </c>
+      <c r="F317" t="s">
+        <v>447</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F308">
-    <sortCondition descending="1" ref="C2:C308"/>
-    <sortCondition ref="D2:D308"/>
-    <sortCondition ref="E2:E308"/>
-    <sortCondition descending="1" ref="A2:A308"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F317">
+    <sortCondition descending="1" ref="C2:C317"/>
+    <sortCondition ref="D2:D317"/>
+    <sortCondition ref="E2:E317"/>
+    <sortCondition descending="1" ref="A2:A317"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/EOAT_data.xlsx
+++ b/data/EOAT_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\procesos.CAZEL\Desktop\Becario Procesos\EOAT Project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8461260A-E646-4DCA-BC8E-BCD9A213AF62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F3B2399-4A02-4E25-9199-AA1C9A8DF6DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{440E3869-3C3F-4E8C-A8BD-ADEB8E2EA552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1256" uniqueCount="636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1259" uniqueCount="640">
   <si>
     <t>I-1937</t>
   </si>
@@ -1944,6 +1944,18 @@
   </si>
   <si>
     <t>3 y 4</t>
+  </si>
+  <si>
+    <t>2 y 3</t>
+  </si>
+  <si>
+    <t>Base para fin de brazo en Maq. 316</t>
+  </si>
+  <si>
+    <t>I-1908</t>
+  </si>
+  <si>
+    <t>I-1908.jpeg</t>
   </si>
 </sst>
 </file>
@@ -2325,7 +2337,7 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="4.7109375" bestFit="1" customWidth="1"/>
@@ -3385,8 +3397,8 @@
       <c r="D53" t="s">
         <v>58</v>
       </c>
-      <c r="E53">
-        <v>2</v>
+      <c r="E53" t="s">
+        <v>636</v>
       </c>
       <c r="F53" t="s">
         <v>192</v>
@@ -3397,7 +3409,7 @@
         <v>61</v>
       </c>
       <c r="B54" t="s">
-        <v>262</v>
+        <v>637</v>
       </c>
       <c r="C54">
         <v>3</v>
@@ -3405,8 +3417,8 @@
       <c r="D54" t="s">
         <v>58</v>
       </c>
-      <c r="E54">
-        <v>3</v>
+      <c r="E54" t="s">
+        <v>636</v>
       </c>
       <c r="F54" t="s">
         <v>194</v>
@@ -4841,10 +4853,10 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>92</v>
+        <v>638</v>
       </c>
       <c r="B128" t="s">
-        <v>92</v>
+        <v>262</v>
       </c>
       <c r="C128">
         <v>2</v>
@@ -4854,6 +4866,9 @@
       </c>
       <c r="E128">
         <v>3</v>
+      </c>
+      <c r="F128" t="s">
+        <v>639</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">

--- a/data/EOAT_data.xlsx
+++ b/data/EOAT_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\procesos.CAZEL\Desktop\Becario Procesos\EOAT Project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F3B2399-4A02-4E25-9199-AA1C9A8DF6DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA9F9CA6-2FF6-427F-AC61-CC3B5B5C5EC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{440E3869-3C3F-4E8C-A8BD-ADEB8E2EA552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1259" uniqueCount="640">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1251" uniqueCount="636">
   <si>
     <t>I-1937</t>
   </si>
@@ -128,12 +128,6 @@
     <t>C05</t>
   </si>
   <si>
-    <t>I-1802</t>
-  </si>
-  <si>
-    <t>I-1800</t>
-  </si>
-  <si>
     <t>I-1789</t>
   </si>
   <si>
@@ -540,12 +534,6 @@
   </si>
   <si>
     <t>I-1812.jpeg</t>
-  </si>
-  <si>
-    <t>I-1802.jpeg</t>
-  </si>
-  <si>
-    <t>I-1800.jpeg</t>
   </si>
   <si>
     <t>I-1789.jpeg</t>
@@ -2333,7 +2321,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B6791C-A8A7-4753-A504-FAA9E3EE8745}">
-  <dimension ref="A1:F317"/>
+  <dimension ref="A1:F315"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -2346,22 +2334,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B1" t="s">
+        <v>253</v>
+      </c>
+      <c r="C1" t="s">
+        <v>254</v>
+      </c>
+      <c r="D1" t="s">
+        <v>255</v>
+      </c>
+      <c r="E1" t="s">
         <v>256</v>
       </c>
-      <c r="B1" t="s">
+      <c r="F1" t="s">
         <v>257</v>
-      </c>
-      <c r="C1" t="s">
-        <v>258</v>
-      </c>
-      <c r="D1" t="s">
-        <v>259</v>
-      </c>
-      <c r="E1" t="s">
-        <v>260</v>
-      </c>
-      <c r="F1" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -2369,7 +2357,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C2">
         <v>3</v>
@@ -2381,7 +2369,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -2389,7 +2377,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -2401,7 +2389,7 @@
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -2409,7 +2397,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -2421,7 +2409,7 @@
         <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -2429,7 +2417,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -2441,7 +2429,7 @@
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -2449,7 +2437,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C6">
         <v>3</v>
@@ -2461,7 +2449,7 @@
         <v>3</v>
       </c>
       <c r="F6" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -2469,7 +2457,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -2481,7 +2469,7 @@
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -2489,7 +2477,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C8">
         <v>3</v>
@@ -2501,7 +2489,7 @@
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -2509,7 +2497,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C9">
         <v>3</v>
@@ -2521,7 +2509,7 @@
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -2529,7 +2517,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C10">
         <v>3</v>
@@ -2541,7 +2529,7 @@
         <v>2</v>
       </c>
       <c r="F10" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -2549,7 +2537,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C11">
         <v>3</v>
@@ -2561,7 +2549,7 @@
         <v>2</v>
       </c>
       <c r="F11" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2569,7 +2557,7 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C12">
         <v>3</v>
@@ -2581,7 +2569,7 @@
         <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -2589,7 +2577,7 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C13">
         <v>3</v>
@@ -2601,7 +2589,7 @@
         <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -2609,7 +2597,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C14">
         <v>3</v>
@@ -2621,7 +2609,7 @@
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -2629,7 +2617,7 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C15">
         <v>3</v>
@@ -2641,7 +2629,7 @@
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -2649,7 +2637,7 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C16">
         <v>3</v>
@@ -2661,7 +2649,7 @@
         <v>2</v>
       </c>
       <c r="F16" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -2669,7 +2657,7 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C17">
         <v>3</v>
@@ -2681,7 +2669,7 @@
         <v>2</v>
       </c>
       <c r="F17" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -2689,7 +2677,7 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C18">
         <v>3</v>
@@ -2701,7 +2689,7 @@
         <v>3</v>
       </c>
       <c r="F18" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -2709,7 +2697,7 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C19">
         <v>3</v>
@@ -2721,7 +2709,7 @@
         <v>3</v>
       </c>
       <c r="F19" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -2729,7 +2717,7 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C20">
         <v>3</v>
@@ -2741,7 +2729,7 @@
         <v>3</v>
       </c>
       <c r="F20" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -2749,7 +2737,7 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C21">
         <v>3</v>
@@ -2761,7 +2749,7 @@
         <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -2769,7 +2757,7 @@
         <v>24</v>
       </c>
       <c r="B22" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C22">
         <v>3</v>
@@ -2781,7 +2769,7 @@
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -2789,7 +2777,7 @@
         <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C23">
         <v>3</v>
@@ -2801,7 +2789,7 @@
         <v>2</v>
       </c>
       <c r="F23" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -2809,7 +2797,7 @@
         <v>26</v>
       </c>
       <c r="B24" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C24">
         <v>3</v>
@@ -2821,7 +2809,7 @@
         <v>2</v>
       </c>
       <c r="F24" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -2829,7 +2817,7 @@
         <v>27</v>
       </c>
       <c r="B25" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C25">
         <v>3</v>
@@ -2841,7 +2829,7 @@
         <v>3</v>
       </c>
       <c r="F25" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -2849,7 +2837,7 @@
         <v>28</v>
       </c>
       <c r="B26" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C26">
         <v>3</v>
@@ -2861,15 +2849,15 @@
         <v>3</v>
       </c>
       <c r="F26" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="B27" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C27">
         <v>3</v>
@@ -2881,15 +2869,15 @@
         <v>1</v>
       </c>
       <c r="F27" t="s">
-        <v>618</v>
+        <v>614</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="B28" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C28">
         <v>3</v>
@@ -2901,7 +2889,7 @@
         <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -2909,7 +2897,7 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C29">
         <v>3</v>
@@ -2921,7 +2909,7 @@
         <v>2</v>
       </c>
       <c r="F29" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -2929,7 +2917,7 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C30">
         <v>3</v>
@@ -2938,10 +2926,10 @@
         <v>29</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F30" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -2949,59 +2937,59 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C31">
         <v>3</v>
       </c>
       <c r="D31" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E31">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F31" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>34</v>
+      </c>
+      <c r="B32" t="s">
+        <v>258</v>
+      </c>
+      <c r="C32">
+        <v>3</v>
+      </c>
+      <c r="D32" t="s">
         <v>33</v>
       </c>
-      <c r="B32" t="s">
-        <v>262</v>
-      </c>
-      <c r="C32">
-        <v>3</v>
-      </c>
-      <c r="D32" t="s">
-        <v>29</v>
-      </c>
       <c r="E32">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B33" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C33">
         <v>3</v>
       </c>
       <c r="D33" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -3009,19 +2997,19 @@
         <v>36</v>
       </c>
       <c r="B34" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C34">
         <v>3</v>
       </c>
       <c r="D34" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -3029,19 +3017,19 @@
         <v>37</v>
       </c>
       <c r="B35" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C35">
         <v>3</v>
       </c>
       <c r="D35" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F35" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -3049,19 +3037,19 @@
         <v>38</v>
       </c>
       <c r="B36" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C36">
         <v>3</v>
       </c>
       <c r="D36" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F36" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -3069,59 +3057,59 @@
         <v>39</v>
       </c>
       <c r="B37" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C37">
         <v>3</v>
       </c>
       <c r="D37" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E37">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F37" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" t="s">
+        <v>258</v>
+      </c>
+      <c r="C38">
+        <v>3</v>
+      </c>
+      <c r="D38" t="s">
         <v>40</v>
       </c>
-      <c r="B38" t="s">
-        <v>262</v>
-      </c>
-      <c r="C38">
-        <v>3</v>
-      </c>
-      <c r="D38" t="s">
-        <v>35</v>
-      </c>
       <c r="E38">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F38" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B39" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C39">
         <v>3</v>
       </c>
       <c r="D39" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -3129,19 +3117,19 @@
         <v>43</v>
       </c>
       <c r="B40" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C40">
         <v>3</v>
       </c>
       <c r="D40" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F40" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -3149,19 +3137,19 @@
         <v>44</v>
       </c>
       <c r="B41" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C41">
         <v>3</v>
       </c>
       <c r="D41" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F41" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -3169,59 +3157,59 @@
         <v>45</v>
       </c>
       <c r="B42" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C42">
         <v>3</v>
       </c>
       <c r="D42" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E42">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>47</v>
+      </c>
+      <c r="B43" t="s">
+        <v>258</v>
+      </c>
+      <c r="C43">
+        <v>3</v>
+      </c>
+      <c r="D43" t="s">
         <v>46</v>
       </c>
-      <c r="B43" t="s">
-        <v>262</v>
-      </c>
-      <c r="C43">
-        <v>3</v>
-      </c>
-      <c r="D43" t="s">
-        <v>42</v>
-      </c>
       <c r="E43">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F43" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B44" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C44">
         <v>3</v>
       </c>
       <c r="D44" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -3229,19 +3217,19 @@
         <v>49</v>
       </c>
       <c r="B45" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C45">
         <v>3</v>
       </c>
       <c r="D45" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F45" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -3249,19 +3237,19 @@
         <v>50</v>
       </c>
       <c r="B46" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C46">
         <v>3</v>
       </c>
       <c r="D46" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E46">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F46" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -3269,59 +3257,59 @@
         <v>51</v>
       </c>
       <c r="B47" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C47">
         <v>3</v>
       </c>
       <c r="D47" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E47">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F47" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>53</v>
+      </c>
+      <c r="B48" t="s">
+        <v>258</v>
+      </c>
+      <c r="C48">
+        <v>3</v>
+      </c>
+      <c r="D48" t="s">
         <v>52</v>
       </c>
-      <c r="B48" t="s">
-        <v>262</v>
-      </c>
-      <c r="C48">
-        <v>3</v>
-      </c>
-      <c r="D48" t="s">
-        <v>48</v>
-      </c>
       <c r="E48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F48" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C49">
         <v>3</v>
       </c>
       <c r="D49" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E49">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F49" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -3329,119 +3317,119 @@
         <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C50">
         <v>3</v>
       </c>
       <c r="D50" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F50" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>57</v>
+      </c>
+      <c r="B51" t="s">
+        <v>258</v>
+      </c>
+      <c r="C51">
+        <v>3</v>
+      </c>
+      <c r="D51" t="s">
         <v>56</v>
       </c>
-      <c r="B51" t="s">
-        <v>262</v>
-      </c>
-      <c r="C51">
-        <v>3</v>
-      </c>
-      <c r="D51" t="s">
-        <v>54</v>
-      </c>
-      <c r="E51">
-        <v>3</v>
+      <c r="E51" t="s">
+        <v>632</v>
       </c>
       <c r="F51" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B52" t="s">
-        <v>262</v>
+        <v>633</v>
       </c>
       <c r="C52">
         <v>3</v>
       </c>
       <c r="D52" t="s">
-        <v>58</v>
-      </c>
-      <c r="E52">
-        <v>1</v>
+        <v>56</v>
+      </c>
+      <c r="E52" t="s">
+        <v>632</v>
       </c>
       <c r="F52" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B53" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C53">
         <v>3</v>
       </c>
       <c r="D53" t="s">
-        <v>58</v>
-      </c>
-      <c r="E53" t="s">
-        <v>636</v>
+        <v>61</v>
+      </c>
+      <c r="E53">
+        <v>1</v>
       </c>
       <c r="F53" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
+        <v>62</v>
+      </c>
+      <c r="B54" t="s">
+        <v>258</v>
+      </c>
+      <c r="C54">
+        <v>3</v>
+      </c>
+      <c r="D54" t="s">
         <v>61</v>
       </c>
-      <c r="B54" t="s">
-        <v>637</v>
-      </c>
-      <c r="C54">
-        <v>3</v>
-      </c>
-      <c r="D54" t="s">
-        <v>58</v>
-      </c>
-      <c r="E54" t="s">
-        <v>636</v>
+      <c r="E54">
+        <v>1</v>
       </c>
       <c r="F54" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B55" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C55">
         <v>3</v>
       </c>
       <c r="D55" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -3449,124 +3437,121 @@
         <v>64</v>
       </c>
       <c r="B56" t="s">
-        <v>262</v>
+        <v>64</v>
       </c>
       <c r="C56">
         <v>3</v>
       </c>
       <c r="D56" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E56">
-        <v>1</v>
-      </c>
-      <c r="F56" t="s">
-        <v>196</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>64</v>
+      </c>
+      <c r="B57" t="s">
+        <v>64</v>
+      </c>
+      <c r="C57">
+        <v>3</v>
+      </c>
+      <c r="D57" t="s">
         <v>65</v>
       </c>
-      <c r="B57" t="s">
-        <v>262</v>
-      </c>
-      <c r="C57">
-        <v>3</v>
-      </c>
-      <c r="D57" t="s">
-        <v>63</v>
-      </c>
       <c r="E57">
-        <v>2</v>
-      </c>
-      <c r="F57" t="s">
-        <v>197</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B58" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C58">
         <v>3</v>
       </c>
       <c r="D58" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E58">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B59" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C59">
         <v>3</v>
       </c>
       <c r="D59" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E59">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="B60" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="C60">
         <v>3</v>
       </c>
       <c r="D60" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="E60">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="B61" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="C61">
         <v>3</v>
       </c>
       <c r="D61" t="s">
-        <v>67</v>
+        <v>91</v>
       </c>
       <c r="E61">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="B62" t="s">
-        <v>92</v>
+        <v>258</v>
       </c>
       <c r="C62">
         <v>3</v>
       </c>
       <c r="D62" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E62">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="F62" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -3574,7 +3559,7 @@
         <v>92</v>
       </c>
       <c r="B63" t="s">
-        <v>92</v>
+        <v>258</v>
       </c>
       <c r="C63">
         <v>3</v>
@@ -3583,15 +3568,18 @@
         <v>93</v>
       </c>
       <c r="E63">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F63" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>60</v>
+        <v>94</v>
       </c>
       <c r="B64" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C64">
         <v>3</v>
@@ -3600,30 +3588,30 @@
         <v>93</v>
       </c>
       <c r="E64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F64" t="s">
-        <v>193</v>
+        <v>215</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B65" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C65">
         <v>3</v>
       </c>
       <c r="D65" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -3631,19 +3619,19 @@
         <v>96</v>
       </c>
       <c r="B66" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C66">
         <v>3</v>
       </c>
       <c r="D66" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E66">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F66" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -3651,59 +3639,59 @@
         <v>97</v>
       </c>
       <c r="B67" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C67">
         <v>3</v>
       </c>
       <c r="D67" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E67">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F67" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>99</v>
+      </c>
+      <c r="B68" t="s">
+        <v>258</v>
+      </c>
+      <c r="C68">
+        <v>3</v>
+      </c>
+      <c r="D68" t="s">
         <v>98</v>
       </c>
-      <c r="B68" t="s">
-        <v>262</v>
-      </c>
-      <c r="C68">
-        <v>3</v>
-      </c>
-      <c r="D68" t="s">
-        <v>95</v>
-      </c>
       <c r="E68">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F68" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B69" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C69">
         <v>3</v>
       </c>
       <c r="D69" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F69" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -3711,19 +3699,19 @@
         <v>101</v>
       </c>
       <c r="B70" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C70">
         <v>3</v>
       </c>
       <c r="D70" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F70" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -3731,19 +3719,19 @@
         <v>102</v>
       </c>
       <c r="B71" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C71">
         <v>3</v>
       </c>
       <c r="D71" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E71">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F71" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -3751,59 +3739,59 @@
         <v>103</v>
       </c>
       <c r="B72" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C72">
         <v>3</v>
       </c>
       <c r="D72" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E72">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F72" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>105</v>
+      </c>
+      <c r="B73" t="s">
+        <v>258</v>
+      </c>
+      <c r="C73">
+        <v>3</v>
+      </c>
+      <c r="D73" t="s">
         <v>104</v>
       </c>
-      <c r="B73" t="s">
-        <v>262</v>
-      </c>
-      <c r="C73">
-        <v>3</v>
-      </c>
-      <c r="D73" t="s">
-        <v>100</v>
-      </c>
       <c r="E73">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F73" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B74" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C74">
         <v>3</v>
       </c>
       <c r="D74" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F74" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -3811,19 +3799,19 @@
         <v>107</v>
       </c>
       <c r="B75" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C75">
         <v>3</v>
       </c>
       <c r="D75" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F75" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
@@ -3831,19 +3819,19 @@
         <v>108</v>
       </c>
       <c r="B76" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C76">
         <v>3</v>
       </c>
       <c r="D76" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F76" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
@@ -3851,79 +3839,79 @@
         <v>109</v>
       </c>
       <c r="B77" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C77">
         <v>3</v>
       </c>
       <c r="D77" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E77">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F77" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>110</v>
+        <v>66</v>
       </c>
       <c r="B78" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D78" t="s">
-        <v>106</v>
+        <v>67</v>
       </c>
       <c r="E78">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F78" t="s">
-        <v>231</v>
+        <v>194</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>111</v>
+        <v>68</v>
       </c>
       <c r="B79" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D79" t="s">
-        <v>106</v>
+        <v>67</v>
       </c>
       <c r="E79">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F79" t="s">
-        <v>232</v>
+        <v>195</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B80" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C80">
         <v>2</v>
       </c>
       <c r="D80" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F80" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -3931,19 +3919,19 @@
         <v>70</v>
       </c>
       <c r="B81" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C81">
         <v>2</v>
       </c>
       <c r="D81" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E81">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F81" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3951,19 +3939,19 @@
         <v>71</v>
       </c>
       <c r="B82" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C82">
         <v>2</v>
       </c>
       <c r="D82" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E82">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -3971,59 +3959,59 @@
         <v>72</v>
       </c>
       <c r="B83" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C83">
         <v>2</v>
       </c>
       <c r="D83" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E83">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F83" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>74</v>
+      </c>
+      <c r="B84" t="s">
+        <v>258</v>
+      </c>
+      <c r="C84">
+        <v>2</v>
+      </c>
+      <c r="D84" t="s">
         <v>73</v>
       </c>
-      <c r="B84" t="s">
-        <v>262</v>
-      </c>
-      <c r="C84">
-        <v>2</v>
-      </c>
-      <c r="D84" t="s">
-        <v>69</v>
-      </c>
       <c r="E84">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F84" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B85" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C85">
         <v>2</v>
       </c>
       <c r="D85" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E85">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F85" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -4031,59 +4019,59 @@
         <v>76</v>
       </c>
       <c r="B86" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C86">
         <v>2</v>
       </c>
       <c r="D86" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E86">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F86" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>78</v>
+      </c>
+      <c r="B87" t="s">
+        <v>258</v>
+      </c>
+      <c r="C87">
+        <v>2</v>
+      </c>
+      <c r="D87" t="s">
         <v>77</v>
       </c>
-      <c r="B87" t="s">
-        <v>262</v>
-      </c>
-      <c r="C87">
-        <v>2</v>
-      </c>
-      <c r="D87" t="s">
-        <v>75</v>
-      </c>
       <c r="E87">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F87" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B88" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C88">
         <v>2</v>
       </c>
       <c r="D88" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E88">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F88" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -4091,19 +4079,19 @@
         <v>80</v>
       </c>
       <c r="B89" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C89">
         <v>2</v>
       </c>
       <c r="D89" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E89">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F89" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -4111,19 +4099,19 @@
         <v>81</v>
       </c>
       <c r="B90" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C90">
         <v>2</v>
       </c>
       <c r="D90" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E90">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F90" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -4131,19 +4119,19 @@
         <v>82</v>
       </c>
       <c r="B91" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C91">
         <v>2</v>
       </c>
       <c r="D91" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E91">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F91" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -4151,59 +4139,59 @@
         <v>83</v>
       </c>
       <c r="B92" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C92">
         <v>2</v>
       </c>
       <c r="D92" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E92">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F92" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>85</v>
+      </c>
+      <c r="B93" t="s">
+        <v>258</v>
+      </c>
+      <c r="C93">
+        <v>2</v>
+      </c>
+      <c r="D93" t="s">
         <v>84</v>
       </c>
-      <c r="B93" t="s">
-        <v>262</v>
-      </c>
-      <c r="C93">
-        <v>2</v>
-      </c>
-      <c r="D93" t="s">
-        <v>79</v>
-      </c>
       <c r="E93">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F93" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B94" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C94">
         <v>2</v>
       </c>
       <c r="D94" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E94">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F94" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -4211,19 +4199,19 @@
         <v>87</v>
       </c>
       <c r="B95" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C95">
         <v>2</v>
       </c>
       <c r="D95" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E95">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F95" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -4231,19 +4219,19 @@
         <v>88</v>
       </c>
       <c r="B96" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C96">
         <v>2</v>
       </c>
       <c r="D96" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E96">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F96" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
@@ -4251,79 +4239,79 @@
         <v>89</v>
       </c>
       <c r="B97" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C97">
         <v>2</v>
       </c>
       <c r="D97" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E97">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F97" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="B98" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C98">
         <v>2</v>
       </c>
       <c r="D98" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="E98">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F98" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="B99" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C99">
         <v>2</v>
       </c>
       <c r="D99" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="E99">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F99" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B100" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C100">
         <v>2</v>
       </c>
       <c r="D100" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E100">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F100" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
@@ -4331,19 +4319,19 @@
         <v>114</v>
       </c>
       <c r="B101" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C101">
         <v>2</v>
       </c>
       <c r="D101" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E101">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F101" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -4351,59 +4339,59 @@
         <v>115</v>
       </c>
       <c r="B102" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C102">
         <v>2</v>
       </c>
       <c r="D102" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="E102">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F102" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>117</v>
+      </c>
+      <c r="B103" t="s">
+        <v>258</v>
+      </c>
+      <c r="C103">
+        <v>2</v>
+      </c>
+      <c r="D103" t="s">
         <v>116</v>
       </c>
-      <c r="B103" t="s">
-        <v>262</v>
-      </c>
-      <c r="C103">
-        <v>2</v>
-      </c>
-      <c r="D103" t="s">
-        <v>113</v>
-      </c>
       <c r="E103">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F103" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B104" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C104">
         <v>2</v>
       </c>
       <c r="D104" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E104">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F104" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -4411,19 +4399,19 @@
         <v>119</v>
       </c>
       <c r="B105" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C105">
         <v>2</v>
       </c>
       <c r="D105" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E105">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F105" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -4431,19 +4419,19 @@
         <v>120</v>
       </c>
       <c r="B106" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C106">
         <v>2</v>
       </c>
       <c r="D106" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E106">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F106" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -4451,39 +4439,39 @@
         <v>121</v>
       </c>
       <c r="B107" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C107">
         <v>2</v>
       </c>
       <c r="D107" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E107">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F107" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
+        <v>124</v>
+      </c>
+      <c r="B108" t="s">
+        <v>258</v>
+      </c>
+      <c r="C108">
+        <v>2</v>
+      </c>
+      <c r="D108" t="s">
         <v>122</v>
       </c>
-      <c r="B108" t="s">
-        <v>262</v>
-      </c>
-      <c r="C108">
-        <v>2</v>
-      </c>
-      <c r="D108" t="s">
-        <v>118</v>
-      </c>
       <c r="E108">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F108" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -4491,99 +4479,99 @@
         <v>123</v>
       </c>
       <c r="B109" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C109">
         <v>2</v>
       </c>
       <c r="D109" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E109">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F109" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B110" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C110">
         <v>2</v>
       </c>
       <c r="D110" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E110">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F110" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B111" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C111">
         <v>2</v>
       </c>
       <c r="D111" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="E111">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F111" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>128</v>
+      </c>
+      <c r="B112" t="s">
+        <v>258</v>
+      </c>
+      <c r="C112">
+        <v>2</v>
+      </c>
+      <c r="D112" t="s">
         <v>127</v>
       </c>
-      <c r="B112" t="s">
-        <v>262</v>
-      </c>
-      <c r="C112">
-        <v>2</v>
-      </c>
-      <c r="D112" t="s">
-        <v>124</v>
-      </c>
       <c r="E112">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F112" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B113" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C113">
         <v>2</v>
       </c>
       <c r="D113" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E113">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F113" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -4591,19 +4579,19 @@
         <v>130</v>
       </c>
       <c r="B114" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C114">
         <v>2</v>
       </c>
       <c r="D114" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="E114">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F114" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -4611,59 +4599,59 @@
         <v>131</v>
       </c>
       <c r="B115" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C115">
         <v>2</v>
       </c>
       <c r="D115" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E115">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F115" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
+        <v>133</v>
+      </c>
+      <c r="B116" t="s">
+        <v>258</v>
+      </c>
+      <c r="C116">
+        <v>2</v>
+      </c>
+      <c r="D116" t="s">
         <v>132</v>
       </c>
-      <c r="B116" t="s">
-        <v>262</v>
-      </c>
-      <c r="C116">
-        <v>2</v>
-      </c>
-      <c r="D116" t="s">
-        <v>129</v>
-      </c>
       <c r="E116">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F116" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B117" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C117">
         <v>2</v>
       </c>
       <c r="D117" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E117">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F117" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
@@ -4671,19 +4659,19 @@
         <v>135</v>
       </c>
       <c r="B118" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C118">
         <v>2</v>
       </c>
       <c r="D118" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E118">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F118" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
@@ -4691,19 +4679,19 @@
         <v>136</v>
       </c>
       <c r="B119" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C119">
         <v>2</v>
       </c>
       <c r="D119" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E119">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F119" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
@@ -4711,223 +4699,223 @@
         <v>137</v>
       </c>
       <c r="B120" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C120">
         <v>2</v>
       </c>
       <c r="D120" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E120">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F120" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
+        <v>90</v>
+      </c>
+      <c r="B121" t="s">
+        <v>90</v>
+      </c>
+      <c r="C121">
+        <v>2</v>
+      </c>
+      <c r="D121" t="s">
         <v>138</v>
       </c>
-      <c r="B121" t="s">
-        <v>262</v>
-      </c>
-      <c r="C121">
-        <v>2</v>
-      </c>
-      <c r="D121" t="s">
-        <v>134</v>
-      </c>
       <c r="E121">
-        <v>3</v>
-      </c>
-      <c r="F121" t="s">
-        <v>254</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>139</v>
+        <v>90</v>
       </c>
       <c r="B122" t="s">
-        <v>262</v>
+        <v>90</v>
       </c>
       <c r="C122">
         <v>2</v>
       </c>
       <c r="D122" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="E122">
-        <v>3</v>
-      </c>
-      <c r="F122" t="s">
-        <v>255</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B123" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C123">
         <v>2</v>
       </c>
       <c r="D123" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E123">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B124" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C124">
         <v>2</v>
       </c>
       <c r="D124" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E124">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B125" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C125">
         <v>2</v>
       </c>
       <c r="D125" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E125">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>92</v>
+        <v>634</v>
       </c>
       <c r="B126" t="s">
-        <v>92</v>
+        <v>258</v>
       </c>
       <c r="C126">
         <v>2</v>
       </c>
       <c r="D126" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E126">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="F126" t="s">
+        <v>635</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B127" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C127">
         <v>2</v>
       </c>
       <c r="D127" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E127">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>638</v>
+        <v>90</v>
       </c>
       <c r="B128" t="s">
-        <v>262</v>
+        <v>90</v>
       </c>
       <c r="C128">
         <v>2</v>
       </c>
       <c r="D128" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E128">
-        <v>3</v>
-      </c>
-      <c r="F128" t="s">
-        <v>639</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B129" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C129">
         <v>2</v>
       </c>
       <c r="D129" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E129">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>92</v>
+        <v>432</v>
       </c>
       <c r="B130" t="s">
-        <v>92</v>
+        <v>258</v>
       </c>
       <c r="C130">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D130" t="s">
-        <v>142</v>
+        <v>1</v>
       </c>
       <c r="E130">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F130" t="s">
+        <v>599</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>92</v>
+        <v>430</v>
       </c>
       <c r="B131" t="s">
-        <v>92</v>
+        <v>258</v>
       </c>
       <c r="C131">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D131" t="s">
-        <v>142</v>
+        <v>1</v>
       </c>
       <c r="E131">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="F131" t="s">
+        <v>597</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="B132" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C132">
         <v>1</v>
@@ -4936,18 +4924,18 @@
         <v>1</v>
       </c>
       <c r="E132">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F132" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B133" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C133">
         <v>1</v>
@@ -4956,18 +4944,18 @@
         <v>1</v>
       </c>
       <c r="E133">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F133" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B134" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C134">
         <v>1</v>
@@ -4979,15 +4967,15 @@
         <v>2</v>
       </c>
       <c r="F134" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B135" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C135">
         <v>1</v>
@@ -4996,18 +4984,18 @@
         <v>1</v>
       </c>
       <c r="E135">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F135" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="B136" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C136">
         <v>1</v>
@@ -5016,18 +5004,18 @@
         <v>1</v>
       </c>
       <c r="E136">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F136" t="s">
-        <v>611</v>
+        <v>601</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>443</v>
+        <v>436</v>
       </c>
       <c r="B137" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C137">
         <v>1</v>
@@ -5036,18 +5024,18 @@
         <v>1</v>
       </c>
       <c r="E137">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F137" t="s">
-        <v>610</v>
+        <v>603</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="B138" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C138">
         <v>1</v>
@@ -5056,18 +5044,18 @@
         <v>1</v>
       </c>
       <c r="E138">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F138" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B139" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C139">
         <v>1</v>
@@ -5079,15 +5067,15 @@
         <v>4</v>
       </c>
       <c r="F139" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>439</v>
+        <v>615</v>
       </c>
       <c r="B140" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C140">
         <v>1</v>
@@ -5099,55 +5087,55 @@
         <v>4</v>
       </c>
       <c r="F140" t="s">
-        <v>606</v>
+        <v>623</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>442</v>
+        <v>423</v>
       </c>
       <c r="B141" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C141">
         <v>1</v>
       </c>
       <c r="D141" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E141">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F141" t="s">
-        <v>609</v>
+        <v>590</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>619</v>
+        <v>422</v>
       </c>
       <c r="B142" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C142">
         <v>1</v>
       </c>
       <c r="D142" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E142">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F142" t="s">
-        <v>627</v>
+        <v>589</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="B143" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C143">
         <v>1</v>
@@ -5159,15 +5147,15 @@
         <v>1</v>
       </c>
       <c r="F143" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B144" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C144">
         <v>1</v>
@@ -5176,18 +5164,18 @@
         <v>8</v>
       </c>
       <c r="E144">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F144" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B145" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C145">
         <v>1</v>
@@ -5196,18 +5184,18 @@
         <v>8</v>
       </c>
       <c r="E145">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F145" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B146" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C146">
         <v>1</v>
@@ -5216,18 +5204,18 @@
         <v>8</v>
       </c>
       <c r="E146">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F146" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B147" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C147">
         <v>1</v>
@@ -5236,10 +5224,10 @@
         <v>8</v>
       </c>
       <c r="E147">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F147" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -5247,7 +5235,7 @@
         <v>431</v>
       </c>
       <c r="B148" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C148">
         <v>1</v>
@@ -5256,7 +5244,7 @@
         <v>8</v>
       </c>
       <c r="E148">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F148" t="s">
         <v>598</v>
@@ -5264,10 +5252,10 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B149" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C149">
         <v>1</v>
@@ -5276,18 +5264,18 @@
         <v>8</v>
       </c>
       <c r="E149">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F149" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
       <c r="B150" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C150">
         <v>1</v>
@@ -5299,55 +5287,55 @@
         <v>4</v>
       </c>
       <c r="F150" t="s">
-        <v>602</v>
+        <v>595</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="B151" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C151">
         <v>1</v>
       </c>
       <c r="D151" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E151">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F151" t="s">
-        <v>600</v>
+        <v>578</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>432</v>
+        <v>413</v>
       </c>
       <c r="B152" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C152">
         <v>1</v>
       </c>
       <c r="D152" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E152">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F152" t="s">
-        <v>599</v>
+        <v>580</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="B153" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C153">
         <v>1</v>
@@ -5356,18 +5344,18 @@
         <v>15</v>
       </c>
       <c r="E153">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F153" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>417</v>
+        <v>616</v>
       </c>
       <c r="B154" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C154">
         <v>1</v>
@@ -5379,7 +5367,7 @@
         <v>2</v>
       </c>
       <c r="F154" t="s">
-        <v>584</v>
+        <v>624</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -5387,7 +5375,7 @@
         <v>416</v>
       </c>
       <c r="B155" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C155">
         <v>1</v>
@@ -5396,7 +5384,7 @@
         <v>15</v>
       </c>
       <c r="E155">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F155" t="s">
         <v>583</v>
@@ -5404,10 +5392,10 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>620</v>
+        <v>415</v>
       </c>
       <c r="B156" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C156">
         <v>1</v>
@@ -5416,18 +5404,18 @@
         <v>15</v>
       </c>
       <c r="E156">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F156" t="s">
-        <v>628</v>
+        <v>582</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="B157" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C157">
         <v>1</v>
@@ -5439,15 +5427,15 @@
         <v>3</v>
       </c>
       <c r="F157" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B158" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C158">
         <v>1</v>
@@ -5456,18 +5444,18 @@
         <v>15</v>
       </c>
       <c r="E158">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F158" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B159" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C159">
         <v>1</v>
@@ -5476,18 +5464,18 @@
         <v>15</v>
       </c>
       <c r="E159">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F159" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="B160" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C160">
         <v>1</v>
@@ -5499,15 +5487,15 @@
         <v>4</v>
       </c>
       <c r="F160" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="B161" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C161">
         <v>1</v>
@@ -5519,55 +5507,55 @@
         <v>4</v>
       </c>
       <c r="F161" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>422</v>
+        <v>401</v>
       </c>
       <c r="B162" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C162">
         <v>1</v>
       </c>
       <c r="D162" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E162">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F162" t="s">
-        <v>589</v>
+        <v>568</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>421</v>
+        <v>400</v>
       </c>
       <c r="B163" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C163">
         <v>1</v>
       </c>
       <c r="D163" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E163">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F163" t="s">
-        <v>588</v>
+        <v>567</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="B164" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C164">
         <v>1</v>
@@ -5579,15 +5567,15 @@
         <v>1</v>
       </c>
       <c r="F164" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="B165" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C165">
         <v>1</v>
@@ -5599,15 +5587,15 @@
         <v>1</v>
       </c>
       <c r="F165" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B166" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C166">
         <v>1</v>
@@ -5616,18 +5604,18 @@
         <v>23</v>
       </c>
       <c r="E166">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F166" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B167" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C167">
         <v>1</v>
@@ -5636,18 +5624,18 @@
         <v>23</v>
       </c>
       <c r="E167">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F167" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="B168" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C168">
         <v>1</v>
@@ -5656,18 +5644,18 @@
         <v>23</v>
       </c>
       <c r="E168">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F168" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B169" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C169">
         <v>1</v>
@@ -5676,18 +5664,18 @@
         <v>23</v>
       </c>
       <c r="E169">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F169" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="B170" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C170">
         <v>1</v>
@@ -5699,15 +5687,15 @@
         <v>3</v>
       </c>
       <c r="F170" t="s">
-        <v>577</v>
+        <v>569</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B171" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C171">
         <v>1</v>
@@ -5716,18 +5704,18 @@
         <v>23</v>
       </c>
       <c r="E171">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F171" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B172" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C172">
         <v>1</v>
@@ -5736,18 +5724,18 @@
         <v>23</v>
       </c>
       <c r="E172">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F172" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="B173" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C173">
         <v>1</v>
@@ -5759,15 +5747,15 @@
         <v>4</v>
       </c>
       <c r="F173" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="B174" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C174">
         <v>1</v>
@@ -5779,55 +5767,55 @@
         <v>4</v>
       </c>
       <c r="F174" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>412</v>
+        <v>387</v>
       </c>
       <c r="B175" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C175">
         <v>1</v>
       </c>
       <c r="D175" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E175">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F175" t="s">
-        <v>579</v>
+        <v>554</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>411</v>
+        <v>386</v>
       </c>
       <c r="B176" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C176">
         <v>1</v>
       </c>
       <c r="D176" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E176">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F176" t="s">
-        <v>578</v>
+        <v>553</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B177" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C177">
         <v>1</v>
@@ -5836,18 +5824,18 @@
         <v>29</v>
       </c>
       <c r="E177">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F177" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B178" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C178">
         <v>1</v>
@@ -5856,18 +5844,18 @@
         <v>29</v>
       </c>
       <c r="E178">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F178" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="B179" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C179">
         <v>1</v>
@@ -5879,15 +5867,15 @@
         <v>2</v>
       </c>
       <c r="F179" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B180" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C180">
         <v>1</v>
@@ -5896,18 +5884,18 @@
         <v>29</v>
       </c>
       <c r="E180">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F180" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B181" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C181">
         <v>1</v>
@@ -5916,18 +5904,18 @@
         <v>29</v>
       </c>
       <c r="E181">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F181" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="B182" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C182">
         <v>1</v>
@@ -5939,15 +5927,15 @@
         <v>3</v>
       </c>
       <c r="F182" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="B183" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C183">
         <v>1</v>
@@ -5959,15 +5947,15 @@
         <v>3</v>
       </c>
       <c r="F183" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B184" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C184">
         <v>1</v>
@@ -5976,18 +5964,18 @@
         <v>29</v>
       </c>
       <c r="E184">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F184" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B185" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C185">
         <v>1</v>
@@ -5996,18 +5984,18 @@
         <v>29</v>
       </c>
       <c r="E185">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F185" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="B186" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C186">
         <v>1</v>
@@ -6019,267 +6007,267 @@
         <v>4</v>
       </c>
       <c r="F186" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>400</v>
+        <v>378</v>
       </c>
       <c r="B187" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C187">
         <v>1</v>
       </c>
       <c r="D187" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E187">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F187" t="s">
-        <v>567</v>
+        <v>545</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>399</v>
+        <v>377</v>
       </c>
       <c r="B188" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C188">
         <v>1</v>
       </c>
       <c r="D188" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E188">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F188" t="s">
-        <v>566</v>
+        <v>544</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="B189" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C189">
         <v>1</v>
       </c>
       <c r="D189" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E189">
         <v>1</v>
       </c>
       <c r="F189" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B190" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C190">
         <v>1</v>
       </c>
       <c r="D190" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E190">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F190" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B191" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C191">
         <v>1</v>
       </c>
       <c r="D191" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E191">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F191" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B192" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C192">
         <v>1</v>
       </c>
       <c r="D192" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E192">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F192" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B193" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C193">
         <v>1</v>
       </c>
       <c r="D193" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E193">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F193" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B194" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C194">
         <v>1</v>
       </c>
       <c r="D194" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E194">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F194" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B195" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C195">
         <v>1</v>
       </c>
       <c r="D195" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E195">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F195" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="B196" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C196">
         <v>1</v>
       </c>
       <c r="D196" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E196">
         <v>4</v>
       </c>
       <c r="F196" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>388</v>
+        <v>369</v>
       </c>
       <c r="B197" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C197">
         <v>1</v>
       </c>
       <c r="D197" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E197">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F197" t="s">
-        <v>555</v>
+        <v>536</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>387</v>
+        <v>368</v>
       </c>
       <c r="B198" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C198">
         <v>1</v>
       </c>
       <c r="D198" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E198">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F198" t="s">
-        <v>554</v>
+        <v>535</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
       <c r="B199" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C199">
         <v>1</v>
       </c>
       <c r="D199" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E199">
         <v>1</v>
       </c>
       <c r="F199" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
@@ -6287,16 +6275,16 @@
         <v>372</v>
       </c>
       <c r="B200" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C200">
         <v>1</v>
       </c>
       <c r="D200" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E200">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F200" t="s">
         <v>539</v>
@@ -6307,16 +6295,16 @@
         <v>371</v>
       </c>
       <c r="B201" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C201">
         <v>1</v>
       </c>
       <c r="D201" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E201">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F201" t="s">
         <v>538</v>
@@ -6324,22 +6312,22 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="B202" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C202">
         <v>1</v>
       </c>
       <c r="D202" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E202">
         <v>2</v>
       </c>
       <c r="F202" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -6347,16 +6335,16 @@
         <v>375</v>
       </c>
       <c r="B203" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C203">
         <v>1</v>
       </c>
       <c r="D203" t="s">
-        <v>42</v>
-      </c>
-      <c r="E203">
-        <v>2</v>
+        <v>40</v>
+      </c>
+      <c r="E203" t="s">
+        <v>631</v>
       </c>
       <c r="F203" t="s">
         <v>542</v>
@@ -6367,16 +6355,16 @@
         <v>374</v>
       </c>
       <c r="B204" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C204">
         <v>1</v>
       </c>
       <c r="D204" t="s">
-        <v>42</v>
-      </c>
-      <c r="E204">
-        <v>2</v>
+        <v>40</v>
+      </c>
+      <c r="E204" t="s">
+        <v>631</v>
       </c>
       <c r="F204" t="s">
         <v>541</v>
@@ -6384,82 +6372,82 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
       <c r="B205" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C205">
         <v>1</v>
       </c>
       <c r="D205" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E205" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="F205" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>378</v>
+        <v>357</v>
       </c>
       <c r="B206" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C206">
         <v>1</v>
       </c>
       <c r="D206" t="s">
-        <v>42</v>
-      </c>
-      <c r="E206" t="s">
-        <v>635</v>
+        <v>46</v>
+      </c>
+      <c r="E206">
+        <v>1</v>
       </c>
       <c r="F206" t="s">
-        <v>545</v>
+        <v>524</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>377</v>
+        <v>356</v>
       </c>
       <c r="B207" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C207">
         <v>1</v>
       </c>
       <c r="D207" t="s">
-        <v>42</v>
-      </c>
-      <c r="E207" t="s">
-        <v>635</v>
+        <v>46</v>
+      </c>
+      <c r="E207">
+        <v>1</v>
       </c>
       <c r="F207" t="s">
-        <v>544</v>
+        <v>523</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="B208" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C208">
         <v>1</v>
       </c>
       <c r="D208" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E208">
         <v>1</v>
       </c>
       <c r="F208" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
@@ -6467,16 +6455,16 @@
         <v>360</v>
       </c>
       <c r="B209" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C209">
         <v>1</v>
       </c>
       <c r="D209" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E209">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F209" t="s">
         <v>527</v>
@@ -6487,16 +6475,16 @@
         <v>359</v>
       </c>
       <c r="B210" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C210">
         <v>1</v>
       </c>
       <c r="D210" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E210">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F210" t="s">
         <v>526</v>
@@ -6504,22 +6492,22 @@
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="B211" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C211">
         <v>1</v>
       </c>
       <c r="D211" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E211">
         <v>2</v>
       </c>
       <c r="F211" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
@@ -6527,16 +6515,16 @@
         <v>363</v>
       </c>
       <c r="B212" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C212">
         <v>1</v>
       </c>
       <c r="D212" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E212">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F212" t="s">
         <v>530</v>
@@ -6547,16 +6535,16 @@
         <v>362</v>
       </c>
       <c r="B213" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C213">
         <v>1</v>
       </c>
       <c r="D213" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E213">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F213" t="s">
         <v>529</v>
@@ -6564,22 +6552,22 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="B214" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C214">
         <v>1</v>
       </c>
       <c r="D214" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E214">
         <v>3</v>
       </c>
       <c r="F214" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
@@ -6587,16 +6575,16 @@
         <v>366</v>
       </c>
       <c r="B215" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C215">
         <v>1</v>
       </c>
       <c r="D215" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E215">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F215" t="s">
         <v>533</v>
@@ -6607,16 +6595,16 @@
         <v>365</v>
       </c>
       <c r="B216" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C216">
         <v>1</v>
       </c>
       <c r="D216" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E216">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F216" t="s">
         <v>532</v>
@@ -6624,942 +6612,942 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="B217" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C217">
         <v>1</v>
       </c>
       <c r="D217" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E217">
         <v>4</v>
       </c>
       <c r="F217" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>369</v>
+        <v>346</v>
       </c>
       <c r="B218" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C218">
         <v>1</v>
       </c>
       <c r="D218" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E218">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F218" t="s">
-        <v>536</v>
+        <v>513</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>368</v>
+        <v>345</v>
       </c>
       <c r="B219" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C219">
         <v>1</v>
       </c>
       <c r="D219" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E219">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F219" t="s">
-        <v>535</v>
+        <v>512</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="B220" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C220">
         <v>1</v>
       </c>
       <c r="D220" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E220">
         <v>1</v>
       </c>
       <c r="F220" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="B221" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C221">
         <v>1</v>
       </c>
       <c r="D221" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E221">
         <v>1</v>
       </c>
       <c r="F221" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B222" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C222">
         <v>1</v>
       </c>
       <c r="D222" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E222">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F222" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B223" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C223">
         <v>1</v>
       </c>
       <c r="D223" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E223">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F223" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="B224" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C224">
         <v>1</v>
       </c>
       <c r="D224" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E224">
         <v>2</v>
       </c>
       <c r="F224" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B225" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C225">
         <v>1</v>
       </c>
       <c r="D225" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E225">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F225" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B226" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C226">
         <v>1</v>
       </c>
       <c r="D226" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E226">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F226" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B227" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C227">
         <v>1</v>
       </c>
       <c r="D227" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E227">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F227" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B228" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C228">
         <v>1</v>
       </c>
       <c r="D228" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E228">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F228" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="B229" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C229">
         <v>1</v>
       </c>
       <c r="D229" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E229">
         <v>4</v>
       </c>
       <c r="F229" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>357</v>
+        <v>330</v>
       </c>
       <c r="B230" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C230">
         <v>1</v>
       </c>
       <c r="D230" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E230">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F230" t="s">
-        <v>524</v>
+        <v>497</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>356</v>
+        <v>329</v>
       </c>
       <c r="B231" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C231">
         <v>1</v>
       </c>
       <c r="D231" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E231">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F231" t="s">
-        <v>523</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B232" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C232">
         <v>1</v>
       </c>
       <c r="D232" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E232">
         <v>1</v>
       </c>
       <c r="F232" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="B233" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C233">
         <v>1</v>
       </c>
       <c r="D233" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E233">
         <v>1</v>
       </c>
       <c r="F233" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B234" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C234">
         <v>1</v>
       </c>
       <c r="D234" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E234">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F234" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B235" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C235">
         <v>1</v>
       </c>
       <c r="D235" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E235">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F235" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="B236" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C236">
         <v>1</v>
       </c>
       <c r="D236" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E236">
         <v>2</v>
       </c>
       <c r="F236" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
       <c r="B237" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C237">
         <v>1</v>
       </c>
       <c r="D237" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E237">
         <v>2</v>
       </c>
       <c r="F237" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="B238" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C238">
         <v>1</v>
       </c>
       <c r="D238" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E238">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F238" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B239" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C239">
         <v>1</v>
       </c>
       <c r="D239" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E239">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F239" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="B240" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C240">
         <v>1</v>
       </c>
       <c r="D240" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E240">
         <v>3</v>
       </c>
       <c r="F240" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="B241" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C241">
         <v>1</v>
       </c>
       <c r="D241" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E241">
         <v>3</v>
       </c>
       <c r="F241" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="B242" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C242">
         <v>1</v>
       </c>
       <c r="D242" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E242">
         <v>3</v>
       </c>
       <c r="F242" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="B243" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C243">
         <v>1</v>
       </c>
       <c r="D243" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E243">
         <v>3</v>
       </c>
       <c r="F243" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B244" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C244">
         <v>1</v>
       </c>
       <c r="D244" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E244">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F244" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B245" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C245">
         <v>1</v>
       </c>
       <c r="D245" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E245">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F245" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>346</v>
+        <v>314</v>
       </c>
       <c r="B246" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C246">
         <v>1</v>
       </c>
       <c r="D246" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E246">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F246" t="s">
-        <v>513</v>
+        <v>481</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>345</v>
+        <v>313</v>
       </c>
       <c r="B247" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C247">
         <v>1</v>
       </c>
       <c r="D247" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E247">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F247" t="s">
-        <v>512</v>
+        <v>480</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B248" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C248">
         <v>1</v>
       </c>
       <c r="D248" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E248">
         <v>1</v>
       </c>
       <c r="F248" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B249" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C249">
         <v>1</v>
       </c>
       <c r="D249" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E249">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F249" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B250" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C250">
         <v>1</v>
       </c>
       <c r="D250" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E250">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F250" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="B251" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C251">
         <v>1</v>
       </c>
       <c r="D251" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E251">
         <v>2</v>
       </c>
       <c r="F251" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="B252" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C252">
         <v>1</v>
       </c>
       <c r="D252" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E252">
         <v>2</v>
       </c>
       <c r="F252" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B253" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C253">
         <v>1</v>
       </c>
       <c r="D253" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E253">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F253" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B254" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C254">
         <v>1</v>
       </c>
       <c r="D254" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E254">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F254" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="B255" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C255">
         <v>1</v>
       </c>
       <c r="D255" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E255">
         <v>3</v>
       </c>
       <c r="F255" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="B256" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C256">
         <v>1</v>
       </c>
       <c r="D256" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E256">
         <v>3</v>
       </c>
       <c r="F256" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B257" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C257">
         <v>1</v>
       </c>
       <c r="D257" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E257">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F257" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B258" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C258">
         <v>1</v>
       </c>
       <c r="D258" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E258">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F258" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="B259" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C259">
         <v>1</v>
       </c>
       <c r="D259" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E259">
         <v>4</v>
       </c>
       <c r="F259" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="B260" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C260">
         <v>1</v>
       </c>
       <c r="D260" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E260">
         <v>4</v>
       </c>
       <c r="F260" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>328</v>
+        <v>304</v>
       </c>
       <c r="B261" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C261">
         <v>1</v>
       </c>
       <c r="D261" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E261">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F261" t="s">
-        <v>495</v>
+        <v>471</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>327</v>
+        <v>303</v>
       </c>
       <c r="B262" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C262">
         <v>1</v>
       </c>
       <c r="D262" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E262">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F262" t="s">
-        <v>494</v>
+        <v>470</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="B263" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C263">
         <v>1</v>
       </c>
       <c r="D263" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E263">
         <v>1</v>
       </c>
       <c r="F263" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
@@ -7567,16 +7555,16 @@
         <v>307</v>
       </c>
       <c r="B264" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C264">
         <v>1</v>
       </c>
       <c r="D264" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E264">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F264" t="s">
         <v>474</v>
@@ -7587,16 +7575,16 @@
         <v>306</v>
       </c>
       <c r="B265" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C265">
         <v>1</v>
       </c>
       <c r="D265" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E265">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F265" t="s">
         <v>473</v>
@@ -7604,42 +7592,42 @@
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="B266" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C266">
         <v>1</v>
       </c>
       <c r="D266" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E266">
         <v>2</v>
       </c>
       <c r="F266" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>310</v>
+        <v>622</v>
       </c>
       <c r="B267" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C267">
         <v>1</v>
       </c>
       <c r="D267" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E267">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F267" t="s">
-        <v>477</v>
+        <v>630</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
@@ -7647,16 +7635,16 @@
         <v>309</v>
       </c>
       <c r="B268" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C268">
         <v>1</v>
       </c>
       <c r="D268" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E268">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F268" t="s">
         <v>476</v>
@@ -7664,70 +7652,70 @@
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>626</v>
+        <v>308</v>
       </c>
       <c r="B269" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C269">
         <v>1</v>
       </c>
       <c r="D269" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E269">
         <v>3</v>
       </c>
       <c r="F269" t="s">
-        <v>634</v>
+        <v>475</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B270" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C270">
         <v>1</v>
       </c>
       <c r="D270" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E270">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F270" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B271" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C271">
         <v>1</v>
       </c>
       <c r="D271" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E271">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F271" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>315</v>
+        <v>296</v>
       </c>
       <c r="B272" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C272">
         <v>1</v>
@@ -7736,18 +7724,18 @@
         <v>67</v>
       </c>
       <c r="E272">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F272" t="s">
-        <v>482</v>
+        <v>463</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>314</v>
+        <v>90</v>
       </c>
       <c r="B273" t="s">
-        <v>262</v>
+        <v>90</v>
       </c>
       <c r="C273">
         <v>1</v>
@@ -7756,507 +7744,507 @@
         <v>67</v>
       </c>
       <c r="E273">
-        <v>4</v>
-      </c>
-      <c r="F273" t="s">
-        <v>481</v>
+        <v>2</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B274" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C274">
         <v>1</v>
       </c>
       <c r="D274" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E274">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F274" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>92</v>
+        <v>298</v>
       </c>
       <c r="B275" t="s">
-        <v>92</v>
+        <v>258</v>
       </c>
       <c r="C275">
         <v>1</v>
       </c>
       <c r="D275" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E275">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="F275" t="s">
+        <v>465</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="B276" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C276">
         <v>1</v>
       </c>
       <c r="D276" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E276">
         <v>3</v>
       </c>
       <c r="F276" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>302</v>
+        <v>441</v>
       </c>
       <c r="B277" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C277">
         <v>1</v>
       </c>
       <c r="D277" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E277">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F277" t="s">
-        <v>469</v>
+        <v>608</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>301</v>
+        <v>609</v>
       </c>
       <c r="B278" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C278">
         <v>1</v>
       </c>
       <c r="D278" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E278">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F278" t="s">
-        <v>468</v>
+        <v>610</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>445</v>
+        <v>301</v>
       </c>
       <c r="B279" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C279">
         <v>1</v>
       </c>
       <c r="D279" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E279">
         <v>4</v>
       </c>
       <c r="F279" t="s">
-        <v>612</v>
+        <v>468</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>613</v>
+        <v>300</v>
       </c>
       <c r="B280" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C280">
         <v>1</v>
       </c>
       <c r="D280" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E280">
         <v>4</v>
       </c>
       <c r="F280" t="s">
-        <v>614</v>
+        <v>467</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="B281" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C281">
         <v>1</v>
       </c>
       <c r="D281" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E281">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F281" t="s">
-        <v>472</v>
+        <v>457</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="B282" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C282">
         <v>1</v>
       </c>
       <c r="D282" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E282">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F282" t="s">
-        <v>471</v>
+        <v>456</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="B283" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C283">
         <v>1</v>
       </c>
       <c r="D283" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E283">
         <v>1</v>
       </c>
       <c r="F283" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B284" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C284">
         <v>1</v>
       </c>
       <c r="D284" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E284">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F284" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B285" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C285">
         <v>1</v>
       </c>
       <c r="D285" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E285">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F285" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>296</v>
+        <v>619</v>
       </c>
       <c r="B286" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C286">
         <v>1</v>
       </c>
       <c r="D286" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E286">
         <v>2</v>
       </c>
       <c r="F286" t="s">
-        <v>463</v>
+        <v>627</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>295</v>
+        <v>618</v>
       </c>
       <c r="B287" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C287">
         <v>1</v>
       </c>
       <c r="D287" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E287">
         <v>2</v>
       </c>
       <c r="F287" t="s">
-        <v>462</v>
+        <v>626</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>623</v>
+        <v>294</v>
       </c>
       <c r="B288" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C288">
         <v>1</v>
       </c>
       <c r="D288" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E288">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F288" t="s">
-        <v>631</v>
+        <v>461</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>622</v>
+        <v>293</v>
       </c>
       <c r="B289" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C289">
         <v>1</v>
       </c>
       <c r="D289" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E289">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F289" t="s">
-        <v>630</v>
+        <v>460</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>298</v>
+        <v>620</v>
       </c>
       <c r="B290" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C290">
         <v>1</v>
       </c>
       <c r="D290" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E290">
         <v>3</v>
       </c>
       <c r="F290" t="s">
-        <v>465</v>
+        <v>628</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B291" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C291">
         <v>1</v>
       </c>
       <c r="D291" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E291">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F291" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>624</v>
+        <v>287</v>
       </c>
       <c r="B292" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C292">
         <v>1</v>
       </c>
       <c r="D292" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E292">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F292" t="s">
-        <v>632</v>
+        <v>454</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>299</v>
+        <v>280</v>
       </c>
       <c r="B293" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C293">
         <v>1</v>
       </c>
       <c r="D293" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E293">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F293" t="s">
-        <v>466</v>
+        <v>447</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>291</v>
+        <v>617</v>
       </c>
       <c r="B294" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C294">
         <v>1</v>
       </c>
       <c r="D294" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E294">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F294" t="s">
-        <v>458</v>
+        <v>625</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="B295" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C295">
         <v>1</v>
       </c>
       <c r="D295" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E295">
         <v>1</v>
       </c>
       <c r="F295" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>621</v>
+        <v>283</v>
       </c>
       <c r="B296" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C296">
         <v>1</v>
       </c>
       <c r="D296" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E296">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F296" t="s">
-        <v>629</v>
+        <v>450</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B297" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C297">
         <v>1</v>
       </c>
       <c r="D297" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E297">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F297" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="B298" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C298">
         <v>1</v>
       </c>
       <c r="D298" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E298">
         <v>2</v>
       </c>
       <c r="F298" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
@@ -8264,16 +8252,16 @@
         <v>286</v>
       </c>
       <c r="B299" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C299">
         <v>1</v>
       </c>
       <c r="D299" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E299">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F299" t="s">
         <v>453</v>
@@ -8284,16 +8272,16 @@
         <v>285</v>
       </c>
       <c r="B300" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C300">
         <v>1</v>
       </c>
       <c r="D300" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E300">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F300" t="s">
         <v>452</v>
@@ -8301,99 +8289,99 @@
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="B301" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C301">
         <v>1</v>
       </c>
       <c r="D301" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E301">
         <v>3</v>
       </c>
       <c r="F301" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>289</v>
+        <v>90</v>
       </c>
       <c r="B302" t="s">
-        <v>262</v>
+        <v>90</v>
       </c>
       <c r="C302">
         <v>1</v>
       </c>
       <c r="D302" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E302">
-        <v>3</v>
-      </c>
-      <c r="F302" t="s">
-        <v>456</v>
+        <v>4</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>288</v>
+        <v>262</v>
       </c>
       <c r="B303" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C303">
         <v>1</v>
       </c>
       <c r="D303" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E303">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F303" t="s">
-        <v>455</v>
+        <v>269</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>92</v>
+        <v>261</v>
       </c>
       <c r="B304" t="s">
-        <v>92</v>
+        <v>258</v>
       </c>
       <c r="C304">
         <v>1</v>
       </c>
       <c r="D304" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E304">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="F304" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="B305" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C305">
         <v>1</v>
       </c>
       <c r="D305" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E305">
         <v>1</v>
       </c>
       <c r="F305" t="s">
-        <v>273</v>
+        <v>260</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
@@ -8401,16 +8389,16 @@
         <v>265</v>
       </c>
       <c r="B306" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C306">
         <v>1</v>
       </c>
       <c r="D306" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E306">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F306" t="s">
         <v>272</v>
@@ -8418,230 +8406,190 @@
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B307" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C307">
         <v>1</v>
       </c>
       <c r="D307" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E307">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F307" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="B308" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C308">
         <v>1</v>
       </c>
       <c r="D308" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E308">
         <v>2</v>
       </c>
       <c r="F308" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="B309" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C309">
         <v>1</v>
       </c>
       <c r="D309" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E309">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F309" t="s">
-        <v>275</v>
+        <v>442</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>267</v>
+        <v>621</v>
       </c>
       <c r="B310" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C310">
         <v>1</v>
       </c>
       <c r="D310" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E310">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F310" t="s">
-        <v>274</v>
+        <v>629</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="B311" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C311">
         <v>1</v>
       </c>
       <c r="D311" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E311">
         <v>3</v>
       </c>
       <c r="F311" t="s">
-        <v>446</v>
+        <v>274</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>625</v>
+        <v>266</v>
       </c>
       <c r="B312" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C312">
         <v>1</v>
       </c>
       <c r="D312" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E312">
         <v>3</v>
       </c>
       <c r="F312" t="s">
-        <v>633</v>
+        <v>273</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="B313" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C313">
         <v>1</v>
       </c>
       <c r="D313" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E313">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F313" t="s">
-        <v>278</v>
+        <v>445</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="B314" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C314">
         <v>1</v>
       </c>
       <c r="D314" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E314">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F314" t="s">
-        <v>277</v>
+        <v>444</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B315" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="C315">
         <v>1</v>
       </c>
       <c r="D315" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E315">
         <v>4</v>
       </c>
       <c r="F315" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A316" t="s">
-        <v>281</v>
-      </c>
-      <c r="B316" t="s">
-        <v>262</v>
-      </c>
-      <c r="C316">
-        <v>1</v>
-      </c>
-      <c r="D316" t="s">
-        <v>86</v>
-      </c>
-      <c r="E316">
-        <v>4</v>
-      </c>
-      <c r="F316" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A317" t="s">
-        <v>280</v>
-      </c>
-      <c r="B317" t="s">
-        <v>262</v>
-      </c>
-      <c r="C317">
-        <v>1</v>
-      </c>
-      <c r="D317" t="s">
-        <v>86</v>
-      </c>
-      <c r="E317">
-        <v>4</v>
-      </c>
-      <c r="F317" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F317">
-    <sortCondition descending="1" ref="C2:C317"/>
-    <sortCondition ref="D2:D317"/>
-    <sortCondition ref="E2:E317"/>
-    <sortCondition descending="1" ref="A2:A317"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F315">
+    <sortCondition descending="1" ref="C2:C315"/>
+    <sortCondition ref="D2:D315"/>
+    <sortCondition ref="E2:E315"/>
+    <sortCondition descending="1" ref="A2:A315"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/EOAT_data.xlsx
+++ b/data/EOAT_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\procesos.CAZEL\Desktop\Becario Procesos\EOAT Project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA9F9CA6-2FF6-427F-AC61-CC3B5B5C5EC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68814C4B-1E6A-4B1E-AF12-0978AE00A2AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{440E3869-3C3F-4E8C-A8BD-ADEB8E2EA552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1251" uniqueCount="636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1248" uniqueCount="636">
   <si>
     <t>I-1937</t>
   </si>
@@ -2321,7 +2321,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B6791C-A8A7-4753-A504-FAA9E3EE8745}">
-  <dimension ref="A1:F315"/>
+  <dimension ref="A1:F314"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -4582,13 +4582,13 @@
         <v>258</v>
       </c>
       <c r="C114">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D114" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="E114">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F114" t="s">
         <v>245</v>
@@ -8309,24 +8309,27 @@
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>90</v>
+        <v>262</v>
       </c>
       <c r="B302" t="s">
-        <v>90</v>
+        <v>258</v>
       </c>
       <c r="C302">
         <v>1</v>
       </c>
       <c r="D302" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="E302">
-        <v>4</v>
+        <v>1</v>
+      </c>
+      <c r="F302" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B303" t="s">
         <v>258</v>
@@ -8341,12 +8344,12 @@
         <v>1</v>
       </c>
       <c r="F303" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B304" t="s">
         <v>258</v>
@@ -8361,12 +8364,12 @@
         <v>1</v>
       </c>
       <c r="F304" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="B305" t="s">
         <v>258</v>
@@ -8378,15 +8381,15 @@
         <v>84</v>
       </c>
       <c r="E305">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F305" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B306" t="s">
         <v>258</v>
@@ -8401,12 +8404,12 @@
         <v>2</v>
       </c>
       <c r="F306" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B307" t="s">
         <v>258</v>
@@ -8421,12 +8424,12 @@
         <v>2</v>
       </c>
       <c r="F307" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="B308" t="s">
         <v>258</v>
@@ -8438,15 +8441,15 @@
         <v>84</v>
       </c>
       <c r="E308">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F308" t="s">
-        <v>270</v>
+        <v>442</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>275</v>
+        <v>621</v>
       </c>
       <c r="B309" t="s">
         <v>258</v>
@@ -8461,12 +8464,12 @@
         <v>3</v>
       </c>
       <c r="F309" t="s">
-        <v>442</v>
+        <v>629</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>621</v>
+        <v>267</v>
       </c>
       <c r="B310" t="s">
         <v>258</v>
@@ -8481,12 +8484,12 @@
         <v>3</v>
       </c>
       <c r="F310" t="s">
-        <v>629</v>
+        <v>274</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B311" t="s">
         <v>258</v>
@@ -8501,12 +8504,12 @@
         <v>3</v>
       </c>
       <c r="F311" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="B312" t="s">
         <v>258</v>
@@ -8518,15 +8521,15 @@
         <v>84</v>
       </c>
       <c r="E312">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F312" t="s">
-        <v>273</v>
+        <v>445</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B313" t="s">
         <v>258</v>
@@ -8541,12 +8544,12 @@
         <v>4</v>
       </c>
       <c r="F313" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B314" t="s">
         <v>258</v>
@@ -8561,35 +8564,15 @@
         <v>4</v>
       </c>
       <c r="F314" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A315" t="s">
-        <v>276</v>
-      </c>
-      <c r="B315" t="s">
-        <v>258</v>
-      </c>
-      <c r="C315">
-        <v>1</v>
-      </c>
-      <c r="D315" t="s">
-        <v>84</v>
-      </c>
-      <c r="E315">
-        <v>4</v>
-      </c>
-      <c r="F315" t="s">
         <v>443</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F315">
-    <sortCondition descending="1" ref="C2:C315"/>
-    <sortCondition ref="D2:D315"/>
-    <sortCondition ref="E2:E315"/>
-    <sortCondition descending="1" ref="A2:A315"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F314">
+    <sortCondition descending="1" ref="C2:C314"/>
+    <sortCondition ref="D2:D314"/>
+    <sortCondition ref="E2:E314"/>
+    <sortCondition descending="1" ref="A2:A314"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/EOAT_data.xlsx
+++ b/data/EOAT_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\procesos.CAZEL\Desktop\Becario Procesos\EOAT Project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68814C4B-1E6A-4B1E-AF12-0978AE00A2AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A524E845-612F-43FA-9915-963291DDE71C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{440E3869-3C3F-4E8C-A8BD-ADEB8E2EA552}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1248" uniqueCount="636">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1252" uniqueCount="638">
   <si>
     <t>I-1937</t>
   </si>
@@ -1944,6 +1944,12 @@
   </si>
   <si>
     <t>I-1908.jpeg</t>
+  </si>
+  <si>
+    <t>I-1945.jpeg</t>
+  </si>
+  <si>
+    <t>I-1945</t>
   </si>
 </sst>
 </file>
@@ -2321,7 +2327,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B6791C-A8A7-4753-A504-FAA9E3EE8745}">
-  <dimension ref="A1:F314"/>
+  <dimension ref="A1:F315"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -3956,7 +3962,7 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>72</v>
+        <v>637</v>
       </c>
       <c r="B83" t="s">
         <v>258</v>
@@ -3971,12 +3977,12 @@
         <v>1</v>
       </c>
       <c r="F83" t="s">
-        <v>199</v>
+        <v>636</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B84" t="s">
         <v>258</v>
@@ -3988,15 +3994,15 @@
         <v>73</v>
       </c>
       <c r="E84">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F84" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B85" t="s">
         <v>258</v>
@@ -4008,15 +4014,15 @@
         <v>73</v>
       </c>
       <c r="E85">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F85" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B86" t="s">
         <v>258</v>
@@ -4025,18 +4031,18 @@
         <v>2</v>
       </c>
       <c r="D86" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E86">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F86" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B87" t="s">
         <v>258</v>
@@ -4051,12 +4057,12 @@
         <v>1</v>
       </c>
       <c r="F87" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B88" t="s">
         <v>258</v>
@@ -4068,15 +4074,15 @@
         <v>77</v>
       </c>
       <c r="E88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F88" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B89" t="s">
         <v>258</v>
@@ -4091,12 +4097,12 @@
         <v>2</v>
       </c>
       <c r="F89" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B90" t="s">
         <v>258</v>
@@ -4108,15 +4114,15 @@
         <v>77</v>
       </c>
       <c r="E90">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F90" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B91" t="s">
         <v>258</v>
@@ -4131,12 +4137,12 @@
         <v>3</v>
       </c>
       <c r="F91" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B92" t="s">
         <v>258</v>
@@ -4145,18 +4151,18 @@
         <v>2</v>
       </c>
       <c r="D92" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="E92">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F92" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B93" t="s">
         <v>258</v>
@@ -4171,12 +4177,12 @@
         <v>1</v>
       </c>
       <c r="F93" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B94" t="s">
         <v>258</v>
@@ -4188,15 +4194,15 @@
         <v>84</v>
       </c>
       <c r="E94">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F94" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B95" t="s">
         <v>258</v>
@@ -4211,12 +4217,12 @@
         <v>2</v>
       </c>
       <c r="F95" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B96" t="s">
         <v>258</v>
@@ -4228,15 +4234,15 @@
         <v>84</v>
       </c>
       <c r="E96">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F96" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B97" t="s">
         <v>258</v>
@@ -4251,12 +4257,12 @@
         <v>3</v>
       </c>
       <c r="F97" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="B98" t="s">
         <v>258</v>
@@ -4265,18 +4271,18 @@
         <v>2</v>
       </c>
       <c r="D98" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="E98">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F98" t="s">
-        <v>229</v>
+        <v>213</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B99" t="s">
         <v>258</v>
@@ -4288,15 +4294,15 @@
         <v>111</v>
       </c>
       <c r="E99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F99" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B100" t="s">
         <v>258</v>
@@ -4308,15 +4314,15 @@
         <v>111</v>
       </c>
       <c r="E100">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F100" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B101" t="s">
         <v>258</v>
@@ -4331,12 +4337,12 @@
         <v>3</v>
       </c>
       <c r="F101" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B102" t="s">
         <v>258</v>
@@ -4345,18 +4351,18 @@
         <v>2</v>
       </c>
       <c r="D102" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="E102">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F102" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B103" t="s">
         <v>258</v>
@@ -4368,15 +4374,15 @@
         <v>116</v>
       </c>
       <c r="E103">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F103" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B104" t="s">
         <v>258</v>
@@ -4391,12 +4397,12 @@
         <v>2</v>
       </c>
       <c r="F104" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B105" t="s">
         <v>258</v>
@@ -4408,15 +4414,15 @@
         <v>116</v>
       </c>
       <c r="E105">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F105" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B106" t="s">
         <v>258</v>
@@ -4431,12 +4437,12 @@
         <v>3</v>
       </c>
       <c r="F106" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B107" t="s">
         <v>258</v>
@@ -4445,18 +4451,18 @@
         <v>2</v>
       </c>
       <c r="D107" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="E107">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F107" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B108" t="s">
         <v>258</v>
@@ -4468,15 +4474,15 @@
         <v>122</v>
       </c>
       <c r="E108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F108" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B109" t="s">
         <v>258</v>
@@ -4488,15 +4494,15 @@
         <v>122</v>
       </c>
       <c r="E109">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F109" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B110" t="s">
         <v>258</v>
@@ -4511,12 +4517,12 @@
         <v>3</v>
       </c>
       <c r="F110" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B111" t="s">
         <v>258</v>
@@ -4525,18 +4531,18 @@
         <v>2</v>
       </c>
       <c r="D111" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E111">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F111" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B112" t="s">
         <v>258</v>
@@ -4548,15 +4554,15 @@
         <v>127</v>
       </c>
       <c r="E112">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F112" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B113" t="s">
         <v>258</v>
@@ -4568,30 +4574,30 @@
         <v>127</v>
       </c>
       <c r="E113">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F113" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B114" t="s">
         <v>258</v>
       </c>
       <c r="C114">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D114" t="s">
-        <v>77</v>
+        <v>127</v>
       </c>
       <c r="E114">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F114" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
@@ -8309,7 +8315,7 @@
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>262</v>
+        <v>130</v>
       </c>
       <c r="B302" t="s">
         <v>258</v>
@@ -8318,18 +8324,18 @@
         <v>1</v>
       </c>
       <c r="D302" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="E302">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F302" t="s">
-        <v>269</v>
+        <v>245</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B303" t="s">
         <v>258</v>
@@ -8344,12 +8350,12 @@
         <v>1</v>
       </c>
       <c r="F303" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B304" t="s">
         <v>258</v>
@@ -8364,12 +8370,12 @@
         <v>1</v>
       </c>
       <c r="F304" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="B305" t="s">
         <v>258</v>
@@ -8381,15 +8387,15 @@
         <v>84</v>
       </c>
       <c r="E305">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F305" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B306" t="s">
         <v>258</v>
@@ -8404,12 +8410,12 @@
         <v>2</v>
       </c>
       <c r="F306" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B307" t="s">
         <v>258</v>
@@ -8424,12 +8430,12 @@
         <v>2</v>
       </c>
       <c r="F307" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="B308" t="s">
         <v>258</v>
@@ -8441,15 +8447,15 @@
         <v>84</v>
       </c>
       <c r="E308">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F308" t="s">
-        <v>442</v>
+        <v>270</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>621</v>
+        <v>275</v>
       </c>
       <c r="B309" t="s">
         <v>258</v>
@@ -8464,12 +8470,12 @@
         <v>3</v>
       </c>
       <c r="F309" t="s">
-        <v>629</v>
+        <v>442</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>267</v>
+        <v>621</v>
       </c>
       <c r="B310" t="s">
         <v>258</v>
@@ -8484,12 +8490,12 @@
         <v>3</v>
       </c>
       <c r="F310" t="s">
-        <v>274</v>
+        <v>629</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B311" t="s">
         <v>258</v>
@@ -8504,12 +8510,12 @@
         <v>3</v>
       </c>
       <c r="F311" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
       <c r="B312" t="s">
         <v>258</v>
@@ -8521,15 +8527,15 @@
         <v>84</v>
       </c>
       <c r="E312">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F312" t="s">
-        <v>445</v>
+        <v>273</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B313" t="s">
         <v>258</v>
@@ -8544,12 +8550,12 @@
         <v>4</v>
       </c>
       <c r="F313" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B314" t="s">
         <v>258</v>
@@ -8564,15 +8570,35 @@
         <v>4</v>
       </c>
       <c r="F314" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>276</v>
+      </c>
+      <c r="B315" t="s">
+        <v>258</v>
+      </c>
+      <c r="C315">
+        <v>1</v>
+      </c>
+      <c r="D315" t="s">
+        <v>84</v>
+      </c>
+      <c r="E315">
+        <v>4</v>
+      </c>
+      <c r="F315" t="s">
         <v>443</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F314">
-    <sortCondition descending="1" ref="C2:C314"/>
-    <sortCondition ref="D2:D314"/>
-    <sortCondition ref="E2:E314"/>
-    <sortCondition descending="1" ref="A2:A314"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F315">
+    <sortCondition descending="1" ref="C2:C315"/>
+    <sortCondition ref="D2:D315"/>
+    <sortCondition ref="E2:E315"/>
+    <sortCondition descending="1" ref="A2:A315"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/EOAT_data.xlsx
+++ b/data/EOAT_data.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\procesos.CAZEL\Desktop\Becario Procesos\EOAT Project\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uramirez\Desktop\Inventario-main\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A524E845-612F-43FA-9915-963291DDE71C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7A38DBE-0396-4C6E-8DD3-12D4EA1C18CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{440E3869-3C3F-4E8C-A8BD-ADEB8E2EA552}"/>
+    <workbookView xWindow="20370" yWindow="-4710" windowWidth="29040" windowHeight="15840" xr2:uid="{440E3869-3C3F-4E8C-A8BD-ADEB8E2EA552}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$F$1</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1252" uniqueCount="638">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1275" uniqueCount="648">
   <si>
     <t>I-1937</t>
   </si>
@@ -245,9 +248,6 @@
     <t>I-1593</t>
   </si>
   <si>
-    <t>I-1620</t>
-  </si>
-  <si>
     <t>I-1598</t>
   </si>
   <si>
@@ -626,9 +626,6 @@
     <t>I-1593.jpeg</t>
   </si>
   <si>
-    <t>I-1620.jpeg</t>
-  </si>
-  <si>
     <t>I-1598.jpeg</t>
   </si>
   <si>
@@ -1950,6 +1947,42 @@
   </si>
   <si>
     <t>I-1945</t>
+  </si>
+  <si>
+    <t>I-1566</t>
+  </si>
+  <si>
+    <t>I-1566.jpeg</t>
+  </si>
+  <si>
+    <t>I-1581</t>
+  </si>
+  <si>
+    <t>I-1581.jpeg</t>
+  </si>
+  <si>
+    <t>I-1774</t>
+  </si>
+  <si>
+    <t>I-1774.jpeg</t>
+  </si>
+  <si>
+    <t>I-1930</t>
+  </si>
+  <si>
+    <t>I-1930.jpeg</t>
+  </si>
+  <si>
+    <t>I-1931.jpeg</t>
+  </si>
+  <si>
+    <t>I-1931</t>
+  </si>
+  <si>
+    <t>I-1556</t>
+  </si>
+  <si>
+    <t>I-1556.jpeg</t>
   </si>
 </sst>
 </file>
@@ -2327,7 +2360,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B6791C-A8A7-4753-A504-FAA9E3EE8745}">
-  <dimension ref="A1:F315"/>
+  <dimension ref="A1:F321"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -2340,22 +2373,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C1" t="s">
         <v>252</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>253</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>254</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>255</v>
-      </c>
-      <c r="E1" t="s">
-        <v>256</v>
-      </c>
-      <c r="F1" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -2363,116 +2396,116 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C3">
         <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C5">
         <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C6">
         <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C7">
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7" t="s">
         <v>146</v>
@@ -2480,16 +2513,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C8">
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -2500,22 +2533,22 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C9">
         <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -2523,36 +2556,36 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C10">
         <v>3</v>
       </c>
       <c r="D10" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C11">
         <v>3</v>
       </c>
       <c r="D11" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" t="s">
         <v>150</v>
@@ -2560,39 +2593,39 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C12">
         <v>3</v>
       </c>
       <c r="D12" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C13">
         <v>3</v>
       </c>
       <c r="D13" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F13" t="s">
         <v>152</v>
@@ -2600,22 +2633,22 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C14">
         <v>3</v>
       </c>
       <c r="D14" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -2623,19 +2656,19 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C15">
         <v>3</v>
       </c>
       <c r="D15" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E15">
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -2643,19 +2676,19 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C16">
         <v>3</v>
       </c>
       <c r="D16" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -2663,19 +2696,19 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C17">
         <v>3</v>
       </c>
       <c r="D17" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -2683,19 +2716,19 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C18">
         <v>3</v>
       </c>
       <c r="D18" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="E18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -2703,36 +2736,36 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C19">
         <v>3</v>
       </c>
       <c r="D19" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="E19">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C20">
         <v>3</v>
       </c>
       <c r="D20" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F20" t="s">
         <v>159</v>
@@ -2740,16 +2773,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B21" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C21">
         <v>3</v>
       </c>
       <c r="D21" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -2760,22 +2793,22 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C22">
         <v>3</v>
       </c>
       <c r="D22" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="E22">
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -2783,19 +2816,19 @@
         <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C23">
         <v>3</v>
       </c>
       <c r="D23" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -2803,19 +2836,19 @@
         <v>26</v>
       </c>
       <c r="B24" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C24">
         <v>3</v>
       </c>
       <c r="D24" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -2823,19 +2856,19 @@
         <v>27</v>
       </c>
       <c r="B25" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C25">
         <v>3</v>
       </c>
       <c r="D25" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="E25">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F25" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -2843,96 +2876,96 @@
         <v>28</v>
       </c>
       <c r="B26" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C26">
         <v>3</v>
       </c>
       <c r="D26" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="E26">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>612</v>
+        <v>30</v>
       </c>
       <c r="B27" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C27">
         <v>3</v>
       </c>
       <c r="D27" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E27">
         <v>1</v>
       </c>
       <c r="F27" t="s">
-        <v>614</v>
+        <v>165</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B28" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C28">
         <v>3</v>
       </c>
       <c r="D28" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E28">
         <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>30</v>
+        <v>609</v>
       </c>
       <c r="B29" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C29">
         <v>3</v>
       </c>
       <c r="D29" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F29" t="s">
-        <v>166</v>
+        <v>611</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B30" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C30">
         <v>3</v>
       </c>
       <c r="D30" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F30" t="s">
         <v>167</v>
@@ -2940,16 +2973,16 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B31" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C31">
         <v>3</v>
       </c>
       <c r="D31" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E31">
         <v>1</v>
@@ -2960,16 +2993,16 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B32" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C32">
         <v>3</v>
       </c>
       <c r="D32" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E32">
         <v>1</v>
@@ -2980,19 +3013,19 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B33" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C33">
         <v>3</v>
       </c>
       <c r="D33" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F33" t="s">
         <v>170</v>
@@ -3000,22 +3033,22 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B34" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C34">
         <v>3</v>
       </c>
       <c r="D34" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -3023,19 +3056,19 @@
         <v>37</v>
       </c>
       <c r="B35" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C35">
         <v>3</v>
       </c>
       <c r="D35" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="E35">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F35" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -3043,19 +3076,19 @@
         <v>38</v>
       </c>
       <c r="B36" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C36">
         <v>3</v>
       </c>
       <c r="D36" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="E36">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F36" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -3063,19 +3096,19 @@
         <v>39</v>
       </c>
       <c r="B37" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C37">
         <v>3</v>
       </c>
       <c r="D37" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E37">
         <v>1</v>
       </c>
       <c r="F37" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -3083,19 +3116,19 @@
         <v>41</v>
       </c>
       <c r="B38" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C38">
         <v>3</v>
       </c>
       <c r="D38" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E38">
         <v>1</v>
       </c>
       <c r="F38" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -3103,19 +3136,19 @@
         <v>42</v>
       </c>
       <c r="B39" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C39">
         <v>3</v>
       </c>
       <c r="D39" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F39" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -3123,19 +3156,19 @@
         <v>43</v>
       </c>
       <c r="B40" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C40">
         <v>3</v>
       </c>
       <c r="D40" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="E40">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F40" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -3143,159 +3176,159 @@
         <v>44</v>
       </c>
       <c r="B41" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C41">
         <v>3</v>
       </c>
       <c r="D41" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="E41">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F41" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B42" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C42">
         <v>3</v>
       </c>
       <c r="D42" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B43" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C43">
         <v>3</v>
       </c>
       <c r="D43" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="E43">
         <v>1</v>
       </c>
       <c r="F43" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B44" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C44">
         <v>3</v>
       </c>
       <c r="D44" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="E44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F44" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B45" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C45">
         <v>3</v>
       </c>
       <c r="D45" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="E45">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F45" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B46" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C46">
         <v>3</v>
       </c>
       <c r="D46" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="E46">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F46" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B47" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C47">
         <v>3</v>
       </c>
       <c r="D47" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="E47">
         <v>1</v>
       </c>
       <c r="F47" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B48" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C48">
         <v>3</v>
       </c>
       <c r="D48" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="E48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F48" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -3303,33 +3336,33 @@
         <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C49">
         <v>3</v>
       </c>
       <c r="D49" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="E49">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F49" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B50" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C50">
         <v>3</v>
       </c>
       <c r="D50" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="E50">
         <v>1</v>
@@ -3340,42 +3373,42 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B51" t="s">
-        <v>258</v>
+        <v>631</v>
       </c>
       <c r="C51">
         <v>3</v>
       </c>
       <c r="D51" t="s">
-        <v>56</v>
-      </c>
-      <c r="E51" t="s">
-        <v>632</v>
+        <v>65</v>
+      </c>
+      <c r="E51">
+        <v>1</v>
       </c>
       <c r="F51" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B52" t="s">
-        <v>633</v>
+        <v>256</v>
       </c>
       <c r="C52">
         <v>3</v>
       </c>
       <c r="D52" t="s">
-        <v>56</v>
-      </c>
-      <c r="E52" t="s">
-        <v>632</v>
+        <v>65</v>
+      </c>
+      <c r="E52">
+        <v>1</v>
       </c>
       <c r="F52" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -3383,76 +3416,76 @@
         <v>60</v>
       </c>
       <c r="B53" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C53">
         <v>3</v>
       </c>
       <c r="D53" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E53">
         <v>1</v>
       </c>
       <c r="F53" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B54" t="s">
-        <v>258</v>
+        <v>64</v>
       </c>
       <c r="C54">
         <v>3</v>
       </c>
       <c r="D54" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E54">
         <v>1</v>
-      </c>
-      <c r="F54" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B55" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C55">
         <v>3</v>
       </c>
       <c r="D55" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F55" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B56" t="s">
-        <v>64</v>
+        <v>256</v>
       </c>
       <c r="C56">
         <v>3</v>
       </c>
       <c r="D56" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E56">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="F56" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -3466,7 +3499,7 @@
         <v>3</v>
       </c>
       <c r="D57" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="E57">
         <v>1</v>
@@ -3483,10 +3516,10 @@
         <v>3</v>
       </c>
       <c r="D58" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="E58">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -3500,24 +3533,24 @@
         <v>3</v>
       </c>
       <c r="D59" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="E59">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B60" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C60">
         <v>3</v>
       </c>
       <c r="D60" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="E60">
         <v>1</v>
@@ -3525,19 +3558,19 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B61" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C61">
         <v>3</v>
       </c>
       <c r="D61" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="E61">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -3545,1343 +3578,1340 @@
         <v>58</v>
       </c>
       <c r="B62" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C62">
         <v>3</v>
       </c>
       <c r="D62" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="E62">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F62" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B63" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C63">
         <v>3</v>
       </c>
       <c r="D63" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="E63">
         <v>1</v>
       </c>
       <c r="F63" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B64" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C64">
         <v>3</v>
       </c>
       <c r="D64" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="E64">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F64" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B65" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C65">
         <v>3</v>
       </c>
       <c r="D65" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="E65">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F65" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B66" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C66">
         <v>3</v>
       </c>
       <c r="D66" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="E66">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F66" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B67" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C67">
         <v>3</v>
       </c>
       <c r="D67" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="E67">
         <v>1</v>
       </c>
       <c r="F67" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B68" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C68">
         <v>3</v>
       </c>
       <c r="D68" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="E68">
         <v>1</v>
       </c>
       <c r="F68" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B69" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C69">
         <v>3</v>
       </c>
       <c r="D69" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="E69">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F69" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B70" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C70">
         <v>3</v>
       </c>
       <c r="D70" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="E70">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F70" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B71" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C71">
         <v>3</v>
       </c>
       <c r="D71" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="E71">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F71" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B72" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C72">
         <v>3</v>
       </c>
       <c r="D72" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="E72">
         <v>1</v>
       </c>
       <c r="F72" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B73" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C73">
         <v>3</v>
       </c>
       <c r="D73" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="E73">
         <v>1</v>
       </c>
       <c r="F73" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B74" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C74">
         <v>3</v>
       </c>
       <c r="D74" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="E74">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F74" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B75" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C75">
         <v>3</v>
       </c>
       <c r="D75" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="E75">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F75" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B76" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C76">
         <v>3</v>
       </c>
       <c r="D76" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E76">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F76" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B77" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C77">
         <v>3</v>
       </c>
       <c r="D77" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E77">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F77" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="B78" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C78">
         <v>2</v>
       </c>
       <c r="D78" t="s">
-        <v>67</v>
+        <v>1</v>
       </c>
       <c r="E78">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F78" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C79">
         <v>2</v>
       </c>
       <c r="D79" t="s">
-        <v>67</v>
+        <v>1</v>
       </c>
       <c r="E79">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F79" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="B80" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C80">
         <v>2</v>
       </c>
       <c r="D80" t="s">
-        <v>67</v>
+        <v>1</v>
       </c>
       <c r="E80">
         <v>2</v>
       </c>
       <c r="F80" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="B81" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C81">
         <v>2</v>
       </c>
       <c r="D81" t="s">
-        <v>67</v>
+        <v>1</v>
       </c>
       <c r="E81">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F81" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="B82" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C82">
         <v>2</v>
       </c>
       <c r="D82" t="s">
-        <v>67</v>
+        <v>1</v>
       </c>
       <c r="E82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F82" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>637</v>
+        <v>82</v>
       </c>
       <c r="B83" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C83">
         <v>2</v>
       </c>
       <c r="D83" t="s">
-        <v>73</v>
+        <v>8</v>
       </c>
       <c r="E83">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F83" t="s">
-        <v>636</v>
+        <v>206</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="B84" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C84">
         <v>2</v>
       </c>
       <c r="D84" t="s">
-        <v>73</v>
+        <v>8</v>
       </c>
       <c r="E84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F84" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="B85" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C85">
         <v>2</v>
       </c>
       <c r="D85" t="s">
-        <v>73</v>
+        <v>8</v>
       </c>
       <c r="E85">
         <v>2</v>
       </c>
       <c r="F85" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="B86" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C86">
         <v>2</v>
       </c>
       <c r="D86" t="s">
-        <v>73</v>
+        <v>8</v>
       </c>
       <c r="E86">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F86" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="B87" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C87">
         <v>2</v>
       </c>
       <c r="D87" t="s">
-        <v>77</v>
+        <v>15</v>
       </c>
       <c r="E87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F87" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="B88" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C88">
         <v>2</v>
       </c>
       <c r="D88" t="s">
-        <v>77</v>
+        <v>15</v>
       </c>
       <c r="E88">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F88" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="B89" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C89">
         <v>2</v>
       </c>
       <c r="D89" t="s">
-        <v>77</v>
+        <v>15</v>
       </c>
       <c r="E89">
         <v>2</v>
       </c>
       <c r="F89" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="B90" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C90">
         <v>2</v>
       </c>
       <c r="D90" t="s">
-        <v>77</v>
+        <v>15</v>
       </c>
       <c r="E90">
         <v>2</v>
       </c>
       <c r="F90" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="B91" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C91">
         <v>2</v>
       </c>
       <c r="D91" t="s">
-        <v>77</v>
+        <v>15</v>
       </c>
       <c r="E91">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F91" t="s">
-        <v>206</v>
+        <v>228</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="B92" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C92">
         <v>2</v>
       </c>
       <c r="D92" t="s">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="E92">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F92" t="s">
-        <v>207</v>
+        <v>231</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="B93" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C93">
         <v>2</v>
       </c>
       <c r="D93" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="E93">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F93" t="s">
-        <v>208</v>
+        <v>229</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="B94" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C94">
         <v>2</v>
       </c>
       <c r="D94" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="E94">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F94" t="s">
-        <v>209</v>
+        <v>230</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="B95" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C95">
         <v>2</v>
       </c>
       <c r="D95" t="s">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="E95">
         <v>2</v>
       </c>
       <c r="F95" t="s">
-        <v>210</v>
+        <v>232</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="B96" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C96">
         <v>2</v>
       </c>
       <c r="D96" t="s">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="E96">
         <v>2</v>
       </c>
       <c r="F96" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="B97" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C97">
         <v>2</v>
       </c>
       <c r="D97" t="s">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="E97">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F97" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="B98" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C98">
         <v>2</v>
       </c>
       <c r="D98" t="s">
-        <v>84</v>
+        <v>29</v>
       </c>
       <c r="E98">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F98" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="B99" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C99">
         <v>2</v>
       </c>
       <c r="D99" t="s">
-        <v>111</v>
+        <v>29</v>
       </c>
       <c r="E99">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F99" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>112</v>
+        <v>127</v>
       </c>
       <c r="B100" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C100">
         <v>2</v>
       </c>
       <c r="D100" t="s">
-        <v>111</v>
+        <v>33</v>
       </c>
       <c r="E100">
         <v>2</v>
       </c>
       <c r="F100" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="B101" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C101">
         <v>2</v>
       </c>
       <c r="D101" t="s">
-        <v>111</v>
+        <v>33</v>
       </c>
       <c r="E101">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F101" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="B102" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C102">
         <v>2</v>
       </c>
       <c r="D102" t="s">
-        <v>111</v>
+        <v>33</v>
       </c>
       <c r="E102">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F102" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="B103" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C103">
         <v>2</v>
       </c>
       <c r="D103" t="s">
-        <v>116</v>
+        <v>33</v>
       </c>
       <c r="E103">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F103" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B104" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C104">
         <v>2</v>
       </c>
       <c r="D104" t="s">
-        <v>116</v>
+        <v>33</v>
       </c>
       <c r="E104">
         <v>2</v>
       </c>
       <c r="F104" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="B105" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C105">
         <v>2</v>
       </c>
       <c r="D105" t="s">
-        <v>116</v>
+        <v>40</v>
       </c>
       <c r="E105">
         <v>2</v>
       </c>
       <c r="F105" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>119</v>
+        <v>132</v>
       </c>
       <c r="B106" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C106">
         <v>2</v>
       </c>
       <c r="D106" t="s">
-        <v>116</v>
+        <v>40</v>
       </c>
       <c r="E106">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F106" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="B107" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C107">
         <v>2</v>
       </c>
       <c r="D107" t="s">
-        <v>116</v>
+        <v>40</v>
       </c>
       <c r="E107">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F107" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="B108" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C108">
         <v>2</v>
       </c>
       <c r="D108" t="s">
-        <v>122</v>
+        <v>40</v>
       </c>
       <c r="E108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F108" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>124</v>
+        <v>89</v>
       </c>
       <c r="B109" t="s">
-        <v>258</v>
+        <v>89</v>
       </c>
       <c r="C109">
         <v>2</v>
       </c>
       <c r="D109" t="s">
-        <v>122</v>
+        <v>46</v>
       </c>
       <c r="E109">
         <v>2</v>
-      </c>
-      <c r="F109" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="B110" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C110">
         <v>2</v>
       </c>
       <c r="D110" t="s">
-        <v>122</v>
+        <v>46</v>
       </c>
       <c r="E110">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F110" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="B111" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C111">
         <v>2</v>
       </c>
       <c r="D111" t="s">
-        <v>122</v>
+        <v>46</v>
       </c>
       <c r="E111">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F111" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="B112" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C112">
         <v>2</v>
       </c>
       <c r="D112" t="s">
-        <v>127</v>
+        <v>46</v>
       </c>
       <c r="E112">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F112" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>128</v>
+        <v>89</v>
       </c>
       <c r="B113" t="s">
-        <v>258</v>
+        <v>89</v>
       </c>
       <c r="C113">
         <v>2</v>
       </c>
       <c r="D113" t="s">
-        <v>127</v>
+        <v>52</v>
       </c>
       <c r="E113">
         <v>2</v>
-      </c>
-      <c r="F113" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>129</v>
+        <v>89</v>
       </c>
       <c r="B114" t="s">
-        <v>258</v>
+        <v>89</v>
       </c>
       <c r="C114">
         <v>2</v>
       </c>
       <c r="D114" t="s">
-        <v>127</v>
+        <v>52</v>
       </c>
       <c r="E114">
-        <v>3</v>
-      </c>
-      <c r="F114" t="s">
-        <v>244</v>
+        <v>2</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>131</v>
+        <v>89</v>
       </c>
       <c r="B115" t="s">
-        <v>258</v>
+        <v>89</v>
       </c>
       <c r="C115">
         <v>2</v>
       </c>
       <c r="D115" t="s">
-        <v>132</v>
+        <v>52</v>
       </c>
       <c r="E115">
-        <v>1</v>
-      </c>
-      <c r="F115" t="s">
-        <v>246</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>133</v>
+        <v>89</v>
       </c>
       <c r="B116" t="s">
-        <v>258</v>
+        <v>89</v>
       </c>
       <c r="C116">
         <v>2</v>
       </c>
       <c r="D116" t="s">
-        <v>132</v>
+        <v>52</v>
       </c>
       <c r="E116">
-        <v>1</v>
-      </c>
-      <c r="F116" t="s">
-        <v>247</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>134</v>
+        <v>89</v>
       </c>
       <c r="B117" t="s">
-        <v>258</v>
+        <v>89</v>
       </c>
       <c r="C117">
         <v>2</v>
       </c>
       <c r="D117" t="s">
-        <v>132</v>
+        <v>56</v>
       </c>
       <c r="E117">
         <v>2</v>
-      </c>
-      <c r="F117" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>135</v>
+        <v>89</v>
       </c>
       <c r="B118" t="s">
-        <v>258</v>
+        <v>89</v>
       </c>
       <c r="C118">
         <v>2</v>
       </c>
       <c r="D118" t="s">
-        <v>132</v>
+        <v>56</v>
       </c>
       <c r="E118">
         <v>2</v>
-      </c>
-      <c r="F118" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="B119" t="s">
-        <v>258</v>
+        <v>89</v>
       </c>
       <c r="C119">
         <v>2</v>
       </c>
       <c r="D119" t="s">
-        <v>132</v>
+        <v>56</v>
       </c>
       <c r="E119">
-        <v>3</v>
-      </c>
-      <c r="F119" t="s">
-        <v>250</v>
+        <v>2</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>137</v>
+        <v>632</v>
       </c>
       <c r="B120" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C120">
         <v>2</v>
       </c>
       <c r="D120" t="s">
-        <v>132</v>
+        <v>56</v>
       </c>
       <c r="E120">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F120" t="s">
-        <v>251</v>
+        <v>633</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>90</v>
+        <v>66</v>
       </c>
       <c r="B121" t="s">
-        <v>90</v>
+        <v>256</v>
       </c>
       <c r="C121">
         <v>2</v>
       </c>
       <c r="D121" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
       <c r="E121">
         <v>1</v>
+      </c>
+      <c r="F121" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="B122" t="s">
-        <v>90</v>
+        <v>256</v>
       </c>
       <c r="C122">
         <v>2</v>
       </c>
       <c r="D122" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="E122">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F122" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B123" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C123">
         <v>2</v>
       </c>
       <c r="D123" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="E123">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="B124" t="s">
-        <v>90</v>
+        <v>256</v>
       </c>
       <c r="C124">
         <v>2</v>
       </c>
       <c r="D124" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="E124">
         <v>1</v>
+      </c>
+      <c r="F124" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>90</v>
+        <v>635</v>
       </c>
       <c r="B125" t="s">
-        <v>90</v>
+        <v>256</v>
       </c>
       <c r="C125">
         <v>2</v>
       </c>
       <c r="D125" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="E125">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F125" t="s">
+        <v>634</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>634</v>
+        <v>70</v>
       </c>
       <c r="B126" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C126">
         <v>2</v>
       </c>
       <c r="D126" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="E126">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F126" t="s">
-        <v>635</v>
+        <v>196</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="B127" t="s">
-        <v>90</v>
+        <v>256</v>
       </c>
       <c r="C127">
         <v>2</v>
       </c>
       <c r="D127" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E127">
         <v>1</v>
+      </c>
+      <c r="F127" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="B128" t="s">
-        <v>90</v>
+        <v>256</v>
       </c>
       <c r="C128">
         <v>2</v>
       </c>
       <c r="D128" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E128">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F128" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="B129" t="s">
-        <v>90</v>
+        <v>256</v>
       </c>
       <c r="C129">
         <v>2</v>
       </c>
       <c r="D129" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E129">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="F129" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>432</v>
+        <v>645</v>
       </c>
       <c r="B130" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C130">
         <v>1</v>
@@ -4893,15 +4923,15 @@
         <v>1</v>
       </c>
       <c r="F130" t="s">
-        <v>599</v>
+        <v>644</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>430</v>
+        <v>642</v>
       </c>
       <c r="B131" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C131">
         <v>1</v>
@@ -4913,15 +4943,15 @@
         <v>1</v>
       </c>
       <c r="F131" t="s">
-        <v>597</v>
+        <v>643</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>433</v>
+        <v>640</v>
       </c>
       <c r="B132" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C132">
         <v>1</v>
@@ -4930,18 +4960,18 @@
         <v>1</v>
       </c>
       <c r="E132">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F132" t="s">
-        <v>600</v>
+        <v>641</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>437</v>
+        <v>638</v>
       </c>
       <c r="B133" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C133">
         <v>1</v>
@@ -4950,18 +4980,18 @@
         <v>1</v>
       </c>
       <c r="E133">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F133" t="s">
-        <v>604</v>
+        <v>639</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>440</v>
+        <v>646</v>
       </c>
       <c r="B134" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C134">
         <v>1</v>
@@ -4970,18 +5000,18 @@
         <v>1</v>
       </c>
       <c r="E134">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F134" t="s">
-        <v>607</v>
+        <v>647</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>439</v>
+        <v>388</v>
       </c>
       <c r="B135" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C135">
         <v>1</v>
@@ -4993,15 +5023,15 @@
         <v>3</v>
       </c>
       <c r="F135" t="s">
-        <v>606</v>
+        <v>555</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>434</v>
+        <v>387</v>
       </c>
       <c r="B136" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C136">
         <v>1</v>
@@ -5013,15 +5043,15 @@
         <v>3</v>
       </c>
       <c r="F136" t="s">
-        <v>601</v>
+        <v>554</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>436</v>
+        <v>385</v>
       </c>
       <c r="B137" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C137">
         <v>1</v>
@@ -5030,18 +5060,18 @@
         <v>1</v>
       </c>
       <c r="E137">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F137" t="s">
-        <v>603</v>
+        <v>552</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>435</v>
+        <v>384</v>
       </c>
       <c r="B138" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C138">
         <v>1</v>
@@ -5050,18 +5080,18 @@
         <v>1</v>
       </c>
       <c r="E138">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F138" t="s">
-        <v>602</v>
+        <v>551</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>438</v>
+        <v>620</v>
       </c>
       <c r="B139" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C139">
         <v>1</v>
@@ -5073,15 +5103,15 @@
         <v>4</v>
       </c>
       <c r="F139" t="s">
-        <v>605</v>
+        <v>628</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>615</v>
+        <v>307</v>
       </c>
       <c r="B140" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C140">
         <v>1</v>
@@ -5093,55 +5123,55 @@
         <v>4</v>
       </c>
       <c r="F140" t="s">
-        <v>623</v>
+        <v>474</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>423</v>
+        <v>306</v>
       </c>
       <c r="B141" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C141">
         <v>1</v>
       </c>
       <c r="D141" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E141">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F141" t="s">
-        <v>590</v>
+        <v>473</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>422</v>
+        <v>303</v>
       </c>
       <c r="B142" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C142">
         <v>1</v>
       </c>
       <c r="D142" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E142">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F142" t="s">
-        <v>589</v>
+        <v>470</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>421</v>
+        <v>636</v>
       </c>
       <c r="B143" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C143">
         <v>1</v>
@@ -5153,15 +5183,15 @@
         <v>1</v>
       </c>
       <c r="F143" t="s">
-        <v>588</v>
+        <v>637</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>425</v>
+        <v>392</v>
       </c>
       <c r="B144" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C144">
         <v>1</v>
@@ -5170,18 +5200,18 @@
         <v>8</v>
       </c>
       <c r="E144">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F144" t="s">
-        <v>592</v>
+        <v>559</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>424</v>
+        <v>391</v>
       </c>
       <c r="B145" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C145">
         <v>1</v>
@@ -5190,18 +5220,18 @@
         <v>8</v>
       </c>
       <c r="E145">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F145" t="s">
-        <v>591</v>
+        <v>558</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>427</v>
+        <v>390</v>
       </c>
       <c r="B146" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C146">
         <v>1</v>
@@ -5213,15 +5243,15 @@
         <v>3</v>
       </c>
       <c r="F146" t="s">
-        <v>594</v>
+        <v>557</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>426</v>
+        <v>386</v>
       </c>
       <c r="B147" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C147">
         <v>1</v>
@@ -5233,15 +5263,15 @@
         <v>3</v>
       </c>
       <c r="F147" t="s">
-        <v>593</v>
+        <v>553</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>431</v>
+        <v>309</v>
       </c>
       <c r="B148" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C148">
         <v>1</v>
@@ -5253,15 +5283,15 @@
         <v>4</v>
       </c>
       <c r="F148" t="s">
-        <v>598</v>
+        <v>476</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>429</v>
+        <v>308</v>
       </c>
       <c r="B149" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C149">
         <v>1</v>
@@ -5273,15 +5303,15 @@
         <v>4</v>
       </c>
       <c r="F149" t="s">
-        <v>596</v>
+        <v>475</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>428</v>
+        <v>294</v>
       </c>
       <c r="B150" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C150">
         <v>1</v>
@@ -5293,15 +5323,15 @@
         <v>4</v>
       </c>
       <c r="F150" t="s">
-        <v>595</v>
+        <v>461</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>411</v>
+        <v>395</v>
       </c>
       <c r="B151" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C151">
         <v>1</v>
@@ -5310,18 +5340,18 @@
         <v>15</v>
       </c>
       <c r="E151">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F151" t="s">
-        <v>578</v>
+        <v>562</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>413</v>
+        <v>394</v>
       </c>
       <c r="B152" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C152">
         <v>1</v>
@@ -5330,18 +5360,18 @@
         <v>15</v>
       </c>
       <c r="E152">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F152" t="s">
-        <v>580</v>
+        <v>561</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>412</v>
+        <v>393</v>
       </c>
       <c r="B153" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C153">
         <v>1</v>
@@ -5350,18 +5380,18 @@
         <v>15</v>
       </c>
       <c r="E153">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F153" t="s">
-        <v>579</v>
+        <v>560</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>616</v>
+        <v>389</v>
       </c>
       <c r="B154" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C154">
         <v>1</v>
@@ -5370,18 +5400,18 @@
         <v>15</v>
       </c>
       <c r="E154">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F154" t="s">
-        <v>624</v>
+        <v>556</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>416</v>
+        <v>376</v>
       </c>
       <c r="B155" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C155">
         <v>1</v>
@@ -5393,15 +5423,15 @@
         <v>3</v>
       </c>
       <c r="F155" t="s">
-        <v>583</v>
+        <v>543</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>415</v>
+        <v>375</v>
       </c>
       <c r="B156" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C156">
         <v>1</v>
@@ -5413,15 +5443,15 @@
         <v>3</v>
       </c>
       <c r="F156" t="s">
-        <v>582</v>
+        <v>542</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>414</v>
+        <v>89</v>
       </c>
       <c r="B157" t="s">
-        <v>258</v>
+        <v>89</v>
       </c>
       <c r="C157">
         <v>1</v>
@@ -5430,18 +5460,15 @@
         <v>15</v>
       </c>
       <c r="E157">
-        <v>3</v>
-      </c>
-      <c r="F157" t="s">
-        <v>581</v>
+        <v>4</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>420</v>
+        <v>297</v>
       </c>
       <c r="B158" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C158">
         <v>1</v>
@@ -5453,15 +5480,15 @@
         <v>4</v>
       </c>
       <c r="F158" t="s">
-        <v>587</v>
+        <v>464</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>419</v>
+        <v>296</v>
       </c>
       <c r="B159" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C159">
         <v>1</v>
@@ -5473,15 +5500,15 @@
         <v>4</v>
       </c>
       <c r="F159" t="s">
-        <v>586</v>
+        <v>463</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>418</v>
+        <v>295</v>
       </c>
       <c r="B160" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C160">
         <v>1</v>
@@ -5493,35 +5520,35 @@
         <v>4</v>
       </c>
       <c r="F160" t="s">
-        <v>585</v>
+        <v>462</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>417</v>
+        <v>380</v>
       </c>
       <c r="B161" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C161">
         <v>1</v>
       </c>
       <c r="D161" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E161">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F161" t="s">
-        <v>584</v>
+        <v>547</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>401</v>
+        <v>379</v>
       </c>
       <c r="B162" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C162">
         <v>1</v>
@@ -5530,18 +5557,18 @@
         <v>23</v>
       </c>
       <c r="E162">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F162" t="s">
-        <v>568</v>
+        <v>546</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>400</v>
+        <v>378</v>
       </c>
       <c r="B163" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C163">
         <v>1</v>
@@ -5550,18 +5577,18 @@
         <v>23</v>
       </c>
       <c r="E163">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F163" t="s">
-        <v>567</v>
+        <v>545</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>399</v>
+        <v>377</v>
       </c>
       <c r="B164" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C164">
         <v>1</v>
@@ -5570,18 +5597,18 @@
         <v>23</v>
       </c>
       <c r="E164">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F164" t="s">
-        <v>566</v>
+        <v>544</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>398</v>
+        <v>374</v>
       </c>
       <c r="B165" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C165">
         <v>1</v>
@@ -5590,18 +5617,18 @@
         <v>23</v>
       </c>
       <c r="E165">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F165" t="s">
-        <v>565</v>
+        <v>541</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>404</v>
+        <v>439</v>
       </c>
       <c r="B166" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C166">
         <v>1</v>
@@ -5610,18 +5637,18 @@
         <v>23</v>
       </c>
       <c r="E166">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F166" t="s">
-        <v>571</v>
+        <v>606</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>403</v>
+        <v>607</v>
       </c>
       <c r="B167" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C167">
         <v>1</v>
@@ -5630,18 +5657,18 @@
         <v>23</v>
       </c>
       <c r="E167">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F167" t="s">
-        <v>570</v>
+        <v>608</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>406</v>
+        <v>299</v>
       </c>
       <c r="B168" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C168">
         <v>1</v>
@@ -5650,18 +5677,18 @@
         <v>23</v>
       </c>
       <c r="E168">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F168" t="s">
-        <v>573</v>
+        <v>466</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>405</v>
+        <v>298</v>
       </c>
       <c r="B169" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C169">
         <v>1</v>
@@ -5670,118 +5697,118 @@
         <v>23</v>
       </c>
       <c r="E169">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F169" t="s">
-        <v>572</v>
+        <v>465</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>402</v>
+        <v>383</v>
       </c>
       <c r="B170" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C170">
         <v>1</v>
       </c>
       <c r="D170" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E170">
         <v>3</v>
       </c>
       <c r="F170" t="s">
-        <v>569</v>
+        <v>550</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>410</v>
+        <v>382</v>
       </c>
       <c r="B171" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C171">
         <v>1</v>
       </c>
       <c r="D171" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E171">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F171" t="s">
-        <v>577</v>
+        <v>549</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="B172" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C172">
         <v>1</v>
       </c>
       <c r="D172" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E172">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F172" t="s">
-        <v>576</v>
+        <v>548</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>408</v>
+        <v>367</v>
       </c>
       <c r="B173" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C173">
         <v>1</v>
       </c>
       <c r="D173" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E173">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F173" t="s">
-        <v>575</v>
+        <v>534</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>407</v>
+        <v>366</v>
       </c>
       <c r="B174" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C174">
         <v>1</v>
       </c>
       <c r="D174" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E174">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F174" t="s">
-        <v>574</v>
+        <v>533</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>387</v>
+        <v>288</v>
       </c>
       <c r="B175" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C175">
         <v>1</v>
@@ -5790,18 +5817,18 @@
         <v>29</v>
       </c>
       <c r="E175">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F175" t="s">
-        <v>554</v>
+        <v>455</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>386</v>
+        <v>287</v>
       </c>
       <c r="B176" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C176">
         <v>1</v>
@@ -5810,18 +5837,18 @@
         <v>29</v>
       </c>
       <c r="E176">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F176" t="s">
-        <v>553</v>
+        <v>454</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>390</v>
+        <v>286</v>
       </c>
       <c r="B177" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C177">
         <v>1</v>
@@ -5830,2167 +5857,2170 @@
         <v>29</v>
       </c>
       <c r="E177">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F177" t="s">
-        <v>557</v>
+        <v>453</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>389</v>
+        <v>373</v>
       </c>
       <c r="B178" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C178">
         <v>1</v>
       </c>
       <c r="D178" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E178">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F178" t="s">
-        <v>556</v>
+        <v>540</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>388</v>
+        <v>370</v>
       </c>
       <c r="B179" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C179">
         <v>1</v>
       </c>
       <c r="D179" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E179">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F179" t="s">
-        <v>555</v>
+        <v>537</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>394</v>
+        <v>369</v>
       </c>
       <c r="B180" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C180">
         <v>1</v>
       </c>
       <c r="D180" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E180">
         <v>3</v>
       </c>
       <c r="F180" t="s">
-        <v>561</v>
+        <v>536</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>393</v>
+        <v>368</v>
       </c>
       <c r="B181" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C181">
         <v>1</v>
       </c>
       <c r="D181" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E181">
         <v>3</v>
       </c>
       <c r="F181" t="s">
-        <v>560</v>
+        <v>535</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>392</v>
+        <v>365</v>
       </c>
       <c r="B182" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C182">
         <v>1</v>
       </c>
       <c r="D182" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E182">
         <v>3</v>
       </c>
       <c r="F182" t="s">
-        <v>559</v>
+        <v>532</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>391</v>
+        <v>290</v>
       </c>
       <c r="B183" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C183">
         <v>1</v>
       </c>
       <c r="D183" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E183">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F183" t="s">
-        <v>558</v>
+        <v>457</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>397</v>
+        <v>289</v>
       </c>
       <c r="B184" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C184">
         <v>1</v>
       </c>
       <c r="D184" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E184">
         <v>4</v>
       </c>
       <c r="F184" t="s">
-        <v>564</v>
+        <v>456</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>396</v>
+        <v>372</v>
       </c>
       <c r="B185" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C185">
         <v>1</v>
       </c>
       <c r="D185" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E185">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F185" t="s">
-        <v>563</v>
+        <v>539</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>395</v>
+        <v>371</v>
       </c>
       <c r="B186" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C186">
         <v>1</v>
       </c>
       <c r="D186" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E186">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F186" t="s">
-        <v>562</v>
+        <v>538</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>378</v>
+        <v>276</v>
       </c>
       <c r="B187" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C187">
         <v>1</v>
       </c>
       <c r="D187" t="s">
-        <v>33</v>
-      </c>
-      <c r="E187">
-        <v>1</v>
+        <v>40</v>
+      </c>
+      <c r="E187" t="s">
+        <v>629</v>
       </c>
       <c r="F187" t="s">
-        <v>545</v>
+        <v>443</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>377</v>
+        <v>275</v>
       </c>
       <c r="B188" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C188">
         <v>1</v>
       </c>
       <c r="D188" t="s">
-        <v>33</v>
-      </c>
-      <c r="E188">
-        <v>1</v>
+        <v>40</v>
+      </c>
+      <c r="E188" t="s">
+        <v>629</v>
       </c>
       <c r="F188" t="s">
-        <v>544</v>
+        <v>442</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>376</v>
+        <v>274</v>
       </c>
       <c r="B189" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C189">
         <v>1</v>
       </c>
       <c r="D189" t="s">
-        <v>33</v>
-      </c>
-      <c r="E189">
-        <v>1</v>
+        <v>40</v>
+      </c>
+      <c r="E189" t="s">
+        <v>629</v>
       </c>
       <c r="F189" t="s">
-        <v>543</v>
+        <v>441</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>380</v>
+        <v>358</v>
       </c>
       <c r="B190" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C190">
         <v>1</v>
       </c>
       <c r="D190" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E190">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F190" t="s">
-        <v>547</v>
+        <v>525</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>379</v>
+        <v>357</v>
       </c>
       <c r="B191" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C191">
         <v>1</v>
       </c>
       <c r="D191" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E191">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F191" t="s">
-        <v>546</v>
+        <v>524</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>382</v>
+        <v>355</v>
       </c>
       <c r="B192" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C192">
         <v>1</v>
       </c>
       <c r="D192" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E192">
         <v>3</v>
       </c>
       <c r="F192" t="s">
-        <v>549</v>
+        <v>522</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>381</v>
+        <v>354</v>
       </c>
       <c r="B193" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C193">
         <v>1</v>
       </c>
       <c r="D193" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E193">
         <v>3</v>
       </c>
       <c r="F193" t="s">
-        <v>548</v>
+        <v>521</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>385</v>
+        <v>353</v>
       </c>
       <c r="B194" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C194">
         <v>1</v>
       </c>
       <c r="D194" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E194">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F194" t="s">
-        <v>552</v>
+        <v>520</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>384</v>
+        <v>292</v>
       </c>
       <c r="B195" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C195">
         <v>1</v>
       </c>
       <c r="D195" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E195">
         <v>4</v>
       </c>
       <c r="F195" t="s">
-        <v>551</v>
+        <v>459</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>383</v>
+        <v>617</v>
       </c>
       <c r="B196" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C196">
         <v>1</v>
       </c>
       <c r="D196" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="E196">
         <v>4</v>
       </c>
       <c r="F196" t="s">
-        <v>550</v>
+        <v>625</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>369</v>
+        <v>616</v>
       </c>
       <c r="B197" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C197">
         <v>1</v>
       </c>
       <c r="D197" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="E197">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F197" t="s">
-        <v>536</v>
+        <v>624</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>368</v>
+        <v>361</v>
       </c>
       <c r="B198" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C198">
         <v>1</v>
       </c>
       <c r="D198" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E198">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F198" t="s">
-        <v>535</v>
+        <v>528</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="B199" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C199">
         <v>1</v>
       </c>
       <c r="D199" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E199">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F199" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>372</v>
+        <v>356</v>
       </c>
       <c r="B200" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C200">
         <v>1</v>
       </c>
       <c r="D200" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E200">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F200" t="s">
-        <v>539</v>
+        <v>523</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>371</v>
+        <v>293</v>
       </c>
       <c r="B201" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C201">
         <v>1</v>
       </c>
       <c r="D201" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E201">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F201" t="s">
-        <v>538</v>
+        <v>460</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>370</v>
+        <v>291</v>
       </c>
       <c r="B202" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C202">
         <v>1</v>
       </c>
       <c r="D202" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E202">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F202" t="s">
-        <v>537</v>
+        <v>458</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>375</v>
+        <v>618</v>
       </c>
       <c r="B203" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C203">
         <v>1</v>
       </c>
       <c r="D203" t="s">
-        <v>40</v>
-      </c>
-      <c r="E203" t="s">
-        <v>631</v>
+        <v>52</v>
+      </c>
+      <c r="E203">
+        <v>4</v>
       </c>
       <c r="F203" t="s">
-        <v>542</v>
+        <v>626</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="B204" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C204">
         <v>1</v>
       </c>
       <c r="D204" t="s">
-        <v>40</v>
-      </c>
-      <c r="E204" t="s">
-        <v>631</v>
+        <v>56</v>
+      </c>
+      <c r="E204">
+        <v>3</v>
       </c>
       <c r="F204" t="s">
-        <v>541</v>
+        <v>531</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="B205" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C205">
         <v>1</v>
       </c>
       <c r="D205" t="s">
-        <v>40</v>
-      </c>
-      <c r="E205" t="s">
-        <v>631</v>
+        <v>56</v>
+      </c>
+      <c r="E205">
+        <v>3</v>
       </c>
       <c r="F205" t="s">
-        <v>540</v>
+        <v>530</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="B206" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C206">
         <v>1</v>
       </c>
       <c r="D206" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="E206">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F206" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B207" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C207">
         <v>1</v>
       </c>
       <c r="D207" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="E207">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F207" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>355</v>
+        <v>344</v>
       </c>
       <c r="B208" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C208">
         <v>1</v>
       </c>
       <c r="D208" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="E208">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F208" t="s">
-        <v>522</v>
+        <v>511</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>360</v>
+        <v>343</v>
       </c>
       <c r="B209" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C209">
         <v>1</v>
       </c>
       <c r="D209" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="E209">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F209" t="s">
-        <v>527</v>
+        <v>510</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>359</v>
+        <v>285</v>
       </c>
       <c r="B210" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C210">
         <v>1</v>
       </c>
       <c r="D210" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="E210">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F210" t="s">
-        <v>526</v>
+        <v>452</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>358</v>
+        <v>278</v>
       </c>
       <c r="B211" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C211">
         <v>1</v>
       </c>
       <c r="D211" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="E211">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F211" t="s">
-        <v>525</v>
+        <v>445</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>363</v>
+        <v>265</v>
       </c>
       <c r="B212" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C212">
         <v>1</v>
       </c>
       <c r="D212" t="s">
-        <v>46</v>
-      </c>
-      <c r="E212">
-        <v>3</v>
+        <v>56</v>
+      </c>
+      <c r="E212" t="s">
+        <v>630</v>
       </c>
       <c r="F212" t="s">
-        <v>530</v>
+        <v>272</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>362</v>
+        <v>264</v>
       </c>
       <c r="B213" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C213">
         <v>1</v>
       </c>
       <c r="D213" t="s">
-        <v>46</v>
-      </c>
-      <c r="E213">
-        <v>3</v>
+        <v>56</v>
+      </c>
+      <c r="E213" t="s">
+        <v>630</v>
       </c>
       <c r="F213" t="s">
-        <v>529</v>
+        <v>271</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>361</v>
+        <v>431</v>
       </c>
       <c r="B214" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C214">
         <v>1</v>
       </c>
       <c r="D214" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="E214">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F214" t="s">
-        <v>528</v>
+        <v>598</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>366</v>
+        <v>435</v>
       </c>
       <c r="B215" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C215">
         <v>1</v>
       </c>
       <c r="D215" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="E215">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F215" t="s">
-        <v>533</v>
+        <v>602</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>365</v>
+        <v>438</v>
       </c>
       <c r="B216" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C216">
         <v>1</v>
       </c>
       <c r="D216" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="E216">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F216" t="s">
-        <v>532</v>
+        <v>605</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>364</v>
+        <v>430</v>
       </c>
       <c r="B217" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C217">
         <v>1</v>
       </c>
       <c r="D217" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="E217">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F217" t="s">
-        <v>531</v>
+        <v>597</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>346</v>
+        <v>428</v>
       </c>
       <c r="B218" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C218">
         <v>1</v>
       </c>
       <c r="D218" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="E218">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F218" t="s">
-        <v>513</v>
+        <v>595</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B219" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C219">
         <v>1</v>
       </c>
       <c r="D219" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="E219">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F219" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B220" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C220">
         <v>1</v>
       </c>
       <c r="D220" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="E220">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F220" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B221" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C221">
         <v>1</v>
       </c>
       <c r="D221" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="E221">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F221" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="B222" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C222">
         <v>1</v>
       </c>
       <c r="D222" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="E222">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F222" t="s">
-        <v>516</v>
+        <v>509</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="B223" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C223">
         <v>1</v>
       </c>
       <c r="D223" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="E223">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F223" t="s">
-        <v>515</v>
+        <v>508</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>347</v>
+        <v>281</v>
       </c>
       <c r="B224" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C224">
         <v>1</v>
       </c>
       <c r="D224" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="E224">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F224" t="s">
-        <v>514</v>
+        <v>448</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>351</v>
+        <v>280</v>
       </c>
       <c r="B225" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C225">
         <v>1</v>
       </c>
       <c r="D225" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="E225">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F225" t="s">
-        <v>518</v>
+        <v>447</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>350</v>
+        <v>615</v>
       </c>
       <c r="B226" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C226">
         <v>1</v>
       </c>
       <c r="D226" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="E226">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F226" t="s">
-        <v>517</v>
+        <v>623</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>354</v>
+        <v>277</v>
       </c>
       <c r="B227" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C227">
         <v>1</v>
       </c>
       <c r="D227" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="E227">
         <v>4</v>
       </c>
       <c r="F227" t="s">
-        <v>521</v>
+        <v>444</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>353</v>
+        <v>434</v>
       </c>
       <c r="B228" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C228">
         <v>1</v>
       </c>
       <c r="D228" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="E228">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F228" t="s">
-        <v>520</v>
+        <v>601</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>352</v>
+        <v>433</v>
       </c>
       <c r="B229" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C229">
         <v>1</v>
       </c>
       <c r="D229" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="E229">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F229" t="s">
-        <v>519</v>
+        <v>600</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>330</v>
+        <v>437</v>
       </c>
       <c r="B230" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C230">
         <v>1</v>
       </c>
       <c r="D230" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="E230">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F230" t="s">
-        <v>497</v>
+        <v>604</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>329</v>
+        <v>432</v>
       </c>
       <c r="B231" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C231">
         <v>1</v>
       </c>
       <c r="D231" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="E231">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F231" t="s">
-        <v>496</v>
+        <v>599</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>328</v>
+        <v>352</v>
       </c>
       <c r="B232" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C232">
         <v>1</v>
       </c>
       <c r="D232" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="E232">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F232" t="s">
-        <v>495</v>
+        <v>519</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>327</v>
+        <v>351</v>
       </c>
       <c r="B233" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C233">
         <v>1</v>
       </c>
       <c r="D233" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="E233">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F233" t="s">
-        <v>494</v>
+        <v>518</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>334</v>
+        <v>349</v>
       </c>
       <c r="B234" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C234">
         <v>1</v>
       </c>
       <c r="D234" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="E234">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F234" t="s">
-        <v>501</v>
+        <v>516</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="B235" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C235">
         <v>1</v>
       </c>
       <c r="D235" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="E235">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F235" t="s">
-        <v>500</v>
+        <v>515</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>332</v>
+        <v>284</v>
       </c>
       <c r="B236" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C236">
         <v>1</v>
       </c>
       <c r="D236" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="E236">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F236" t="s">
-        <v>499</v>
+        <v>451</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>331</v>
+        <v>279</v>
       </c>
       <c r="B237" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C237">
         <v>1</v>
       </c>
       <c r="D237" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="E237">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F237" t="s">
-        <v>498</v>
+        <v>446</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>340</v>
+        <v>436</v>
       </c>
       <c r="B238" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C238">
         <v>1</v>
       </c>
       <c r="D238" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E238">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F238" t="s">
-        <v>507</v>
+        <v>603</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>339</v>
+        <v>613</v>
       </c>
       <c r="B239" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C239">
         <v>1</v>
       </c>
       <c r="D239" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E239">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F239" t="s">
-        <v>506</v>
+        <v>621</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>338</v>
+        <v>421</v>
       </c>
       <c r="B240" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C240">
         <v>1</v>
       </c>
       <c r="D240" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E240">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F240" t="s">
-        <v>505</v>
+        <v>588</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>337</v>
+        <v>350</v>
       </c>
       <c r="B241" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C241">
         <v>1</v>
       </c>
       <c r="D241" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E241">
         <v>3</v>
       </c>
       <c r="F241" t="s">
-        <v>504</v>
+        <v>517</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="B242" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C242">
         <v>1</v>
       </c>
       <c r="D242" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E242">
         <v>3</v>
       </c>
       <c r="F242" t="s">
-        <v>503</v>
+        <v>495</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="B243" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C243">
         <v>1</v>
       </c>
       <c r="D243" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E243">
         <v>3</v>
       </c>
       <c r="F243" t="s">
-        <v>502</v>
+        <v>494</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>342</v>
+        <v>326</v>
       </c>
       <c r="B244" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C244">
         <v>1</v>
       </c>
       <c r="D244" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E244">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F244" t="s">
-        <v>509</v>
+        <v>493</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>341</v>
+        <v>325</v>
       </c>
       <c r="B245" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C245">
         <v>1</v>
       </c>
       <c r="D245" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="E245">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F245" t="s">
-        <v>508</v>
+        <v>492</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>314</v>
+        <v>283</v>
       </c>
       <c r="B246" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C246">
         <v>1</v>
       </c>
       <c r="D246" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E246">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F246" t="s">
-        <v>481</v>
+        <v>450</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>313</v>
+        <v>282</v>
       </c>
       <c r="B247" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C247">
         <v>1</v>
       </c>
       <c r="D247" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E247">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F247" t="s">
-        <v>480</v>
+        <v>449</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>312</v>
+        <v>129</v>
       </c>
       <c r="B248" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C248">
         <v>1</v>
       </c>
       <c r="D248" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E248">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F248" t="s">
-        <v>479</v>
+        <v>243</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>318</v>
+        <v>260</v>
       </c>
       <c r="B249" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C249">
         <v>1</v>
       </c>
       <c r="D249" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E249">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F249" t="s">
-        <v>485</v>
+        <v>267</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>317</v>
+        <v>425</v>
       </c>
       <c r="B250" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C250">
         <v>1</v>
       </c>
       <c r="D250" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="E250">
         <v>2</v>
       </c>
       <c r="F250" t="s">
-        <v>484</v>
+        <v>592</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>316</v>
+        <v>423</v>
       </c>
       <c r="B251" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C251">
         <v>1</v>
       </c>
       <c r="D251" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="E251">
         <v>2</v>
       </c>
       <c r="F251" t="s">
-        <v>483</v>
+        <v>590</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>315</v>
+        <v>422</v>
       </c>
       <c r="B252" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C252">
         <v>1</v>
       </c>
       <c r="D252" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="E252">
         <v>2</v>
       </c>
       <c r="F252" t="s">
-        <v>482</v>
+        <v>589</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>322</v>
+        <v>420</v>
       </c>
       <c r="B253" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C253">
         <v>1</v>
       </c>
       <c r="D253" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="E253">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F253" t="s">
-        <v>489</v>
+        <v>587</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>321</v>
+        <v>419</v>
       </c>
       <c r="B254" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C254">
         <v>1</v>
       </c>
       <c r="D254" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="E254">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F254" t="s">
-        <v>488</v>
+        <v>586</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="B255" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C255">
         <v>1</v>
       </c>
       <c r="D255" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="E255">
         <v>3</v>
       </c>
       <c r="F255" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="B256" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C256">
         <v>1</v>
       </c>
       <c r="D256" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="E256">
         <v>3</v>
       </c>
       <c r="F256" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="B257" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C257">
         <v>1</v>
       </c>
       <c r="D257" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="E257">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F257" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B258" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C258">
         <v>1</v>
       </c>
       <c r="D258" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="E258">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F258" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>324</v>
+        <v>263</v>
       </c>
       <c r="B259" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C259">
         <v>1</v>
       </c>
       <c r="D259" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="E259">
         <v>4</v>
       </c>
       <c r="F259" t="s">
-        <v>491</v>
+        <v>270</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>323</v>
+        <v>259</v>
       </c>
       <c r="B260" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C260">
         <v>1</v>
       </c>
       <c r="D260" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="E260">
         <v>4</v>
       </c>
       <c r="F260" t="s">
-        <v>490</v>
+        <v>266</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>304</v>
+        <v>257</v>
       </c>
       <c r="B261" t="s">
+        <v>256</v>
+      </c>
+      <c r="C261">
+        <v>1</v>
+      </c>
+      <c r="D261" t="s">
+        <v>72</v>
+      </c>
+      <c r="E261">
+        <v>4</v>
+      </c>
+      <c r="F261" t="s">
         <v>258</v>
-      </c>
-      <c r="C261">
-        <v>1</v>
-      </c>
-      <c r="D261" t="s">
-        <v>65</v>
-      </c>
-      <c r="E261">
-        <v>1</v>
-      </c>
-      <c r="F261" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>303</v>
+        <v>429</v>
       </c>
       <c r="B262" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C262">
         <v>1</v>
       </c>
       <c r="D262" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="E262">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F262" t="s">
-        <v>470</v>
+        <v>596</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>302</v>
+        <v>427</v>
       </c>
       <c r="B263" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C263">
         <v>1</v>
       </c>
       <c r="D263" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="E263">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F263" t="s">
-        <v>469</v>
+        <v>594</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>307</v>
+        <v>426</v>
       </c>
       <c r="B264" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C264">
         <v>1</v>
       </c>
       <c r="D264" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="E264">
         <v>2</v>
       </c>
       <c r="F264" t="s">
-        <v>474</v>
+        <v>593</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>306</v>
+        <v>424</v>
       </c>
       <c r="B265" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C265">
         <v>1</v>
       </c>
       <c r="D265" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="E265">
         <v>2</v>
       </c>
       <c r="F265" t="s">
-        <v>473</v>
+        <v>591</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>305</v>
+        <v>411</v>
       </c>
       <c r="B266" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C266">
         <v>1</v>
       </c>
       <c r="D266" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="E266">
         <v>2</v>
       </c>
       <c r="F266" t="s">
-        <v>472</v>
+        <v>578</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>622</v>
+        <v>409</v>
       </c>
       <c r="B267" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C267">
         <v>1</v>
       </c>
       <c r="D267" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="E267">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F267" t="s">
-        <v>630</v>
+        <v>576</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>309</v>
+        <v>338</v>
       </c>
       <c r="B268" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C268">
         <v>1</v>
       </c>
       <c r="D268" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="E268">
         <v>3</v>
       </c>
       <c r="F268" t="s">
-        <v>476</v>
+        <v>505</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>308</v>
+        <v>337</v>
       </c>
       <c r="B269" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C269">
         <v>1</v>
       </c>
       <c r="D269" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="E269">
         <v>3</v>
       </c>
       <c r="F269" t="s">
-        <v>475</v>
+        <v>504</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>311</v>
+        <v>336</v>
       </c>
       <c r="B270" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C270">
         <v>1</v>
       </c>
       <c r="D270" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="E270">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F270" t="s">
-        <v>478</v>
+        <v>503</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>310</v>
+        <v>335</v>
       </c>
       <c r="B271" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C271">
         <v>1</v>
       </c>
       <c r="D271" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="E271">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F271" t="s">
-        <v>477</v>
+        <v>502</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>296</v>
+        <v>334</v>
       </c>
       <c r="B272" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C272">
         <v>1</v>
       </c>
       <c r="D272" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="E272">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F272" t="s">
-        <v>463</v>
+        <v>501</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>90</v>
+        <v>262</v>
       </c>
       <c r="B273" t="s">
-        <v>90</v>
+        <v>256</v>
       </c>
       <c r="C273">
         <v>1</v>
       </c>
       <c r="D273" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="E273">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="F273" t="s">
+        <v>269</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>299</v>
+        <v>414</v>
       </c>
       <c r="B274" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C274">
         <v>1</v>
       </c>
       <c r="D274" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="E274">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F274" t="s">
-        <v>466</v>
+        <v>581</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>298</v>
+        <v>413</v>
       </c>
       <c r="B275" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C275">
         <v>1</v>
       </c>
       <c r="D275" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="E275">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F275" t="s">
-        <v>465</v>
+        <v>580</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>297</v>
+        <v>412</v>
       </c>
       <c r="B276" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C276">
         <v>1</v>
       </c>
       <c r="D276" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="E276">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F276" t="s">
-        <v>464</v>
+        <v>579</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>441</v>
+        <v>410</v>
       </c>
       <c r="B277" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C277">
         <v>1</v>
       </c>
       <c r="D277" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="E277">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F277" t="s">
-        <v>608</v>
+        <v>577</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="B278" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C278">
         <v>1</v>
       </c>
       <c r="D278" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="E278">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F278" t="s">
-        <v>610</v>
+        <v>622</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>301</v>
+        <v>340</v>
       </c>
       <c r="B279" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C279">
         <v>1</v>
       </c>
       <c r="D279" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="E279">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F279" t="s">
-        <v>468</v>
+        <v>507</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>300</v>
+        <v>339</v>
       </c>
       <c r="B280" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C280">
         <v>1</v>
       </c>
       <c r="D280" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="E280">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F280" t="s">
-        <v>467</v>
+        <v>506</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>290</v>
+        <v>333</v>
       </c>
       <c r="B281" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C281">
         <v>1</v>
       </c>
       <c r="D281" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="E281">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F281" t="s">
-        <v>457</v>
+        <v>500</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>289</v>
+        <v>312</v>
       </c>
       <c r="B282" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C282">
         <v>1</v>
       </c>
       <c r="D282" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="E282">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F282" t="s">
-        <v>456</v>
+        <v>479</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>288</v>
+        <v>311</v>
       </c>
       <c r="B283" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C283">
         <v>1</v>
       </c>
       <c r="D283" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="E283">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F283" t="s">
-        <v>455</v>
+        <v>478</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="B284" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C284">
         <v>1</v>
       </c>
       <c r="D284" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="E284">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F284" t="s">
-        <v>459</v>
+        <v>477</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>291</v>
+        <v>273</v>
       </c>
       <c r="B285" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C285">
         <v>1</v>
       </c>
       <c r="D285" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="E285">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F285" t="s">
-        <v>458</v>
+        <v>440</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
@@ -7998,16 +8028,16 @@
         <v>619</v>
       </c>
       <c r="B286" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C286">
         <v>1</v>
       </c>
       <c r="D286" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="E286">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F286" t="s">
         <v>627</v>
@@ -8015,590 +8045,710 @@
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>618</v>
+        <v>261</v>
       </c>
       <c r="B287" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C287">
         <v>1</v>
       </c>
       <c r="D287" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="E287">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F287" t="s">
-        <v>626</v>
+        <v>268</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>294</v>
+        <v>418</v>
       </c>
       <c r="B288" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C288">
         <v>1</v>
       </c>
       <c r="D288" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="E288">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F288" t="s">
-        <v>461</v>
+        <v>585</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>293</v>
+        <v>316</v>
       </c>
       <c r="B289" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C289">
         <v>1</v>
       </c>
       <c r="D289" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="E289">
         <v>3</v>
       </c>
       <c r="F289" t="s">
-        <v>460</v>
+        <v>483</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>620</v>
+        <v>417</v>
       </c>
       <c r="B290" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C290">
         <v>1</v>
       </c>
       <c r="D290" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="E290">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F290" t="s">
-        <v>628</v>
+        <v>584</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>295</v>
+        <v>416</v>
       </c>
       <c r="B291" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C291">
         <v>1</v>
       </c>
       <c r="D291" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="E291">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F291" t="s">
-        <v>462</v>
+        <v>583</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>287</v>
+        <v>315</v>
       </c>
       <c r="B292" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C292">
         <v>1</v>
       </c>
       <c r="D292" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="E292">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F292" t="s">
-        <v>454</v>
+        <v>482</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>280</v>
+        <v>415</v>
       </c>
       <c r="B293" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C293">
         <v>1</v>
       </c>
       <c r="D293" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="E293">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F293" t="s">
-        <v>447</v>
+        <v>582</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>617</v>
+        <v>399</v>
       </c>
       <c r="B294" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C294">
         <v>1</v>
       </c>
       <c r="D294" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="E294">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F294" t="s">
-        <v>625</v>
+        <v>566</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>279</v>
+        <v>314</v>
       </c>
       <c r="B295" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C295">
         <v>1</v>
       </c>
       <c r="D295" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="E295">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F295" t="s">
-        <v>446</v>
+        <v>481</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>283</v>
+        <v>398</v>
       </c>
       <c r="B296" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C296">
         <v>1</v>
       </c>
       <c r="D296" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="E296">
         <v>2</v>
       </c>
       <c r="F296" t="s">
-        <v>450</v>
+        <v>565</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>282</v>
+        <v>397</v>
       </c>
       <c r="B297" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C297">
         <v>1</v>
       </c>
       <c r="D297" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="E297">
         <v>2</v>
       </c>
       <c r="F297" t="s">
-        <v>449</v>
+        <v>564</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>281</v>
+        <v>320</v>
       </c>
       <c r="B298" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C298">
         <v>1</v>
       </c>
       <c r="D298" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="E298">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F298" t="s">
-        <v>448</v>
+        <v>487</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>286</v>
+        <v>313</v>
       </c>
       <c r="B299" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C299">
         <v>1</v>
       </c>
       <c r="D299" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="E299">
         <v>3</v>
       </c>
       <c r="F299" t="s">
-        <v>453</v>
+        <v>480</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>285</v>
+        <v>396</v>
       </c>
       <c r="B300" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C300">
         <v>1</v>
       </c>
       <c r="D300" t="s">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="E300">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F300" t="s">
-        <v>452</v>
+        <v>563</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>284</v>
+        <v>319</v>
       </c>
       <c r="B301" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C301">
         <v>1</v>
       </c>
       <c r="D301" t="s">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="E301">
         <v>3</v>
       </c>
       <c r="F301" t="s">
-        <v>451</v>
+        <v>486</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>130</v>
+        <v>318</v>
       </c>
       <c r="B302" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C302">
         <v>1</v>
       </c>
       <c r="D302" t="s">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="E302">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F302" t="s">
-        <v>245</v>
+        <v>485</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>262</v>
+        <v>402</v>
       </c>
       <c r="B303" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C303">
         <v>1</v>
       </c>
       <c r="D303" t="s">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="E303">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F303" t="s">
-        <v>269</v>
+        <v>569</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>261</v>
+        <v>401</v>
       </c>
       <c r="B304" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C304">
         <v>1</v>
       </c>
       <c r="D304" t="s">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="E304">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F304" t="s">
-        <v>268</v>
+        <v>568</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>259</v>
+        <v>324</v>
       </c>
       <c r="B305" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C305">
         <v>1</v>
       </c>
       <c r="D305" t="s">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="E305">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F305" t="s">
-        <v>260</v>
+        <v>491</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>265</v>
+        <v>317</v>
       </c>
       <c r="B306" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C306">
         <v>1</v>
       </c>
       <c r="D306" t="s">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="E306">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F306" t="s">
-        <v>272</v>
+        <v>484</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>264</v>
+        <v>404</v>
       </c>
       <c r="B307" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C307">
         <v>1</v>
       </c>
       <c r="D307" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="E307">
         <v>2</v>
       </c>
       <c r="F307" t="s">
-        <v>271</v>
+        <v>571</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>263</v>
+        <v>323</v>
       </c>
       <c r="B308" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C308">
         <v>1</v>
       </c>
       <c r="D308" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="E308">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F308" t="s">
-        <v>270</v>
+        <v>490</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>275</v>
+        <v>322</v>
       </c>
       <c r="B309" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C309">
         <v>1</v>
       </c>
       <c r="D309" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="E309">
         <v>3</v>
       </c>
       <c r="F309" t="s">
-        <v>442</v>
+        <v>489</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>621</v>
+        <v>403</v>
       </c>
       <c r="B310" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C310">
         <v>1</v>
       </c>
       <c r="D310" t="s">
-        <v>84</v>
+        <v>126</v>
       </c>
       <c r="E310">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F310" t="s">
-        <v>629</v>
+        <v>570</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>267</v>
+        <v>321</v>
       </c>
       <c r="B311" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C311">
         <v>1</v>
       </c>
       <c r="D311" t="s">
-        <v>84</v>
+        <v>126</v>
       </c>
       <c r="E311">
         <v>3</v>
       </c>
       <c r="F311" t="s">
-        <v>274</v>
+        <v>488</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>266</v>
+        <v>408</v>
       </c>
       <c r="B312" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C312">
         <v>1</v>
       </c>
       <c r="D312" t="s">
-        <v>84</v>
+        <v>131</v>
       </c>
       <c r="E312">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F312" t="s">
-        <v>273</v>
+        <v>575</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>278</v>
+        <v>400</v>
       </c>
       <c r="B313" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C313">
         <v>1</v>
       </c>
       <c r="D313" t="s">
-        <v>84</v>
+        <v>131</v>
       </c>
       <c r="E313">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F313" t="s">
-        <v>445</v>
+        <v>567</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>277</v>
+        <v>302</v>
       </c>
       <c r="B314" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C314">
         <v>1</v>
       </c>
       <c r="D314" t="s">
-        <v>84</v>
+        <v>131</v>
       </c>
       <c r="E314">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F314" t="s">
-        <v>444</v>
+        <v>469</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>276</v>
+        <v>301</v>
       </c>
       <c r="B315" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C315">
         <v>1</v>
       </c>
       <c r="D315" t="s">
-        <v>84</v>
+        <v>131</v>
       </c>
       <c r="E315">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F315" t="s">
-        <v>443</v>
+        <v>468</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>407</v>
+      </c>
+      <c r="B316" t="s">
+        <v>256</v>
+      </c>
+      <c r="C316">
+        <v>1</v>
+      </c>
+      <c r="D316" t="s">
+        <v>137</v>
+      </c>
+      <c r="E316">
+        <v>2</v>
+      </c>
+      <c r="F316" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>300</v>
+      </c>
+      <c r="B317" t="s">
+        <v>256</v>
+      </c>
+      <c r="C317">
+        <v>1</v>
+      </c>
+      <c r="D317" t="s">
+        <v>137</v>
+      </c>
+      <c r="E317">
+        <v>3</v>
+      </c>
+      <c r="F317" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
+        <v>406</v>
+      </c>
+      <c r="B318" t="s">
+        <v>256</v>
+      </c>
+      <c r="C318">
+        <v>1</v>
+      </c>
+      <c r="D318" t="s">
+        <v>138</v>
+      </c>
+      <c r="E318">
+        <v>2</v>
+      </c>
+      <c r="F318" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>305</v>
+      </c>
+      <c r="B319" t="s">
+        <v>256</v>
+      </c>
+      <c r="C319">
+        <v>1</v>
+      </c>
+      <c r="D319" t="s">
+        <v>138</v>
+      </c>
+      <c r="E319">
+        <v>3</v>
+      </c>
+      <c r="F319" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>405</v>
+      </c>
+      <c r="B320" t="s">
+        <v>256</v>
+      </c>
+      <c r="C320">
+        <v>1</v>
+      </c>
+      <c r="D320" t="s">
+        <v>139</v>
+      </c>
+      <c r="E320">
+        <v>2</v>
+      </c>
+      <c r="F320" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A321" t="s">
+        <v>304</v>
+      </c>
+      <c r="B321" t="s">
+        <v>256</v>
+      </c>
+      <c r="C321">
+        <v>1</v>
+      </c>
+      <c r="D321" t="s">
+        <v>139</v>
+      </c>
+      <c r="E321">
+        <v>3</v>
+      </c>
+      <c r="F321" t="s">
+        <v>471</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F315">
-    <sortCondition descending="1" ref="C2:C315"/>
-    <sortCondition ref="D2:D315"/>
-    <sortCondition ref="E2:E315"/>
-    <sortCondition descending="1" ref="A2:A315"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F321">
+    <sortCondition descending="1" ref="C2:C321"/>
+    <sortCondition ref="D2:D321"/>
+    <sortCondition ref="E2:E321"/>
+    <sortCondition descending="1" ref="A2:A321"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/EOAT_data.xlsx
+++ b/data/EOAT_data.xlsx
@@ -1,23 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uramirez\Desktop\Inventario-main\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\procesos.CAZEL\Desktop\Becario Procesos\EOAT Project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7A38DBE-0396-4C6E-8DD3-12D4EA1C18CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A524E845-612F-43FA-9915-963291DDE71C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-4710" windowWidth="29040" windowHeight="15840" xr2:uid="{440E3869-3C3F-4E8C-A8BD-ADEB8E2EA552}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{440E3869-3C3F-4E8C-A8BD-ADEB8E2EA552}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$F$1</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1275" uniqueCount="648">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1252" uniqueCount="638">
   <si>
     <t>I-1937</t>
   </si>
@@ -248,6 +245,9 @@
     <t>I-1593</t>
   </si>
   <si>
+    <t>I-1620</t>
+  </si>
+  <si>
     <t>I-1598</t>
   </si>
   <si>
@@ -626,6 +626,9 @@
     <t>I-1593.jpeg</t>
   </si>
   <si>
+    <t>I-1620.jpeg</t>
+  </si>
+  <si>
     <t>I-1598.jpeg</t>
   </si>
   <si>
@@ -1947,42 +1950,6 @@
   </si>
   <si>
     <t>I-1945</t>
-  </si>
-  <si>
-    <t>I-1566</t>
-  </si>
-  <si>
-    <t>I-1566.jpeg</t>
-  </si>
-  <si>
-    <t>I-1581</t>
-  </si>
-  <si>
-    <t>I-1581.jpeg</t>
-  </si>
-  <si>
-    <t>I-1774</t>
-  </si>
-  <si>
-    <t>I-1774.jpeg</t>
-  </si>
-  <si>
-    <t>I-1930</t>
-  </si>
-  <si>
-    <t>I-1930.jpeg</t>
-  </si>
-  <si>
-    <t>I-1931.jpeg</t>
-  </si>
-  <si>
-    <t>I-1931</t>
-  </si>
-  <si>
-    <t>I-1556</t>
-  </si>
-  <si>
-    <t>I-1556.jpeg</t>
   </si>
 </sst>
 </file>
@@ -2360,7 +2327,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B6791C-A8A7-4753-A504-FAA9E3EE8745}">
-  <dimension ref="A1:F321"/>
+  <dimension ref="A1:F315"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -2373,22 +2340,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B1" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="C1" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D1" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E1" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F1" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -2396,116 +2363,116 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C3">
         <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C5">
         <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C6">
         <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C7">
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F7" t="s">
         <v>146</v>
@@ -2513,16 +2480,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C8">
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -2533,22 +2500,22 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C9">
         <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E9">
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -2556,36 +2523,36 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C10">
         <v>3</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C11">
         <v>3</v>
       </c>
       <c r="D11" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" t="s">
         <v>150</v>
@@ -2593,39 +2560,39 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C12">
         <v>3</v>
       </c>
       <c r="D12" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C13">
         <v>3</v>
       </c>
       <c r="D13" t="s">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F13" t="s">
         <v>152</v>
@@ -2633,22 +2600,22 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C14">
         <v>3</v>
       </c>
       <c r="D14" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -2656,19 +2623,19 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C15">
         <v>3</v>
       </c>
       <c r="D15" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E15">
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -2676,19 +2643,19 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C16">
         <v>3</v>
       </c>
       <c r="D16" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -2696,19 +2663,19 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C17">
         <v>3</v>
       </c>
       <c r="D17" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -2716,19 +2683,19 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C18">
         <v>3</v>
       </c>
       <c r="D18" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F18" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -2736,36 +2703,36 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C19">
         <v>3</v>
       </c>
       <c r="D19" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="E19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F19" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C20">
         <v>3</v>
       </c>
       <c r="D20" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F20" t="s">
         <v>159</v>
@@ -2773,16 +2740,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C21">
         <v>3</v>
       </c>
       <c r="D21" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="E21">
         <v>1</v>
@@ -2793,22 +2760,22 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B22" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C22">
         <v>3</v>
       </c>
       <c r="D22" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="E22">
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -2816,19 +2783,19 @@
         <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C23">
         <v>3</v>
       </c>
       <c r="D23" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="E23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -2836,19 +2803,19 @@
         <v>26</v>
       </c>
       <c r="B24" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C24">
         <v>3</v>
       </c>
       <c r="D24" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="E24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F24" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -2856,19 +2823,19 @@
         <v>27</v>
       </c>
       <c r="B25" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C25">
         <v>3</v>
       </c>
       <c r="D25" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="E25">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F25" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -2876,96 +2843,96 @@
         <v>28</v>
       </c>
       <c r="B26" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C26">
         <v>3</v>
       </c>
       <c r="D26" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="E26">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F26" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>30</v>
+        <v>612</v>
       </c>
       <c r="B27" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C27">
         <v>3</v>
       </c>
       <c r="D27" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E27">
         <v>1</v>
       </c>
       <c r="F27" t="s">
-        <v>165</v>
+        <v>614</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B28" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C28">
         <v>3</v>
       </c>
       <c r="D28" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E28">
         <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>609</v>
+        <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C29">
         <v>3</v>
       </c>
       <c r="D29" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29" t="s">
-        <v>611</v>
+        <v>166</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C30">
         <v>3</v>
       </c>
       <c r="D30" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F30" t="s">
         <v>167</v>
@@ -2973,16 +2940,16 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C31">
         <v>3</v>
       </c>
       <c r="D31" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="E31">
         <v>1</v>
@@ -2993,16 +2960,16 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B32" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C32">
         <v>3</v>
       </c>
       <c r="D32" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="E32">
         <v>1</v>
@@ -3013,19 +2980,19 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B33" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C33">
         <v>3</v>
       </c>
       <c r="D33" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="E33">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F33" t="s">
         <v>170</v>
@@ -3033,22 +3000,22 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B34" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C34">
         <v>3</v>
       </c>
       <c r="D34" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="E34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F34" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -3056,19 +3023,19 @@
         <v>37</v>
       </c>
       <c r="B35" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C35">
         <v>3</v>
       </c>
       <c r="D35" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="E35">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F35" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -3076,19 +3043,19 @@
         <v>38</v>
       </c>
       <c r="B36" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C36">
         <v>3</v>
       </c>
       <c r="D36" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="E36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F36" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -3096,19 +3063,19 @@
         <v>39</v>
       </c>
       <c r="B37" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C37">
         <v>3</v>
       </c>
       <c r="D37" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="E37">
         <v>1</v>
       </c>
       <c r="F37" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -3116,19 +3083,19 @@
         <v>41</v>
       </c>
       <c r="B38" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C38">
         <v>3</v>
       </c>
       <c r="D38" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="E38">
         <v>1</v>
       </c>
       <c r="F38" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -3136,19 +3103,19 @@
         <v>42</v>
       </c>
       <c r="B39" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C39">
         <v>3</v>
       </c>
       <c r="D39" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="E39">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F39" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -3156,19 +3123,19 @@
         <v>43</v>
       </c>
       <c r="B40" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C40">
         <v>3</v>
       </c>
       <c r="D40" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="E40">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F40" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -3176,159 +3143,159 @@
         <v>44</v>
       </c>
       <c r="B41" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C41">
         <v>3</v>
       </c>
       <c r="D41" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="E41">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F41" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B42" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C42">
         <v>3</v>
       </c>
       <c r="D42" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="E42">
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B43" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C43">
         <v>3</v>
       </c>
       <c r="D43" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="E43">
         <v>1</v>
       </c>
       <c r="F43" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B44" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C44">
         <v>3</v>
       </c>
       <c r="D44" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="E44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F44" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B45" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C45">
         <v>3</v>
       </c>
       <c r="D45" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="E45">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F45" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B46" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C46">
         <v>3</v>
       </c>
       <c r="D46" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="E46">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F46" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B47" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C47">
         <v>3</v>
       </c>
       <c r="D47" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="E47">
         <v>1</v>
       </c>
       <c r="F47" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C48">
         <v>3</v>
       </c>
       <c r="D48" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="E48">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F48" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -3336,33 +3303,33 @@
         <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C49">
         <v>3</v>
       </c>
       <c r="D49" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="E49">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F49" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C50">
         <v>3</v>
       </c>
       <c r="D50" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="E50">
         <v>1</v>
@@ -3373,42 +3340,42 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B51" t="s">
-        <v>631</v>
+        <v>258</v>
       </c>
       <c r="C51">
         <v>3</v>
       </c>
       <c r="D51" t="s">
-        <v>65</v>
-      </c>
-      <c r="E51">
-        <v>1</v>
+        <v>56</v>
+      </c>
+      <c r="E51" t="s">
+        <v>632</v>
       </c>
       <c r="F51" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B52" t="s">
-        <v>256</v>
+        <v>633</v>
       </c>
       <c r="C52">
         <v>3</v>
       </c>
       <c r="D52" t="s">
-        <v>65</v>
-      </c>
-      <c r="E52">
-        <v>1</v>
+        <v>56</v>
+      </c>
+      <c r="E52" t="s">
+        <v>632</v>
       </c>
       <c r="F52" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -3416,76 +3383,76 @@
         <v>60</v>
       </c>
       <c r="B53" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C53">
         <v>3</v>
       </c>
       <c r="D53" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E53">
         <v>1</v>
       </c>
       <c r="F53" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B54" t="s">
-        <v>64</v>
+        <v>258</v>
       </c>
       <c r="C54">
         <v>3</v>
       </c>
       <c r="D54" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E54">
         <v>1</v>
+      </c>
+      <c r="F54" t="s">
+        <v>192</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B55" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C55">
         <v>3</v>
       </c>
       <c r="D55" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E55">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B56" t="s">
-        <v>256</v>
+        <v>64</v>
       </c>
       <c r="C56">
         <v>3</v>
       </c>
       <c r="D56" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E56">
-        <v>1</v>
-      </c>
-      <c r="F56" t="s">
-        <v>192</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -3499,7 +3466,7 @@
         <v>3</v>
       </c>
       <c r="D57" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="E57">
         <v>1</v>
@@ -3516,10 +3483,10 @@
         <v>3</v>
       </c>
       <c r="D58" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="E58">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -3533,24 +3500,24 @@
         <v>3</v>
       </c>
       <c r="D59" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="E59">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B60" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C60">
         <v>3</v>
       </c>
       <c r="D60" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="E60">
         <v>1</v>
@@ -3558,19 +3525,19 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B61" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C61">
         <v>3</v>
       </c>
       <c r="D61" t="s">
-        <v>72</v>
+        <v>91</v>
       </c>
       <c r="E61">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -3578,1340 +3545,1343 @@
         <v>58</v>
       </c>
       <c r="B62" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C62">
         <v>3</v>
       </c>
       <c r="D62" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="E62">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F62" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B63" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C63">
         <v>3</v>
       </c>
       <c r="D63" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="E63">
         <v>1</v>
       </c>
       <c r="F63" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>94</v>
+      </c>
+      <c r="B64" t="s">
+        <v>258</v>
+      </c>
+      <c r="C64">
+        <v>3</v>
+      </c>
+      <c r="D64" t="s">
         <v>93</v>
       </c>
-      <c r="B64" t="s">
-        <v>256</v>
-      </c>
-      <c r="C64">
-        <v>3</v>
-      </c>
-      <c r="D64" t="s">
-        <v>76</v>
-      </c>
       <c r="E64">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F64" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B65" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C65">
         <v>3</v>
       </c>
       <c r="D65" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="E65">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F65" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B66" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C66">
         <v>3</v>
       </c>
       <c r="D66" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="E66">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F66" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B67" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C67">
         <v>3</v>
       </c>
       <c r="D67" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="E67">
         <v>1</v>
       </c>
       <c r="F67" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>99</v>
+      </c>
+      <c r="B68" t="s">
+        <v>258</v>
+      </c>
+      <c r="C68">
+        <v>3</v>
+      </c>
+      <c r="D68" t="s">
         <v>98</v>
       </c>
-      <c r="B68" t="s">
-        <v>256</v>
-      </c>
-      <c r="C68">
-        <v>3</v>
-      </c>
-      <c r="D68" t="s">
-        <v>83</v>
-      </c>
       <c r="E68">
         <v>1</v>
       </c>
       <c r="F68" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B69" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C69">
         <v>3</v>
       </c>
       <c r="D69" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="E69">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F69" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B70" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C70">
         <v>3</v>
       </c>
       <c r="D70" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="E70">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F70" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B71" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C71">
         <v>3</v>
       </c>
       <c r="D71" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="E71">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F71" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B72" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C72">
         <v>3</v>
       </c>
       <c r="D72" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="E72">
         <v>1</v>
       </c>
       <c r="F72" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>105</v>
+      </c>
+      <c r="B73" t="s">
+        <v>258</v>
+      </c>
+      <c r="C73">
+        <v>3</v>
+      </c>
+      <c r="D73" t="s">
         <v>104</v>
       </c>
-      <c r="B73" t="s">
-        <v>256</v>
-      </c>
-      <c r="C73">
-        <v>3</v>
-      </c>
-      <c r="D73" t="s">
-        <v>92</v>
-      </c>
       <c r="E73">
         <v>1</v>
       </c>
       <c r="F73" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B74" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C74">
         <v>3</v>
       </c>
       <c r="D74" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="E74">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F74" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B75" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C75">
         <v>3</v>
       </c>
       <c r="D75" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="E75">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F75" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B76" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C76">
         <v>3</v>
       </c>
       <c r="D76" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E76">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F76" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B77" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C77">
         <v>3</v>
       </c>
       <c r="D77" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E77">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F77" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="B78" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C78">
         <v>2</v>
       </c>
       <c r="D78" t="s">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="E78">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F78" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="B79" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C79">
         <v>2</v>
       </c>
       <c r="D79" t="s">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="E79">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F79" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="B80" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C80">
         <v>2</v>
       </c>
       <c r="D80" t="s">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="E80">
         <v>2</v>
       </c>
       <c r="F80" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="B81" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C81">
         <v>2</v>
       </c>
       <c r="D81" t="s">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="E81">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F81" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="B82" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C82">
         <v>2</v>
       </c>
       <c r="D82" t="s">
-        <v>1</v>
+        <v>67</v>
       </c>
       <c r="E82">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>82</v>
+        <v>637</v>
       </c>
       <c r="B83" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C83">
         <v>2</v>
       </c>
       <c r="D83" t="s">
-        <v>8</v>
+        <v>73</v>
       </c>
       <c r="E83">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F83" t="s">
-        <v>206</v>
+        <v>636</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="B84" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C84">
         <v>2</v>
       </c>
       <c r="D84" t="s">
-        <v>8</v>
+        <v>73</v>
       </c>
       <c r="E84">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F84" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="B85" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C85">
         <v>2</v>
       </c>
       <c r="D85" t="s">
-        <v>8</v>
+        <v>73</v>
       </c>
       <c r="E85">
         <v>2</v>
       </c>
       <c r="F85" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B86" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C86">
         <v>2</v>
       </c>
       <c r="D86" t="s">
-        <v>8</v>
+        <v>73</v>
       </c>
       <c r="E86">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F86" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="B87" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C87">
         <v>2</v>
       </c>
       <c r="D87" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="E87">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F87" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="B88" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C88">
         <v>2</v>
       </c>
       <c r="D88" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="E88">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F88" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="B89" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C89">
         <v>2</v>
       </c>
       <c r="D89" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="E89">
         <v>2</v>
       </c>
       <c r="F89" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="B90" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C90">
         <v>2</v>
       </c>
       <c r="D90" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="E90">
         <v>2</v>
       </c>
       <c r="F90" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="B91" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C91">
         <v>2</v>
       </c>
       <c r="D91" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="E91">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F91" t="s">
-        <v>228</v>
+        <v>206</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>114</v>
+        <v>82</v>
       </c>
       <c r="B92" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C92">
         <v>2</v>
       </c>
       <c r="D92" t="s">
-        <v>23</v>
+        <v>77</v>
       </c>
       <c r="E92">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F92" t="s">
-        <v>231</v>
+        <v>207</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>112</v>
+        <v>83</v>
       </c>
       <c r="B93" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C93">
         <v>2</v>
       </c>
       <c r="D93" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="E93">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F93" t="s">
-        <v>229</v>
+        <v>208</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>113</v>
+        <v>85</v>
       </c>
       <c r="B94" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C94">
         <v>2</v>
       </c>
       <c r="D94" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="E94">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F94" t="s">
-        <v>230</v>
+        <v>209</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="B95" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C95">
         <v>2</v>
       </c>
       <c r="D95" t="s">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="E95">
         <v>2</v>
       </c>
       <c r="F95" t="s">
-        <v>232</v>
+        <v>210</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="B96" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C96">
         <v>2</v>
       </c>
       <c r="D96" t="s">
-        <v>29</v>
+        <v>84</v>
       </c>
       <c r="E96">
         <v>2</v>
       </c>
       <c r="F96" t="s">
-        <v>233</v>
+        <v>211</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>118</v>
+        <v>88</v>
       </c>
       <c r="B97" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C97">
         <v>2</v>
       </c>
       <c r="D97" t="s">
-        <v>29</v>
+        <v>84</v>
       </c>
       <c r="E97">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F97" t="s">
-        <v>234</v>
+        <v>212</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="B98" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C98">
         <v>2</v>
       </c>
       <c r="D98" t="s">
-        <v>29</v>
+        <v>84</v>
       </c>
       <c r="E98">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F98" t="s">
-        <v>235</v>
+        <v>213</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="B99" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C99">
         <v>2</v>
       </c>
       <c r="D99" t="s">
-        <v>29</v>
+        <v>111</v>
       </c>
       <c r="E99">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F99" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>127</v>
+        <v>112</v>
       </c>
       <c r="B100" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C100">
         <v>2</v>
       </c>
       <c r="D100" t="s">
-        <v>33</v>
+        <v>111</v>
       </c>
       <c r="E100">
         <v>2</v>
       </c>
       <c r="F100" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="B101" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C101">
         <v>2</v>
       </c>
       <c r="D101" t="s">
-        <v>33</v>
+        <v>111</v>
       </c>
       <c r="E101">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F101" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="B102" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C102">
         <v>2</v>
       </c>
       <c r="D102" t="s">
-        <v>33</v>
+        <v>111</v>
       </c>
       <c r="E102">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F102" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="B103" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C103">
         <v>2</v>
       </c>
       <c r="D103" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="E103">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F103" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="B104" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C104">
         <v>2</v>
       </c>
       <c r="D104" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="E104">
         <v>2</v>
       </c>
       <c r="F104" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="B105" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C105">
         <v>2</v>
       </c>
       <c r="D105" t="s">
-        <v>40</v>
+        <v>116</v>
       </c>
       <c r="E105">
         <v>2</v>
       </c>
       <c r="F105" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="B106" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C106">
         <v>2</v>
       </c>
       <c r="D106" t="s">
-        <v>40</v>
+        <v>116</v>
       </c>
       <c r="E106">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F106" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B107" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C107">
         <v>2</v>
       </c>
       <c r="D107" t="s">
-        <v>40</v>
+        <v>116</v>
       </c>
       <c r="E107">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F107" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="B108" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C108">
         <v>2</v>
       </c>
       <c r="D108" t="s">
-        <v>40</v>
+        <v>122</v>
       </c>
       <c r="E108">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F108" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="B109" t="s">
-        <v>89</v>
+        <v>258</v>
       </c>
       <c r="C109">
         <v>2</v>
       </c>
       <c r="D109" t="s">
-        <v>46</v>
+        <v>122</v>
       </c>
       <c r="E109">
         <v>2</v>
+      </c>
+      <c r="F109" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="B110" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C110">
         <v>2</v>
       </c>
       <c r="D110" t="s">
-        <v>46</v>
+        <v>122</v>
       </c>
       <c r="E110">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F110" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="B111" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C111">
         <v>2</v>
       </c>
       <c r="D111" t="s">
-        <v>46</v>
+        <v>122</v>
       </c>
       <c r="E111">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F111" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="B112" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C112">
         <v>2</v>
       </c>
       <c r="D112" t="s">
-        <v>46</v>
+        <v>127</v>
       </c>
       <c r="E112">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F112" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>89</v>
+        <v>128</v>
       </c>
       <c r="B113" t="s">
-        <v>89</v>
+        <v>258</v>
       </c>
       <c r="C113">
         <v>2</v>
       </c>
       <c r="D113" t="s">
-        <v>52</v>
+        <v>127</v>
       </c>
       <c r="E113">
         <v>2</v>
+      </c>
+      <c r="F113" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>89</v>
+        <v>129</v>
       </c>
       <c r="B114" t="s">
-        <v>89</v>
+        <v>258</v>
       </c>
       <c r="C114">
         <v>2</v>
       </c>
       <c r="D114" t="s">
-        <v>52</v>
+        <v>127</v>
       </c>
       <c r="E114">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="F114" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>89</v>
+        <v>131</v>
       </c>
       <c r="B115" t="s">
-        <v>89</v>
+        <v>258</v>
       </c>
       <c r="C115">
         <v>2</v>
       </c>
       <c r="D115" t="s">
-        <v>52</v>
+        <v>132</v>
       </c>
       <c r="E115">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F115" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>89</v>
+        <v>133</v>
       </c>
       <c r="B116" t="s">
-        <v>89</v>
+        <v>258</v>
       </c>
       <c r="C116">
         <v>2</v>
       </c>
       <c r="D116" t="s">
-        <v>52</v>
+        <v>132</v>
       </c>
       <c r="E116">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="F116" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>89</v>
+        <v>134</v>
       </c>
       <c r="B117" t="s">
-        <v>89</v>
+        <v>258</v>
       </c>
       <c r="C117">
         <v>2</v>
       </c>
       <c r="D117" t="s">
-        <v>56</v>
+        <v>132</v>
       </c>
       <c r="E117">
         <v>2</v>
+      </c>
+      <c r="F117" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>89</v>
+        <v>135</v>
       </c>
       <c r="B118" t="s">
-        <v>89</v>
+        <v>258</v>
       </c>
       <c r="C118">
         <v>2</v>
       </c>
       <c r="D118" t="s">
-        <v>56</v>
+        <v>132</v>
       </c>
       <c r="E118">
         <v>2</v>
+      </c>
+      <c r="F118" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>89</v>
+        <v>136</v>
       </c>
       <c r="B119" t="s">
-        <v>89</v>
+        <v>258</v>
       </c>
       <c r="C119">
         <v>2</v>
       </c>
       <c r="D119" t="s">
-        <v>56</v>
+        <v>132</v>
       </c>
       <c r="E119">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="F119" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>632</v>
+        <v>137</v>
       </c>
       <c r="B120" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C120">
         <v>2</v>
       </c>
       <c r="D120" t="s">
-        <v>56</v>
+        <v>132</v>
       </c>
       <c r="E120">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F120" t="s">
-        <v>633</v>
+        <v>251</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="B121" t="s">
-        <v>256</v>
+        <v>90</v>
       </c>
       <c r="C121">
         <v>2</v>
       </c>
       <c r="D121" t="s">
-        <v>110</v>
+        <v>138</v>
       </c>
       <c r="E121">
         <v>1</v>
-      </c>
-      <c r="F121" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="B122" t="s">
-        <v>256</v>
+        <v>90</v>
       </c>
       <c r="C122">
         <v>2</v>
       </c>
       <c r="D122" t="s">
-        <v>115</v>
+        <v>138</v>
       </c>
       <c r="E122">
-        <v>1</v>
-      </c>
-      <c r="F122" t="s">
-        <v>194</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B123" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C123">
         <v>2</v>
       </c>
       <c r="D123" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="E123">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="B124" t="s">
-        <v>256</v>
+        <v>90</v>
       </c>
       <c r="C124">
         <v>2</v>
       </c>
       <c r="D124" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="E124">
         <v>1</v>
-      </c>
-      <c r="F124" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>635</v>
+        <v>90</v>
       </c>
       <c r="B125" t="s">
-        <v>256</v>
+        <v>90</v>
       </c>
       <c r="C125">
         <v>2</v>
       </c>
       <c r="D125" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E125">
-        <v>1</v>
-      </c>
-      <c r="F125" t="s">
-        <v>634</v>
+        <v>2</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>70</v>
+        <v>634</v>
       </c>
       <c r="B126" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C126">
         <v>2</v>
       </c>
       <c r="D126" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="E126">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F126" t="s">
-        <v>196</v>
+        <v>635</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="B127" t="s">
-        <v>256</v>
+        <v>90</v>
       </c>
       <c r="C127">
         <v>2</v>
       </c>
       <c r="D127" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E127">
         <v>1</v>
-      </c>
-      <c r="F127" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="B128" t="s">
-        <v>256</v>
+        <v>90</v>
       </c>
       <c r="C128">
         <v>2</v>
       </c>
       <c r="D128" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E128">
-        <v>1</v>
-      </c>
-      <c r="F128" t="s">
-        <v>198</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="B129" t="s">
-        <v>256</v>
+        <v>90</v>
       </c>
       <c r="C129">
         <v>2</v>
       </c>
       <c r="D129" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E129">
-        <v>1</v>
-      </c>
-      <c r="F129" t="s">
-        <v>199</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>645</v>
+        <v>432</v>
       </c>
       <c r="B130" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C130">
         <v>1</v>
@@ -4923,15 +4893,15 @@
         <v>1</v>
       </c>
       <c r="F130" t="s">
-        <v>644</v>
+        <v>599</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>642</v>
+        <v>430</v>
       </c>
       <c r="B131" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C131">
         <v>1</v>
@@ -4943,15 +4913,15 @@
         <v>1</v>
       </c>
       <c r="F131" t="s">
-        <v>643</v>
+        <v>597</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>640</v>
+        <v>433</v>
       </c>
       <c r="B132" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C132">
         <v>1</v>
@@ -4960,18 +4930,18 @@
         <v>1</v>
       </c>
       <c r="E132">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F132" t="s">
-        <v>641</v>
+        <v>600</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>638</v>
+        <v>437</v>
       </c>
       <c r="B133" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C133">
         <v>1</v>
@@ -4980,18 +4950,18 @@
         <v>1</v>
       </c>
       <c r="E133">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F133" t="s">
-        <v>639</v>
+        <v>604</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>646</v>
+        <v>440</v>
       </c>
       <c r="B134" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C134">
         <v>1</v>
@@ -5000,18 +4970,18 @@
         <v>1</v>
       </c>
       <c r="E134">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F134" t="s">
-        <v>647</v>
+        <v>607</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>388</v>
+        <v>439</v>
       </c>
       <c r="B135" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C135">
         <v>1</v>
@@ -5023,15 +4993,15 @@
         <v>3</v>
       </c>
       <c r="F135" t="s">
-        <v>555</v>
+        <v>606</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>387</v>
+        <v>434</v>
       </c>
       <c r="B136" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C136">
         <v>1</v>
@@ -5043,15 +5013,15 @@
         <v>3</v>
       </c>
       <c r="F136" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>385</v>
+        <v>436</v>
       </c>
       <c r="B137" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C137">
         <v>1</v>
@@ -5060,18 +5030,18 @@
         <v>1</v>
       </c>
       <c r="E137">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F137" t="s">
-        <v>552</v>
+        <v>603</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>384</v>
+        <v>435</v>
       </c>
       <c r="B138" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C138">
         <v>1</v>
@@ -5080,18 +5050,18 @@
         <v>1</v>
       </c>
       <c r="E138">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F138" t="s">
-        <v>551</v>
+        <v>602</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>620</v>
+        <v>438</v>
       </c>
       <c r="B139" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C139">
         <v>1</v>
@@ -5103,15 +5073,15 @@
         <v>4</v>
       </c>
       <c r="F139" t="s">
-        <v>628</v>
+        <v>605</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>307</v>
+        <v>615</v>
       </c>
       <c r="B140" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C140">
         <v>1</v>
@@ -5123,55 +5093,55 @@
         <v>4</v>
       </c>
       <c r="F140" t="s">
-        <v>474</v>
+        <v>623</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>306</v>
+        <v>423</v>
       </c>
       <c r="B141" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C141">
         <v>1</v>
       </c>
       <c r="D141" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E141">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F141" t="s">
-        <v>473</v>
+        <v>590</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>303</v>
+        <v>422</v>
       </c>
       <c r="B142" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C142">
         <v>1</v>
       </c>
       <c r="D142" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="E142">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F142" t="s">
-        <v>470</v>
+        <v>589</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>636</v>
+        <v>421</v>
       </c>
       <c r="B143" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C143">
         <v>1</v>
@@ -5183,15 +5153,15 @@
         <v>1</v>
       </c>
       <c r="F143" t="s">
-        <v>637</v>
+        <v>588</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>392</v>
+        <v>425</v>
       </c>
       <c r="B144" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C144">
         <v>1</v>
@@ -5200,18 +5170,18 @@
         <v>8</v>
       </c>
       <c r="E144">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F144" t="s">
-        <v>559</v>
+        <v>592</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>391</v>
+        <v>424</v>
       </c>
       <c r="B145" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C145">
         <v>1</v>
@@ -5220,18 +5190,18 @@
         <v>8</v>
       </c>
       <c r="E145">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F145" t="s">
-        <v>558</v>
+        <v>591</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>390</v>
+        <v>427</v>
       </c>
       <c r="B146" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C146">
         <v>1</v>
@@ -5243,15 +5213,15 @@
         <v>3</v>
       </c>
       <c r="F146" t="s">
-        <v>557</v>
+        <v>594</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>386</v>
+        <v>426</v>
       </c>
       <c r="B147" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C147">
         <v>1</v>
@@ -5263,15 +5233,15 @@
         <v>3</v>
       </c>
       <c r="F147" t="s">
-        <v>553</v>
+        <v>593</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>309</v>
+        <v>431</v>
       </c>
       <c r="B148" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C148">
         <v>1</v>
@@ -5283,15 +5253,15 @@
         <v>4</v>
       </c>
       <c r="F148" t="s">
-        <v>476</v>
+        <v>598</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>308</v>
+        <v>429</v>
       </c>
       <c r="B149" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C149">
         <v>1</v>
@@ -5303,15 +5273,15 @@
         <v>4</v>
       </c>
       <c r="F149" t="s">
-        <v>475</v>
+        <v>596</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>294</v>
+        <v>428</v>
       </c>
       <c r="B150" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C150">
         <v>1</v>
@@ -5323,15 +5293,15 @@
         <v>4</v>
       </c>
       <c r="F150" t="s">
-        <v>461</v>
+        <v>595</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>395</v>
+        <v>411</v>
       </c>
       <c r="B151" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C151">
         <v>1</v>
@@ -5340,18 +5310,18 @@
         <v>15</v>
       </c>
       <c r="E151">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F151" t="s">
-        <v>562</v>
+        <v>578</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>394</v>
+        <v>413</v>
       </c>
       <c r="B152" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C152">
         <v>1</v>
@@ -5360,18 +5330,18 @@
         <v>15</v>
       </c>
       <c r="E152">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F152" t="s">
-        <v>561</v>
+        <v>580</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>393</v>
+        <v>412</v>
       </c>
       <c r="B153" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C153">
         <v>1</v>
@@ -5380,18 +5350,18 @@
         <v>15</v>
       </c>
       <c r="E153">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F153" t="s">
-        <v>560</v>
+        <v>579</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>389</v>
+        <v>616</v>
       </c>
       <c r="B154" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C154">
         <v>1</v>
@@ -5400,18 +5370,18 @@
         <v>15</v>
       </c>
       <c r="E154">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F154" t="s">
-        <v>556</v>
+        <v>624</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>376</v>
+        <v>416</v>
       </c>
       <c r="B155" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C155">
         <v>1</v>
@@ -5423,15 +5393,15 @@
         <v>3</v>
       </c>
       <c r="F155" t="s">
-        <v>543</v>
+        <v>583</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>375</v>
+        <v>415</v>
       </c>
       <c r="B156" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C156">
         <v>1</v>
@@ -5443,15 +5413,15 @@
         <v>3</v>
       </c>
       <c r="F156" t="s">
-        <v>542</v>
+        <v>582</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>89</v>
+        <v>414</v>
       </c>
       <c r="B157" t="s">
-        <v>89</v>
+        <v>258</v>
       </c>
       <c r="C157">
         <v>1</v>
@@ -5460,15 +5430,18 @@
         <v>15</v>
       </c>
       <c r="E157">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="F157" t="s">
+        <v>581</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>297</v>
+        <v>420</v>
       </c>
       <c r="B158" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C158">
         <v>1</v>
@@ -5480,15 +5453,15 @@
         <v>4</v>
       </c>
       <c r="F158" t="s">
-        <v>464</v>
+        <v>587</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>296</v>
+        <v>419</v>
       </c>
       <c r="B159" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C159">
         <v>1</v>
@@ -5500,15 +5473,15 @@
         <v>4</v>
       </c>
       <c r="F159" t="s">
-        <v>463</v>
+        <v>586</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>295</v>
+        <v>418</v>
       </c>
       <c r="B160" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C160">
         <v>1</v>
@@ -5520,35 +5493,35 @@
         <v>4</v>
       </c>
       <c r="F160" t="s">
-        <v>462</v>
+        <v>585</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>380</v>
+        <v>417</v>
       </c>
       <c r="B161" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C161">
         <v>1</v>
       </c>
       <c r="D161" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E161">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F161" t="s">
-        <v>547</v>
+        <v>584</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>379</v>
+        <v>401</v>
       </c>
       <c r="B162" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C162">
         <v>1</v>
@@ -5557,18 +5530,18 @@
         <v>23</v>
       </c>
       <c r="E162">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F162" t="s">
-        <v>546</v>
+        <v>568</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>378</v>
+        <v>400</v>
       </c>
       <c r="B163" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C163">
         <v>1</v>
@@ -5577,18 +5550,18 @@
         <v>23</v>
       </c>
       <c r="E163">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F163" t="s">
-        <v>545</v>
+        <v>567</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>377</v>
+        <v>399</v>
       </c>
       <c r="B164" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C164">
         <v>1</v>
@@ -5597,18 +5570,18 @@
         <v>23</v>
       </c>
       <c r="E164">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F164" t="s">
-        <v>544</v>
+        <v>566</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>374</v>
+        <v>398</v>
       </c>
       <c r="B165" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C165">
         <v>1</v>
@@ -5617,18 +5590,18 @@
         <v>23</v>
       </c>
       <c r="E165">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F165" t="s">
-        <v>541</v>
+        <v>565</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>439</v>
+        <v>404</v>
       </c>
       <c r="B166" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C166">
         <v>1</v>
@@ -5637,18 +5610,18 @@
         <v>23</v>
       </c>
       <c r="E166">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F166" t="s">
-        <v>606</v>
+        <v>571</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>607</v>
+        <v>403</v>
       </c>
       <c r="B167" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C167">
         <v>1</v>
@@ -5657,18 +5630,18 @@
         <v>23</v>
       </c>
       <c r="E167">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F167" t="s">
-        <v>608</v>
+        <v>570</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>299</v>
+        <v>406</v>
       </c>
       <c r="B168" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C168">
         <v>1</v>
@@ -5677,18 +5650,18 @@
         <v>23</v>
       </c>
       <c r="E168">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F168" t="s">
-        <v>466</v>
+        <v>573</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>298</v>
+        <v>405</v>
       </c>
       <c r="B169" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C169">
         <v>1</v>
@@ -5697,118 +5670,118 @@
         <v>23</v>
       </c>
       <c r="E169">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F169" t="s">
-        <v>465</v>
+        <v>572</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>383</v>
+        <v>402</v>
       </c>
       <c r="B170" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C170">
         <v>1</v>
       </c>
       <c r="D170" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E170">
         <v>3</v>
       </c>
       <c r="F170" t="s">
-        <v>550</v>
+        <v>569</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>382</v>
+        <v>410</v>
       </c>
       <c r="B171" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C171">
         <v>1</v>
       </c>
       <c r="D171" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E171">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F171" t="s">
-        <v>549</v>
+        <v>577</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>381</v>
+        <v>409</v>
       </c>
       <c r="B172" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C172">
         <v>1</v>
       </c>
       <c r="D172" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E172">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F172" t="s">
-        <v>548</v>
+        <v>576</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>367</v>
+        <v>408</v>
       </c>
       <c r="B173" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C173">
         <v>1</v>
       </c>
       <c r="D173" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E173">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F173" t="s">
-        <v>534</v>
+        <v>575</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>366</v>
+        <v>407</v>
       </c>
       <c r="B174" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C174">
         <v>1</v>
       </c>
       <c r="D174" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E174">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F174" t="s">
-        <v>533</v>
+        <v>574</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>288</v>
+        <v>387</v>
       </c>
       <c r="B175" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C175">
         <v>1</v>
@@ -5817,18 +5790,18 @@
         <v>29</v>
       </c>
       <c r="E175">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F175" t="s">
-        <v>455</v>
+        <v>554</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>287</v>
+        <v>386</v>
       </c>
       <c r="B176" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C176">
         <v>1</v>
@@ -5837,18 +5810,18 @@
         <v>29</v>
       </c>
       <c r="E176">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F176" t="s">
-        <v>454</v>
+        <v>553</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>286</v>
+        <v>390</v>
       </c>
       <c r="B177" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C177">
         <v>1</v>
@@ -5857,2170 +5830,2167 @@
         <v>29</v>
       </c>
       <c r="E177">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F177" t="s">
-        <v>453</v>
+        <v>557</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>373</v>
+        <v>389</v>
       </c>
       <c r="B178" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C178">
         <v>1</v>
       </c>
       <c r="D178" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E178">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F178" t="s">
-        <v>540</v>
+        <v>556</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>370</v>
+        <v>388</v>
       </c>
       <c r="B179" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C179">
         <v>1</v>
       </c>
       <c r="D179" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E179">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F179" t="s">
-        <v>537</v>
+        <v>555</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>369</v>
+        <v>394</v>
       </c>
       <c r="B180" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C180">
         <v>1</v>
       </c>
       <c r="D180" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E180">
         <v>3</v>
       </c>
       <c r="F180" t="s">
-        <v>536</v>
+        <v>561</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>368</v>
+        <v>393</v>
       </c>
       <c r="B181" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C181">
         <v>1</v>
       </c>
       <c r="D181" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E181">
         <v>3</v>
       </c>
       <c r="F181" t="s">
-        <v>535</v>
+        <v>560</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>365</v>
+        <v>392</v>
       </c>
       <c r="B182" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C182">
         <v>1</v>
       </c>
       <c r="D182" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E182">
         <v>3</v>
       </c>
       <c r="F182" t="s">
-        <v>532</v>
+        <v>559</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>290</v>
+        <v>391</v>
       </c>
       <c r="B183" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C183">
         <v>1</v>
       </c>
       <c r="D183" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E183">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F183" t="s">
-        <v>457</v>
+        <v>558</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>289</v>
+        <v>397</v>
       </c>
       <c r="B184" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C184">
         <v>1</v>
       </c>
       <c r="D184" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E184">
         <v>4</v>
       </c>
       <c r="F184" t="s">
-        <v>456</v>
+        <v>564</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>372</v>
+        <v>396</v>
       </c>
       <c r="B185" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C185">
         <v>1</v>
       </c>
       <c r="D185" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E185">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F185" t="s">
-        <v>539</v>
+        <v>563</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>371</v>
+        <v>395</v>
       </c>
       <c r="B186" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C186">
         <v>1</v>
       </c>
       <c r="D186" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E186">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F186" t="s">
-        <v>538</v>
+        <v>562</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>276</v>
+        <v>378</v>
       </c>
       <c r="B187" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C187">
         <v>1</v>
       </c>
       <c r="D187" t="s">
-        <v>40</v>
-      </c>
-      <c r="E187" t="s">
-        <v>629</v>
+        <v>33</v>
+      </c>
+      <c r="E187">
+        <v>1</v>
       </c>
       <c r="F187" t="s">
-        <v>443</v>
+        <v>545</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>275</v>
+        <v>377</v>
       </c>
       <c r="B188" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C188">
         <v>1</v>
       </c>
       <c r="D188" t="s">
-        <v>40</v>
-      </c>
-      <c r="E188" t="s">
-        <v>629</v>
+        <v>33</v>
+      </c>
+      <c r="E188">
+        <v>1</v>
       </c>
       <c r="F188" t="s">
-        <v>442</v>
+        <v>544</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>274</v>
+        <v>376</v>
       </c>
       <c r="B189" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C189">
         <v>1</v>
       </c>
       <c r="D189" t="s">
-        <v>40</v>
-      </c>
-      <c r="E189" t="s">
-        <v>629</v>
+        <v>33</v>
+      </c>
+      <c r="E189">
+        <v>1</v>
       </c>
       <c r="F189" t="s">
-        <v>441</v>
+        <v>543</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>358</v>
+        <v>380</v>
       </c>
       <c r="B190" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C190">
         <v>1</v>
       </c>
       <c r="D190" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="E190">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F190" t="s">
-        <v>525</v>
+        <v>547</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="B191" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C191">
         <v>1</v>
       </c>
       <c r="D191" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="E191">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F191" t="s">
-        <v>524</v>
+        <v>546</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>355</v>
+        <v>382</v>
       </c>
       <c r="B192" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C192">
         <v>1</v>
       </c>
       <c r="D192" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="E192">
         <v>3</v>
       </c>
       <c r="F192" t="s">
-        <v>522</v>
+        <v>549</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>354</v>
+        <v>381</v>
       </c>
       <c r="B193" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C193">
         <v>1</v>
       </c>
       <c r="D193" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="E193">
         <v>3</v>
       </c>
       <c r="F193" t="s">
-        <v>521</v>
+        <v>548</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>353</v>
+        <v>385</v>
       </c>
       <c r="B194" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C194">
         <v>1</v>
       </c>
       <c r="D194" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="E194">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F194" t="s">
-        <v>520</v>
+        <v>552</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>292</v>
+        <v>384</v>
       </c>
       <c r="B195" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C195">
         <v>1</v>
       </c>
       <c r="D195" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="E195">
         <v>4</v>
       </c>
       <c r="F195" t="s">
-        <v>459</v>
+        <v>551</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>617</v>
+        <v>383</v>
       </c>
       <c r="B196" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C196">
         <v>1</v>
       </c>
       <c r="D196" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="E196">
         <v>4</v>
       </c>
       <c r="F196" t="s">
-        <v>625</v>
+        <v>550</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>616</v>
+        <v>369</v>
       </c>
       <c r="B197" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C197">
         <v>1</v>
       </c>
       <c r="D197" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E197">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F197" t="s">
-        <v>624</v>
+        <v>536</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="B198" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C198">
         <v>1</v>
       </c>
       <c r="D198" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="E198">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F198" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="B199" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C199">
         <v>1</v>
       </c>
       <c r="D199" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="E199">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F199" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>356</v>
+        <v>372</v>
       </c>
       <c r="B200" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C200">
         <v>1</v>
       </c>
       <c r="D200" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="E200">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F200" t="s">
-        <v>523</v>
+        <v>539</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>293</v>
+        <v>371</v>
       </c>
       <c r="B201" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C201">
         <v>1</v>
       </c>
       <c r="D201" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="E201">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F201" t="s">
-        <v>460</v>
+        <v>538</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>291</v>
+        <v>370</v>
       </c>
       <c r="B202" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C202">
         <v>1</v>
       </c>
       <c r="D202" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="E202">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F202" t="s">
-        <v>458</v>
+        <v>537</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>618</v>
+        <v>375</v>
       </c>
       <c r="B203" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C203">
         <v>1</v>
       </c>
       <c r="D203" t="s">
-        <v>52</v>
-      </c>
-      <c r="E203">
-        <v>4</v>
+        <v>40</v>
+      </c>
+      <c r="E203" t="s">
+        <v>631</v>
       </c>
       <c r="F203" t="s">
-        <v>626</v>
+        <v>542</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="B204" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C204">
         <v>1</v>
       </c>
       <c r="D204" t="s">
-        <v>56</v>
-      </c>
-      <c r="E204">
-        <v>3</v>
+        <v>40</v>
+      </c>
+      <c r="E204" t="s">
+        <v>631</v>
       </c>
       <c r="F204" t="s">
-        <v>531</v>
+        <v>541</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="B205" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C205">
         <v>1</v>
       </c>
       <c r="D205" t="s">
-        <v>56</v>
-      </c>
-      <c r="E205">
-        <v>3</v>
+        <v>40</v>
+      </c>
+      <c r="E205" t="s">
+        <v>631</v>
       </c>
       <c r="F205" t="s">
-        <v>530</v>
+        <v>540</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="B206" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C206">
         <v>1</v>
       </c>
       <c r="D206" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="E206">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F206" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B207" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C207">
         <v>1</v>
       </c>
       <c r="D207" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="E207">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F207" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="B208" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C208">
         <v>1</v>
       </c>
       <c r="D208" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="E208">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F208" t="s">
-        <v>511</v>
+        <v>522</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>343</v>
+        <v>360</v>
       </c>
       <c r="B209" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C209">
         <v>1</v>
       </c>
       <c r="D209" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="E209">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F209" t="s">
-        <v>510</v>
+        <v>527</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>285</v>
+        <v>359</v>
       </c>
       <c r="B210" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C210">
         <v>1</v>
       </c>
       <c r="D210" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="E210">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F210" t="s">
-        <v>452</v>
+        <v>526</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>278</v>
+        <v>358</v>
       </c>
       <c r="B211" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C211">
         <v>1</v>
       </c>
       <c r="D211" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="E211">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F211" t="s">
-        <v>445</v>
+        <v>525</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>265</v>
+        <v>363</v>
       </c>
       <c r="B212" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C212">
         <v>1</v>
       </c>
       <c r="D212" t="s">
-        <v>56</v>
-      </c>
-      <c r="E212" t="s">
-        <v>630</v>
+        <v>46</v>
+      </c>
+      <c r="E212">
+        <v>3</v>
       </c>
       <c r="F212" t="s">
-        <v>272</v>
+        <v>530</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>264</v>
+        <v>362</v>
       </c>
       <c r="B213" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C213">
         <v>1</v>
       </c>
       <c r="D213" t="s">
-        <v>56</v>
-      </c>
-      <c r="E213" t="s">
-        <v>630</v>
+        <v>46</v>
+      </c>
+      <c r="E213">
+        <v>3</v>
       </c>
       <c r="F213" t="s">
-        <v>271</v>
+        <v>529</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>431</v>
+        <v>361</v>
       </c>
       <c r="B214" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C214">
         <v>1</v>
       </c>
       <c r="D214" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="E214">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F214" t="s">
-        <v>598</v>
+        <v>528</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>435</v>
+        <v>366</v>
       </c>
       <c r="B215" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C215">
         <v>1</v>
       </c>
       <c r="D215" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="E215">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F215" t="s">
-        <v>602</v>
+        <v>533</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>438</v>
+        <v>365</v>
       </c>
       <c r="B216" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C216">
         <v>1</v>
       </c>
       <c r="D216" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="E216">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F216" t="s">
-        <v>605</v>
+        <v>532</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>430</v>
+        <v>364</v>
       </c>
       <c r="B217" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C217">
         <v>1</v>
       </c>
       <c r="D217" t="s">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="E217">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F217" t="s">
-        <v>597</v>
+        <v>531</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>428</v>
+        <v>346</v>
       </c>
       <c r="B218" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C218">
         <v>1</v>
       </c>
       <c r="D218" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="E218">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F218" t="s">
-        <v>595</v>
+        <v>513</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B219" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C219">
         <v>1</v>
       </c>
       <c r="D219" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="E219">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F219" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B220" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C220">
         <v>1</v>
       </c>
       <c r="D220" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="E220">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F220" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B221" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C221">
         <v>1</v>
       </c>
       <c r="D221" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="E221">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F221" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="B222" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C222">
         <v>1</v>
       </c>
       <c r="D222" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="E222">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F222" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="B223" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C223">
         <v>1</v>
       </c>
       <c r="D223" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="E223">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F223" t="s">
-        <v>508</v>
+        <v>515</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>281</v>
+        <v>347</v>
       </c>
       <c r="B224" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C224">
         <v>1</v>
       </c>
       <c r="D224" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="E224">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F224" t="s">
-        <v>448</v>
+        <v>514</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>280</v>
+        <v>351</v>
       </c>
       <c r="B225" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C225">
         <v>1</v>
       </c>
       <c r="D225" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="E225">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F225" t="s">
-        <v>447</v>
+        <v>518</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>615</v>
+        <v>350</v>
       </c>
       <c r="B226" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C226">
         <v>1</v>
       </c>
       <c r="D226" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="E226">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F226" t="s">
-        <v>623</v>
+        <v>517</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>277</v>
+        <v>354</v>
       </c>
       <c r="B227" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C227">
         <v>1</v>
       </c>
       <c r="D227" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="E227">
         <v>4</v>
       </c>
       <c r="F227" t="s">
-        <v>444</v>
+        <v>521</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>434</v>
+        <v>353</v>
       </c>
       <c r="B228" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C228">
         <v>1</v>
       </c>
       <c r="D228" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="E228">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F228" t="s">
-        <v>601</v>
+        <v>520</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>433</v>
+        <v>352</v>
       </c>
       <c r="B229" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C229">
         <v>1</v>
       </c>
       <c r="D229" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="E229">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F229" t="s">
-        <v>600</v>
+        <v>519</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>437</v>
+        <v>330</v>
       </c>
       <c r="B230" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C230">
         <v>1</v>
       </c>
       <c r="D230" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="E230">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F230" t="s">
-        <v>604</v>
+        <v>497</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>432</v>
+        <v>329</v>
       </c>
       <c r="B231" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C231">
         <v>1</v>
       </c>
       <c r="D231" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="E231">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F231" t="s">
-        <v>599</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>352</v>
+        <v>328</v>
       </c>
       <c r="B232" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C232">
         <v>1</v>
       </c>
       <c r="D232" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="E232">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F232" t="s">
-        <v>519</v>
+        <v>495</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>351</v>
+        <v>327</v>
       </c>
       <c r="B233" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C233">
         <v>1</v>
       </c>
       <c r="D233" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="E233">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F233" t="s">
-        <v>518</v>
+        <v>494</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>349</v>
+        <v>334</v>
       </c>
       <c r="B234" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C234">
         <v>1</v>
       </c>
       <c r="D234" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="E234">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F234" t="s">
-        <v>516</v>
+        <v>501</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>348</v>
+        <v>333</v>
       </c>
       <c r="B235" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C235">
         <v>1</v>
       </c>
       <c r="D235" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="E235">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F235" t="s">
-        <v>515</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>284</v>
+        <v>332</v>
       </c>
       <c r="B236" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C236">
         <v>1</v>
       </c>
       <c r="D236" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="E236">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F236" t="s">
-        <v>451</v>
+        <v>499</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>279</v>
+        <v>331</v>
       </c>
       <c r="B237" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C237">
         <v>1</v>
       </c>
       <c r="D237" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="E237">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F237" t="s">
-        <v>446</v>
+        <v>498</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>436</v>
+        <v>340</v>
       </c>
       <c r="B238" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C238">
         <v>1</v>
       </c>
       <c r="D238" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="E238">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F238" t="s">
-        <v>603</v>
+        <v>507</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>613</v>
+        <v>339</v>
       </c>
       <c r="B239" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C239">
         <v>1</v>
       </c>
       <c r="D239" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="E239">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F239" t="s">
-        <v>621</v>
+        <v>506</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>421</v>
+        <v>338</v>
       </c>
       <c r="B240" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C240">
         <v>1</v>
       </c>
       <c r="D240" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="E240">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F240" t="s">
-        <v>588</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="B241" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C241">
         <v>1</v>
       </c>
       <c r="D241" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="E241">
         <v>3</v>
       </c>
       <c r="F241" t="s">
-        <v>517</v>
+        <v>504</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="B242" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C242">
         <v>1</v>
       </c>
       <c r="D242" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="E242">
         <v>3</v>
       </c>
       <c r="F242" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="B243" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C243">
         <v>1</v>
       </c>
       <c r="D243" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="E243">
         <v>3</v>
       </c>
       <c r="F243" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="B244" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C244">
         <v>1</v>
       </c>
       <c r="D244" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="E244">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F244" t="s">
-        <v>493</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>325</v>
+        <v>341</v>
       </c>
       <c r="B245" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C245">
         <v>1</v>
       </c>
       <c r="D245" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="E245">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F245" t="s">
-        <v>492</v>
+        <v>508</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>283</v>
+        <v>314</v>
       </c>
       <c r="B246" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C246">
         <v>1</v>
       </c>
       <c r="D246" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E246">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F246" t="s">
-        <v>450</v>
+        <v>481</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>282</v>
+        <v>313</v>
       </c>
       <c r="B247" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C247">
         <v>1</v>
       </c>
       <c r="D247" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E247">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F247" t="s">
-        <v>449</v>
+        <v>480</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>129</v>
+        <v>312</v>
       </c>
       <c r="B248" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C248">
         <v>1</v>
       </c>
       <c r="D248" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E248">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F248" t="s">
-        <v>243</v>
+        <v>479</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>260</v>
+        <v>318</v>
       </c>
       <c r="B249" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C249">
         <v>1</v>
       </c>
       <c r="D249" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="E249">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F249" t="s">
-        <v>267</v>
+        <v>485</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>425</v>
+        <v>317</v>
       </c>
       <c r="B250" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C250">
         <v>1</v>
       </c>
       <c r="D250" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E250">
         <v>2</v>
       </c>
       <c r="F250" t="s">
-        <v>592</v>
+        <v>484</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>423</v>
+        <v>316</v>
       </c>
       <c r="B251" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C251">
         <v>1</v>
       </c>
       <c r="D251" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E251">
         <v>2</v>
       </c>
       <c r="F251" t="s">
-        <v>590</v>
+        <v>483</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>422</v>
+        <v>315</v>
       </c>
       <c r="B252" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C252">
         <v>1</v>
       </c>
       <c r="D252" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E252">
         <v>2</v>
       </c>
       <c r="F252" t="s">
-        <v>589</v>
+        <v>482</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>420</v>
+        <v>322</v>
       </c>
       <c r="B253" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C253">
         <v>1</v>
       </c>
       <c r="D253" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E253">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F253" t="s">
-        <v>587</v>
+        <v>489</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>419</v>
+        <v>321</v>
       </c>
       <c r="B254" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C254">
         <v>1</v>
       </c>
       <c r="D254" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E254">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F254" t="s">
-        <v>586</v>
+        <v>488</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="B255" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C255">
         <v>1</v>
       </c>
       <c r="D255" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E255">
         <v>3</v>
       </c>
       <c r="F255" t="s">
-        <v>499</v>
+        <v>487</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="B256" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C256">
         <v>1</v>
       </c>
       <c r="D256" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E256">
         <v>3</v>
       </c>
       <c r="F256" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="B257" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C257">
         <v>1</v>
       </c>
       <c r="D257" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E257">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F257" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="B258" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C258">
         <v>1</v>
       </c>
       <c r="D258" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E258">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F258" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>263</v>
+        <v>324</v>
       </c>
       <c r="B259" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C259">
         <v>1</v>
       </c>
       <c r="D259" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E259">
         <v>4</v>
       </c>
       <c r="F259" t="s">
-        <v>270</v>
+        <v>491</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>259</v>
+        <v>323</v>
       </c>
       <c r="B260" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C260">
         <v>1</v>
       </c>
       <c r="D260" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E260">
         <v>4</v>
       </c>
       <c r="F260" t="s">
-        <v>266</v>
+        <v>490</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>257</v>
+        <v>304</v>
       </c>
       <c r="B261" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C261">
         <v>1</v>
       </c>
       <c r="D261" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="E261">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F261" t="s">
-        <v>258</v>
+        <v>471</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>429</v>
+        <v>303</v>
       </c>
       <c r="B262" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C262">
         <v>1</v>
       </c>
       <c r="D262" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="E262">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F262" t="s">
-        <v>596</v>
+        <v>470</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>427</v>
+        <v>302</v>
       </c>
       <c r="B263" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C263">
         <v>1</v>
       </c>
       <c r="D263" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="E263">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F263" t="s">
-        <v>594</v>
+        <v>469</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>426</v>
+        <v>307</v>
       </c>
       <c r="B264" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C264">
         <v>1</v>
       </c>
       <c r="D264" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="E264">
         <v>2</v>
       </c>
       <c r="F264" t="s">
-        <v>593</v>
+        <v>474</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>424</v>
+        <v>306</v>
       </c>
       <c r="B265" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C265">
         <v>1</v>
       </c>
       <c r="D265" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="E265">
         <v>2</v>
       </c>
       <c r="F265" t="s">
-        <v>591</v>
+        <v>473</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>411</v>
+        <v>305</v>
       </c>
       <c r="B266" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C266">
         <v>1</v>
       </c>
       <c r="D266" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="E266">
         <v>2</v>
       </c>
       <c r="F266" t="s">
-        <v>578</v>
+        <v>472</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>409</v>
+        <v>622</v>
       </c>
       <c r="B267" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C267">
         <v>1</v>
       </c>
       <c r="D267" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="E267">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F267" t="s">
-        <v>576</v>
+        <v>630</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>338</v>
+        <v>309</v>
       </c>
       <c r="B268" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C268">
         <v>1</v>
       </c>
       <c r="D268" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="E268">
         <v>3</v>
       </c>
       <c r="F268" t="s">
-        <v>505</v>
+        <v>476</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>337</v>
+        <v>308</v>
       </c>
       <c r="B269" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C269">
         <v>1</v>
       </c>
       <c r="D269" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="E269">
         <v>3</v>
       </c>
       <c r="F269" t="s">
-        <v>504</v>
+        <v>475</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>336</v>
+        <v>311</v>
       </c>
       <c r="B270" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C270">
         <v>1</v>
       </c>
       <c r="D270" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="E270">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F270" t="s">
-        <v>503</v>
+        <v>478</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>335</v>
+        <v>310</v>
       </c>
       <c r="B271" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C271">
         <v>1</v>
       </c>
       <c r="D271" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="E271">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F271" t="s">
-        <v>502</v>
+        <v>477</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>334</v>
+        <v>296</v>
       </c>
       <c r="B272" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C272">
         <v>1</v>
       </c>
       <c r="D272" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="E272">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F272" t="s">
-        <v>501</v>
+        <v>463</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>262</v>
+        <v>90</v>
       </c>
       <c r="B273" t="s">
-        <v>256</v>
+        <v>90</v>
       </c>
       <c r="C273">
         <v>1</v>
       </c>
       <c r="D273" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="E273">
-        <v>4</v>
-      </c>
-      <c r="F273" t="s">
-        <v>269</v>
+        <v>2</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>414</v>
+        <v>299</v>
       </c>
       <c r="B274" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C274">
         <v>1</v>
       </c>
       <c r="D274" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="E274">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F274" t="s">
-        <v>581</v>
+        <v>466</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>413</v>
+        <v>298</v>
       </c>
       <c r="B275" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C275">
         <v>1</v>
       </c>
       <c r="D275" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="E275">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F275" t="s">
-        <v>580</v>
+        <v>465</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>412</v>
+        <v>297</v>
       </c>
       <c r="B276" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C276">
         <v>1</v>
       </c>
       <c r="D276" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="E276">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F276" t="s">
-        <v>579</v>
+        <v>464</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>410</v>
+        <v>441</v>
       </c>
       <c r="B277" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C277">
         <v>1</v>
       </c>
       <c r="D277" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="E277">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F277" t="s">
-        <v>577</v>
+        <v>608</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="B278" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C278">
         <v>1</v>
       </c>
       <c r="D278" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="E278">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F278" t="s">
-        <v>622</v>
+        <v>610</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>340</v>
+        <v>301</v>
       </c>
       <c r="B279" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C279">
         <v>1</v>
       </c>
       <c r="D279" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="E279">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F279" t="s">
-        <v>507</v>
+        <v>468</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>339</v>
+        <v>300</v>
       </c>
       <c r="B280" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C280">
         <v>1</v>
       </c>
       <c r="D280" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="E280">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F280" t="s">
-        <v>506</v>
+        <v>467</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>333</v>
+        <v>290</v>
       </c>
       <c r="B281" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C281">
         <v>1</v>
       </c>
       <c r="D281" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="E281">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F281" t="s">
-        <v>500</v>
+        <v>457</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>312</v>
+        <v>289</v>
       </c>
       <c r="B282" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C282">
         <v>1</v>
       </c>
       <c r="D282" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="E282">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F282" t="s">
-        <v>479</v>
+        <v>456</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>311</v>
+        <v>288</v>
       </c>
       <c r="B283" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C283">
         <v>1</v>
       </c>
       <c r="D283" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="E283">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F283" t="s">
-        <v>478</v>
+        <v>455</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>310</v>
+        <v>292</v>
       </c>
       <c r="B284" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C284">
         <v>1</v>
       </c>
       <c r="D284" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="E284">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F284" t="s">
-        <v>477</v>
+        <v>459</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="B285" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C285">
         <v>1</v>
       </c>
       <c r="D285" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="E285">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F285" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
@@ -8028,16 +7998,16 @@
         <v>619</v>
       </c>
       <c r="B286" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C286">
         <v>1</v>
       </c>
       <c r="D286" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="E286">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F286" t="s">
         <v>627</v>
@@ -8045,710 +8015,590 @@
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>261</v>
+        <v>618</v>
       </c>
       <c r="B287" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C287">
         <v>1</v>
       </c>
       <c r="D287" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="E287">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F287" t="s">
-        <v>268</v>
+        <v>626</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>418</v>
+        <v>294</v>
       </c>
       <c r="B288" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C288">
         <v>1</v>
       </c>
       <c r="D288" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="E288">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F288" t="s">
-        <v>585</v>
+        <v>461</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>316</v>
+        <v>293</v>
       </c>
       <c r="B289" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C289">
         <v>1</v>
       </c>
       <c r="D289" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="E289">
         <v>3</v>
       </c>
       <c r="F289" t="s">
-        <v>483</v>
+        <v>460</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>417</v>
+        <v>620</v>
       </c>
       <c r="B290" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C290">
         <v>1</v>
       </c>
       <c r="D290" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="E290">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F290" t="s">
-        <v>584</v>
+        <v>628</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>416</v>
+        <v>295</v>
       </c>
       <c r="B291" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C291">
         <v>1</v>
       </c>
       <c r="D291" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="E291">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F291" t="s">
-        <v>583</v>
+        <v>462</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>315</v>
+        <v>287</v>
       </c>
       <c r="B292" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C292">
         <v>1</v>
       </c>
       <c r="D292" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="E292">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F292" t="s">
-        <v>482</v>
+        <v>454</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>415</v>
+        <v>280</v>
       </c>
       <c r="B293" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C293">
         <v>1</v>
       </c>
       <c r="D293" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="E293">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F293" t="s">
-        <v>582</v>
+        <v>447</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>399</v>
+        <v>617</v>
       </c>
       <c r="B294" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C294">
         <v>1</v>
       </c>
       <c r="D294" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="E294">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F294" t="s">
-        <v>566</v>
+        <v>625</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>314</v>
+        <v>279</v>
       </c>
       <c r="B295" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C295">
         <v>1</v>
       </c>
       <c r="D295" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="E295">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F295" t="s">
-        <v>481</v>
+        <v>446</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>398</v>
+        <v>283</v>
       </c>
       <c r="B296" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C296">
         <v>1</v>
       </c>
       <c r="D296" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="E296">
         <v>2</v>
       </c>
       <c r="F296" t="s">
-        <v>565</v>
+        <v>450</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>397</v>
+        <v>282</v>
       </c>
       <c r="B297" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C297">
         <v>1</v>
       </c>
       <c r="D297" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="E297">
         <v>2</v>
       </c>
       <c r="F297" t="s">
-        <v>564</v>
+        <v>449</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>320</v>
+        <v>281</v>
       </c>
       <c r="B298" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C298">
         <v>1</v>
       </c>
       <c r="D298" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="E298">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F298" t="s">
-        <v>487</v>
+        <v>448</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>313</v>
+        <v>286</v>
       </c>
       <c r="B299" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C299">
         <v>1</v>
       </c>
       <c r="D299" t="s">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="E299">
         <v>3</v>
       </c>
       <c r="F299" t="s">
-        <v>480</v>
+        <v>453</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>396</v>
+        <v>285</v>
       </c>
       <c r="B300" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C300">
         <v>1</v>
       </c>
       <c r="D300" t="s">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="E300">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F300" t="s">
-        <v>563</v>
+        <v>452</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>319</v>
+        <v>284</v>
       </c>
       <c r="B301" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C301">
         <v>1</v>
       </c>
       <c r="D301" t="s">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="E301">
         <v>3</v>
       </c>
       <c r="F301" t="s">
-        <v>486</v>
+        <v>451</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>318</v>
+        <v>130</v>
       </c>
       <c r="B302" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C302">
         <v>1</v>
       </c>
       <c r="D302" t="s">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="E302">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F302" t="s">
-        <v>485</v>
+        <v>245</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>402</v>
+        <v>262</v>
       </c>
       <c r="B303" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C303">
         <v>1</v>
       </c>
       <c r="D303" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="E303">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F303" t="s">
-        <v>569</v>
+        <v>269</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>401</v>
+        <v>261</v>
       </c>
       <c r="B304" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C304">
         <v>1</v>
       </c>
       <c r="D304" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="E304">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F304" t="s">
-        <v>568</v>
+        <v>268</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>324</v>
+        <v>259</v>
       </c>
       <c r="B305" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C305">
         <v>1</v>
       </c>
       <c r="D305" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="E305">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F305" t="s">
-        <v>491</v>
+        <v>260</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>317</v>
+        <v>265</v>
       </c>
       <c r="B306" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C306">
         <v>1</v>
       </c>
       <c r="D306" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="E306">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F306" t="s">
-        <v>484</v>
+        <v>272</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>404</v>
+        <v>264</v>
       </c>
       <c r="B307" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C307">
         <v>1</v>
       </c>
       <c r="D307" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="E307">
         <v>2</v>
       </c>
       <c r="F307" t="s">
-        <v>571</v>
+        <v>271</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>323</v>
+        <v>263</v>
       </c>
       <c r="B308" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C308">
         <v>1</v>
       </c>
       <c r="D308" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="E308">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F308" t="s">
-        <v>490</v>
+        <v>270</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>322</v>
+        <v>275</v>
       </c>
       <c r="B309" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C309">
         <v>1</v>
       </c>
       <c r="D309" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="E309">
         <v>3</v>
       </c>
       <c r="F309" t="s">
-        <v>489</v>
+        <v>442</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>403</v>
+        <v>621</v>
       </c>
       <c r="B310" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C310">
         <v>1</v>
       </c>
       <c r="D310" t="s">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="E310">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F310" t="s">
-        <v>570</v>
+        <v>629</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>321</v>
+        <v>267</v>
       </c>
       <c r="B311" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C311">
         <v>1</v>
       </c>
       <c r="D311" t="s">
-        <v>126</v>
+        <v>84</v>
       </c>
       <c r="E311">
         <v>3</v>
       </c>
       <c r="F311" t="s">
-        <v>488</v>
+        <v>274</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>408</v>
+        <v>266</v>
       </c>
       <c r="B312" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C312">
         <v>1</v>
       </c>
       <c r="D312" t="s">
-        <v>131</v>
+        <v>84</v>
       </c>
       <c r="E312">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F312" t="s">
-        <v>575</v>
+        <v>273</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>400</v>
+        <v>278</v>
       </c>
       <c r="B313" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C313">
         <v>1</v>
       </c>
       <c r="D313" t="s">
-        <v>131</v>
+        <v>84</v>
       </c>
       <c r="E313">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F313" t="s">
-        <v>567</v>
+        <v>445</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>302</v>
+        <v>277</v>
       </c>
       <c r="B314" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C314">
         <v>1</v>
       </c>
       <c r="D314" t="s">
-        <v>131</v>
+        <v>84</v>
       </c>
       <c r="E314">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F314" t="s">
-        <v>469</v>
+        <v>444</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>301</v>
+        <v>276</v>
       </c>
       <c r="B315" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C315">
         <v>1</v>
       </c>
       <c r="D315" t="s">
-        <v>131</v>
+        <v>84</v>
       </c>
       <c r="E315">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F315" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A316" t="s">
-        <v>407</v>
-      </c>
-      <c r="B316" t="s">
-        <v>256</v>
-      </c>
-      <c r="C316">
-        <v>1</v>
-      </c>
-      <c r="D316" t="s">
-        <v>137</v>
-      </c>
-      <c r="E316">
-        <v>2</v>
-      </c>
-      <c r="F316" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A317" t="s">
-        <v>300</v>
-      </c>
-      <c r="B317" t="s">
-        <v>256</v>
-      </c>
-      <c r="C317">
-        <v>1</v>
-      </c>
-      <c r="D317" t="s">
-        <v>137</v>
-      </c>
-      <c r="E317">
-        <v>3</v>
-      </c>
-      <c r="F317" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A318" t="s">
-        <v>406</v>
-      </c>
-      <c r="B318" t="s">
-        <v>256</v>
-      </c>
-      <c r="C318">
-        <v>1</v>
-      </c>
-      <c r="D318" t="s">
-        <v>138</v>
-      </c>
-      <c r="E318">
-        <v>2</v>
-      </c>
-      <c r="F318" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A319" t="s">
-        <v>305</v>
-      </c>
-      <c r="B319" t="s">
-        <v>256</v>
-      </c>
-      <c r="C319">
-        <v>1</v>
-      </c>
-      <c r="D319" t="s">
-        <v>138</v>
-      </c>
-      <c r="E319">
-        <v>3</v>
-      </c>
-      <c r="F319" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A320" t="s">
-        <v>405</v>
-      </c>
-      <c r="B320" t="s">
-        <v>256</v>
-      </c>
-      <c r="C320">
-        <v>1</v>
-      </c>
-      <c r="D320" t="s">
-        <v>139</v>
-      </c>
-      <c r="E320">
-        <v>2</v>
-      </c>
-      <c r="F320" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="321" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A321" t="s">
-        <v>304</v>
-      </c>
-      <c r="B321" t="s">
-        <v>256</v>
-      </c>
-      <c r="C321">
-        <v>1</v>
-      </c>
-      <c r="D321" t="s">
-        <v>139</v>
-      </c>
-      <c r="E321">
-        <v>3</v>
-      </c>
-      <c r="F321" t="s">
-        <v>471</v>
+        <v>443</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F321">
-    <sortCondition descending="1" ref="C2:C321"/>
-    <sortCondition ref="D2:D321"/>
-    <sortCondition ref="E2:E321"/>
-    <sortCondition descending="1" ref="A2:A321"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F315">
+    <sortCondition descending="1" ref="C2:C315"/>
+    <sortCondition ref="D2:D315"/>
+    <sortCondition ref="E2:E315"/>
+    <sortCondition descending="1" ref="A2:A315"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/EOAT_data.xlsx
+++ b/data/EOAT_data.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\procesos.CAZEL\Desktop\Becario Procesos\EOAT Project\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uramirez\Desktop\Inventario-main\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A524E845-612F-43FA-9915-963291DDE71C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14E6EE5F-C324-40BD-9F69-E723379C9E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{440E3869-3C3F-4E8C-A8BD-ADEB8E2EA552}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{440E3869-3C3F-4E8C-A8BD-ADEB8E2EA552}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$F$320</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1252" uniqueCount="638">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1271" uniqueCount="646">
   <si>
     <t>I-1937</t>
   </si>
@@ -245,9 +248,6 @@
     <t>I-1593</t>
   </si>
   <si>
-    <t>I-1620</t>
-  </si>
-  <si>
     <t>I-1598</t>
   </si>
   <si>
@@ -626,9 +626,6 @@
     <t>I-1593.jpeg</t>
   </si>
   <si>
-    <t>I-1620.jpeg</t>
-  </si>
-  <si>
     <t>I-1598.jpeg</t>
   </si>
   <si>
@@ -1950,6 +1947,36 @@
   </si>
   <si>
     <t>I-1945</t>
+  </si>
+  <si>
+    <t>I-1566</t>
+  </si>
+  <si>
+    <t>I-1566.jpeg</t>
+  </si>
+  <si>
+    <t>I-1581.jpeg</t>
+  </si>
+  <si>
+    <t>I-1581</t>
+  </si>
+  <si>
+    <t>I-1774</t>
+  </si>
+  <si>
+    <t>I-1774.jpeg</t>
+  </si>
+  <si>
+    <t>I-1930</t>
+  </si>
+  <si>
+    <t>I-1930.jpeg</t>
+  </si>
+  <si>
+    <t>I-1931</t>
+  </si>
+  <si>
+    <t>I-1931.jpeg</t>
   </si>
 </sst>
 </file>
@@ -2327,7 +2354,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B6791C-A8A7-4753-A504-FAA9E3EE8745}">
-  <dimension ref="A1:F315"/>
+  <dimension ref="A1:F320"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
@@ -2340,22 +2367,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B1" t="s">
+        <v>251</v>
+      </c>
+      <c r="C1" t="s">
         <v>252</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>253</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>254</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>255</v>
-      </c>
-      <c r="E1" t="s">
-        <v>256</v>
-      </c>
-      <c r="F1" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -2363,7 +2390,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C2">
         <v>3</v>
@@ -2375,7 +2402,7 @@
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -2383,7 +2410,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C3">
         <v>3</v>
@@ -2395,7 +2422,7 @@
         <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -2403,7 +2430,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C4">
         <v>3</v>
@@ -2415,7 +2442,7 @@
         <v>2</v>
       </c>
       <c r="F4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -2423,7 +2450,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C5">
         <v>3</v>
@@ -2435,7 +2462,7 @@
         <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -2443,7 +2470,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C6">
         <v>3</v>
@@ -2455,7 +2482,7 @@
         <v>3</v>
       </c>
       <c r="F6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -2463,7 +2490,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -2475,7 +2502,7 @@
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -2483,7 +2510,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C8">
         <v>3</v>
@@ -2495,7 +2522,7 @@
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -2503,7 +2530,7 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C9">
         <v>3</v>
@@ -2515,7 +2542,7 @@
         <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -2523,7 +2550,7 @@
         <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C10">
         <v>3</v>
@@ -2535,7 +2562,7 @@
         <v>2</v>
       </c>
       <c r="F10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -2543,7 +2570,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C11">
         <v>3</v>
@@ -2555,7 +2582,7 @@
         <v>2</v>
       </c>
       <c r="F11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2563,7 +2590,7 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C12">
         <v>3</v>
@@ -2575,7 +2602,7 @@
         <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -2583,7 +2610,7 @@
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C13">
         <v>3</v>
@@ -2595,7 +2622,7 @@
         <v>3</v>
       </c>
       <c r="F13" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -2603,7 +2630,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C14">
         <v>3</v>
@@ -2615,7 +2642,7 @@
         <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -2623,7 +2650,7 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C15">
         <v>3</v>
@@ -2635,7 +2662,7 @@
         <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -2643,7 +2670,7 @@
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C16">
         <v>3</v>
@@ -2655,7 +2682,7 @@
         <v>2</v>
       </c>
       <c r="F16" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -2663,7 +2690,7 @@
         <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C17">
         <v>3</v>
@@ -2675,7 +2702,7 @@
         <v>2</v>
       </c>
       <c r="F17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -2683,7 +2710,7 @@
         <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C18">
         <v>3</v>
@@ -2695,7 +2722,7 @@
         <v>3</v>
       </c>
       <c r="F18" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -2703,7 +2730,7 @@
         <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C19">
         <v>3</v>
@@ -2715,7 +2742,7 @@
         <v>3</v>
       </c>
       <c r="F19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -2723,7 +2750,7 @@
         <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C20">
         <v>3</v>
@@ -2735,7 +2762,7 @@
         <v>3</v>
       </c>
       <c r="F20" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -2743,7 +2770,7 @@
         <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C21">
         <v>3</v>
@@ -2755,7 +2782,7 @@
         <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -2763,7 +2790,7 @@
         <v>24</v>
       </c>
       <c r="B22" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C22">
         <v>3</v>
@@ -2775,7 +2802,7 @@
         <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -2783,7 +2810,7 @@
         <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C23">
         <v>3</v>
@@ -2795,7 +2822,7 @@
         <v>2</v>
       </c>
       <c r="F23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -2803,7 +2830,7 @@
         <v>26</v>
       </c>
       <c r="B24" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C24">
         <v>3</v>
@@ -2815,7 +2842,7 @@
         <v>2</v>
       </c>
       <c r="F24" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -2823,7 +2850,7 @@
         <v>27</v>
       </c>
       <c r="B25" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C25">
         <v>3</v>
@@ -2835,7 +2862,7 @@
         <v>3</v>
       </c>
       <c r="F25" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -2843,7 +2870,7 @@
         <v>28</v>
       </c>
       <c r="B26" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C26">
         <v>3</v>
@@ -2855,15 +2882,15 @@
         <v>3</v>
       </c>
       <c r="F26" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B27" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C27">
         <v>3</v>
@@ -2875,15 +2902,15 @@
         <v>1</v>
       </c>
       <c r="F27" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B28" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C28">
         <v>3</v>
@@ -2895,7 +2922,7 @@
         <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -2903,7 +2930,7 @@
         <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C29">
         <v>3</v>
@@ -2915,7 +2942,7 @@
         <v>2</v>
       </c>
       <c r="F29" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -2923,7 +2950,7 @@
         <v>31</v>
       </c>
       <c r="B30" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C30">
         <v>3</v>
@@ -2935,7 +2962,7 @@
         <v>3</v>
       </c>
       <c r="F30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -2943,7 +2970,7 @@
         <v>32</v>
       </c>
       <c r="B31" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C31">
         <v>3</v>
@@ -2955,7 +2982,7 @@
         <v>1</v>
       </c>
       <c r="F31" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -2963,7 +2990,7 @@
         <v>34</v>
       </c>
       <c r="B32" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C32">
         <v>3</v>
@@ -2975,7 +3002,7 @@
         <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -2983,7 +3010,7 @@
         <v>35</v>
       </c>
       <c r="B33" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C33">
         <v>3</v>
@@ -2995,7 +3022,7 @@
         <v>2</v>
       </c>
       <c r="F33" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -3003,7 +3030,7 @@
         <v>36</v>
       </c>
       <c r="B34" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C34">
         <v>3</v>
@@ -3015,7 +3042,7 @@
         <v>2</v>
       </c>
       <c r="F34" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -3023,7 +3050,7 @@
         <v>37</v>
       </c>
       <c r="B35" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C35">
         <v>3</v>
@@ -3035,7 +3062,7 @@
         <v>3</v>
       </c>
       <c r="F35" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -3043,7 +3070,7 @@
         <v>38</v>
       </c>
       <c r="B36" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C36">
         <v>3</v>
@@ -3055,7 +3082,7 @@
         <v>3</v>
       </c>
       <c r="F36" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -3063,7 +3090,7 @@
         <v>39</v>
       </c>
       <c r="B37" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C37">
         <v>3</v>
@@ -3075,7 +3102,7 @@
         <v>1</v>
       </c>
       <c r="F37" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -3083,7 +3110,7 @@
         <v>41</v>
       </c>
       <c r="B38" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C38">
         <v>3</v>
@@ -3095,7 +3122,7 @@
         <v>1</v>
       </c>
       <c r="F38" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -3103,7 +3130,7 @@
         <v>42</v>
       </c>
       <c r="B39" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C39">
         <v>3</v>
@@ -3115,7 +3142,7 @@
         <v>2</v>
       </c>
       <c r="F39" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -3123,7 +3150,7 @@
         <v>43</v>
       </c>
       <c r="B40" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C40">
         <v>3</v>
@@ -3135,7 +3162,7 @@
         <v>3</v>
       </c>
       <c r="F40" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -3143,7 +3170,7 @@
         <v>44</v>
       </c>
       <c r="B41" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C41">
         <v>3</v>
@@ -3155,7 +3182,7 @@
         <v>3</v>
       </c>
       <c r="F41" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -3163,7 +3190,7 @@
         <v>45</v>
       </c>
       <c r="B42" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C42">
         <v>3</v>
@@ -3175,7 +3202,7 @@
         <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -3183,7 +3210,7 @@
         <v>47</v>
       </c>
       <c r="B43" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C43">
         <v>3</v>
@@ -3195,7 +3222,7 @@
         <v>1</v>
       </c>
       <c r="F43" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -3203,7 +3230,7 @@
         <v>48</v>
       </c>
       <c r="B44" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C44">
         <v>3</v>
@@ -3215,7 +3242,7 @@
         <v>2</v>
       </c>
       <c r="F44" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -3223,7 +3250,7 @@
         <v>49</v>
       </c>
       <c r="B45" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C45">
         <v>3</v>
@@ -3235,7 +3262,7 @@
         <v>3</v>
       </c>
       <c r="F45" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -3243,7 +3270,7 @@
         <v>50</v>
       </c>
       <c r="B46" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C46">
         <v>3</v>
@@ -3255,7 +3282,7 @@
         <v>3</v>
       </c>
       <c r="F46" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -3263,7 +3290,7 @@
         <v>51</v>
       </c>
       <c r="B47" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C47">
         <v>3</v>
@@ -3275,7 +3302,7 @@
         <v>1</v>
       </c>
       <c r="F47" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -3283,7 +3310,7 @@
         <v>53</v>
       </c>
       <c r="B48" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C48">
         <v>3</v>
@@ -3295,7 +3322,7 @@
         <v>2</v>
       </c>
       <c r="F48" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -3303,7 +3330,7 @@
         <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C49">
         <v>3</v>
@@ -3315,7 +3342,7 @@
         <v>3</v>
       </c>
       <c r="F49" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -3323,7 +3350,7 @@
         <v>55</v>
       </c>
       <c r="B50" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C50">
         <v>3</v>
@@ -3335,7 +3362,7 @@
         <v>1</v>
       </c>
       <c r="F50" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -3343,7 +3370,7 @@
         <v>57</v>
       </c>
       <c r="B51" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C51">
         <v>3</v>
@@ -3352,10 +3379,10 @@
         <v>56</v>
       </c>
       <c r="E51" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="F51" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -3363,7 +3390,7 @@
         <v>59</v>
       </c>
       <c r="B52" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C52">
         <v>3</v>
@@ -3372,10 +3399,10 @@
         <v>56</v>
       </c>
       <c r="E52" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="F52" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -3383,7 +3410,7 @@
         <v>60</v>
       </c>
       <c r="B53" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C53">
         <v>3</v>
@@ -3395,7 +3422,7 @@
         <v>1</v>
       </c>
       <c r="F53" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -3403,7 +3430,7 @@
         <v>62</v>
       </c>
       <c r="B54" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C54">
         <v>3</v>
@@ -3415,7 +3442,7 @@
         <v>1</v>
       </c>
       <c r="F54" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -3423,7 +3450,7 @@
         <v>63</v>
       </c>
       <c r="B55" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C55">
         <v>3</v>
@@ -3435,7 +3462,7 @@
         <v>2</v>
       </c>
       <c r="F55" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -3508,16 +3535,16 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>89</v>
+      </c>
+      <c r="B60" t="s">
+        <v>89</v>
+      </c>
+      <c r="C60">
+        <v>3</v>
+      </c>
+      <c r="D60" t="s">
         <v>90</v>
-      </c>
-      <c r="B60" t="s">
-        <v>90</v>
-      </c>
-      <c r="C60">
-        <v>3</v>
-      </c>
-      <c r="D60" t="s">
-        <v>91</v>
       </c>
       <c r="E60">
         <v>1</v>
@@ -3525,16 +3552,16 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>89</v>
+      </c>
+      <c r="B61" t="s">
+        <v>89</v>
+      </c>
+      <c r="C61">
+        <v>3</v>
+      </c>
+      <c r="D61" t="s">
         <v>90</v>
-      </c>
-      <c r="B61" t="s">
-        <v>90</v>
-      </c>
-      <c r="C61">
-        <v>3</v>
-      </c>
-      <c r="D61" t="s">
-        <v>91</v>
       </c>
       <c r="E61">
         <v>2</v>
@@ -3545,319 +3572,319 @@
         <v>58</v>
       </c>
       <c r="B62" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C62">
         <v>3</v>
       </c>
       <c r="D62" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E62">
         <v>3</v>
       </c>
       <c r="F62" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>91</v>
+      </c>
+      <c r="B63" t="s">
+        <v>256</v>
+      </c>
+      <c r="C63">
+        <v>3</v>
+      </c>
+      <c r="D63" t="s">
         <v>92</v>
       </c>
-      <c r="B63" t="s">
-        <v>258</v>
-      </c>
-      <c r="C63">
-        <v>3</v>
-      </c>
-      <c r="D63" t="s">
-        <v>93</v>
-      </c>
       <c r="E63">
         <v>1</v>
       </c>
       <c r="F63" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B64" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C64">
         <v>3</v>
       </c>
       <c r="D64" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E64">
         <v>2</v>
       </c>
       <c r="F64" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B65" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C65">
         <v>3</v>
       </c>
       <c r="D65" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E65">
         <v>2</v>
       </c>
       <c r="F65" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B66" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C66">
         <v>3</v>
       </c>
       <c r="D66" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E66">
         <v>3</v>
       </c>
       <c r="F66" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
+        <v>96</v>
+      </c>
+      <c r="B67" t="s">
+        <v>256</v>
+      </c>
+      <c r="C67">
+        <v>3</v>
+      </c>
+      <c r="D67" t="s">
         <v>97</v>
       </c>
-      <c r="B67" t="s">
-        <v>258</v>
-      </c>
-      <c r="C67">
-        <v>3</v>
-      </c>
-      <c r="D67" t="s">
-        <v>98</v>
-      </c>
       <c r="E67">
         <v>1</v>
       </c>
       <c r="F67" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B68" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C68">
         <v>3</v>
       </c>
       <c r="D68" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E68">
         <v>1</v>
       </c>
       <c r="F68" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B69" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C69">
         <v>3</v>
       </c>
       <c r="D69" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E69">
         <v>2</v>
       </c>
       <c r="F69" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B70" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C70">
         <v>3</v>
       </c>
       <c r="D70" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E70">
         <v>2</v>
       </c>
       <c r="F70" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B71" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C71">
         <v>3</v>
       </c>
       <c r="D71" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E71">
         <v>3</v>
       </c>
       <c r="F71" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>102</v>
+      </c>
+      <c r="B72" t="s">
+        <v>256</v>
+      </c>
+      <c r="C72">
+        <v>3</v>
+      </c>
+      <c r="D72" t="s">
         <v>103</v>
       </c>
-      <c r="B72" t="s">
-        <v>258</v>
-      </c>
-      <c r="C72">
-        <v>3</v>
-      </c>
-      <c r="D72" t="s">
-        <v>104</v>
-      </c>
       <c r="E72">
         <v>1</v>
       </c>
       <c r="F72" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B73" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C73">
         <v>3</v>
       </c>
       <c r="D73" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E73">
         <v>1</v>
       </c>
       <c r="F73" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B74" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C74">
         <v>3</v>
       </c>
       <c r="D74" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E74">
         <v>2</v>
       </c>
       <c r="F74" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B75" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C75">
         <v>3</v>
       </c>
       <c r="D75" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E75">
         <v>2</v>
       </c>
       <c r="F75" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B76" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C76">
         <v>3</v>
       </c>
       <c r="D76" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E76">
         <v>3</v>
       </c>
       <c r="F76" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B77" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C77">
         <v>3</v>
       </c>
       <c r="D77" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E77">
         <v>3</v>
       </c>
       <c r="F77" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -3865,7 +3892,7 @@
         <v>66</v>
       </c>
       <c r="B78" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C78">
         <v>2</v>
@@ -3877,7 +3904,7 @@
         <v>1</v>
       </c>
       <c r="F78" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -3885,7 +3912,7 @@
         <v>68</v>
       </c>
       <c r="B79" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C79">
         <v>2</v>
@@ -3897,15 +3924,15 @@
         <v>1</v>
       </c>
       <c r="F79" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>69</v>
+        <v>89</v>
       </c>
       <c r="B80" t="s">
-        <v>258</v>
+        <v>89</v>
       </c>
       <c r="C80">
         <v>2</v>
@@ -3916,16 +3943,13 @@
       <c r="E80">
         <v>2</v>
       </c>
-      <c r="F80" t="s">
-        <v>196</v>
-      </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B81" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C81">
         <v>2</v>
@@ -3937,15 +3961,15 @@
         <v>3</v>
       </c>
       <c r="F81" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B82" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C82">
         <v>2</v>
@@ -3957,781 +3981,781 @@
         <v>3</v>
       </c>
       <c r="F82" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B83" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C83">
         <v>2</v>
       </c>
       <c r="D83" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E83">
         <v>1</v>
       </c>
       <c r="F83" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
+        <v>71</v>
+      </c>
+      <c r="B84" t="s">
+        <v>256</v>
+      </c>
+      <c r="C84">
+        <v>2</v>
+      </c>
+      <c r="D84" t="s">
         <v>72</v>
       </c>
-      <c r="B84" t="s">
-        <v>258</v>
-      </c>
-      <c r="C84">
-        <v>2</v>
-      </c>
-      <c r="D84" t="s">
-        <v>73</v>
-      </c>
       <c r="E84">
         <v>1</v>
       </c>
       <c r="F84" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B85" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C85">
         <v>2</v>
       </c>
       <c r="D85" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E85">
         <v>2</v>
       </c>
       <c r="F85" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B86" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C86">
         <v>2</v>
       </c>
       <c r="D86" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E86">
         <v>3</v>
       </c>
       <c r="F86" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
+        <v>75</v>
+      </c>
+      <c r="B87" t="s">
+        <v>256</v>
+      </c>
+      <c r="C87">
+        <v>2</v>
+      </c>
+      <c r="D87" t="s">
         <v>76</v>
       </c>
-      <c r="B87" t="s">
-        <v>258</v>
-      </c>
-      <c r="C87">
-        <v>2</v>
-      </c>
-      <c r="D87" t="s">
-        <v>77</v>
-      </c>
       <c r="E87">
         <v>1</v>
       </c>
       <c r="F87" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B88" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C88">
         <v>2</v>
       </c>
       <c r="D88" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E88">
         <v>1</v>
       </c>
       <c r="F88" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B89" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C89">
         <v>2</v>
       </c>
       <c r="D89" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E89">
         <v>2</v>
       </c>
       <c r="F89" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B90" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C90">
         <v>2</v>
       </c>
       <c r="D90" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E90">
         <v>2</v>
       </c>
       <c r="F90" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B91" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C91">
         <v>2</v>
       </c>
       <c r="D91" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E91">
         <v>3</v>
       </c>
       <c r="F91" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B92" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C92">
         <v>2</v>
       </c>
       <c r="D92" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E92">
         <v>3</v>
       </c>
       <c r="F92" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>82</v>
+      </c>
+      <c r="B93" t="s">
+        <v>256</v>
+      </c>
+      <c r="C93">
+        <v>2</v>
+      </c>
+      <c r="D93" t="s">
         <v>83</v>
       </c>
-      <c r="B93" t="s">
-        <v>258</v>
-      </c>
-      <c r="C93">
-        <v>2</v>
-      </c>
-      <c r="D93" t="s">
-        <v>84</v>
-      </c>
       <c r="E93">
         <v>1</v>
       </c>
       <c r="F93" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B94" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C94">
         <v>2</v>
       </c>
       <c r="D94" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E94">
         <v>1</v>
       </c>
       <c r="F94" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B95" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C95">
         <v>2</v>
       </c>
       <c r="D95" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E95">
         <v>2</v>
       </c>
       <c r="F95" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B96" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C96">
         <v>2</v>
       </c>
       <c r="D96" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E96">
         <v>2</v>
       </c>
       <c r="F96" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B97" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C97">
         <v>2</v>
       </c>
       <c r="D97" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E97">
         <v>3</v>
       </c>
       <c r="F97" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B98" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C98">
         <v>2</v>
       </c>
       <c r="D98" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E98">
         <v>3</v>
       </c>
       <c r="F98" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
+        <v>109</v>
+      </c>
+      <c r="B99" t="s">
+        <v>256</v>
+      </c>
+      <c r="C99">
+        <v>2</v>
+      </c>
+      <c r="D99" t="s">
         <v>110</v>
       </c>
-      <c r="B99" t="s">
-        <v>258</v>
-      </c>
-      <c r="C99">
-        <v>2</v>
-      </c>
-      <c r="D99" t="s">
-        <v>111</v>
-      </c>
       <c r="E99">
         <v>1</v>
       </c>
       <c r="F99" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B100" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C100">
         <v>2</v>
       </c>
       <c r="D100" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E100">
         <v>2</v>
       </c>
       <c r="F100" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B101" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C101">
         <v>2</v>
       </c>
       <c r="D101" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E101">
         <v>3</v>
       </c>
       <c r="F101" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B102" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C102">
         <v>2</v>
       </c>
       <c r="D102" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E102">
         <v>3</v>
       </c>
       <c r="F102" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>114</v>
+      </c>
+      <c r="B103" t="s">
+        <v>256</v>
+      </c>
+      <c r="C103">
+        <v>2</v>
+      </c>
+      <c r="D103" t="s">
         <v>115</v>
       </c>
-      <c r="B103" t="s">
-        <v>258</v>
-      </c>
-      <c r="C103">
-        <v>2</v>
-      </c>
-      <c r="D103" t="s">
-        <v>116</v>
-      </c>
       <c r="E103">
         <v>1</v>
       </c>
       <c r="F103" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B104" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C104">
         <v>2</v>
       </c>
       <c r="D104" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E104">
         <v>2</v>
       </c>
       <c r="F104" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B105" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C105">
         <v>2</v>
       </c>
       <c r="D105" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E105">
         <v>2</v>
       </c>
       <c r="F105" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B106" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C106">
         <v>2</v>
       </c>
       <c r="D106" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E106">
         <v>3</v>
       </c>
       <c r="F106" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B107" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C107">
         <v>2</v>
       </c>
       <c r="D107" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E107">
         <v>3</v>
       </c>
       <c r="F107" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
+        <v>120</v>
+      </c>
+      <c r="B108" t="s">
+        <v>256</v>
+      </c>
+      <c r="C108">
+        <v>2</v>
+      </c>
+      <c r="D108" t="s">
         <v>121</v>
       </c>
-      <c r="B108" t="s">
-        <v>258</v>
-      </c>
-      <c r="C108">
-        <v>2</v>
-      </c>
-      <c r="D108" t="s">
-        <v>122</v>
-      </c>
       <c r="E108">
         <v>1</v>
       </c>
       <c r="F108" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B109" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C109">
         <v>2</v>
       </c>
       <c r="D109" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E109">
         <v>2</v>
       </c>
       <c r="F109" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B110" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C110">
         <v>2</v>
       </c>
       <c r="D110" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E110">
         <v>3</v>
       </c>
       <c r="F110" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B111" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C111">
         <v>2</v>
       </c>
       <c r="D111" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E111">
         <v>3</v>
       </c>
       <c r="F111" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
+        <v>125</v>
+      </c>
+      <c r="B112" t="s">
+        <v>256</v>
+      </c>
+      <c r="C112">
+        <v>2</v>
+      </c>
+      <c r="D112" t="s">
         <v>126</v>
       </c>
-      <c r="B112" t="s">
-        <v>258</v>
-      </c>
-      <c r="C112">
-        <v>2</v>
-      </c>
-      <c r="D112" t="s">
-        <v>127</v>
-      </c>
       <c r="E112">
         <v>1</v>
       </c>
       <c r="F112" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B113" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C113">
         <v>2</v>
       </c>
       <c r="D113" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E113">
         <v>2</v>
       </c>
       <c r="F113" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B114" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C114">
         <v>2</v>
       </c>
       <c r="D114" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E114">
         <v>3</v>
       </c>
       <c r="F114" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
+        <v>130</v>
+      </c>
+      <c r="B115" t="s">
+        <v>256</v>
+      </c>
+      <c r="C115">
+        <v>2</v>
+      </c>
+      <c r="D115" t="s">
         <v>131</v>
       </c>
-      <c r="B115" t="s">
-        <v>258</v>
-      </c>
-      <c r="C115">
-        <v>2</v>
-      </c>
-      <c r="D115" t="s">
-        <v>132</v>
-      </c>
       <c r="E115">
         <v>1</v>
       </c>
       <c r="F115" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B116" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C116">
         <v>2</v>
       </c>
       <c r="D116" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E116">
         <v>1</v>
       </c>
       <c r="F116" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B117" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C117">
         <v>2</v>
       </c>
       <c r="D117" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E117">
         <v>2</v>
       </c>
       <c r="F117" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B118" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C118">
         <v>2</v>
       </c>
       <c r="D118" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E118">
         <v>2</v>
       </c>
       <c r="F118" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B119" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C119">
         <v>2</v>
       </c>
       <c r="D119" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E119">
         <v>3</v>
       </c>
       <c r="F119" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B120" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C120">
         <v>2</v>
       </c>
       <c r="D120" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E120">
         <v>3</v>
       </c>
       <c r="F120" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B121" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C121">
         <v>2</v>
       </c>
       <c r="D121" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E121">
         <v>1</v>
@@ -4739,16 +4763,16 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B122" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C122">
         <v>2</v>
       </c>
       <c r="D122" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E122">
         <v>2</v>
@@ -4756,16 +4780,16 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B123" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C123">
         <v>2</v>
       </c>
       <c r="D123" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E123">
         <v>3</v>
@@ -4773,16 +4797,16 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B124" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C124">
         <v>2</v>
       </c>
       <c r="D124" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E124">
         <v>1</v>
@@ -4790,16 +4814,16 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B125" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C125">
         <v>2</v>
       </c>
       <c r="D125" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E125">
         <v>2</v>
@@ -4807,36 +4831,36 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B126" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C126">
         <v>2</v>
       </c>
       <c r="D126" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E126">
         <v>3</v>
       </c>
       <c r="F126" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B127" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C127">
         <v>2</v>
       </c>
       <c r="D127" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E127">
         <v>1</v>
@@ -4844,16 +4868,16 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B128" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C128">
         <v>2</v>
       </c>
       <c r="D128" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E128">
         <v>2</v>
@@ -4861,16 +4885,16 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B129" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C129">
         <v>2</v>
       </c>
       <c r="D129" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E129">
         <v>3</v>
@@ -4878,10 +4902,10 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="B130" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C130">
         <v>1</v>
@@ -4893,15 +4917,15 @@
         <v>1</v>
       </c>
       <c r="F130" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B131" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C131">
         <v>1</v>
@@ -4913,15 +4937,15 @@
         <v>1</v>
       </c>
       <c r="F131" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>433</v>
+        <v>642</v>
       </c>
       <c r="B132" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C132">
         <v>1</v>
@@ -4930,18 +4954,18 @@
         <v>1</v>
       </c>
       <c r="E132">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F132" t="s">
-        <v>600</v>
+        <v>643</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
       <c r="B133" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C133">
         <v>1</v>
@@ -4953,15 +4977,15 @@
         <v>2</v>
       </c>
       <c r="F133" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="B134" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C134">
         <v>1</v>
@@ -4973,15 +4997,15 @@
         <v>2</v>
       </c>
       <c r="F134" t="s">
-        <v>607</v>
+        <v>602</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B135" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C135">
         <v>1</v>
@@ -4990,18 +5014,18 @@
         <v>1</v>
       </c>
       <c r="E135">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F135" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B136" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C136">
         <v>1</v>
@@ -5013,15 +5037,15 @@
         <v>3</v>
       </c>
       <c r="F136" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="B137" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C137">
         <v>1</v>
@@ -5030,18 +5054,18 @@
         <v>1</v>
       </c>
       <c r="E137">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F137" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B138" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C138">
         <v>1</v>
@@ -5053,15 +5077,15 @@
         <v>4</v>
       </c>
       <c r="F138" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="B139" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C139">
         <v>1</v>
@@ -5073,15 +5097,15 @@
         <v>4</v>
       </c>
       <c r="F139" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>615</v>
+        <v>436</v>
       </c>
       <c r="B140" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C140">
         <v>1</v>
@@ -5093,35 +5117,35 @@
         <v>4</v>
       </c>
       <c r="F140" t="s">
-        <v>623</v>
+        <v>603</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>423</v>
+        <v>613</v>
       </c>
       <c r="B141" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C141">
         <v>1</v>
       </c>
       <c r="D141" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E141">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F141" t="s">
-        <v>590</v>
+        <v>621</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B142" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C142">
         <v>1</v>
@@ -5133,15 +5157,15 @@
         <v>1</v>
       </c>
       <c r="F142" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B143" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C143">
         <v>1</v>
@@ -5153,15 +5177,15 @@
         <v>1</v>
       </c>
       <c r="F143" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="B144" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C144">
         <v>1</v>
@@ -5170,18 +5194,18 @@
         <v>8</v>
       </c>
       <c r="E144">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F144" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>424</v>
+        <v>644</v>
       </c>
       <c r="B145" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C145">
         <v>1</v>
@@ -5190,18 +5214,18 @@
         <v>8</v>
       </c>
       <c r="E145">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F145" t="s">
-        <v>591</v>
+        <v>645</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="B146" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C146">
         <v>1</v>
@@ -5210,18 +5234,18 @@
         <v>8</v>
       </c>
       <c r="E146">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F146" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="B147" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C147">
         <v>1</v>
@@ -5230,18 +5254,18 @@
         <v>8</v>
       </c>
       <c r="E147">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F147" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="B148" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C148">
         <v>1</v>
@@ -5250,18 +5274,18 @@
         <v>8</v>
       </c>
       <c r="E148">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F148" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="B149" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C149">
         <v>1</v>
@@ -5270,18 +5294,18 @@
         <v>8</v>
       </c>
       <c r="E149">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F149" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B150" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C150">
         <v>1</v>
@@ -5293,55 +5317,55 @@
         <v>4</v>
       </c>
       <c r="F150" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>411</v>
+        <v>427</v>
       </c>
       <c r="B151" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C151">
         <v>1</v>
       </c>
       <c r="D151" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E151">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F151" t="s">
-        <v>578</v>
+        <v>594</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>413</v>
+        <v>426</v>
       </c>
       <c r="B152" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C152">
         <v>1</v>
       </c>
       <c r="D152" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="E152">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F152" t="s">
-        <v>580</v>
+        <v>593</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="B153" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C153">
         <v>1</v>
@@ -5350,18 +5374,18 @@
         <v>15</v>
       </c>
       <c r="E153">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F153" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>616</v>
+        <v>411</v>
       </c>
       <c r="B154" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C154">
         <v>1</v>
@@ -5373,15 +5397,15 @@
         <v>2</v>
       </c>
       <c r="F154" t="s">
-        <v>624</v>
+        <v>578</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="B155" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C155">
         <v>1</v>
@@ -5390,18 +5414,18 @@
         <v>15</v>
       </c>
       <c r="E155">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F155" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>415</v>
+        <v>614</v>
       </c>
       <c r="B156" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C156">
         <v>1</v>
@@ -5410,10 +5434,10 @@
         <v>15</v>
       </c>
       <c r="E156">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F156" t="s">
-        <v>582</v>
+        <v>622</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -5421,7 +5445,7 @@
         <v>414</v>
       </c>
       <c r="B157" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C157">
         <v>1</v>
@@ -5438,10 +5462,10 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>420</v>
+        <v>413</v>
       </c>
       <c r="B158" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C158">
         <v>1</v>
@@ -5450,18 +5474,18 @@
         <v>15</v>
       </c>
       <c r="E158">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F158" t="s">
-        <v>587</v>
+        <v>580</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="B159" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C159">
         <v>1</v>
@@ -5470,10 +5494,10 @@
         <v>15</v>
       </c>
       <c r="E159">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F159" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -5481,7 +5505,7 @@
         <v>418</v>
       </c>
       <c r="B160" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C160">
         <v>1</v>
@@ -5501,7 +5525,7 @@
         <v>417</v>
       </c>
       <c r="B161" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C161">
         <v>1</v>
@@ -5518,42 +5542,42 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>401</v>
+        <v>416</v>
       </c>
       <c r="B162" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C162">
         <v>1</v>
       </c>
       <c r="D162" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E162">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F162" t="s">
-        <v>568</v>
+        <v>583</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>400</v>
+        <v>415</v>
       </c>
       <c r="B163" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C163">
         <v>1</v>
       </c>
       <c r="D163" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="E163">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F163" t="s">
-        <v>567</v>
+        <v>582</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
@@ -5561,7 +5585,7 @@
         <v>399</v>
       </c>
       <c r="B164" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C164">
         <v>1</v>
@@ -5581,7 +5605,7 @@
         <v>398</v>
       </c>
       <c r="B165" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C165">
         <v>1</v>
@@ -5598,10 +5622,10 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="B166" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C166">
         <v>1</v>
@@ -5610,18 +5634,18 @@
         <v>23</v>
       </c>
       <c r="E166">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F166" t="s">
-        <v>571</v>
+        <v>564</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="B167" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C167">
         <v>1</v>
@@ -5630,18 +5654,18 @@
         <v>23</v>
       </c>
       <c r="E167">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F167" t="s">
-        <v>570</v>
+        <v>563</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="B168" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C168">
         <v>1</v>
@@ -5650,18 +5674,18 @@
         <v>23</v>
       </c>
       <c r="E168">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F168" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="B169" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C169">
         <v>1</v>
@@ -5670,18 +5694,18 @@
         <v>23</v>
       </c>
       <c r="E169">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F169" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B170" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C170">
         <v>1</v>
@@ -5693,15 +5717,15 @@
         <v>3</v>
       </c>
       <c r="F170" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="B171" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C171">
         <v>1</v>
@@ -5710,18 +5734,18 @@
         <v>23</v>
       </c>
       <c r="E171">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F171" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="B172" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C172">
         <v>1</v>
@@ -5730,10 +5754,10 @@
         <v>23</v>
       </c>
       <c r="E172">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F172" t="s">
-        <v>576</v>
+        <v>567</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -5741,7 +5765,7 @@
         <v>408</v>
       </c>
       <c r="B173" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C173">
         <v>1</v>
@@ -5761,7 +5785,7 @@
         <v>407</v>
       </c>
       <c r="B174" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C174">
         <v>1</v>
@@ -5778,50 +5802,50 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>387</v>
+        <v>406</v>
       </c>
       <c r="B175" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C175">
         <v>1</v>
       </c>
       <c r="D175" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E175">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F175" t="s">
-        <v>554</v>
+        <v>573</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>386</v>
+        <v>405</v>
       </c>
       <c r="B176" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C176">
         <v>1</v>
       </c>
       <c r="D176" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E176">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F176" t="s">
-        <v>553</v>
+        <v>572</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="B177" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C177">
         <v>1</v>
@@ -5830,18 +5854,18 @@
         <v>29</v>
       </c>
       <c r="E177">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F177" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="B178" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C178">
         <v>1</v>
@@ -5850,10 +5874,10 @@
         <v>29</v>
       </c>
       <c r="E178">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F178" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -5861,7 +5885,7 @@
         <v>388</v>
       </c>
       <c r="B179" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C179">
         <v>1</v>
@@ -5878,10 +5902,10 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="B180" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C180">
         <v>1</v>
@@ -5890,18 +5914,18 @@
         <v>29</v>
       </c>
       <c r="E180">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F180" t="s">
-        <v>561</v>
+        <v>554</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>393</v>
+        <v>386</v>
       </c>
       <c r="B181" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C181">
         <v>1</v>
@@ -5910,10 +5934,10 @@
         <v>29</v>
       </c>
       <c r="E181">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F181" t="s">
-        <v>560</v>
+        <v>553</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -5921,7 +5945,7 @@
         <v>392</v>
       </c>
       <c r="B182" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C182">
         <v>1</v>
@@ -5941,7 +5965,7 @@
         <v>391</v>
       </c>
       <c r="B183" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C183">
         <v>1</v>
@@ -5958,10 +5982,10 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>397</v>
+        <v>390</v>
       </c>
       <c r="B184" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C184">
         <v>1</v>
@@ -5970,18 +5994,18 @@
         <v>29</v>
       </c>
       <c r="E184">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F184" t="s">
-        <v>564</v>
+        <v>557</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="B185" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C185">
         <v>1</v>
@@ -5990,10 +6014,10 @@
         <v>29</v>
       </c>
       <c r="E185">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F185" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -6001,7 +6025,7 @@
         <v>395</v>
       </c>
       <c r="B186" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C186">
         <v>1</v>
@@ -6018,42 +6042,42 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>378</v>
+        <v>394</v>
       </c>
       <c r="B187" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C187">
         <v>1</v>
       </c>
       <c r="D187" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E187">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F187" t="s">
-        <v>545</v>
+        <v>561</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>377</v>
+        <v>393</v>
       </c>
       <c r="B188" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C188">
         <v>1</v>
       </c>
       <c r="D188" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E188">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F188" t="s">
-        <v>544</v>
+        <v>560</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -6061,7 +6085,7 @@
         <v>376</v>
       </c>
       <c r="B189" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C189">
         <v>1</v>
@@ -6078,10 +6102,10 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="B190" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C190">
         <v>1</v>
@@ -6090,18 +6114,18 @@
         <v>33</v>
       </c>
       <c r="E190">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F190" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="B191" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C191">
         <v>1</v>
@@ -6110,18 +6134,18 @@
         <v>33</v>
       </c>
       <c r="E191">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F191" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="B192" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C192">
         <v>1</v>
@@ -6130,18 +6154,18 @@
         <v>33</v>
       </c>
       <c r="E192">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F192" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B193" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C193">
         <v>1</v>
@@ -6150,18 +6174,18 @@
         <v>33</v>
       </c>
       <c r="E193">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F193" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>385</v>
+        <v>640</v>
       </c>
       <c r="B194" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C194">
         <v>1</v>
@@ -6170,18 +6194,18 @@
         <v>33</v>
       </c>
       <c r="E194">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F194" t="s">
-        <v>552</v>
+        <v>641</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B195" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C195">
         <v>1</v>
@@ -6190,18 +6214,18 @@
         <v>33</v>
       </c>
       <c r="E195">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F195" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B196" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C196">
         <v>1</v>
@@ -6210,78 +6234,78 @@
         <v>33</v>
       </c>
       <c r="E196">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F196" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="B197" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C197">
         <v>1</v>
       </c>
       <c r="D197" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E197">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F197" t="s">
-        <v>536</v>
+        <v>548</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="B198" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C198">
         <v>1</v>
       </c>
       <c r="D198" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E198">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F198" t="s">
-        <v>535</v>
+        <v>547</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="B199" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C199">
         <v>1</v>
       </c>
       <c r="D199" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E199">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F199" t="s">
-        <v>534</v>
+        <v>546</v>
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="B200" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C200">
         <v>1</v>
@@ -6290,18 +6314,18 @@
         <v>40</v>
       </c>
       <c r="E200">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F200" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="B201" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C201">
         <v>1</v>
@@ -6310,18 +6334,18 @@
         <v>40</v>
       </c>
       <c r="E201">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F201" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="B202" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C202">
         <v>1</v>
@@ -6330,18 +6354,18 @@
         <v>40</v>
       </c>
       <c r="E202">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F202" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="B203" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C203">
         <v>1</v>
@@ -6349,19 +6373,19 @@
       <c r="D203" t="s">
         <v>40</v>
       </c>
-      <c r="E203" t="s">
-        <v>631</v>
+      <c r="E203">
+        <v>2</v>
       </c>
       <c r="F203" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="B204" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C204">
         <v>1</v>
@@ -6369,19 +6393,19 @@
       <c r="D204" t="s">
         <v>40</v>
       </c>
-      <c r="E204" t="s">
-        <v>631</v>
+      <c r="E204">
+        <v>2</v>
       </c>
       <c r="F204" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="B205" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C205">
         <v>1</v>
@@ -6389,79 +6413,79 @@
       <c r="D205" t="s">
         <v>40</v>
       </c>
-      <c r="E205" t="s">
-        <v>631</v>
+      <c r="E205">
+        <v>2</v>
       </c>
       <c r="F205" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>357</v>
+        <v>373</v>
       </c>
       <c r="B206" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C206">
         <v>1</v>
       </c>
       <c r="D206" t="s">
-        <v>46</v>
-      </c>
-      <c r="E206">
-        <v>1</v>
+        <v>40</v>
+      </c>
+      <c r="E206" t="s">
+        <v>629</v>
       </c>
       <c r="F206" t="s">
-        <v>524</v>
+        <v>540</v>
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>356</v>
+        <v>372</v>
       </c>
       <c r="B207" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C207">
         <v>1</v>
       </c>
       <c r="D207" t="s">
-        <v>46</v>
-      </c>
-      <c r="E207">
-        <v>1</v>
+        <v>40</v>
+      </c>
+      <c r="E207" t="s">
+        <v>629</v>
       </c>
       <c r="F207" t="s">
-        <v>523</v>
+        <v>539</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="B208" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C208">
         <v>1</v>
       </c>
       <c r="D208" t="s">
-        <v>46</v>
-      </c>
-      <c r="E208">
-        <v>1</v>
+        <v>40</v>
+      </c>
+      <c r="E208" t="s">
+        <v>629</v>
       </c>
       <c r="F208" t="s">
-        <v>522</v>
+        <v>538</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B209" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C209">
         <v>1</v>
@@ -6470,18 +6494,18 @@
         <v>46</v>
       </c>
       <c r="E209">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F209" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="B210" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C210">
         <v>1</v>
@@ -6490,18 +6514,18 @@
         <v>46</v>
       </c>
       <c r="E210">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F210" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="B211" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C211">
         <v>1</v>
@@ -6510,18 +6534,18 @@
         <v>46</v>
       </c>
       <c r="E211">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F211" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="B212" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C212">
         <v>1</v>
@@ -6530,18 +6554,18 @@
         <v>46</v>
       </c>
       <c r="E212">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F212" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="B213" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C213">
         <v>1</v>
@@ -6550,18 +6574,18 @@
         <v>46</v>
       </c>
       <c r="E213">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F213" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="B214" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C214">
         <v>1</v>
@@ -6570,18 +6594,18 @@
         <v>46</v>
       </c>
       <c r="E214">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F214" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="B215" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C215">
         <v>1</v>
@@ -6590,18 +6614,18 @@
         <v>46</v>
       </c>
       <c r="E215">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F215" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="B216" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C216">
         <v>1</v>
@@ -6610,18 +6634,18 @@
         <v>46</v>
       </c>
       <c r="E216">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F216" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="B217" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C217">
         <v>1</v>
@@ -6630,78 +6654,78 @@
         <v>46</v>
       </c>
       <c r="E217">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F217" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>346</v>
+        <v>364</v>
       </c>
       <c r="B218" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C218">
         <v>1</v>
       </c>
       <c r="D218" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E218">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F218" t="s">
-        <v>513</v>
+        <v>531</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>345</v>
+        <v>363</v>
       </c>
       <c r="B219" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C219">
         <v>1</v>
       </c>
       <c r="D219" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E219">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F219" t="s">
-        <v>512</v>
+        <v>530</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>344</v>
+        <v>362</v>
       </c>
       <c r="B220" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C220">
         <v>1</v>
       </c>
       <c r="D220" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="E220">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F220" t="s">
-        <v>511</v>
+        <v>529</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B221" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C221">
         <v>1</v>
@@ -6713,15 +6737,15 @@
         <v>1</v>
       </c>
       <c r="F221" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="B222" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C222">
         <v>1</v>
@@ -6730,18 +6754,18 @@
         <v>52</v>
       </c>
       <c r="E222">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F222" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="B223" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C223">
         <v>1</v>
@@ -6750,18 +6774,18 @@
         <v>52</v>
       </c>
       <c r="E223">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F223" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="B224" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C224">
         <v>1</v>
@@ -6770,18 +6794,18 @@
         <v>52</v>
       </c>
       <c r="E224">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F224" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="B225" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C225">
         <v>1</v>
@@ -6790,18 +6814,18 @@
         <v>52</v>
       </c>
       <c r="E225">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F225" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="B226" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C226">
         <v>1</v>
@@ -6810,18 +6834,18 @@
         <v>52</v>
       </c>
       <c r="E226">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F226" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="B227" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C227">
         <v>1</v>
@@ -6830,18 +6854,18 @@
         <v>52</v>
       </c>
       <c r="E227">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F227" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="B228" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C228">
         <v>1</v>
@@ -6850,18 +6874,18 @@
         <v>52</v>
       </c>
       <c r="E228">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F228" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="B229" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C229">
         <v>1</v>
@@ -6870,78 +6894,78 @@
         <v>52</v>
       </c>
       <c r="E229">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F229" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>330</v>
+        <v>352</v>
       </c>
       <c r="B230" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C230">
         <v>1</v>
       </c>
       <c r="D230" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E230">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F230" t="s">
-        <v>497</v>
+        <v>519</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="B231" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C231">
         <v>1</v>
       </c>
       <c r="D231" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E231">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F231" t="s">
-        <v>496</v>
+        <v>518</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>328</v>
+        <v>350</v>
       </c>
       <c r="B232" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C232">
         <v>1</v>
       </c>
       <c r="D232" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="E232">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F232" t="s">
-        <v>495</v>
+        <v>517</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B233" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C233">
         <v>1</v>
@@ -6953,15 +6977,15 @@
         <v>1</v>
       </c>
       <c r="F233" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="B234" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C234">
         <v>1</v>
@@ -6970,18 +6994,18 @@
         <v>56</v>
       </c>
       <c r="E234">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F234" t="s">
-        <v>501</v>
+        <v>494</v>
       </c>
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="B235" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C235">
         <v>1</v>
@@ -6990,18 +7014,18 @@
         <v>56</v>
       </c>
       <c r="E235">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F235" t="s">
-        <v>500</v>
+        <v>493</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="B236" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C236">
         <v>1</v>
@@ -7010,18 +7034,18 @@
         <v>56</v>
       </c>
       <c r="E236">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F236" t="s">
-        <v>499</v>
+        <v>492</v>
       </c>
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B237" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C237">
         <v>1</v>
@@ -7033,15 +7057,15 @@
         <v>2</v>
       </c>
       <c r="F237" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="B238" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C238">
         <v>1</v>
@@ -7050,18 +7074,18 @@
         <v>56</v>
       </c>
       <c r="E238">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F238" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="B239" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C239">
         <v>1</v>
@@ -7070,18 +7094,18 @@
         <v>56</v>
       </c>
       <c r="E239">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F239" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="B240" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C240">
         <v>1</v>
@@ -7090,18 +7114,18 @@
         <v>56</v>
       </c>
       <c r="E240">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F240" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B241" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C241">
         <v>1</v>
@@ -7113,15 +7137,15 @@
         <v>3</v>
       </c>
       <c r="F241" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B242" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C242">
         <v>1</v>
@@ -7133,15 +7157,15 @@
         <v>3</v>
       </c>
       <c r="F242" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B243" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C243">
         <v>1</v>
@@ -7153,15 +7177,15 @@
         <v>3</v>
       </c>
       <c r="F243" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="B244" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C244">
         <v>1</v>
@@ -7170,18 +7194,18 @@
         <v>56</v>
       </c>
       <c r="E244">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F244" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="B245" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C245">
         <v>1</v>
@@ -7190,78 +7214,78 @@
         <v>56</v>
       </c>
       <c r="E245">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F245" t="s">
-        <v>508</v>
+        <v>501</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>314</v>
+        <v>333</v>
       </c>
       <c r="B246" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C246">
         <v>1</v>
       </c>
       <c r="D246" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E246">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F246" t="s">
-        <v>481</v>
+        <v>500</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>313</v>
+        <v>340</v>
       </c>
       <c r="B247" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C247">
         <v>1</v>
       </c>
       <c r="D247" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E247">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F247" t="s">
-        <v>480</v>
+        <v>507</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>312</v>
+        <v>339</v>
       </c>
       <c r="B248" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C248">
         <v>1</v>
       </c>
       <c r="D248" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="E248">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F248" t="s">
-        <v>479</v>
+        <v>506</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B249" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C249">
         <v>1</v>
@@ -7270,18 +7294,18 @@
         <v>61</v>
       </c>
       <c r="E249">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F249" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="B250" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C250">
         <v>1</v>
@@ -7290,18 +7314,18 @@
         <v>61</v>
       </c>
       <c r="E250">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F250" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="B251" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C251">
         <v>1</v>
@@ -7310,18 +7334,18 @@
         <v>61</v>
       </c>
       <c r="E251">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F251" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B252" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C252">
         <v>1</v>
@@ -7333,15 +7357,15 @@
         <v>2</v>
       </c>
       <c r="F252" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="B253" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C253">
         <v>1</v>
@@ -7350,18 +7374,18 @@
         <v>61</v>
       </c>
       <c r="E253">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F253" t="s">
-        <v>489</v>
+        <v>482</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="B254" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C254">
         <v>1</v>
@@ -7370,18 +7394,18 @@
         <v>61</v>
       </c>
       <c r="E254">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F254" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="B255" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C255">
         <v>1</v>
@@ -7390,18 +7414,18 @@
         <v>61</v>
       </c>
       <c r="E255">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F255" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B256" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C256">
         <v>1</v>
@@ -7413,15 +7437,15 @@
         <v>3</v>
       </c>
       <c r="F256" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="B257" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C257">
         <v>1</v>
@@ -7430,18 +7454,18 @@
         <v>61</v>
       </c>
       <c r="E257">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F257" t="s">
-        <v>493</v>
+        <v>486</v>
       </c>
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="B258" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C258">
         <v>1</v>
@@ -7450,18 +7474,18 @@
         <v>61</v>
       </c>
       <c r="E258">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F258" t="s">
-        <v>492</v>
+        <v>485</v>
       </c>
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="B259" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C259">
         <v>1</v>
@@ -7470,18 +7494,18 @@
         <v>61</v>
       </c>
       <c r="E259">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F259" t="s">
-        <v>491</v>
+        <v>484</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B260" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C260">
         <v>1</v>
@@ -7493,75 +7517,75 @@
         <v>4</v>
       </c>
       <c r="F260" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>304</v>
+        <v>323</v>
       </c>
       <c r="B261" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C261">
         <v>1</v>
       </c>
       <c r="D261" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E261">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F261" t="s">
-        <v>471</v>
+        <v>490</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>303</v>
+        <v>322</v>
       </c>
       <c r="B262" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C262">
         <v>1</v>
       </c>
       <c r="D262" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E262">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F262" t="s">
-        <v>470</v>
+        <v>489</v>
       </c>
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>302</v>
+        <v>321</v>
       </c>
       <c r="B263" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C263">
         <v>1</v>
       </c>
       <c r="D263" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E263">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F263" t="s">
-        <v>469</v>
+        <v>488</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="B264" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C264">
         <v>1</v>
@@ -7570,18 +7594,18 @@
         <v>65</v>
       </c>
       <c r="E264">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F264" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="B265" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C265">
         <v>1</v>
@@ -7590,18 +7614,18 @@
         <v>65</v>
       </c>
       <c r="E265">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F265" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="B266" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C266">
         <v>1</v>
@@ -7610,18 +7634,18 @@
         <v>65</v>
       </c>
       <c r="E266">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F266" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>622</v>
+        <v>305</v>
       </c>
       <c r="B267" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C267">
         <v>1</v>
@@ -7630,18 +7654,18 @@
         <v>65</v>
       </c>
       <c r="E267">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F267" t="s">
-        <v>630</v>
+        <v>472</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="B268" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C268">
         <v>1</v>
@@ -7650,18 +7674,18 @@
         <v>65</v>
       </c>
       <c r="E268">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F268" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="B269" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C269">
         <v>1</v>
@@ -7670,18 +7694,18 @@
         <v>65</v>
       </c>
       <c r="E269">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F269" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>311</v>
+        <v>620</v>
       </c>
       <c r="B270" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C270">
         <v>1</v>
@@ -7690,18 +7714,18 @@
         <v>65</v>
       </c>
       <c r="E270">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F270" t="s">
-        <v>478</v>
+        <v>628</v>
       </c>
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B271" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C271">
         <v>1</v>
@@ -7710,75 +7734,78 @@
         <v>65</v>
       </c>
       <c r="E271">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F271" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="B272" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C272">
         <v>1</v>
       </c>
       <c r="D272" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E272">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F272" t="s">
-        <v>463</v>
+        <v>473</v>
       </c>
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>90</v>
+        <v>309</v>
       </c>
       <c r="B273" t="s">
-        <v>90</v>
+        <v>256</v>
       </c>
       <c r="C273">
         <v>1</v>
       </c>
       <c r="D273" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E273">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="F273" t="s">
+        <v>476</v>
       </c>
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="B274" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C274">
         <v>1</v>
       </c>
       <c r="D274" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E274">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F274" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B275" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C275">
         <v>1</v>
@@ -7787,18 +7814,18 @@
         <v>67</v>
       </c>
       <c r="E275">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F275" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>297</v>
+        <v>89</v>
       </c>
       <c r="B276" t="s">
-        <v>258</v>
+        <v>89</v>
       </c>
       <c r="C276">
         <v>1</v>
@@ -7807,18 +7834,15 @@
         <v>67</v>
       </c>
       <c r="E276">
-        <v>3</v>
-      </c>
-      <c r="F276" t="s">
-        <v>464</v>
+        <v>2</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>441</v>
+        <v>297</v>
       </c>
       <c r="B277" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C277">
         <v>1</v>
@@ -7827,18 +7851,18 @@
         <v>67</v>
       </c>
       <c r="E277">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F277" t="s">
-        <v>608</v>
+        <v>464</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>609</v>
+        <v>296</v>
       </c>
       <c r="B278" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C278">
         <v>1</v>
@@ -7847,18 +7871,18 @@
         <v>67</v>
       </c>
       <c r="E278">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F278" t="s">
-        <v>610</v>
+        <v>463</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B279" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C279">
         <v>1</v>
@@ -7867,18 +7891,18 @@
         <v>67</v>
       </c>
       <c r="E279">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F279" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>300</v>
+        <v>439</v>
       </c>
       <c r="B280" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C280">
         <v>1</v>
@@ -7890,715 +7914,822 @@
         <v>4</v>
       </c>
       <c r="F280" t="s">
-        <v>467</v>
+        <v>606</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>290</v>
+        <v>607</v>
       </c>
       <c r="B281" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C281">
         <v>1</v>
       </c>
       <c r="D281" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E281">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F281" t="s">
-        <v>457</v>
+        <v>608</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="B282" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C282">
         <v>1</v>
       </c>
       <c r="D282" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E282">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F282" t="s">
-        <v>456</v>
+        <v>466</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="B283" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C283">
         <v>1</v>
       </c>
       <c r="D283" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="E283">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F283" t="s">
-        <v>455</v>
+        <v>465</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B284" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C284">
         <v>1</v>
       </c>
       <c r="D284" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E284">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F284" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="B285" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C285">
         <v>1</v>
       </c>
       <c r="D285" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E285">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F285" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>619</v>
+        <v>286</v>
       </c>
       <c r="B286" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C286">
         <v>1</v>
       </c>
       <c r="D286" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E286">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F286" t="s">
-        <v>627</v>
+        <v>453</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>618</v>
+        <v>290</v>
       </c>
       <c r="B287" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C287">
         <v>1</v>
       </c>
       <c r="D287" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E287">
         <v>2</v>
       </c>
       <c r="F287" t="s">
-        <v>626</v>
+        <v>457</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="B288" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C288">
         <v>1</v>
       </c>
       <c r="D288" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E288">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F288" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>293</v>
+        <v>617</v>
       </c>
       <c r="B289" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C289">
         <v>1</v>
       </c>
       <c r="D289" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E289">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F289" t="s">
-        <v>460</v>
+        <v>625</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="B290" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C290">
         <v>1</v>
       </c>
       <c r="D290" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E290">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F290" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="B291" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C291">
         <v>1</v>
       </c>
       <c r="D291" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E291">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F291" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B292" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C292">
         <v>1</v>
       </c>
       <c r="D292" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E292">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F292" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>280</v>
+        <v>618</v>
       </c>
       <c r="B293" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C293">
         <v>1</v>
       </c>
       <c r="D293" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E293">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F293" t="s">
-        <v>447</v>
+        <v>626</v>
       </c>
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>617</v>
+        <v>293</v>
       </c>
       <c r="B294" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C294">
         <v>1</v>
       </c>
       <c r="D294" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E294">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F294" t="s">
-        <v>625</v>
+        <v>460</v>
       </c>
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B295" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C295">
         <v>1</v>
       </c>
       <c r="D295" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E295">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F295" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>283</v>
+        <v>639</v>
       </c>
       <c r="B296" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C296">
         <v>1</v>
       </c>
       <c r="D296" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="E296">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F296" t="s">
-        <v>450</v>
+        <v>638</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B297" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C297">
         <v>1</v>
       </c>
       <c r="D297" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E297">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F297" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>281</v>
+        <v>615</v>
       </c>
       <c r="B298" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C298">
         <v>1</v>
       </c>
       <c r="D298" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E298">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F298" t="s">
-        <v>448</v>
+        <v>623</v>
       </c>
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="B299" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C299">
         <v>1</v>
       </c>
       <c r="D299" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E299">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F299" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B300" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C300">
         <v>1</v>
       </c>
       <c r="D300" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E300">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F300" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B301" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C301">
         <v>1</v>
       </c>
       <c r="D301" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E301">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F301" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>130</v>
+        <v>279</v>
       </c>
       <c r="B302" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C302">
         <v>1</v>
       </c>
       <c r="D302" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E302">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F302" t="s">
-        <v>245</v>
+        <v>446</v>
       </c>
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>262</v>
+        <v>636</v>
       </c>
       <c r="B303" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C303">
         <v>1</v>
       </c>
       <c r="D303" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E303">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F303" t="s">
-        <v>269</v>
+        <v>637</v>
       </c>
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>261</v>
+        <v>284</v>
       </c>
       <c r="B304" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C304">
         <v>1</v>
       </c>
       <c r="D304" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E304">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F304" t="s">
-        <v>268</v>
+        <v>451</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>259</v>
+        <v>283</v>
       </c>
       <c r="B305" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C305">
         <v>1</v>
       </c>
       <c r="D305" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E305">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F305" t="s">
-        <v>260</v>
+        <v>450</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="B306" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C306">
         <v>1</v>
       </c>
       <c r="D306" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E306">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F306" t="s">
-        <v>272</v>
+        <v>449</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>264</v>
+        <v>129</v>
       </c>
       <c r="B307" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C307">
         <v>1</v>
       </c>
       <c r="D307" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E307">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F307" t="s">
-        <v>271</v>
+        <v>243</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B308" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C308">
         <v>1</v>
       </c>
       <c r="D308" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E308">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F308" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>275</v>
+        <v>259</v>
       </c>
       <c r="B309" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C309">
         <v>1</v>
       </c>
       <c r="D309" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E309">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F309" t="s">
-        <v>442</v>
+        <v>266</v>
       </c>
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>621</v>
+        <v>257</v>
       </c>
       <c r="B310" t="s">
+        <v>256</v>
+      </c>
+      <c r="C310">
+        <v>1</v>
+      </c>
+      <c r="D310" t="s">
+        <v>83</v>
+      </c>
+      <c r="E310">
+        <v>1</v>
+      </c>
+      <c r="F310" t="s">
         <v>258</v>
-      </c>
-      <c r="C310">
-        <v>1</v>
-      </c>
-      <c r="D310" t="s">
-        <v>84</v>
-      </c>
-      <c r="E310">
-        <v>3</v>
-      </c>
-      <c r="F310" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B311" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C311">
         <v>1</v>
       </c>
       <c r="D311" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E311">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F311" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B312" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C312">
         <v>1</v>
       </c>
       <c r="D312" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E312">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F312" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>278</v>
+        <v>261</v>
       </c>
       <c r="B313" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C313">
         <v>1</v>
       </c>
       <c r="D313" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E313">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F313" t="s">
-        <v>445</v>
+        <v>268</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="B314" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C314">
         <v>1</v>
       </c>
       <c r="D314" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E314">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F314" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
+        <v>619</v>
+      </c>
+      <c r="B315" t="s">
+        <v>256</v>
+      </c>
+      <c r="C315">
+        <v>1</v>
+      </c>
+      <c r="D315" t="s">
+        <v>83</v>
+      </c>
+      <c r="E315">
+        <v>3</v>
+      </c>
+      <c r="F315" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>265</v>
+      </c>
+      <c r="B316" t="s">
+        <v>256</v>
+      </c>
+      <c r="C316">
+        <v>1</v>
+      </c>
+      <c r="D316" t="s">
+        <v>83</v>
+      </c>
+      <c r="E316">
+        <v>3</v>
+      </c>
+      <c r="F316" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>264</v>
+      </c>
+      <c r="B317" t="s">
+        <v>256</v>
+      </c>
+      <c r="C317">
+        <v>1</v>
+      </c>
+      <c r="D317" t="s">
+        <v>83</v>
+      </c>
+      <c r="E317">
+        <v>3</v>
+      </c>
+      <c r="F317" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
         <v>276</v>
       </c>
-      <c r="B315" t="s">
-        <v>258</v>
-      </c>
-      <c r="C315">
-        <v>1</v>
-      </c>
-      <c r="D315" t="s">
-        <v>84</v>
-      </c>
-      <c r="E315">
+      <c r="B318" t="s">
+        <v>256</v>
+      </c>
+      <c r="C318">
+        <v>1</v>
+      </c>
+      <c r="D318" t="s">
+        <v>83</v>
+      </c>
+      <c r="E318">
         <v>4</v>
       </c>
-      <c r="F315" t="s">
+      <c r="F318" t="s">
         <v>443</v>
       </c>
     </row>
+    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A319" t="s">
+        <v>275</v>
+      </c>
+      <c r="B319" t="s">
+        <v>256</v>
+      </c>
+      <c r="C319">
+        <v>1</v>
+      </c>
+      <c r="D319" t="s">
+        <v>83</v>
+      </c>
+      <c r="E319">
+        <v>4</v>
+      </c>
+      <c r="F319" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A320" t="s">
+        <v>274</v>
+      </c>
+      <c r="B320" t="s">
+        <v>256</v>
+      </c>
+      <c r="C320">
+        <v>1</v>
+      </c>
+      <c r="D320" t="s">
+        <v>83</v>
+      </c>
+      <c r="E320">
+        <v>4</v>
+      </c>
+      <c r="F320" t="s">
+        <v>441</v>
+      </c>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F315">
-    <sortCondition descending="1" ref="C2:C315"/>
-    <sortCondition ref="D2:D315"/>
-    <sortCondition ref="E2:E315"/>
-    <sortCondition descending="1" ref="A2:A315"/>
+  <autoFilter ref="A1:F320" xr:uid="{E6B6791C-A8A7-4753-A504-FAA9E3EE8745}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F320">
+      <sortCondition descending="1" ref="C2:C320"/>
+      <sortCondition ref="D2:D320"/>
+      <sortCondition ref="E2:E320"/>
+    </sortState>
+  </autoFilter>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F319">
+    <sortCondition descending="1" ref="C2:C319"/>
+    <sortCondition ref="D2:D319"/>
+    <sortCondition ref="E2:E319"/>
+    <sortCondition descending="1" ref="A2:A319"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/EOAT_data.xlsx
+++ b/data/EOAT_data.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uramirez\Desktop\Inventario-main\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://industriascazelmx-my.sharepoint.com/personal/agaytan_cazel_mx/Documents/Imágenes/MOLIDO PELETIZADO/EOAT Project/EOAT Project/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14E6EE5F-C324-40BD-9F69-E723379C9E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1D609F45-9D1A-4AA8-BF9F-42F184022876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{440E3869-3C3F-4E8C-A8BD-ADEB8E2EA552}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{440E3869-3C3F-4E8C-A8BD-ADEB8E2EA552}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$F$320</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$F$321</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1271" uniqueCount="646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1270" uniqueCount="646">
   <si>
     <t>I-1937</t>
   </si>
@@ -863,1120 +863,1120 @@
     <t>I-1468</t>
   </si>
   <si>
+    <t>I-1493</t>
+  </si>
+  <si>
+    <t>I-1494</t>
+  </si>
+  <si>
+    <t>I-1514</t>
+  </si>
+  <si>
+    <t>I-1516</t>
+  </si>
+  <si>
+    <t>I-1538</t>
+  </si>
+  <si>
+    <t>I-1545</t>
+  </si>
+  <si>
+    <t>I-1557</t>
+  </si>
+  <si>
+    <t>I-1558</t>
+  </si>
+  <si>
+    <t>I-1559</t>
+  </si>
+  <si>
+    <t>I-1560</t>
+  </si>
+  <si>
+    <t>I-1562</t>
+  </si>
+  <si>
+    <t>I-1572</t>
+  </si>
+  <si>
+    <t>I-1573</t>
+  </si>
+  <si>
+    <t>I-1574</t>
+  </si>
+  <si>
+    <t>I-1584</t>
+  </si>
+  <si>
+    <t>I-1586</t>
+  </si>
+  <si>
+    <t>I-1587</t>
+  </si>
+  <si>
+    <t>I-1588</t>
+  </si>
+  <si>
+    <t>I-1589</t>
+  </si>
+  <si>
+    <t>I-1594</t>
+  </si>
+  <si>
+    <t>I-1600</t>
+  </si>
+  <si>
+    <t>I-1605</t>
+  </si>
+  <si>
+    <t>I-1606</t>
+  </si>
+  <si>
+    <t>I-1607</t>
+  </si>
+  <si>
+    <t>I-1611</t>
+  </si>
+  <si>
+    <t>I-1615</t>
+  </si>
+  <si>
+    <t>I-1616</t>
+  </si>
+  <si>
+    <t>I-1617</t>
+  </si>
+  <si>
+    <t>I-1618</t>
+  </si>
+  <si>
+    <t>I-1621</t>
+  </si>
+  <si>
+    <t>I-1624</t>
+  </si>
+  <si>
+    <t>I-1625</t>
+  </si>
+  <si>
+    <t>I-1627</t>
+  </si>
+  <si>
+    <t>I-1631</t>
+  </si>
+  <si>
+    <t>I-1632</t>
+  </si>
+  <si>
+    <t>I-1633</t>
+  </si>
+  <si>
+    <t>I-1636</t>
+  </si>
+  <si>
+    <t>I-1637</t>
+  </si>
+  <si>
+    <t>I-1638</t>
+  </si>
+  <si>
+    <t>I-1639</t>
+  </si>
+  <si>
+    <t>I-1642</t>
+  </si>
+  <si>
+    <t>I-1643</t>
+  </si>
+  <si>
+    <t>I-1644</t>
+  </si>
+  <si>
+    <t>I-1645</t>
+  </si>
+  <si>
+    <t>I-1646</t>
+  </si>
+  <si>
+    <t>I-1647</t>
+  </si>
+  <si>
+    <t>I-1648</t>
+  </si>
+  <si>
+    <t>I-1649</t>
+  </si>
+  <si>
+    <t>I-1650</t>
+  </si>
+  <si>
+    <t>I-1651</t>
+  </si>
+  <si>
+    <t>I-1652</t>
+  </si>
+  <si>
+    <t>I-1653</t>
+  </si>
+  <si>
+    <t>I-1654</t>
+  </si>
+  <si>
+    <t>I-1655</t>
+  </si>
+  <si>
+    <t>I-1656</t>
+  </si>
+  <si>
+    <t>I-1658</t>
+  </si>
+  <si>
+    <t>I-1659</t>
+  </si>
+  <si>
+    <t>I-1660</t>
+  </si>
+  <si>
+    <t>I-1661</t>
+  </si>
+  <si>
+    <t>I-1662</t>
+  </si>
+  <si>
+    <t>I-1664</t>
+  </si>
+  <si>
+    <t>I-1665</t>
+  </si>
+  <si>
+    <t>I-1667</t>
+  </si>
+  <si>
+    <t>I-1669</t>
+  </si>
+  <si>
+    <t>I-1670</t>
+  </si>
+  <si>
+    <t>I-1671</t>
+  </si>
+  <si>
+    <t>I-1672</t>
+  </si>
+  <si>
+    <t>I-1673</t>
+  </si>
+  <si>
+    <t>I-1674</t>
+  </si>
+  <si>
+    <t>I-1675</t>
+  </si>
+  <si>
+    <t>I-1676</t>
+  </si>
+  <si>
+    <t>I-1677</t>
+  </si>
+  <si>
+    <t>I-1679</t>
+  </si>
+  <si>
+    <t>I-1681</t>
+  </si>
+  <si>
+    <t>I-1687</t>
+  </si>
+  <si>
+    <t>I-1690</t>
+  </si>
+  <si>
+    <t>I-1708</t>
+  </si>
+  <si>
+    <t>I-1709</t>
+  </si>
+  <si>
+    <t>I-1710</t>
+  </si>
+  <si>
+    <t>I-1715</t>
+  </si>
+  <si>
+    <t>I-1716</t>
+  </si>
+  <si>
+    <t>I-1717</t>
+  </si>
+  <si>
+    <t>I-1721</t>
+  </si>
+  <si>
+    <t>I-1722</t>
+  </si>
+  <si>
+    <t>I-1725</t>
+  </si>
+  <si>
+    <t>I-1728</t>
+  </si>
+  <si>
+    <t>I-1729</t>
+  </si>
+  <si>
+    <t>I-1730</t>
+  </si>
+  <si>
+    <t>I-1731</t>
+  </si>
+  <si>
+    <t>I-1732</t>
+  </si>
+  <si>
+    <t>I-1733</t>
+  </si>
+  <si>
+    <t>I-1734</t>
+  </si>
+  <si>
+    <t>I-1735</t>
+  </si>
+  <si>
+    <t>I-1751</t>
+  </si>
+  <si>
+    <t>I-1766</t>
+  </si>
+  <si>
+    <t>I-1767</t>
+  </si>
+  <si>
+    <t>I-1771</t>
+  </si>
+  <si>
+    <t>I-1772</t>
+  </si>
+  <si>
+    <t>I-1773</t>
+  </si>
+  <si>
+    <t>I-1775</t>
+  </si>
+  <si>
+    <t>I-1776</t>
+  </si>
+  <si>
+    <t>I-1777</t>
+  </si>
+  <si>
+    <t>I-1778</t>
+  </si>
+  <si>
+    <t>I-1779</t>
+  </si>
+  <si>
+    <t>I-1780</t>
+  </si>
+  <si>
+    <t>I-1782</t>
+  </si>
+  <si>
+    <t>I-1783</t>
+  </si>
+  <si>
+    <t>I-1784</t>
+  </si>
+  <si>
+    <t>I-1785</t>
+  </si>
+  <si>
+    <t>I-1786</t>
+  </si>
+  <si>
+    <t>I-1787</t>
+  </si>
+  <si>
+    <t>I-1813</t>
+  </si>
+  <si>
+    <t>I-1814</t>
+  </si>
+  <si>
+    <t>I-1815</t>
+  </si>
+  <si>
+    <t>I-1818</t>
+  </si>
+  <si>
+    <t>I-1819</t>
+  </si>
+  <si>
+    <t>I-1822</t>
+  </si>
+  <si>
+    <t>I-1823</t>
+  </si>
+  <si>
+    <t>I-1827</t>
+  </si>
+  <si>
+    <t>I-1828</t>
+  </si>
+  <si>
+    <t>I-1830</t>
+  </si>
+  <si>
+    <t>I-1833</t>
+  </si>
+  <si>
+    <t>I-1841</t>
+  </si>
+  <si>
+    <t>I-1842</t>
+  </si>
+  <si>
+    <t>I-1843</t>
+  </si>
+  <si>
+    <t>I-1845</t>
+  </si>
+  <si>
+    <t>I-1847</t>
+  </si>
+  <si>
+    <t>I-1848</t>
+  </si>
+  <si>
+    <t>I-1849</t>
+  </si>
+  <si>
+    <t>I-1851</t>
+  </si>
+  <si>
+    <t>I-1852</t>
+  </si>
+  <si>
+    <t>I-1853</t>
+  </si>
+  <si>
+    <t>I-1854</t>
+  </si>
+  <si>
+    <t>I-1855</t>
+  </si>
+  <si>
+    <t>I-1865</t>
+  </si>
+  <si>
+    <t>I-1872</t>
+  </si>
+  <si>
+    <t>I-1873</t>
+  </si>
+  <si>
+    <t>I-1874</t>
+  </si>
+  <si>
+    <t>I-1876</t>
+  </si>
+  <si>
+    <t>I-1877</t>
+  </si>
+  <si>
+    <t>I-1878</t>
+  </si>
+  <si>
+    <t>I-1889</t>
+  </si>
+  <si>
+    <t>I-1890</t>
+  </si>
+  <si>
+    <t>I-1891</t>
+  </si>
+  <si>
+    <t>I-1892</t>
+  </si>
+  <si>
+    <t>I-1893</t>
+  </si>
+  <si>
+    <t>I-1894</t>
+  </si>
+  <si>
+    <t>I-1895</t>
+  </si>
+  <si>
+    <t>I-1897</t>
+  </si>
+  <si>
+    <t>I-1899</t>
+  </si>
+  <si>
+    <t>I-1900</t>
+  </si>
+  <si>
+    <t>I-1902</t>
+  </si>
+  <si>
+    <t>I-1909</t>
+  </si>
+  <si>
+    <t>I-1910</t>
+  </si>
+  <si>
+    <t>I-1912</t>
+  </si>
+  <si>
+    <t>I-1915</t>
+  </si>
+  <si>
+    <t>I-1924</t>
+  </si>
+  <si>
+    <t>I-1925</t>
+  </si>
+  <si>
+    <t>I-1934</t>
+  </si>
+  <si>
+    <t>I-1935</t>
+  </si>
+  <si>
+    <t>I-1922</t>
+  </si>
+  <si>
+    <t>I-1933</t>
+  </si>
+  <si>
+    <t>I-1928</t>
+  </si>
+  <si>
+    <t>I-1921</t>
+  </si>
+  <si>
+    <t>I-1614</t>
+  </si>
+  <si>
+    <t>I-1468.jpeg</t>
+  </si>
+  <si>
+    <t>I-1493.jpeg</t>
+  </si>
+  <si>
+    <t>I-1494.jpeg</t>
+  </si>
+  <si>
+    <t>I-1514.jpeg</t>
+  </si>
+  <si>
+    <t>I-1516.jpeg</t>
+  </si>
+  <si>
+    <t>I-1538.jpeg</t>
+  </si>
+  <si>
+    <t>I-1545.jpeg</t>
+  </si>
+  <si>
+    <t>I-1557.jpeg</t>
+  </si>
+  <si>
+    <t>I-1558.jpeg</t>
+  </si>
+  <si>
+    <t>I-1559.jpeg</t>
+  </si>
+  <si>
+    <t>I-1560.jpeg</t>
+  </si>
+  <si>
+    <t>I-1562.jpeg</t>
+  </si>
+  <si>
+    <t>I-1572.jpeg</t>
+  </si>
+  <si>
+    <t>I-1573.jpeg</t>
+  </si>
+  <si>
+    <t>I-1574.jpeg</t>
+  </si>
+  <si>
+    <t>I-1584.jpeg</t>
+  </si>
+  <si>
+    <t>I-1586.jpeg</t>
+  </si>
+  <si>
+    <t>I-1587.jpeg</t>
+  </si>
+  <si>
+    <t>I-1588.jpeg</t>
+  </si>
+  <si>
+    <t>I-1589.jpeg</t>
+  </si>
+  <si>
+    <t>I-1594.jpeg</t>
+  </si>
+  <si>
+    <t>I-1600.jpeg</t>
+  </si>
+  <si>
+    <t>I-1605.jpeg</t>
+  </si>
+  <si>
+    <t>I-1606.jpeg</t>
+  </si>
+  <si>
+    <t>I-1607.jpeg</t>
+  </si>
+  <si>
+    <t>I-1611.jpeg</t>
+  </si>
+  <si>
+    <t>I-1615.jpeg</t>
+  </si>
+  <si>
+    <t>I-1616.jpeg</t>
+  </si>
+  <si>
+    <t>I-1617.jpeg</t>
+  </si>
+  <si>
+    <t>I-1618.jpeg</t>
+  </si>
+  <si>
+    <t>I-1621.jpeg</t>
+  </si>
+  <si>
+    <t>I-1624.jpeg</t>
+  </si>
+  <si>
+    <t>I-1625.jpeg</t>
+  </si>
+  <si>
+    <t>I-1627.jpeg</t>
+  </si>
+  <si>
+    <t>I-1631.jpeg</t>
+  </si>
+  <si>
+    <t>I-1632.jpeg</t>
+  </si>
+  <si>
+    <t>I-1633.jpeg</t>
+  </si>
+  <si>
+    <t>I-1636.jpeg</t>
+  </si>
+  <si>
+    <t>I-1637.jpeg</t>
+  </si>
+  <si>
+    <t>I-1638.jpeg</t>
+  </si>
+  <si>
+    <t>I-1639.jpeg</t>
+  </si>
+  <si>
+    <t>I-1642.jpeg</t>
+  </si>
+  <si>
+    <t>I-1643.jpeg</t>
+  </si>
+  <si>
+    <t>I-1644.jpeg</t>
+  </si>
+  <si>
+    <t>I-1645.jpeg</t>
+  </si>
+  <si>
+    <t>I-1646.jpeg</t>
+  </si>
+  <si>
+    <t>I-1647.jpeg</t>
+  </si>
+  <si>
+    <t>I-1648.jpeg</t>
+  </si>
+  <si>
+    <t>I-1649.jpeg</t>
+  </si>
+  <si>
+    <t>I-1650.jpeg</t>
+  </si>
+  <si>
+    <t>I-1651.jpeg</t>
+  </si>
+  <si>
+    <t>I-1652.jpeg</t>
+  </si>
+  <si>
+    <t>I-1653.jpeg</t>
+  </si>
+  <si>
+    <t>I-1654.jpeg</t>
+  </si>
+  <si>
+    <t>I-1655.jpeg</t>
+  </si>
+  <si>
+    <t>I-1656.jpeg</t>
+  </si>
+  <si>
+    <t>I-1658.jpeg</t>
+  </si>
+  <si>
+    <t>I-1659.jpeg</t>
+  </si>
+  <si>
+    <t>I-1660.jpeg</t>
+  </si>
+  <si>
+    <t>I-1661.jpeg</t>
+  </si>
+  <si>
+    <t>I-1662.jpeg</t>
+  </si>
+  <si>
+    <t>I-1664.jpeg</t>
+  </si>
+  <si>
+    <t>I-1665.jpeg</t>
+  </si>
+  <si>
+    <t>I-1667.jpeg</t>
+  </si>
+  <si>
+    <t>I-1669.jpeg</t>
+  </si>
+  <si>
+    <t>I-1670.jpeg</t>
+  </si>
+  <si>
+    <t>I-1671.jpeg</t>
+  </si>
+  <si>
+    <t>I-1672.jpeg</t>
+  </si>
+  <si>
+    <t>I-1673.jpeg</t>
+  </si>
+  <si>
+    <t>I-1674.jpeg</t>
+  </si>
+  <si>
+    <t>I-1675.jpeg</t>
+  </si>
+  <si>
+    <t>I-1676.jpeg</t>
+  </si>
+  <si>
+    <t>I-1677.jpeg</t>
+  </si>
+  <si>
+    <t>I-1679.jpeg</t>
+  </si>
+  <si>
+    <t>I-1681.jpeg</t>
+  </si>
+  <si>
+    <t>I-1687.jpeg</t>
+  </si>
+  <si>
+    <t>I-1690.jpeg</t>
+  </si>
+  <si>
+    <t>I-1708.jpeg</t>
+  </si>
+  <si>
+    <t>I-1709.jpeg</t>
+  </si>
+  <si>
+    <t>I-1710.jpeg</t>
+  </si>
+  <si>
+    <t>I-1715.jpeg</t>
+  </si>
+  <si>
+    <t>I-1716.jpeg</t>
+  </si>
+  <si>
+    <t>I-1717.jpeg</t>
+  </si>
+  <si>
+    <t>I-1721.jpeg</t>
+  </si>
+  <si>
+    <t>I-1722.jpeg</t>
+  </si>
+  <si>
+    <t>I-1725.jpeg</t>
+  </si>
+  <si>
+    <t>I-1728.jpeg</t>
+  </si>
+  <si>
+    <t>I-1729.jpeg</t>
+  </si>
+  <si>
+    <t>I-1730.jpeg</t>
+  </si>
+  <si>
+    <t>I-1731.jpeg</t>
+  </si>
+  <si>
+    <t>I-1732.jpeg</t>
+  </si>
+  <si>
+    <t>I-1733.jpeg</t>
+  </si>
+  <si>
+    <t>I-1734.jpeg</t>
+  </si>
+  <si>
+    <t>I-1735.jpeg</t>
+  </si>
+  <si>
+    <t>I-1751.jpeg</t>
+  </si>
+  <si>
+    <t>I-1766.jpeg</t>
+  </si>
+  <si>
+    <t>I-1767.jpeg</t>
+  </si>
+  <si>
+    <t>I-1771.jpeg</t>
+  </si>
+  <si>
+    <t>I-1772.jpeg</t>
+  </si>
+  <si>
+    <t>I-1773.jpeg</t>
+  </si>
+  <si>
+    <t>I-1775.jpeg</t>
+  </si>
+  <si>
+    <t>I-1776.jpeg</t>
+  </si>
+  <si>
+    <t>I-1777.jpeg</t>
+  </si>
+  <si>
+    <t>I-1778.jpeg</t>
+  </si>
+  <si>
+    <t>I-1779.jpeg</t>
+  </si>
+  <si>
+    <t>I-1780.jpeg</t>
+  </si>
+  <si>
+    <t>I-1782.jpeg</t>
+  </si>
+  <si>
+    <t>I-1783.jpeg</t>
+  </si>
+  <si>
+    <t>I-1784.jpeg</t>
+  </si>
+  <si>
+    <t>I-1785.jpeg</t>
+  </si>
+  <si>
+    <t>I-1786.jpeg</t>
+  </si>
+  <si>
+    <t>I-1787.jpeg</t>
+  </si>
+  <si>
+    <t>I-1813.jpeg</t>
+  </si>
+  <si>
+    <t>I-1814.jpeg</t>
+  </si>
+  <si>
+    <t>I-1815.jpeg</t>
+  </si>
+  <si>
+    <t>I-1818.jpeg</t>
+  </si>
+  <si>
+    <t>I-1819.jpeg</t>
+  </si>
+  <si>
+    <t>I-1822.jpeg</t>
+  </si>
+  <si>
+    <t>I-1823.jpeg</t>
+  </si>
+  <si>
+    <t>I-1827.jpeg</t>
+  </si>
+  <si>
+    <t>I-1828.jpeg</t>
+  </si>
+  <si>
+    <t>I-1830.jpeg</t>
+  </si>
+  <si>
+    <t>I-1833.jpeg</t>
+  </si>
+  <si>
+    <t>I-1841.jpeg</t>
+  </si>
+  <si>
+    <t>I-1842.jpeg</t>
+  </si>
+  <si>
+    <t>I-1843.jpeg</t>
+  </si>
+  <si>
+    <t>I-1845.jpeg</t>
+  </si>
+  <si>
+    <t>I-1847.jpeg</t>
+  </si>
+  <si>
+    <t>I-1848.jpeg</t>
+  </si>
+  <si>
+    <t>I-1849.jpeg</t>
+  </si>
+  <si>
+    <t>I-1851.jpeg</t>
+  </si>
+  <si>
+    <t>I-1852.jpeg</t>
+  </si>
+  <si>
+    <t>I-1853.jpeg</t>
+  </si>
+  <si>
+    <t>I-1854.jpeg</t>
+  </si>
+  <si>
+    <t>I-1855.jpeg</t>
+  </si>
+  <si>
+    <t>I-1865.jpeg</t>
+  </si>
+  <si>
+    <t>I-1872.jpeg</t>
+  </si>
+  <si>
+    <t>I-1873.jpeg</t>
+  </si>
+  <si>
+    <t>I-1874.jpeg</t>
+  </si>
+  <si>
+    <t>I-1876.jpeg</t>
+  </si>
+  <si>
+    <t>I-1877.jpeg</t>
+  </si>
+  <si>
+    <t>I-1878.jpeg</t>
+  </si>
+  <si>
+    <t>I-1889.jpeg</t>
+  </si>
+  <si>
+    <t>I-1890.jpeg</t>
+  </si>
+  <si>
+    <t>I-1891.jpeg</t>
+  </si>
+  <si>
+    <t>I-1892.jpeg</t>
+  </si>
+  <si>
+    <t>I-1893.jpeg</t>
+  </si>
+  <si>
+    <t>I-1894.jpeg</t>
+  </si>
+  <si>
+    <t>I-1895.jpeg</t>
+  </si>
+  <si>
+    <t>I-1897.jpeg</t>
+  </si>
+  <si>
+    <t>I-1899.jpeg</t>
+  </si>
+  <si>
+    <t>I-1900.jpeg</t>
+  </si>
+  <si>
+    <t>I-1902.jpeg</t>
+  </si>
+  <si>
+    <t>I-1909.jpeg</t>
+  </si>
+  <si>
+    <t>I-1910.jpeg</t>
+  </si>
+  <si>
+    <t>I-1912.jpeg</t>
+  </si>
+  <si>
+    <t>I-1915.jpeg</t>
+  </si>
+  <si>
+    <t>I-1924.jpeg</t>
+  </si>
+  <si>
+    <t>I-1925.jpeg</t>
+  </si>
+  <si>
+    <t>I-1934.jpeg</t>
+  </si>
+  <si>
+    <t>I-1935.jpeg</t>
+  </si>
+  <si>
+    <t>I-1922.jpeg</t>
+  </si>
+  <si>
+    <t>I-1933.jpeg</t>
+  </si>
+  <si>
+    <t>I-1928.jpeg</t>
+  </si>
+  <si>
+    <t>I-1921.jpeg</t>
+  </si>
+  <si>
+    <t>I-1614.jpeg</t>
+  </si>
+  <si>
+    <t>I-1612</t>
+  </si>
+  <si>
+    <t>I-1612.jpeg</t>
+  </si>
+  <si>
+    <t>I-1565</t>
+  </si>
+  <si>
+    <t>I-1699</t>
+  </si>
+  <si>
+    <t>I-1565.jpeg</t>
+  </si>
+  <si>
+    <t>I-1699.jpeg</t>
+  </si>
+  <si>
+    <t>I-1898</t>
+  </si>
+  <si>
+    <t>I-1866</t>
+  </si>
+  <si>
+    <t>I-1515</t>
+  </si>
+  <si>
+    <t>I-1582</t>
+  </si>
+  <si>
+    <t>I-1583</t>
+  </si>
+  <si>
+    <t>I-1585</t>
+  </si>
+  <si>
+    <t>I-1463</t>
+  </si>
+  <si>
+    <t>I-1628</t>
+  </si>
+  <si>
+    <t>I-1898.jpeg</t>
+  </si>
+  <si>
+    <t>I-1866.jpeg</t>
+  </si>
+  <si>
+    <t>I-1515.jpeg</t>
+  </si>
+  <si>
+    <t>I-1582.jpeg</t>
+  </si>
+  <si>
+    <t>I-1583.jpeg</t>
+  </si>
+  <si>
+    <t>I-1585.jpeg</t>
+  </si>
+  <si>
+    <t>I-1463.jpeg</t>
+  </si>
+  <si>
+    <t>I-1628.jpeg</t>
+  </si>
+  <si>
+    <t>3 y 4</t>
+  </si>
+  <si>
+    <t>2 y 3</t>
+  </si>
+  <si>
+    <t>Base para fin de brazo en Maq. 316</t>
+  </si>
+  <si>
+    <t>I-1908</t>
+  </si>
+  <si>
+    <t>I-1908.jpeg</t>
+  </si>
+  <si>
+    <t>I-1945.jpeg</t>
+  </si>
+  <si>
+    <t>I-1945</t>
+  </si>
+  <si>
+    <t>I-1566</t>
+  </si>
+  <si>
+    <t>I-1566.jpeg</t>
+  </si>
+  <si>
+    <t>I-1581.jpeg</t>
+  </si>
+  <si>
+    <t>I-1581</t>
+  </si>
+  <si>
+    <t>I-1774</t>
+  </si>
+  <si>
+    <t>I-1774.jpeg</t>
+  </si>
+  <si>
+    <t>I-1930</t>
+  </si>
+  <si>
+    <t>I-1930.jpeg</t>
+  </si>
+  <si>
+    <t>I-1931</t>
+  </si>
+  <si>
+    <t>I-1931.jpeg</t>
+  </si>
+  <si>
     <t>I-1474</t>
   </si>
   <si>
-    <t>I-1493</t>
-  </si>
-  <si>
-    <t>I-1494</t>
-  </si>
-  <si>
-    <t>I-1514</t>
-  </si>
-  <si>
-    <t>I-1516</t>
-  </si>
-  <si>
-    <t>I-1538</t>
-  </si>
-  <si>
-    <t>I-1545</t>
-  </si>
-  <si>
-    <t>I-1557</t>
-  </si>
-  <si>
-    <t>I-1558</t>
-  </si>
-  <si>
-    <t>I-1559</t>
-  </si>
-  <si>
-    <t>I-1560</t>
-  </si>
-  <si>
-    <t>I-1562</t>
-  </si>
-  <si>
-    <t>I-1572</t>
-  </si>
-  <si>
-    <t>I-1573</t>
-  </si>
-  <si>
-    <t>I-1574</t>
-  </si>
-  <si>
-    <t>I-1584</t>
-  </si>
-  <si>
-    <t>I-1586</t>
-  </si>
-  <si>
-    <t>I-1587</t>
-  </si>
-  <si>
-    <t>I-1588</t>
-  </si>
-  <si>
-    <t>I-1589</t>
-  </si>
-  <si>
-    <t>I-1594</t>
-  </si>
-  <si>
-    <t>I-1600</t>
-  </si>
-  <si>
-    <t>I-1605</t>
-  </si>
-  <si>
-    <t>I-1606</t>
-  </si>
-  <si>
-    <t>I-1607</t>
-  </si>
-  <si>
-    <t>I-1611</t>
-  </si>
-  <si>
-    <t>I-1615</t>
-  </si>
-  <si>
-    <t>I-1616</t>
-  </si>
-  <si>
-    <t>I-1617</t>
-  </si>
-  <si>
-    <t>I-1618</t>
-  </si>
-  <si>
-    <t>I-1621</t>
-  </si>
-  <si>
-    <t>I-1624</t>
-  </si>
-  <si>
-    <t>I-1625</t>
-  </si>
-  <si>
-    <t>I-1627</t>
-  </si>
-  <si>
-    <t>I-1631</t>
-  </si>
-  <si>
-    <t>I-1632</t>
-  </si>
-  <si>
-    <t>I-1633</t>
-  </si>
-  <si>
-    <t>I-1636</t>
-  </si>
-  <si>
-    <t>I-1637</t>
-  </si>
-  <si>
-    <t>I-1638</t>
-  </si>
-  <si>
-    <t>I-1639</t>
-  </si>
-  <si>
-    <t>I-1642</t>
-  </si>
-  <si>
-    <t>I-1643</t>
-  </si>
-  <si>
-    <t>I-1644</t>
-  </si>
-  <si>
-    <t>I-1645</t>
-  </si>
-  <si>
-    <t>I-1646</t>
-  </si>
-  <si>
-    <t>I-1647</t>
-  </si>
-  <si>
-    <t>I-1648</t>
-  </si>
-  <si>
-    <t>I-1649</t>
-  </si>
-  <si>
-    <t>I-1650</t>
-  </si>
-  <si>
-    <t>I-1651</t>
-  </si>
-  <si>
-    <t>I-1652</t>
-  </si>
-  <si>
-    <t>I-1653</t>
-  </si>
-  <si>
-    <t>I-1654</t>
-  </si>
-  <si>
-    <t>I-1655</t>
-  </si>
-  <si>
-    <t>I-1656</t>
-  </si>
-  <si>
-    <t>I-1658</t>
-  </si>
-  <si>
-    <t>I-1659</t>
-  </si>
-  <si>
-    <t>I-1660</t>
-  </si>
-  <si>
-    <t>I-1661</t>
-  </si>
-  <si>
-    <t>I-1662</t>
-  </si>
-  <si>
-    <t>I-1664</t>
-  </si>
-  <si>
-    <t>I-1665</t>
-  </si>
-  <si>
-    <t>I-1667</t>
-  </si>
-  <si>
-    <t>I-1669</t>
-  </si>
-  <si>
-    <t>I-1670</t>
-  </si>
-  <si>
-    <t>I-1671</t>
-  </si>
-  <si>
-    <t>I-1672</t>
-  </si>
-  <si>
-    <t>I-1673</t>
-  </si>
-  <si>
-    <t>I-1674</t>
-  </si>
-  <si>
-    <t>I-1675</t>
-  </si>
-  <si>
-    <t>I-1676</t>
-  </si>
-  <si>
-    <t>I-1677</t>
-  </si>
-  <si>
-    <t>I-1679</t>
-  </si>
-  <si>
-    <t>I-1681</t>
-  </si>
-  <si>
-    <t>I-1687</t>
-  </si>
-  <si>
-    <t>I-1690</t>
-  </si>
-  <si>
-    <t>I-1708</t>
-  </si>
-  <si>
-    <t>I-1709</t>
-  </si>
-  <si>
-    <t>I-1710</t>
-  </si>
-  <si>
-    <t>I-1715</t>
-  </si>
-  <si>
-    <t>I-1716</t>
-  </si>
-  <si>
-    <t>I-1717</t>
-  </si>
-  <si>
-    <t>I-1721</t>
-  </si>
-  <si>
-    <t>I-1722</t>
-  </si>
-  <si>
-    <t>I-1725</t>
-  </si>
-  <si>
-    <t>I-1728</t>
-  </si>
-  <si>
-    <t>I-1729</t>
-  </si>
-  <si>
-    <t>I-1730</t>
-  </si>
-  <si>
-    <t>I-1731</t>
-  </si>
-  <si>
-    <t>I-1732</t>
-  </si>
-  <si>
-    <t>I-1733</t>
-  </si>
-  <si>
-    <t>I-1734</t>
-  </si>
-  <si>
-    <t>I-1735</t>
-  </si>
-  <si>
-    <t>I-1751</t>
-  </si>
-  <si>
-    <t>I-1766</t>
-  </si>
-  <si>
-    <t>I-1767</t>
-  </si>
-  <si>
-    <t>I-1771</t>
-  </si>
-  <si>
-    <t>I-1772</t>
-  </si>
-  <si>
-    <t>I-1773</t>
-  </si>
-  <si>
-    <t>I-1775</t>
-  </si>
-  <si>
-    <t>I-1776</t>
-  </si>
-  <si>
-    <t>I-1777</t>
-  </si>
-  <si>
-    <t>I-1778</t>
-  </si>
-  <si>
-    <t>I-1779</t>
-  </si>
-  <si>
-    <t>I-1780</t>
-  </si>
-  <si>
-    <t>I-1782</t>
-  </si>
-  <si>
-    <t>I-1783</t>
-  </si>
-  <si>
-    <t>I-1784</t>
-  </si>
-  <si>
-    <t>I-1785</t>
-  </si>
-  <si>
-    <t>I-1786</t>
-  </si>
-  <si>
-    <t>I-1787</t>
-  </si>
-  <si>
-    <t>I-1813</t>
-  </si>
-  <si>
-    <t>I-1814</t>
-  </si>
-  <si>
-    <t>I-1815</t>
-  </si>
-  <si>
-    <t>I-1818</t>
-  </si>
-  <si>
-    <t>I-1819</t>
-  </si>
-  <si>
-    <t>I-1822</t>
-  </si>
-  <si>
-    <t>I-1823</t>
-  </si>
-  <si>
-    <t>I-1827</t>
-  </si>
-  <si>
-    <t>I-1828</t>
-  </si>
-  <si>
-    <t>I-1830</t>
-  </si>
-  <si>
-    <t>I-1833</t>
-  </si>
-  <si>
-    <t>I-1841</t>
-  </si>
-  <si>
-    <t>I-1842</t>
-  </si>
-  <si>
-    <t>I-1843</t>
-  </si>
-  <si>
-    <t>I-1845</t>
-  </si>
-  <si>
-    <t>I-1847</t>
-  </si>
-  <si>
-    <t>I-1848</t>
-  </si>
-  <si>
-    <t>I-1849</t>
-  </si>
-  <si>
-    <t>I-1851</t>
-  </si>
-  <si>
-    <t>I-1852</t>
-  </si>
-  <si>
-    <t>I-1853</t>
-  </si>
-  <si>
-    <t>I-1854</t>
-  </si>
-  <si>
-    <t>I-1855</t>
-  </si>
-  <si>
-    <t>I-1865</t>
-  </si>
-  <si>
-    <t>I-1872</t>
-  </si>
-  <si>
-    <t>I-1873</t>
-  </si>
-  <si>
-    <t>I-1874</t>
-  </si>
-  <si>
-    <t>I-1876</t>
-  </si>
-  <si>
-    <t>I-1877</t>
-  </si>
-  <si>
-    <t>I-1878</t>
-  </si>
-  <si>
-    <t>I-1889</t>
-  </si>
-  <si>
-    <t>I-1890</t>
-  </si>
-  <si>
-    <t>I-1891</t>
-  </si>
-  <si>
-    <t>I-1892</t>
-  </si>
-  <si>
-    <t>I-1893</t>
-  </si>
-  <si>
-    <t>I-1894</t>
-  </si>
-  <si>
-    <t>I-1895</t>
-  </si>
-  <si>
-    <t>I-1897</t>
-  </si>
-  <si>
-    <t>I-1899</t>
-  </si>
-  <si>
-    <t>I-1900</t>
-  </si>
-  <si>
-    <t>I-1902</t>
-  </si>
-  <si>
-    <t>I-1909</t>
-  </si>
-  <si>
-    <t>I-1910</t>
-  </si>
-  <si>
-    <t>I-1912</t>
-  </si>
-  <si>
-    <t>I-1915</t>
-  </si>
-  <si>
-    <t>I-1924</t>
-  </si>
-  <si>
-    <t>I-1925</t>
-  </si>
-  <si>
-    <t>I-1934</t>
-  </si>
-  <si>
-    <t>I-1935</t>
-  </si>
-  <si>
-    <t>I-1922</t>
-  </si>
-  <si>
-    <t>I-1933</t>
-  </si>
-  <si>
-    <t>I-1928</t>
-  </si>
-  <si>
-    <t>I-1921</t>
-  </si>
-  <si>
-    <t>I-1614</t>
-  </si>
-  <si>
-    <t>I-1468.jpeg</t>
-  </si>
-  <si>
     <t>I-1474.jpeg</t>
-  </si>
-  <si>
-    <t>I-1493.jpeg</t>
-  </si>
-  <si>
-    <t>I-1494.jpeg</t>
-  </si>
-  <si>
-    <t>I-1514.jpeg</t>
-  </si>
-  <si>
-    <t>I-1516.jpeg</t>
-  </si>
-  <si>
-    <t>I-1538.jpeg</t>
-  </si>
-  <si>
-    <t>I-1545.jpeg</t>
-  </si>
-  <si>
-    <t>I-1557.jpeg</t>
-  </si>
-  <si>
-    <t>I-1558.jpeg</t>
-  </si>
-  <si>
-    <t>I-1559.jpeg</t>
-  </si>
-  <si>
-    <t>I-1560.jpeg</t>
-  </si>
-  <si>
-    <t>I-1562.jpeg</t>
-  </si>
-  <si>
-    <t>I-1572.jpeg</t>
-  </si>
-  <si>
-    <t>I-1573.jpeg</t>
-  </si>
-  <si>
-    <t>I-1574.jpeg</t>
-  </si>
-  <si>
-    <t>I-1584.jpeg</t>
-  </si>
-  <si>
-    <t>I-1586.jpeg</t>
-  </si>
-  <si>
-    <t>I-1587.jpeg</t>
-  </si>
-  <si>
-    <t>I-1588.jpeg</t>
-  </si>
-  <si>
-    <t>I-1589.jpeg</t>
-  </si>
-  <si>
-    <t>I-1594.jpeg</t>
-  </si>
-  <si>
-    <t>I-1600.jpeg</t>
-  </si>
-  <si>
-    <t>I-1605.jpeg</t>
-  </si>
-  <si>
-    <t>I-1606.jpeg</t>
-  </si>
-  <si>
-    <t>I-1607.jpeg</t>
-  </si>
-  <si>
-    <t>I-1611.jpeg</t>
-  </si>
-  <si>
-    <t>I-1615.jpeg</t>
-  </si>
-  <si>
-    <t>I-1616.jpeg</t>
-  </si>
-  <si>
-    <t>I-1617.jpeg</t>
-  </si>
-  <si>
-    <t>I-1618.jpeg</t>
-  </si>
-  <si>
-    <t>I-1621.jpeg</t>
-  </si>
-  <si>
-    <t>I-1624.jpeg</t>
-  </si>
-  <si>
-    <t>I-1625.jpeg</t>
-  </si>
-  <si>
-    <t>I-1627.jpeg</t>
-  </si>
-  <si>
-    <t>I-1631.jpeg</t>
-  </si>
-  <si>
-    <t>I-1632.jpeg</t>
-  </si>
-  <si>
-    <t>I-1633.jpeg</t>
-  </si>
-  <si>
-    <t>I-1636.jpeg</t>
-  </si>
-  <si>
-    <t>I-1637.jpeg</t>
-  </si>
-  <si>
-    <t>I-1638.jpeg</t>
-  </si>
-  <si>
-    <t>I-1639.jpeg</t>
-  </si>
-  <si>
-    <t>I-1642.jpeg</t>
-  </si>
-  <si>
-    <t>I-1643.jpeg</t>
-  </si>
-  <si>
-    <t>I-1644.jpeg</t>
-  </si>
-  <si>
-    <t>I-1645.jpeg</t>
-  </si>
-  <si>
-    <t>I-1646.jpeg</t>
-  </si>
-  <si>
-    <t>I-1647.jpeg</t>
-  </si>
-  <si>
-    <t>I-1648.jpeg</t>
-  </si>
-  <si>
-    <t>I-1649.jpeg</t>
-  </si>
-  <si>
-    <t>I-1650.jpeg</t>
-  </si>
-  <si>
-    <t>I-1651.jpeg</t>
-  </si>
-  <si>
-    <t>I-1652.jpeg</t>
-  </si>
-  <si>
-    <t>I-1653.jpeg</t>
-  </si>
-  <si>
-    <t>I-1654.jpeg</t>
-  </si>
-  <si>
-    <t>I-1655.jpeg</t>
-  </si>
-  <si>
-    <t>I-1656.jpeg</t>
-  </si>
-  <si>
-    <t>I-1658.jpeg</t>
-  </si>
-  <si>
-    <t>I-1659.jpeg</t>
-  </si>
-  <si>
-    <t>I-1660.jpeg</t>
-  </si>
-  <si>
-    <t>I-1661.jpeg</t>
-  </si>
-  <si>
-    <t>I-1662.jpeg</t>
-  </si>
-  <si>
-    <t>I-1664.jpeg</t>
-  </si>
-  <si>
-    <t>I-1665.jpeg</t>
-  </si>
-  <si>
-    <t>I-1667.jpeg</t>
-  </si>
-  <si>
-    <t>I-1669.jpeg</t>
-  </si>
-  <si>
-    <t>I-1670.jpeg</t>
-  </si>
-  <si>
-    <t>I-1671.jpeg</t>
-  </si>
-  <si>
-    <t>I-1672.jpeg</t>
-  </si>
-  <si>
-    <t>I-1673.jpeg</t>
-  </si>
-  <si>
-    <t>I-1674.jpeg</t>
-  </si>
-  <si>
-    <t>I-1675.jpeg</t>
-  </si>
-  <si>
-    <t>I-1676.jpeg</t>
-  </si>
-  <si>
-    <t>I-1677.jpeg</t>
-  </si>
-  <si>
-    <t>I-1679.jpeg</t>
-  </si>
-  <si>
-    <t>I-1681.jpeg</t>
-  </si>
-  <si>
-    <t>I-1687.jpeg</t>
-  </si>
-  <si>
-    <t>I-1690.jpeg</t>
-  </si>
-  <si>
-    <t>I-1708.jpeg</t>
-  </si>
-  <si>
-    <t>I-1709.jpeg</t>
-  </si>
-  <si>
-    <t>I-1710.jpeg</t>
-  </si>
-  <si>
-    <t>I-1715.jpeg</t>
-  </si>
-  <si>
-    <t>I-1716.jpeg</t>
-  </si>
-  <si>
-    <t>I-1717.jpeg</t>
-  </si>
-  <si>
-    <t>I-1721.jpeg</t>
-  </si>
-  <si>
-    <t>I-1722.jpeg</t>
-  </si>
-  <si>
-    <t>I-1725.jpeg</t>
-  </si>
-  <si>
-    <t>I-1728.jpeg</t>
-  </si>
-  <si>
-    <t>I-1729.jpeg</t>
-  </si>
-  <si>
-    <t>I-1730.jpeg</t>
-  </si>
-  <si>
-    <t>I-1731.jpeg</t>
-  </si>
-  <si>
-    <t>I-1732.jpeg</t>
-  </si>
-  <si>
-    <t>I-1733.jpeg</t>
-  </si>
-  <si>
-    <t>I-1734.jpeg</t>
-  </si>
-  <si>
-    <t>I-1735.jpeg</t>
-  </si>
-  <si>
-    <t>I-1751.jpeg</t>
-  </si>
-  <si>
-    <t>I-1766.jpeg</t>
-  </si>
-  <si>
-    <t>I-1767.jpeg</t>
-  </si>
-  <si>
-    <t>I-1771.jpeg</t>
-  </si>
-  <si>
-    <t>I-1772.jpeg</t>
-  </si>
-  <si>
-    <t>I-1773.jpeg</t>
-  </si>
-  <si>
-    <t>I-1775.jpeg</t>
-  </si>
-  <si>
-    <t>I-1776.jpeg</t>
-  </si>
-  <si>
-    <t>I-1777.jpeg</t>
-  </si>
-  <si>
-    <t>I-1778.jpeg</t>
-  </si>
-  <si>
-    <t>I-1779.jpeg</t>
-  </si>
-  <si>
-    <t>I-1780.jpeg</t>
-  </si>
-  <si>
-    <t>I-1782.jpeg</t>
-  </si>
-  <si>
-    <t>I-1783.jpeg</t>
-  </si>
-  <si>
-    <t>I-1784.jpeg</t>
-  </si>
-  <si>
-    <t>I-1785.jpeg</t>
-  </si>
-  <si>
-    <t>I-1786.jpeg</t>
-  </si>
-  <si>
-    <t>I-1787.jpeg</t>
-  </si>
-  <si>
-    <t>I-1813.jpeg</t>
-  </si>
-  <si>
-    <t>I-1814.jpeg</t>
-  </si>
-  <si>
-    <t>I-1815.jpeg</t>
-  </si>
-  <si>
-    <t>I-1818.jpeg</t>
-  </si>
-  <si>
-    <t>I-1819.jpeg</t>
-  </si>
-  <si>
-    <t>I-1822.jpeg</t>
-  </si>
-  <si>
-    <t>I-1823.jpeg</t>
-  </si>
-  <si>
-    <t>I-1827.jpeg</t>
-  </si>
-  <si>
-    <t>I-1828.jpeg</t>
-  </si>
-  <si>
-    <t>I-1830.jpeg</t>
-  </si>
-  <si>
-    <t>I-1833.jpeg</t>
-  </si>
-  <si>
-    <t>I-1841.jpeg</t>
-  </si>
-  <si>
-    <t>I-1842.jpeg</t>
-  </si>
-  <si>
-    <t>I-1843.jpeg</t>
-  </si>
-  <si>
-    <t>I-1845.jpeg</t>
-  </si>
-  <si>
-    <t>I-1847.jpeg</t>
-  </si>
-  <si>
-    <t>I-1848.jpeg</t>
-  </si>
-  <si>
-    <t>I-1849.jpeg</t>
-  </si>
-  <si>
-    <t>I-1851.jpeg</t>
-  </si>
-  <si>
-    <t>I-1852.jpeg</t>
-  </si>
-  <si>
-    <t>I-1853.jpeg</t>
-  </si>
-  <si>
-    <t>I-1854.jpeg</t>
-  </si>
-  <si>
-    <t>I-1855.jpeg</t>
-  </si>
-  <si>
-    <t>I-1865.jpeg</t>
-  </si>
-  <si>
-    <t>I-1872.jpeg</t>
-  </si>
-  <si>
-    <t>I-1873.jpeg</t>
-  </si>
-  <si>
-    <t>I-1874.jpeg</t>
-  </si>
-  <si>
-    <t>I-1876.jpeg</t>
-  </si>
-  <si>
-    <t>I-1877.jpeg</t>
-  </si>
-  <si>
-    <t>I-1878.jpeg</t>
-  </si>
-  <si>
-    <t>I-1889.jpeg</t>
-  </si>
-  <si>
-    <t>I-1890.jpeg</t>
-  </si>
-  <si>
-    <t>I-1891.jpeg</t>
-  </si>
-  <si>
-    <t>I-1892.jpeg</t>
-  </si>
-  <si>
-    <t>I-1893.jpeg</t>
-  </si>
-  <si>
-    <t>I-1894.jpeg</t>
-  </si>
-  <si>
-    <t>I-1895.jpeg</t>
-  </si>
-  <si>
-    <t>I-1897.jpeg</t>
-  </si>
-  <si>
-    <t>I-1899.jpeg</t>
-  </si>
-  <si>
-    <t>I-1900.jpeg</t>
-  </si>
-  <si>
-    <t>I-1902.jpeg</t>
-  </si>
-  <si>
-    <t>I-1909.jpeg</t>
-  </si>
-  <si>
-    <t>I-1910.jpeg</t>
-  </si>
-  <si>
-    <t>I-1912.jpeg</t>
-  </si>
-  <si>
-    <t>I-1915.jpeg</t>
-  </si>
-  <si>
-    <t>I-1924.jpeg</t>
-  </si>
-  <si>
-    <t>I-1925.jpeg</t>
-  </si>
-  <si>
-    <t>I-1934.jpeg</t>
-  </si>
-  <si>
-    <t>I-1935.jpeg</t>
-  </si>
-  <si>
-    <t>I-1922.jpeg</t>
-  </si>
-  <si>
-    <t>I-1933.jpeg</t>
-  </si>
-  <si>
-    <t>I-1928.jpeg</t>
-  </si>
-  <si>
-    <t>I-1921.jpeg</t>
-  </si>
-  <si>
-    <t>I-1614.jpeg</t>
-  </si>
-  <si>
-    <t>I-1612</t>
-  </si>
-  <si>
-    <t>I-1612.jpeg</t>
-  </si>
-  <si>
-    <t>I-1565</t>
-  </si>
-  <si>
-    <t>I-1699</t>
-  </si>
-  <si>
-    <t>I-1565.jpeg</t>
-  </si>
-  <si>
-    <t>I-1699.jpeg</t>
-  </si>
-  <si>
-    <t>I-1898</t>
-  </si>
-  <si>
-    <t>I-1866</t>
-  </si>
-  <si>
-    <t>I-1515</t>
-  </si>
-  <si>
-    <t>I-1582</t>
-  </si>
-  <si>
-    <t>I-1583</t>
-  </si>
-  <si>
-    <t>I-1585</t>
-  </si>
-  <si>
-    <t>I-1463</t>
-  </si>
-  <si>
-    <t>I-1628</t>
-  </si>
-  <si>
-    <t>I-1898.jpeg</t>
-  </si>
-  <si>
-    <t>I-1866.jpeg</t>
-  </si>
-  <si>
-    <t>I-1515.jpeg</t>
-  </si>
-  <si>
-    <t>I-1582.jpeg</t>
-  </si>
-  <si>
-    <t>I-1583.jpeg</t>
-  </si>
-  <si>
-    <t>I-1585.jpeg</t>
-  </si>
-  <si>
-    <t>I-1463.jpeg</t>
-  </si>
-  <si>
-    <t>I-1628.jpeg</t>
-  </si>
-  <si>
-    <t>3 y 4</t>
-  </si>
-  <si>
-    <t>2 y 3</t>
-  </si>
-  <si>
-    <t>Base para fin de brazo en Maq. 316</t>
-  </si>
-  <si>
-    <t>I-1908</t>
-  </si>
-  <si>
-    <t>I-1908.jpeg</t>
-  </si>
-  <si>
-    <t>I-1945.jpeg</t>
-  </si>
-  <si>
-    <t>I-1945</t>
-  </si>
-  <si>
-    <t>I-1566</t>
-  </si>
-  <si>
-    <t>I-1566.jpeg</t>
-  </si>
-  <si>
-    <t>I-1581.jpeg</t>
-  </si>
-  <si>
-    <t>I-1581</t>
-  </si>
-  <si>
-    <t>I-1774</t>
-  </si>
-  <si>
-    <t>I-1774.jpeg</t>
-  </si>
-  <si>
-    <t>I-1930</t>
-  </si>
-  <si>
-    <t>I-1930.jpeg</t>
-  </si>
-  <si>
-    <t>I-1931</t>
-  </si>
-  <si>
-    <t>I-1931.jpeg</t>
   </si>
 </sst>
 </file>
@@ -2354,14 +2354,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B6791C-A8A7-4753-A504-FAA9E3EE8745}">
-  <dimension ref="A1:F320"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:F321"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2385,7 +2386,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -2405,7 +2406,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2425,7 +2426,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2445,7 +2446,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -2465,7 +2466,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -2485,7 +2486,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -2505,7 +2506,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -2525,7 +2526,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -2545,7 +2546,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -2565,7 +2566,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -2585,7 +2586,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -2605,7 +2606,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -2625,7 +2626,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -2645,7 +2646,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -2665,7 +2666,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -2685,7 +2686,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -2705,7 +2706,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -2725,7 +2726,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -2745,7 +2746,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -2765,7 +2766,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -2785,7 +2786,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -2805,7 +2806,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -2825,7 +2826,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -2845,7 +2846,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -2865,7 +2866,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -2885,9 +2886,9 @@
         <v>164</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B27" t="s">
         <v>256</v>
@@ -2902,12 +2903,12 @@
         <v>1</v>
       </c>
       <c r="F27" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B28" t="s">
         <v>256</v>
@@ -2922,10 +2923,10 @@
         <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>30</v>
       </c>
@@ -2945,7 +2946,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>31</v>
       </c>
@@ -2965,7 +2966,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>32</v>
       </c>
@@ -2985,7 +2986,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>34</v>
       </c>
@@ -3005,7 +3006,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>35</v>
       </c>
@@ -3025,7 +3026,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>36</v>
       </c>
@@ -3045,7 +3046,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>37</v>
       </c>
@@ -3065,7 +3066,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>38</v>
       </c>
@@ -3085,7 +3086,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>39</v>
       </c>
@@ -3105,7 +3106,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>41</v>
       </c>
@@ -3125,7 +3126,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>42</v>
       </c>
@@ -3145,7 +3146,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>43</v>
       </c>
@@ -3165,7 +3166,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>44</v>
       </c>
@@ -3185,7 +3186,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>45</v>
       </c>
@@ -3205,7 +3206,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>47</v>
       </c>
@@ -3225,7 +3226,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>48</v>
       </c>
@@ -3245,7 +3246,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>49</v>
       </c>
@@ -3265,7 +3266,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>50</v>
       </c>
@@ -3285,7 +3286,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>51</v>
       </c>
@@ -3305,7 +3306,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>53</v>
       </c>
@@ -3325,7 +3326,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>54</v>
       </c>
@@ -3345,7 +3346,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>55</v>
       </c>
@@ -3365,7 +3366,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>57</v>
       </c>
@@ -3379,18 +3380,18 @@
         <v>56</v>
       </c>
       <c r="E51" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="F51" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>59</v>
       </c>
       <c r="B52" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C52">
         <v>3</v>
@@ -3399,13 +3400,13 @@
         <v>56</v>
       </c>
       <c r="E52" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="F52" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>60</v>
       </c>
@@ -3425,7 +3426,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>62</v>
       </c>
@@ -3445,7 +3446,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>63</v>
       </c>
@@ -3465,7 +3466,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>64</v>
       </c>
@@ -3482,7 +3483,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>64</v>
       </c>
@@ -3499,7 +3500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>64</v>
       </c>
@@ -3516,7 +3517,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>64</v>
       </c>
@@ -3533,7 +3534,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>89</v>
       </c>
@@ -3550,7 +3551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>89</v>
       </c>
@@ -3567,7 +3568,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>58</v>
       </c>
@@ -3587,7 +3588,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>91</v>
       </c>
@@ -3607,7 +3608,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>93</v>
       </c>
@@ -3627,7 +3628,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>94</v>
       </c>
@@ -3647,7 +3648,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>95</v>
       </c>
@@ -3667,7 +3668,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>96</v>
       </c>
@@ -3687,7 +3688,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>98</v>
       </c>
@@ -3707,7 +3708,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>99</v>
       </c>
@@ -3727,7 +3728,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>100</v>
       </c>
@@ -3747,7 +3748,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>101</v>
       </c>
@@ -3767,7 +3768,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>102</v>
       </c>
@@ -3787,7 +3788,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>104</v>
       </c>
@@ -3807,7 +3808,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>105</v>
       </c>
@@ -3827,7 +3828,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>106</v>
       </c>
@@ -3847,7 +3848,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>107</v>
       </c>
@@ -3867,7 +3868,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>108</v>
       </c>
@@ -3887,7 +3888,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>66</v>
       </c>
@@ -3907,7 +3908,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>68</v>
       </c>
@@ -3927,7 +3928,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>89</v>
       </c>
@@ -3944,7 +3945,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>69</v>
       </c>
@@ -3964,7 +3965,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>70</v>
       </c>
@@ -3984,9 +3985,9 @@
         <v>196</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B83" t="s">
         <v>256</v>
@@ -4001,10 +4002,10 @@
         <v>1</v>
       </c>
       <c r="F83" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>71</v>
       </c>
@@ -4024,7 +4025,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>73</v>
       </c>
@@ -4044,7 +4045,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>74</v>
       </c>
@@ -4064,7 +4065,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>75</v>
       </c>
@@ -4084,7 +4085,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>77</v>
       </c>
@@ -4104,7 +4105,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>78</v>
       </c>
@@ -4124,7 +4125,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>79</v>
       </c>
@@ -4144,7 +4145,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>80</v>
       </c>
@@ -4164,7 +4165,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>81</v>
       </c>
@@ -4184,7 +4185,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>82</v>
       </c>
@@ -4204,7 +4205,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>84</v>
       </c>
@@ -4224,7 +4225,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>85</v>
       </c>
@@ -4244,7 +4245,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>86</v>
       </c>
@@ -4264,7 +4265,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>87</v>
       </c>
@@ -4284,7 +4285,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>88</v>
       </c>
@@ -4304,7 +4305,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>109</v>
       </c>
@@ -4324,7 +4325,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>111</v>
       </c>
@@ -4344,7 +4345,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>112</v>
       </c>
@@ -4364,7 +4365,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>113</v>
       </c>
@@ -4384,7 +4385,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>114</v>
       </c>
@@ -4404,7 +4405,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>116</v>
       </c>
@@ -4424,7 +4425,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>117</v>
       </c>
@@ -4444,7 +4445,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>118</v>
       </c>
@@ -4464,7 +4465,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>119</v>
       </c>
@@ -4484,7 +4485,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>120</v>
       </c>
@@ -4504,7 +4505,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>123</v>
       </c>
@@ -4524,7 +4525,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>122</v>
       </c>
@@ -4544,7 +4545,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>124</v>
       </c>
@@ -4564,7 +4565,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>125</v>
       </c>
@@ -4584,7 +4585,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>127</v>
       </c>
@@ -4604,7 +4605,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>128</v>
       </c>
@@ -4624,7 +4625,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>130</v>
       </c>
@@ -4644,7 +4645,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>132</v>
       </c>
@@ -4664,7 +4665,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>133</v>
       </c>
@@ -4684,7 +4685,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>134</v>
       </c>
@@ -4704,7 +4705,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>135</v>
       </c>
@@ -4724,7 +4725,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>136</v>
       </c>
@@ -4744,7 +4745,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>89</v>
       </c>
@@ -4761,7 +4762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>89</v>
       </c>
@@ -4778,7 +4779,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>89</v>
       </c>
@@ -4795,7 +4796,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>89</v>
       </c>
@@ -4812,7 +4813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>89</v>
       </c>
@@ -4829,9 +4830,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B126" t="s">
         <v>256</v>
@@ -4846,10 +4847,10 @@
         <v>3</v>
       </c>
       <c r="F126" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>89</v>
       </c>
@@ -4866,7 +4867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>89</v>
       </c>
@@ -4883,7 +4884,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>89</v>
       </c>
@@ -4900,9 +4901,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>430</v>
+        <v>640</v>
       </c>
       <c r="B130" t="s">
         <v>256</v>
@@ -4917,12 +4918,12 @@
         <v>1</v>
       </c>
       <c r="F130" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B131" t="s">
         <v>256</v>
@@ -4940,9 +4941,9 @@
         <v>595</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>642</v>
+        <v>427</v>
       </c>
       <c r="B132" t="s">
         <v>256</v>
@@ -4957,93 +4958,93 @@
         <v>1</v>
       </c>
       <c r="F132" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
+        <v>430</v>
+      </c>
+      <c r="B133" t="s">
+        <v>256</v>
+      </c>
+      <c r="C133">
+        <v>1</v>
+      </c>
+      <c r="D133" t="s">
+        <v>1</v>
+      </c>
+      <c r="E133">
+        <v>2</v>
+      </c>
+      <c r="F133" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>434</v>
+      </c>
+      <c r="B134" t="s">
+        <v>256</v>
+      </c>
+      <c r="C134">
+        <v>1</v>
+      </c>
+      <c r="D134" t="s">
+        <v>1</v>
+      </c>
+      <c r="E134">
+        <v>2</v>
+      </c>
+      <c r="F134" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>437</v>
+      </c>
+      <c r="B135" t="s">
+        <v>256</v>
+      </c>
+      <c r="C135">
+        <v>1</v>
+      </c>
+      <c r="D135" t="s">
+        <v>1</v>
+      </c>
+      <c r="E135">
+        <v>2</v>
+      </c>
+      <c r="F135" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>436</v>
+      </c>
+      <c r="B136" t="s">
+        <v>256</v>
+      </c>
+      <c r="C136">
+        <v>1</v>
+      </c>
+      <c r="D136" t="s">
+        <v>1</v>
+      </c>
+      <c r="E136">
+        <v>3</v>
+      </c>
+      <c r="F136" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
         <v>431</v>
       </c>
-      <c r="B133" t="s">
-        <v>256</v>
-      </c>
-      <c r="C133">
-        <v>1</v>
-      </c>
-      <c r="D133" t="s">
-        <v>1</v>
-      </c>
-      <c r="E133">
-        <v>2</v>
-      </c>
-      <c r="F133" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
-        <v>435</v>
-      </c>
-      <c r="B134" t="s">
-        <v>256</v>
-      </c>
-      <c r="C134">
-        <v>1</v>
-      </c>
-      <c r="D134" t="s">
-        <v>1</v>
-      </c>
-      <c r="E134">
-        <v>2</v>
-      </c>
-      <c r="F134" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
-        <v>438</v>
-      </c>
-      <c r="B135" t="s">
-        <v>256</v>
-      </c>
-      <c r="C135">
-        <v>1</v>
-      </c>
-      <c r="D135" t="s">
-        <v>1</v>
-      </c>
-      <c r="E135">
-        <v>2</v>
-      </c>
-      <c r="F135" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
-        <v>437</v>
-      </c>
-      <c r="B136" t="s">
-        <v>256</v>
-      </c>
-      <c r="C136">
-        <v>1</v>
-      </c>
-      <c r="D136" t="s">
-        <v>1</v>
-      </c>
-      <c r="E136">
-        <v>3</v>
-      </c>
-      <c r="F136" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
-        <v>432</v>
-      </c>
       <c r="B137" t="s">
         <v>256</v>
       </c>
@@ -5057,12 +5058,12 @@
         <v>3</v>
       </c>
       <c r="F137" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B138" t="s">
         <v>256</v>
@@ -5077,12 +5078,12 @@
         <v>4</v>
       </c>
       <c r="F138" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B139" t="s">
         <v>256</v>
@@ -5097,12 +5098,12 @@
         <v>4</v>
       </c>
       <c r="F139" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B140" t="s">
         <v>256</v>
@@ -5117,12 +5118,12 @@
         <v>4</v>
       </c>
       <c r="F140" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="B141" t="s">
         <v>256</v>
@@ -5137,12 +5138,12 @@
         <v>4</v>
       </c>
       <c r="F141" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>421</v>
+        <v>642</v>
       </c>
       <c r="B142" t="s">
         <v>256</v>
@@ -5157,10 +5158,10 @@
         <v>1</v>
       </c>
       <c r="F142" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>420</v>
       </c>
@@ -5177,10 +5178,10 @@
         <v>1</v>
       </c>
       <c r="F143" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>419</v>
       </c>
@@ -5197,12 +5198,12 @@
         <v>1</v>
       </c>
       <c r="F144" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>644</v>
+        <v>418</v>
       </c>
       <c r="B145" t="s">
         <v>256</v>
@@ -5217,12 +5218,12 @@
         <v>1</v>
       </c>
       <c r="F145" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B146" t="s">
         <v>256</v>
@@ -5237,12 +5238,12 @@
         <v>2</v>
       </c>
       <c r="F146" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B147" t="s">
         <v>256</v>
@@ -5257,12 +5258,12 @@
         <v>2</v>
       </c>
       <c r="F147" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B148" t="s">
         <v>256</v>
@@ -5277,12 +5278,12 @@
         <v>3</v>
       </c>
       <c r="F148" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B149" t="s">
         <v>256</v>
@@ -5297,12 +5298,12 @@
         <v>3</v>
       </c>
       <c r="F149" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B150" t="s">
         <v>256</v>
@@ -5317,12 +5318,12 @@
         <v>4</v>
       </c>
       <c r="F150" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B151" t="s">
         <v>256</v>
@@ -5337,12 +5338,12 @@
         <v>4</v>
       </c>
       <c r="F151" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B152" t="s">
         <v>256</v>
@@ -5357,12 +5358,12 @@
         <v>4</v>
       </c>
       <c r="F152" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B153" t="s">
         <v>256</v>
@@ -5377,12 +5378,12 @@
         <v>1</v>
       </c>
       <c r="F153" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B154" t="s">
         <v>256</v>
@@ -5397,12 +5398,12 @@
         <v>2</v>
       </c>
       <c r="F154" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B155" t="s">
         <v>256</v>
@@ -5417,12 +5418,12 @@
         <v>2</v>
       </c>
       <c r="F155" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B156" t="s">
         <v>256</v>
@@ -5437,12 +5438,12 @@
         <v>2</v>
       </c>
       <c r="F156" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B157" t="s">
         <v>256</v>
@@ -5457,12 +5458,12 @@
         <v>3</v>
       </c>
       <c r="F157" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B158" t="s">
         <v>256</v>
@@ -5477,12 +5478,12 @@
         <v>3</v>
       </c>
       <c r="F158" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B159" t="s">
         <v>256</v>
@@ -5497,12 +5498,12 @@
         <v>3</v>
       </c>
       <c r="F159" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B160" t="s">
         <v>256</v>
@@ -5517,12 +5518,12 @@
         <v>4</v>
       </c>
       <c r="F160" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B161" t="s">
         <v>256</v>
@@ -5537,12 +5538,12 @@
         <v>4</v>
       </c>
       <c r="F161" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B162" t="s">
         <v>256</v>
@@ -5557,12 +5558,12 @@
         <v>4</v>
       </c>
       <c r="F162" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B163" t="s">
         <v>256</v>
@@ -5577,12 +5578,12 @@
         <v>4</v>
       </c>
       <c r="F163" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B164" t="s">
         <v>256</v>
@@ -5597,12 +5598,12 @@
         <v>1</v>
       </c>
       <c r="F164" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B165" t="s">
         <v>256</v>
@@ -5617,12 +5618,12 @@
         <v>1</v>
       </c>
       <c r="F165" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B166" t="s">
         <v>256</v>
@@ -5637,12 +5638,12 @@
         <v>1</v>
       </c>
       <c r="F166" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B167" t="s">
         <v>256</v>
@@ -5657,12 +5658,12 @@
         <v>1</v>
       </c>
       <c r="F167" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B168" t="s">
         <v>256</v>
@@ -5677,12 +5678,12 @@
         <v>2</v>
       </c>
       <c r="F168" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B169" t="s">
         <v>256</v>
@@ -5697,12 +5698,12 @@
         <v>2</v>
       </c>
       <c r="F169" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B170" t="s">
         <v>256</v>
@@ -5717,12 +5718,12 @@
         <v>3</v>
       </c>
       <c r="F170" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B171" t="s">
         <v>256</v>
@@ -5737,12 +5738,12 @@
         <v>3</v>
       </c>
       <c r="F171" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B172" t="s">
         <v>256</v>
@@ -5757,12 +5758,12 @@
         <v>3</v>
       </c>
       <c r="F172" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B173" t="s">
         <v>256</v>
@@ -5777,12 +5778,12 @@
         <v>4</v>
       </c>
       <c r="F173" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B174" t="s">
         <v>256</v>
@@ -5797,12 +5798,12 @@
         <v>4</v>
       </c>
       <c r="F174" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B175" t="s">
         <v>256</v>
@@ -5817,12 +5818,12 @@
         <v>4</v>
       </c>
       <c r="F175" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B176" t="s">
         <v>256</v>
@@ -5837,12 +5838,12 @@
         <v>4</v>
       </c>
       <c r="F176" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B177" t="s">
         <v>256</v>
@@ -5857,12 +5858,12 @@
         <v>1</v>
       </c>
       <c r="F177" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B178" t="s">
         <v>256</v>
@@ -5877,12 +5878,12 @@
         <v>1</v>
       </c>
       <c r="F178" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B179" t="s">
         <v>256</v>
@@ -5897,12 +5898,12 @@
         <v>2</v>
       </c>
       <c r="F179" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B180" t="s">
         <v>256</v>
@@ -5917,12 +5918,12 @@
         <v>2</v>
       </c>
       <c r="F180" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B181" t="s">
         <v>256</v>
@@ -5937,12 +5938,12 @@
         <v>2</v>
       </c>
       <c r="F181" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B182" t="s">
         <v>256</v>
@@ -5957,12 +5958,12 @@
         <v>3</v>
       </c>
       <c r="F182" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B183" t="s">
         <v>256</v>
@@ -5977,12 +5978,12 @@
         <v>3</v>
       </c>
       <c r="F183" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B184" t="s">
         <v>256</v>
@@ -5997,12 +5998,12 @@
         <v>3</v>
       </c>
       <c r="F184" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B185" t="s">
         <v>256</v>
@@ -6017,12 +6018,12 @@
         <v>3</v>
       </c>
       <c r="F185" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B186" t="s">
         <v>256</v>
@@ -6037,12 +6038,12 @@
         <v>4</v>
       </c>
       <c r="F186" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B187" t="s">
         <v>256</v>
@@ -6057,12 +6058,12 @@
         <v>4</v>
       </c>
       <c r="F187" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B188" t="s">
         <v>256</v>
@@ -6077,12 +6078,12 @@
         <v>4</v>
       </c>
       <c r="F188" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B189" t="s">
         <v>256</v>
@@ -6097,12 +6098,12 @@
         <v>1</v>
       </c>
       <c r="F189" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B190" t="s">
         <v>256</v>
@@ -6117,12 +6118,12 @@
         <v>1</v>
       </c>
       <c r="F190" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B191" t="s">
         <v>256</v>
@@ -6137,12 +6138,12 @@
         <v>1</v>
       </c>
       <c r="F191" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B192" t="s">
         <v>256</v>
@@ -6157,12 +6158,12 @@
         <v>2</v>
       </c>
       <c r="F192" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B193" t="s">
         <v>256</v>
@@ -6177,12 +6178,12 @@
         <v>2</v>
       </c>
       <c r="F193" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B194" t="s">
         <v>256</v>
@@ -6197,12 +6198,12 @@
         <v>2</v>
       </c>
       <c r="F194" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B195" t="s">
         <v>256</v>
@@ -6217,12 +6218,12 @@
         <v>3</v>
       </c>
       <c r="F195" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B196" t="s">
         <v>256</v>
@@ -6237,12 +6238,12 @@
         <v>3</v>
       </c>
       <c r="F196" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B197" t="s">
         <v>256</v>
@@ -6257,12 +6258,12 @@
         <v>3</v>
       </c>
       <c r="F197" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B198" t="s">
         <v>256</v>
@@ -6277,12 +6278,12 @@
         <v>4</v>
       </c>
       <c r="F198" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B199" t="s">
         <v>256</v>
@@ -6297,12 +6298,12 @@
         <v>4</v>
       </c>
       <c r="F199" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B200" t="s">
         <v>256</v>
@@ -6317,12 +6318,12 @@
         <v>1</v>
       </c>
       <c r="F200" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B201" t="s">
         <v>256</v>
@@ -6337,12 +6338,12 @@
         <v>1</v>
       </c>
       <c r="F201" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B202" t="s">
         <v>256</v>
@@ -6357,12 +6358,12 @@
         <v>1</v>
       </c>
       <c r="F202" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B203" t="s">
         <v>256</v>
@@ -6377,12 +6378,12 @@
         <v>2</v>
       </c>
       <c r="F203" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B204" t="s">
         <v>256</v>
@@ -6397,12 +6398,12 @@
         <v>2</v>
       </c>
       <c r="F204" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B205" t="s">
         <v>256</v>
@@ -6417,12 +6418,12 @@
         <v>2</v>
       </c>
       <c r="F205" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B206" t="s">
         <v>256</v>
@@ -6434,15 +6435,15 @@
         <v>40</v>
       </c>
       <c r="E206" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="F206" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B207" t="s">
         <v>256</v>
@@ -6454,15 +6455,15 @@
         <v>40</v>
       </c>
       <c r="E207" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="F207" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B208" t="s">
         <v>256</v>
@@ -6474,15 +6475,15 @@
         <v>40</v>
       </c>
       <c r="E208" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="F208" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B209" t="s">
         <v>256</v>
@@ -6497,12 +6498,12 @@
         <v>1</v>
       </c>
       <c r="F209" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B210" t="s">
         <v>256</v>
@@ -6517,12 +6518,12 @@
         <v>1</v>
       </c>
       <c r="F210" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B211" t="s">
         <v>256</v>
@@ -6537,12 +6538,12 @@
         <v>1</v>
       </c>
       <c r="F211" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B212" t="s">
         <v>256</v>
@@ -6557,12 +6558,12 @@
         <v>2</v>
       </c>
       <c r="F212" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B213" t="s">
         <v>256</v>
@@ -6577,12 +6578,12 @@
         <v>2</v>
       </c>
       <c r="F213" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B214" t="s">
         <v>256</v>
@@ -6597,12 +6598,12 @@
         <v>2</v>
       </c>
       <c r="F214" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B215" t="s">
         <v>256</v>
@@ -6617,12 +6618,12 @@
         <v>3</v>
       </c>
       <c r="F215" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B216" t="s">
         <v>256</v>
@@ -6637,12 +6638,12 @@
         <v>3</v>
       </c>
       <c r="F216" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B217" t="s">
         <v>256</v>
@@ -6657,12 +6658,12 @@
         <v>3</v>
       </c>
       <c r="F217" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B218" t="s">
         <v>256</v>
@@ -6677,12 +6678,12 @@
         <v>4</v>
       </c>
       <c r="F218" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B219" t="s">
         <v>256</v>
@@ -6697,12 +6698,12 @@
         <v>4</v>
       </c>
       <c r="F219" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B220" t="s">
         <v>256</v>
@@ -6717,12 +6718,12 @@
         <v>4</v>
       </c>
       <c r="F220" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B221" t="s">
         <v>256</v>
@@ -6737,12 +6738,12 @@
         <v>1</v>
       </c>
       <c r="F221" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B222" t="s">
         <v>256</v>
@@ -6757,12 +6758,12 @@
         <v>1</v>
       </c>
       <c r="F222" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B223" t="s">
         <v>256</v>
@@ -6777,12 +6778,12 @@
         <v>1</v>
       </c>
       <c r="F223" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B224" t="s">
         <v>256</v>
@@ -6797,12 +6798,12 @@
         <v>1</v>
       </c>
       <c r="F224" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B225" t="s">
         <v>256</v>
@@ -6817,12 +6818,12 @@
         <v>2</v>
       </c>
       <c r="F225" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B226" t="s">
         <v>256</v>
@@ -6837,12 +6838,12 @@
         <v>2</v>
       </c>
       <c r="F226" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B227" t="s">
         <v>256</v>
@@ -6857,12 +6858,12 @@
         <v>2</v>
       </c>
       <c r="F227" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B228" t="s">
         <v>256</v>
@@ -6877,12 +6878,12 @@
         <v>3</v>
       </c>
       <c r="F228" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B229" t="s">
         <v>256</v>
@@ -6897,12 +6898,12 @@
         <v>3</v>
       </c>
       <c r="F229" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B230" t="s">
         <v>256</v>
@@ -6917,12 +6918,12 @@
         <v>4</v>
       </c>
       <c r="F230" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B231" t="s">
         <v>256</v>
@@ -6937,12 +6938,12 @@
         <v>4</v>
       </c>
       <c r="F231" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B232" t="s">
         <v>256</v>
@@ -6957,12 +6958,12 @@
         <v>4</v>
       </c>
       <c r="F232" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B233" t="s">
         <v>256</v>
@@ -6977,12 +6978,12 @@
         <v>1</v>
       </c>
       <c r="F233" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B234" t="s">
         <v>256</v>
@@ -6997,12 +6998,12 @@
         <v>1</v>
       </c>
       <c r="F234" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B235" t="s">
         <v>256</v>
@@ -7017,12 +7018,12 @@
         <v>1</v>
       </c>
       <c r="F235" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B236" t="s">
         <v>256</v>
@@ -7037,12 +7038,12 @@
         <v>1</v>
       </c>
       <c r="F236" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B237" t="s">
         <v>256</v>
@@ -7057,12 +7058,12 @@
         <v>2</v>
       </c>
       <c r="F237" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B238" t="s">
         <v>256</v>
@@ -7077,12 +7078,12 @@
         <v>2</v>
       </c>
       <c r="F238" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B239" t="s">
         <v>256</v>
@@ -7097,12 +7098,12 @@
         <v>2</v>
       </c>
       <c r="F239" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B240" t="s">
         <v>256</v>
@@ -7117,12 +7118,12 @@
         <v>2</v>
       </c>
       <c r="F240" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B241" t="s">
         <v>256</v>
@@ -7137,12 +7138,12 @@
         <v>3</v>
       </c>
       <c r="F241" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B242" t="s">
         <v>256</v>
@@ -7157,12 +7158,12 @@
         <v>3</v>
       </c>
       <c r="F242" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B243" t="s">
         <v>256</v>
@@ -7177,12 +7178,12 @@
         <v>3</v>
       </c>
       <c r="F243" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B244" t="s">
         <v>256</v>
@@ -7197,12 +7198,12 @@
         <v>3</v>
       </c>
       <c r="F244" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B245" t="s">
         <v>256</v>
@@ -7217,12 +7218,12 @@
         <v>3</v>
       </c>
       <c r="F245" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B246" t="s">
         <v>256</v>
@@ -7237,12 +7238,12 @@
         <v>3</v>
       </c>
       <c r="F246" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B247" t="s">
         <v>256</v>
@@ -7257,12 +7258,12 @@
         <v>4</v>
       </c>
       <c r="F247" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B248" t="s">
         <v>256</v>
@@ -7277,12 +7278,12 @@
         <v>4</v>
       </c>
       <c r="F248" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B249" t="s">
         <v>256</v>
@@ -7297,12 +7298,12 @@
         <v>1</v>
       </c>
       <c r="F249" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B250" t="s">
         <v>256</v>
@@ -7317,12 +7318,12 @@
         <v>1</v>
       </c>
       <c r="F250" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B251" t="s">
         <v>256</v>
@@ -7337,12 +7338,12 @@
         <v>1</v>
       </c>
       <c r="F251" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B252" t="s">
         <v>256</v>
@@ -7357,12 +7358,12 @@
         <v>2</v>
       </c>
       <c r="F252" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B253" t="s">
         <v>256</v>
@@ -7377,12 +7378,12 @@
         <v>2</v>
       </c>
       <c r="F253" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B254" t="s">
         <v>256</v>
@@ -7397,12 +7398,12 @@
         <v>2</v>
       </c>
       <c r="F254" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B255" t="s">
         <v>256</v>
@@ -7417,12 +7418,12 @@
         <v>2</v>
       </c>
       <c r="F255" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B256" t="s">
         <v>256</v>
@@ -7437,12 +7438,12 @@
         <v>3</v>
       </c>
       <c r="F256" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B257" t="s">
         <v>256</v>
@@ -7457,12 +7458,12 @@
         <v>3</v>
       </c>
       <c r="F257" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B258" t="s">
         <v>256</v>
@@ -7477,12 +7478,12 @@
         <v>3</v>
       </c>
       <c r="F258" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B259" t="s">
         <v>256</v>
@@ -7497,12 +7498,12 @@
         <v>3</v>
       </c>
       <c r="F259" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B260" t="s">
         <v>256</v>
@@ -7517,12 +7518,12 @@
         <v>4</v>
       </c>
       <c r="F260" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B261" t="s">
         <v>256</v>
@@ -7537,12 +7538,12 @@
         <v>4</v>
       </c>
       <c r="F261" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B262" t="s">
         <v>256</v>
@@ -7557,12 +7558,12 @@
         <v>4</v>
       </c>
       <c r="F262" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B263" t="s">
         <v>256</v>
@@ -7577,12 +7578,12 @@
         <v>4</v>
       </c>
       <c r="F263" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B264" t="s">
         <v>256</v>
@@ -7597,12 +7598,12 @@
         <v>1</v>
       </c>
       <c r="F264" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B265" t="s">
         <v>256</v>
@@ -7617,12 +7618,12 @@
         <v>1</v>
       </c>
       <c r="F265" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B266" t="s">
         <v>256</v>
@@ -7637,12 +7638,12 @@
         <v>1</v>
       </c>
       <c r="F266" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B267" t="s">
         <v>256</v>
@@ -7657,12 +7658,12 @@
         <v>2</v>
       </c>
       <c r="F267" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B268" t="s">
         <v>256</v>
@@ -7677,12 +7678,12 @@
         <v>2</v>
       </c>
       <c r="F268" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B269" t="s">
         <v>256</v>
@@ -7697,12 +7698,12 @@
         <v>2</v>
       </c>
       <c r="F269" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B270" t="s">
         <v>256</v>
@@ -7717,12 +7718,12 @@
         <v>3</v>
       </c>
       <c r="F270" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B271" t="s">
         <v>256</v>
@@ -7737,12 +7738,12 @@
         <v>3</v>
       </c>
       <c r="F271" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B272" t="s">
         <v>256</v>
@@ -7757,12 +7758,12 @@
         <v>3</v>
       </c>
       <c r="F272" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B273" t="s">
         <v>256</v>
@@ -7777,12 +7778,12 @@
         <v>4</v>
       </c>
       <c r="F273" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B274" t="s">
         <v>256</v>
@@ -7797,12 +7798,12 @@
         <v>4</v>
       </c>
       <c r="F274" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B275" t="s">
         <v>256</v>
@@ -7817,10 +7818,10 @@
         <v>1</v>
       </c>
       <c r="F275" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>89</v>
       </c>
@@ -7837,9 +7838,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B277" t="s">
         <v>256</v>
@@ -7854,12 +7855,12 @@
         <v>3</v>
       </c>
       <c r="F277" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B278" t="s">
         <v>256</v>
@@ -7874,12 +7875,12 @@
         <v>3</v>
       </c>
       <c r="F278" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B279" t="s">
         <v>256</v>
@@ -7894,12 +7895,12 @@
         <v>3</v>
       </c>
       <c r="F279" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B280" t="s">
         <v>256</v>
@@ -7914,12 +7915,12 @@
         <v>4</v>
       </c>
       <c r="F280" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B281" t="s">
         <v>256</v>
@@ -7934,12 +7935,12 @@
         <v>4</v>
       </c>
       <c r="F281" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B282" t="s">
         <v>256</v>
@@ -7954,12 +7955,12 @@
         <v>4</v>
       </c>
       <c r="F282" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B283" t="s">
         <v>256</v>
@@ -7974,12 +7975,12 @@
         <v>4</v>
       </c>
       <c r="F283" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B284" t="s">
         <v>256</v>
@@ -7994,12 +7995,12 @@
         <v>1</v>
       </c>
       <c r="F284" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B285" t="s">
         <v>256</v>
@@ -8014,12 +8015,12 @@
         <v>1</v>
       </c>
       <c r="F285" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B286" t="s">
         <v>256</v>
@@ -8034,12 +8035,12 @@
         <v>1</v>
       </c>
       <c r="F286" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B287" t="s">
         <v>256</v>
@@ -8054,12 +8055,12 @@
         <v>2</v>
       </c>
       <c r="F287" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B288" t="s">
         <v>256</v>
@@ -8074,12 +8075,12 @@
         <v>2</v>
       </c>
       <c r="F288" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B289" t="s">
         <v>256</v>
@@ -8094,12 +8095,12 @@
         <v>2</v>
       </c>
       <c r="F289" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B290" t="s">
         <v>256</v>
@@ -8114,12 +8115,12 @@
         <v>2</v>
       </c>
       <c r="F290" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B291" t="s">
         <v>256</v>
@@ -8134,12 +8135,12 @@
         <v>3</v>
       </c>
       <c r="F291" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B292" t="s">
         <v>256</v>
@@ -8154,12 +8155,12 @@
         <v>3</v>
       </c>
       <c r="F292" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="B293" t="s">
         <v>256</v>
@@ -8174,12 +8175,12 @@
         <v>3</v>
       </c>
       <c r="F293" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B294" t="s">
         <v>256</v>
@@ -8194,12 +8195,12 @@
         <v>4</v>
       </c>
       <c r="F294" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>285</v>
+        <v>637</v>
       </c>
       <c r="B295" t="s">
         <v>256</v>
@@ -8214,12 +8215,12 @@
         <v>4</v>
       </c>
       <c r="F295" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>639</v>
+        <v>284</v>
       </c>
       <c r="B296" t="s">
         <v>256</v>
@@ -8234,12 +8235,12 @@
         <v>4</v>
       </c>
       <c r="F296" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B297" t="s">
         <v>256</v>
@@ -8254,12 +8255,12 @@
         <v>1</v>
       </c>
       <c r="F297" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B298" t="s">
         <v>256</v>
@@ -8274,12 +8275,12 @@
         <v>1</v>
       </c>
       <c r="F298" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B299" t="s">
         <v>256</v>
@@ -8294,12 +8295,12 @@
         <v>1</v>
       </c>
       <c r="F299" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>281</v>
+        <v>634</v>
       </c>
       <c r="B300" t="s">
         <v>256</v>
@@ -8314,10 +8315,10 @@
         <v>2</v>
       </c>
       <c r="F300" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>280</v>
       </c>
@@ -8334,10 +8335,10 @@
         <v>2</v>
       </c>
       <c r="F301" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>279</v>
       </c>
@@ -8354,12 +8355,12 @@
         <v>2</v>
       </c>
       <c r="F302" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>636</v>
+        <v>278</v>
       </c>
       <c r="B303" t="s">
         <v>256</v>
@@ -8374,12 +8375,12 @@
         <v>2</v>
       </c>
       <c r="F303" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B304" t="s">
         <v>256</v>
@@ -8394,12 +8395,12 @@
         <v>3</v>
       </c>
       <c r="F304" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B305" t="s">
         <v>256</v>
@@ -8414,12 +8415,12 @@
         <v>3</v>
       </c>
       <c r="F305" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B306" t="s">
         <v>256</v>
@@ -8434,10 +8435,10 @@
         <v>3</v>
       </c>
       <c r="F306" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>129</v>
       </c>
@@ -8457,7 +8458,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>260</v>
       </c>
@@ -8477,7 +8478,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>259</v>
       </c>
@@ -8497,7 +8498,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>257</v>
       </c>
@@ -8517,7 +8518,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>263</v>
       </c>
@@ -8537,7 +8538,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>262</v>
       </c>
@@ -8557,7 +8558,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>261</v>
       </c>
@@ -8577,7 +8578,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>273</v>
       </c>
@@ -8594,12 +8595,12 @@
         <v>3</v>
       </c>
       <c r="F314" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B315" t="s">
         <v>256</v>
@@ -8614,10 +8615,10 @@
         <v>3</v>
       </c>
       <c r="F315" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>265</v>
       </c>
@@ -8637,7 +8638,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>264</v>
       </c>
@@ -8657,9 +8658,9 @@
         <v>271</v>
       </c>
     </row>
-    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B318" t="s">
         <v>256</v>
@@ -8674,12 +8675,12 @@
         <v>4</v>
       </c>
       <c r="F318" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B319" t="s">
         <v>256</v>
@@ -8694,15 +8695,12 @@
         <v>4</v>
       </c>
       <c r="F319" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>274</v>
-      </c>
-      <c r="B320" t="s">
-        <v>256</v>
+        <v>644</v>
       </c>
       <c r="C320">
         <v>1</v>
@@ -8714,22 +8712,28 @@
         <v>4</v>
       </c>
       <c r="F320" t="s">
-        <v>441</v>
-      </c>
-    </row>
+        <v>645</v>
+      </c>
+    </row>
+    <row r="321" hidden="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:F320" xr:uid="{E6B6791C-A8A7-4753-A504-FAA9E3EE8745}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F320">
-      <sortCondition descending="1" ref="C2:C320"/>
-      <sortCondition ref="D2:D320"/>
-      <sortCondition ref="E2:E320"/>
+  <autoFilter ref="A1:F321" xr:uid="{E6B6791C-A8A7-4753-A504-FAA9E3EE8745}">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="I-1474.jpeg"/>
+      </filters>
+    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F321">
+      <sortCondition descending="1" ref="C2:C321"/>
+      <sortCondition ref="D2:D321"/>
+      <sortCondition ref="E2:E321"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F319">
-    <sortCondition descending="1" ref="C2:C319"/>
-    <sortCondition ref="D2:D319"/>
-    <sortCondition ref="E2:E319"/>
-    <sortCondition descending="1" ref="A2:A319"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F320">
+    <sortCondition descending="1" ref="C2:C320"/>
+    <sortCondition ref="D2:D320"/>
+    <sortCondition ref="E2:E320"/>
+    <sortCondition descending="1" ref="A2:A320"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/EOAT_data.xlsx
+++ b/data/EOAT_data.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://industriascazelmx-my.sharepoint.com/personal/agaytan_cazel_mx/Documents/Imágenes/MOLIDO PELETIZADO/EOAT Project/EOAT Project/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\procesos.CAZEL\Desktop\Becario Procesos\EOAT Project\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1D609F45-9D1A-4AA8-BF9F-42F184022876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C67F98C-612F-4E93-AAB4-A4E5E423296B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{440E3869-3C3F-4E8C-A8BD-ADEB8E2EA552}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{440E3869-3C3F-4E8C-A8BD-ADEB8E2EA552}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$F$321</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">data!$A$1:$F$320</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1270" uniqueCount="646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1271" uniqueCount="662">
   <si>
     <t>I-1937</t>
   </si>
@@ -863,6 +863,9 @@
     <t>I-1468</t>
   </si>
   <si>
+    <t>I-1474</t>
+  </si>
+  <si>
     <t>I-1493</t>
   </si>
   <si>
@@ -1361,6 +1364,9 @@
     <t>I-1468.jpeg</t>
   </si>
   <si>
+    <t>I-1474.jpeg</t>
+  </si>
+  <si>
     <t>I-1493.jpeg</t>
   </si>
   <si>
@@ -1973,10 +1979,52 @@
     <t>I-1931.jpeg</t>
   </si>
   <si>
-    <t>I-1474</t>
-  </si>
-  <si>
-    <t>I-1474.jpeg</t>
+    <t>4 ventosas, 2 dedos, 3 pinzas</t>
+  </si>
+  <si>
+    <t>4 ventosas, 6 pinzas</t>
+  </si>
+  <si>
+    <t>4 ventosas, 2 pinzas</t>
+  </si>
+  <si>
+    <t>4 pinzas</t>
+  </si>
+  <si>
+    <t>4 ventosas, 1 pinza</t>
+  </si>
+  <si>
+    <t>2 ventosas, 2 pinzas</t>
+  </si>
+  <si>
+    <t>2 ventosas, 3 pinzas</t>
+  </si>
+  <si>
+    <t>4 ventosas, 4 pinzas</t>
+  </si>
+  <si>
+    <t>4 ventosas</t>
+  </si>
+  <si>
+    <t>4 ventosas, 2 pinzas, 4 dedos</t>
+  </si>
+  <si>
+    <t>2 pinzas</t>
+  </si>
+  <si>
+    <t>2 ventosas, 1 pinza</t>
+  </si>
+  <si>
+    <t>12 ventosas</t>
+  </si>
+  <si>
+    <t>8 ventosas, 1 pinza</t>
+  </si>
+  <si>
+    <t>2 ventosas</t>
+  </si>
+  <si>
+    <t>4 ventosas, se agregaron pinzas de corte</t>
   </si>
 </sst>
 </file>
@@ -2354,12 +2402,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6B6791C-A8A7-4753-A504-FAA9E3EE8745}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:F321"/>
+  <dimension ref="A1:F320"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.140625" bestFit="1" customWidth="1"/>
@@ -2386,7 +2433,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -2406,7 +2453,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -2426,7 +2473,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -2446,7 +2493,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -2466,7 +2513,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -2486,7 +2533,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -2506,7 +2553,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -2526,7 +2573,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -2546,7 +2593,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -2566,7 +2613,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
@@ -2586,7 +2633,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="12" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -2606,7 +2653,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
@@ -2626,7 +2673,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="14" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>14</v>
       </c>
@@ -2646,7 +2693,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -2666,12 +2713,12 @@
         <v>153</v>
       </c>
     </row>
-    <row r="16" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>256</v>
+        <v>647</v>
       </c>
       <c r="C16">
         <v>3</v>
@@ -2686,7 +2733,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -2706,7 +2753,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="18" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -2726,7 +2773,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -2746,7 +2793,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="20" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -2766,7 +2813,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -2786,7 +2833,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="22" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -2806,7 +2853,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -2826,12 +2873,12 @@
         <v>161</v>
       </c>
     </row>
-    <row r="24" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>26</v>
       </c>
       <c r="B24" t="s">
-        <v>256</v>
+        <v>646</v>
       </c>
       <c r="C24">
         <v>3</v>
@@ -2846,7 +2893,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -2866,7 +2913,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="26" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -2886,9 +2933,9 @@
         <v>164</v>
       </c>
     </row>
-    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B27" t="s">
         <v>256</v>
@@ -2903,12 +2950,12 @@
         <v>1</v>
       </c>
       <c r="F27" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B28" t="s">
         <v>256</v>
@@ -2923,10 +2970,10 @@
         <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>30</v>
       </c>
@@ -2946,7 +2993,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="30" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>31</v>
       </c>
@@ -2966,7 +3013,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>32</v>
       </c>
@@ -2986,7 +3033,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="32" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>34</v>
       </c>
@@ -3006,7 +3053,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>35</v>
       </c>
@@ -3026,7 +3073,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>36</v>
       </c>
@@ -3046,7 +3093,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>37</v>
       </c>
@@ -3066,7 +3113,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>38</v>
       </c>
@@ -3086,7 +3133,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>39</v>
       </c>
@@ -3106,7 +3153,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>41</v>
       </c>
@@ -3126,7 +3173,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>42</v>
       </c>
@@ -3146,7 +3193,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>43</v>
       </c>
@@ -3166,7 +3213,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>44</v>
       </c>
@@ -3186,12 +3233,12 @@
         <v>177</v>
       </c>
     </row>
-    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>45</v>
       </c>
       <c r="B42" t="s">
-        <v>256</v>
+        <v>652</v>
       </c>
       <c r="C42">
         <v>3</v>
@@ -3206,7 +3253,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>47</v>
       </c>
@@ -3226,7 +3273,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>48</v>
       </c>
@@ -3246,7 +3293,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>49</v>
       </c>
@@ -3266,7 +3313,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>50</v>
       </c>
@@ -3286,7 +3333,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>51</v>
       </c>
@@ -3306,7 +3353,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>53</v>
       </c>
@@ -3326,7 +3373,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>54</v>
       </c>
@@ -3346,7 +3393,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>55</v>
       </c>
@@ -3366,7 +3413,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>57</v>
       </c>
@@ -3380,18 +3427,18 @@
         <v>56</v>
       </c>
       <c r="E51" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="F51" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>59</v>
       </c>
       <c r="B52" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C52">
         <v>3</v>
@@ -3400,13 +3447,13 @@
         <v>56</v>
       </c>
       <c r="E52" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="F52" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>60</v>
       </c>
@@ -3426,7 +3473,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>62</v>
       </c>
@@ -3446,7 +3493,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>63</v>
       </c>
@@ -3466,7 +3513,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>64</v>
       </c>
@@ -3483,7 +3530,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>64</v>
       </c>
@@ -3500,7 +3547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>64</v>
       </c>
@@ -3517,7 +3564,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>64</v>
       </c>
@@ -3534,7 +3581,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>89</v>
       </c>
@@ -3551,7 +3598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>89</v>
       </c>
@@ -3568,7 +3615,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>58</v>
       </c>
@@ -3588,7 +3635,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>91</v>
       </c>
@@ -3608,7 +3655,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>93</v>
       </c>
@@ -3628,7 +3675,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="65" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>94</v>
       </c>
@@ -3648,7 +3695,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="66" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>95</v>
       </c>
@@ -3668,7 +3715,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="67" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>96</v>
       </c>
@@ -3688,7 +3735,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="68" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>98</v>
       </c>
@@ -3708,12 +3755,12 @@
         <v>217</v>
       </c>
     </row>
-    <row r="69" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>99</v>
       </c>
       <c r="B69" t="s">
-        <v>256</v>
+        <v>653</v>
       </c>
       <c r="C69">
         <v>3</v>
@@ -3728,7 +3775,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="70" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>100</v>
       </c>
@@ -3748,7 +3795,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="71" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>101</v>
       </c>
@@ -3768,7 +3815,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="72" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>102</v>
       </c>
@@ -3788,7 +3835,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="73" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>104</v>
       </c>
@@ -3808,7 +3855,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="74" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>105</v>
       </c>
@@ -3828,7 +3875,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="75" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>106</v>
       </c>
@@ -3848,7 +3895,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="76" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>107</v>
       </c>
@@ -3868,7 +3915,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="77" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>108</v>
       </c>
@@ -3888,7 +3935,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="78" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>66</v>
       </c>
@@ -3908,7 +3955,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="79" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>68</v>
       </c>
@@ -3928,7 +3975,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="80" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>89</v>
       </c>
@@ -3945,7 +3992,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>69</v>
       </c>
@@ -3965,7 +4012,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="82" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>70</v>
       </c>
@@ -3985,9 +4032,9 @@
         <v>196</v>
       </c>
     </row>
-    <row r="83" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="B83" t="s">
         <v>256</v>
@@ -4002,10 +4049,10 @@
         <v>1</v>
       </c>
       <c r="F83" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>71</v>
       </c>
@@ -4025,7 +4072,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="85" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>73</v>
       </c>
@@ -4045,7 +4092,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="86" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>74</v>
       </c>
@@ -4065,7 +4112,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="87" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>75</v>
       </c>
@@ -4085,7 +4132,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="88" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>77</v>
       </c>
@@ -4105,7 +4152,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="89" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>78</v>
       </c>
@@ -4125,7 +4172,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="90" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>79</v>
       </c>
@@ -4145,7 +4192,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="91" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>80</v>
       </c>
@@ -4165,7 +4212,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="92" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>81</v>
       </c>
@@ -4185,7 +4232,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="93" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>82</v>
       </c>
@@ -4205,7 +4252,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="94" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>84</v>
       </c>
@@ -4225,7 +4272,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="95" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>85</v>
       </c>
@@ -4245,12 +4292,12 @@
         <v>208</v>
       </c>
     </row>
-    <row r="96" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>86</v>
       </c>
       <c r="B96" t="s">
-        <v>256</v>
+        <v>648</v>
       </c>
       <c r="C96">
         <v>2</v>
@@ -4265,7 +4312,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>87</v>
       </c>
@@ -4285,7 +4332,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>88</v>
       </c>
@@ -4305,7 +4352,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>109</v>
       </c>
@@ -4325,7 +4372,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>111</v>
       </c>
@@ -4345,7 +4392,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>112</v>
       </c>
@@ -4365,7 +4412,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>113</v>
       </c>
@@ -4385,7 +4432,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>114</v>
       </c>
@@ -4405,7 +4452,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>116</v>
       </c>
@@ -4425,7 +4472,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>117</v>
       </c>
@@ -4445,7 +4492,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="106" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>118</v>
       </c>
@@ -4465,7 +4512,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="107" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>119</v>
       </c>
@@ -4485,7 +4532,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="108" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>120</v>
       </c>
@@ -4505,7 +4552,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="109" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>123</v>
       </c>
@@ -4525,7 +4572,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="110" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>122</v>
       </c>
@@ -4545,7 +4592,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="111" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>124</v>
       </c>
@@ -4565,7 +4612,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="112" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>125</v>
       </c>
@@ -4585,7 +4632,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="113" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>127</v>
       </c>
@@ -4605,7 +4652,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="114" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>128</v>
       </c>
@@ -4625,7 +4672,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="115" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>130</v>
       </c>
@@ -4645,7 +4692,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="116" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>132</v>
       </c>
@@ -4665,7 +4712,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="117" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>133</v>
       </c>
@@ -4685,7 +4732,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="118" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>134</v>
       </c>
@@ -4705,7 +4752,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="119" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>135</v>
       </c>
@@ -4725,7 +4772,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="120" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>136</v>
       </c>
@@ -4745,7 +4792,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="121" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>89</v>
       </c>
@@ -4762,7 +4809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>89</v>
       </c>
@@ -4779,7 +4826,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="123" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>89</v>
       </c>
@@ -4796,7 +4843,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="124" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>89</v>
       </c>
@@ -4813,7 +4860,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>89</v>
       </c>
@@ -4830,9 +4877,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="126" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B126" t="s">
         <v>256</v>
@@ -4847,10 +4894,10 @@
         <v>3</v>
       </c>
       <c r="F126" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>89</v>
       </c>
@@ -4867,7 +4914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>89</v>
       </c>
@@ -4884,7 +4931,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>89</v>
       </c>
@@ -4901,9 +4948,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="130" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B130" t="s">
         <v>256</v>
@@ -4918,12 +4965,12 @@
         <v>1</v>
       </c>
       <c r="F130" t="s">
-        <v>641</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B131" t="s">
         <v>256</v>
@@ -4938,32 +4985,32 @@
         <v>1</v>
       </c>
       <c r="F131" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>428</v>
+      </c>
+      <c r="B132" t="s">
+        <v>256</v>
+      </c>
+      <c r="C132">
+        <v>1</v>
+      </c>
+      <c r="D132" t="s">
+        <v>1</v>
+      </c>
+      <c r="E132">
+        <v>1</v>
+      </c>
+      <c r="F132" t="s">
         <v>595</v>
       </c>
     </row>
-    <row r="132" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A132" t="s">
-        <v>427</v>
-      </c>
-      <c r="B132" t="s">
-        <v>256</v>
-      </c>
-      <c r="C132">
-        <v>1</v>
-      </c>
-      <c r="D132" t="s">
-        <v>1</v>
-      </c>
-      <c r="E132">
-        <v>1</v>
-      </c>
-      <c r="F132" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B133" t="s">
         <v>256</v>
@@ -4978,92 +5025,92 @@
         <v>2</v>
       </c>
       <c r="F133" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
+        <v>435</v>
+      </c>
+      <c r="B134" t="s">
+        <v>256</v>
+      </c>
+      <c r="C134">
+        <v>1</v>
+      </c>
+      <c r="D134" t="s">
+        <v>1</v>
+      </c>
+      <c r="E134">
+        <v>2</v>
+      </c>
+      <c r="F134" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>438</v>
+      </c>
+      <c r="B135" t="s">
+        <v>256</v>
+      </c>
+      <c r="C135">
+        <v>1</v>
+      </c>
+      <c r="D135" t="s">
+        <v>1</v>
+      </c>
+      <c r="E135">
+        <v>2</v>
+      </c>
+      <c r="F135" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>437</v>
+      </c>
+      <c r="B136" t="s">
+        <v>256</v>
+      </c>
+      <c r="C136">
+        <v>1</v>
+      </c>
+      <c r="D136" t="s">
+        <v>1</v>
+      </c>
+      <c r="E136">
+        <v>3</v>
+      </c>
+      <c r="F136" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>432</v>
+      </c>
+      <c r="B137" t="s">
+        <v>256</v>
+      </c>
+      <c r="C137">
+        <v>1</v>
+      </c>
+      <c r="D137" t="s">
+        <v>1</v>
+      </c>
+      <c r="E137">
+        <v>3</v>
+      </c>
+      <c r="F137" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
         <v>434</v>
-      </c>
-      <c r="B134" t="s">
-        <v>256</v>
-      </c>
-      <c r="C134">
-        <v>1</v>
-      </c>
-      <c r="D134" t="s">
-        <v>1</v>
-      </c>
-      <c r="E134">
-        <v>2</v>
-      </c>
-      <c r="F134" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
-        <v>437</v>
-      </c>
-      <c r="B135" t="s">
-        <v>256</v>
-      </c>
-      <c r="C135">
-        <v>1</v>
-      </c>
-      <c r="D135" t="s">
-        <v>1</v>
-      </c>
-      <c r="E135">
-        <v>2</v>
-      </c>
-      <c r="F135" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A136" t="s">
-        <v>436</v>
-      </c>
-      <c r="B136" t="s">
-        <v>256</v>
-      </c>
-      <c r="C136">
-        <v>1</v>
-      </c>
-      <c r="D136" t="s">
-        <v>1</v>
-      </c>
-      <c r="E136">
-        <v>3</v>
-      </c>
-      <c r="F136" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A137" t="s">
-        <v>431</v>
-      </c>
-      <c r="B137" t="s">
-        <v>256</v>
-      </c>
-      <c r="C137">
-        <v>1</v>
-      </c>
-      <c r="D137" t="s">
-        <v>1</v>
-      </c>
-      <c r="E137">
-        <v>3</v>
-      </c>
-      <c r="F137" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="138" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A138" t="s">
-        <v>433</v>
       </c>
       <c r="B138" t="s">
         <v>256</v>
@@ -5078,15 +5125,15 @@
         <v>4</v>
       </c>
       <c r="F138" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B139" t="s">
-        <v>256</v>
+        <v>649</v>
       </c>
       <c r="C139">
         <v>1</v>
@@ -5098,12 +5145,12 @@
         <v>4</v>
       </c>
       <c r="F139" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B140" t="s">
         <v>256</v>
@@ -5118,12 +5165,12 @@
         <v>4</v>
       </c>
       <c r="F140" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B141" t="s">
         <v>256</v>
@@ -5138,12 +5185,12 @@
         <v>4</v>
       </c>
       <c r="F141" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="142" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B142" t="s">
         <v>256</v>
@@ -5158,12 +5205,12 @@
         <v>1</v>
       </c>
       <c r="F142" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B143" t="s">
         <v>256</v>
@@ -5178,12 +5225,12 @@
         <v>1</v>
       </c>
       <c r="F143" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="144" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B144" t="s">
         <v>256</v>
@@ -5198,12 +5245,12 @@
         <v>1</v>
       </c>
       <c r="F144" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B145" t="s">
         <v>256</v>
@@ -5218,12 +5265,12 @@
         <v>1</v>
       </c>
       <c r="F145" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B146" t="s">
         <v>256</v>
@@ -5238,12 +5285,12 @@
         <v>2</v>
       </c>
       <c r="F146" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="147" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B147" t="s">
         <v>256</v>
@@ -5258,12 +5305,12 @@
         <v>2</v>
       </c>
       <c r="F147" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B148" t="s">
         <v>256</v>
@@ -5278,12 +5325,12 @@
         <v>3</v>
       </c>
       <c r="F148" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B149" t="s">
         <v>256</v>
@@ -5298,12 +5345,12 @@
         <v>3</v>
       </c>
       <c r="F149" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B150" t="s">
         <v>256</v>
@@ -5318,12 +5365,12 @@
         <v>4</v>
       </c>
       <c r="F150" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B151" t="s">
         <v>256</v>
@@ -5338,15 +5385,15 @@
         <v>4</v>
       </c>
       <c r="F151" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="152" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B152" t="s">
-        <v>256</v>
+        <v>648</v>
       </c>
       <c r="C152">
         <v>1</v>
@@ -5358,12 +5405,12 @@
         <v>4</v>
       </c>
       <c r="F152" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B153" t="s">
         <v>256</v>
@@ -5378,12 +5425,12 @@
         <v>1</v>
       </c>
       <c r="F153" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="154" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B154" t="s">
         <v>256</v>
@@ -5398,12 +5445,12 @@
         <v>2</v>
       </c>
       <c r="F154" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B155" t="s">
         <v>256</v>
@@ -5418,12 +5465,12 @@
         <v>2</v>
       </c>
       <c r="F155" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B156" t="s">
         <v>256</v>
@@ -5438,12 +5485,12 @@
         <v>2</v>
       </c>
       <c r="F156" t="s">
-        <v>620</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B157" t="s">
         <v>256</v>
@@ -5458,12 +5505,12 @@
         <v>3</v>
       </c>
       <c r="F157" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B158" t="s">
         <v>256</v>
@@ -5478,12 +5525,12 @@
         <v>3</v>
       </c>
       <c r="F158" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B159" t="s">
         <v>256</v>
@@ -5498,12 +5545,12 @@
         <v>3</v>
       </c>
       <c r="F159" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B160" t="s">
         <v>256</v>
@@ -5518,12 +5565,12 @@
         <v>4</v>
       </c>
       <c r="F160" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B161" t="s">
         <v>256</v>
@@ -5538,12 +5585,12 @@
         <v>4</v>
       </c>
       <c r="F161" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="162" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B162" t="s">
         <v>256</v>
@@ -5558,12 +5605,12 @@
         <v>4</v>
       </c>
       <c r="F162" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="163" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B163" t="s">
         <v>256</v>
@@ -5578,12 +5625,12 @@
         <v>4</v>
       </c>
       <c r="F163" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B164" t="s">
         <v>256</v>
@@ -5598,12 +5645,12 @@
         <v>1</v>
       </c>
       <c r="F164" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="165" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B165" t="s">
         <v>256</v>
@@ -5618,12 +5665,12 @@
         <v>1</v>
       </c>
       <c r="F165" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="166" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B166" t="s">
         <v>256</v>
@@ -5638,15 +5685,15 @@
         <v>1</v>
       </c>
       <c r="F166" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B167" t="s">
-        <v>256</v>
+        <v>651</v>
       </c>
       <c r="C167">
         <v>1</v>
@@ -5658,12 +5705,12 @@
         <v>1</v>
       </c>
       <c r="F167" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="168" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B168" t="s">
         <v>256</v>
@@ -5678,12 +5725,12 @@
         <v>2</v>
       </c>
       <c r="F168" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="169" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B169" t="s">
         <v>256</v>
@@ -5698,12 +5745,12 @@
         <v>2</v>
       </c>
       <c r="F169" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B170" t="s">
         <v>256</v>
@@ -5718,12 +5765,12 @@
         <v>3</v>
       </c>
       <c r="F170" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B171" t="s">
         <v>256</v>
@@ -5738,12 +5785,12 @@
         <v>3</v>
       </c>
       <c r="F171" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="172" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B172" t="s">
         <v>256</v>
@@ -5758,12 +5805,12 @@
         <v>3</v>
       </c>
       <c r="F172" t="s">
-        <v>565</v>
-      </c>
-    </row>
-    <row r="173" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B173" t="s">
         <v>256</v>
@@ -5778,12 +5825,12 @@
         <v>4</v>
       </c>
       <c r="F173" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="174" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B174" t="s">
         <v>256</v>
@@ -5798,12 +5845,12 @@
         <v>4</v>
       </c>
       <c r="F174" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="175" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B175" t="s">
         <v>256</v>
@@ -5818,12 +5865,12 @@
         <v>4</v>
       </c>
       <c r="F175" t="s">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="176" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B176" t="s">
         <v>256</v>
@@ -5838,12 +5885,12 @@
         <v>4</v>
       </c>
       <c r="F176" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="177" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B177" t="s">
         <v>256</v>
@@ -5858,12 +5905,12 @@
         <v>1</v>
       </c>
       <c r="F177" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="178" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B178" t="s">
         <v>256</v>
@@ -5878,15 +5925,15 @@
         <v>1</v>
       </c>
       <c r="F178" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="179" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B179" t="s">
-        <v>256</v>
+        <v>650</v>
       </c>
       <c r="C179">
         <v>1</v>
@@ -5898,15 +5945,15 @@
         <v>2</v>
       </c>
       <c r="F179" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="180" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B180" t="s">
-        <v>256</v>
+        <v>650</v>
       </c>
       <c r="C180">
         <v>1</v>
@@ -5918,12 +5965,12 @@
         <v>2</v>
       </c>
       <c r="F180" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="181" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B181" t="s">
         <v>256</v>
@@ -5938,12 +5985,12 @@
         <v>2</v>
       </c>
       <c r="F181" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="182" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B182" t="s">
         <v>256</v>
@@ -5958,12 +6005,12 @@
         <v>3</v>
       </c>
       <c r="F182" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="183" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B183" t="s">
         <v>256</v>
@@ -5978,12 +6025,12 @@
         <v>3</v>
       </c>
       <c r="F183" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="184" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B184" t="s">
         <v>256</v>
@@ -5998,12 +6045,12 @@
         <v>3</v>
       </c>
       <c r="F184" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="185" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B185" t="s">
         <v>256</v>
@@ -6018,12 +6065,12 @@
         <v>3</v>
       </c>
       <c r="F185" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="186" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B186" t="s">
         <v>256</v>
@@ -6038,15 +6085,15 @@
         <v>4</v>
       </c>
       <c r="F186" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="187" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B187" t="s">
-        <v>256</v>
+        <v>654</v>
       </c>
       <c r="C187">
         <v>1</v>
@@ -6058,12 +6105,12 @@
         <v>4</v>
       </c>
       <c r="F187" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="188" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B188" t="s">
         <v>256</v>
@@ -6078,12 +6125,12 @@
         <v>4</v>
       </c>
       <c r="F188" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="189" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B189" t="s">
         <v>256</v>
@@ -6098,12 +6145,12 @@
         <v>1</v>
       </c>
       <c r="F189" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="190" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B190" t="s">
         <v>256</v>
@@ -6118,12 +6165,12 @@
         <v>1</v>
       </c>
       <c r="F190" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="191" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B191" t="s">
         <v>256</v>
@@ -6138,15 +6185,15 @@
         <v>1</v>
       </c>
       <c r="F191" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="192" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B192" t="s">
-        <v>256</v>
+        <v>648</v>
       </c>
       <c r="C192">
         <v>1</v>
@@ -6158,15 +6205,15 @@
         <v>2</v>
       </c>
       <c r="F192" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="193" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B193" t="s">
-        <v>256</v>
+        <v>648</v>
       </c>
       <c r="C193">
         <v>1</v>
@@ -6178,12 +6225,12 @@
         <v>2</v>
       </c>
       <c r="F193" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="194" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B194" t="s">
         <v>256</v>
@@ -6198,15 +6245,15 @@
         <v>2</v>
       </c>
       <c r="F194" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="195" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B195" t="s">
-        <v>256</v>
+        <v>650</v>
       </c>
       <c r="C195">
         <v>1</v>
@@ -6218,15 +6265,15 @@
         <v>3</v>
       </c>
       <c r="F195" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="196" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B196" t="s">
-        <v>256</v>
+        <v>650</v>
       </c>
       <c r="C196">
         <v>1</v>
@@ -6238,12 +6285,12 @@
         <v>3</v>
       </c>
       <c r="F196" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="197" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B197" t="s">
         <v>256</v>
@@ -6258,15 +6305,15 @@
         <v>3</v>
       </c>
       <c r="F197" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="198" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B198" t="s">
-        <v>256</v>
+        <v>655</v>
       </c>
       <c r="C198">
         <v>1</v>
@@ -6278,12 +6325,12 @@
         <v>4</v>
       </c>
       <c r="F198" t="s">
-        <v>545</v>
-      </c>
-    </row>
-    <row r="199" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B199" t="s">
         <v>256</v>
@@ -6298,12 +6345,12 @@
         <v>4</v>
       </c>
       <c r="F199" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="200" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B200" t="s">
         <v>256</v>
@@ -6318,12 +6365,12 @@
         <v>1</v>
       </c>
       <c r="F200" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="201" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B201" t="s">
         <v>256</v>
@@ -6338,15 +6385,15 @@
         <v>1</v>
       </c>
       <c r="F201" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="202" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B202" t="s">
-        <v>256</v>
+        <v>650</v>
       </c>
       <c r="C202">
         <v>1</v>
@@ -6358,12 +6405,12 @@
         <v>1</v>
       </c>
       <c r="F202" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="203" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B203" t="s">
         <v>256</v>
@@ -6378,12 +6425,12 @@
         <v>2</v>
       </c>
       <c r="F203" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="204" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B204" t="s">
         <v>256</v>
@@ -6398,12 +6445,12 @@
         <v>2</v>
       </c>
       <c r="F204" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="205" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B205" t="s">
         <v>256</v>
@@ -6418,12 +6465,12 @@
         <v>2</v>
       </c>
       <c r="F205" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="206" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B206" t="s">
         <v>256</v>
@@ -6435,15 +6482,15 @@
         <v>40</v>
       </c>
       <c r="E206" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="F206" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="207" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B207" t="s">
         <v>256</v>
@@ -6455,15 +6502,15 @@
         <v>40</v>
       </c>
       <c r="E207" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="F207" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="208" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B208" t="s">
         <v>256</v>
@@ -6475,15 +6522,15 @@
         <v>40</v>
       </c>
       <c r="E208" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="F208" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="209" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B209" t="s">
         <v>256</v>
@@ -6498,12 +6545,12 @@
         <v>1</v>
       </c>
       <c r="F209" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="210" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B210" t="s">
         <v>256</v>
@@ -6518,12 +6565,12 @@
         <v>1</v>
       </c>
       <c r="F210" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="211" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B211" t="s">
         <v>256</v>
@@ -6538,12 +6585,12 @@
         <v>1</v>
       </c>
       <c r="F211" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="212" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B212" t="s">
         <v>256</v>
@@ -6558,12 +6605,12 @@
         <v>2</v>
       </c>
       <c r="F212" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="213" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B213" t="s">
         <v>256</v>
@@ -6578,12 +6625,12 @@
         <v>2</v>
       </c>
       <c r="F213" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="214" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B214" t="s">
         <v>256</v>
@@ -6598,12 +6645,12 @@
         <v>2</v>
       </c>
       <c r="F214" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="215" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B215" t="s">
         <v>256</v>
@@ -6618,12 +6665,12 @@
         <v>3</v>
       </c>
       <c r="F215" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="216" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B216" t="s">
         <v>256</v>
@@ -6638,12 +6685,12 @@
         <v>3</v>
       </c>
       <c r="F216" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="217" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B217" t="s">
         <v>256</v>
@@ -6658,12 +6705,12 @@
         <v>3</v>
       </c>
       <c r="F217" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="218" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B218" t="s">
         <v>256</v>
@@ -6678,12 +6725,12 @@
         <v>4</v>
       </c>
       <c r="F218" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="219" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B219" t="s">
         <v>256</v>
@@ -6698,12 +6745,12 @@
         <v>4</v>
       </c>
       <c r="F219" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="220" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B220" t="s">
         <v>256</v>
@@ -6718,12 +6765,12 @@
         <v>4</v>
       </c>
       <c r="F220" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="221" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B221" t="s">
         <v>256</v>
@@ -6738,12 +6785,12 @@
         <v>1</v>
       </c>
       <c r="F221" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="222" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B222" t="s">
         <v>256</v>
@@ -6758,12 +6805,12 @@
         <v>1</v>
       </c>
       <c r="F222" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="223" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B223" t="s">
         <v>256</v>
@@ -6778,12 +6825,12 @@
         <v>1</v>
       </c>
       <c r="F223" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="224" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B224" t="s">
         <v>256</v>
@@ -6798,12 +6845,12 @@
         <v>1</v>
       </c>
       <c r="F224" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="225" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B225" t="s">
         <v>256</v>
@@ -6818,12 +6865,12 @@
         <v>2</v>
       </c>
       <c r="F225" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="226" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B226" t="s">
         <v>256</v>
@@ -6838,15 +6885,15 @@
         <v>2</v>
       </c>
       <c r="F226" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="227" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B227" t="s">
-        <v>256</v>
+        <v>648</v>
       </c>
       <c r="C227">
         <v>1</v>
@@ -6858,12 +6905,12 @@
         <v>2</v>
       </c>
       <c r="F227" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="228" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B228" t="s">
         <v>256</v>
@@ -6878,12 +6925,12 @@
         <v>3</v>
       </c>
       <c r="F228" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="229" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B229" t="s">
         <v>256</v>
@@ -6898,12 +6945,12 @@
         <v>3</v>
       </c>
       <c r="F229" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="230" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B230" t="s">
         <v>256</v>
@@ -6918,12 +6965,12 @@
         <v>4</v>
       </c>
       <c r="F230" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="231" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B231" t="s">
         <v>256</v>
@@ -6938,12 +6985,12 @@
         <v>4</v>
       </c>
       <c r="F231" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="232" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B232" t="s">
         <v>256</v>
@@ -6958,12 +7005,12 @@
         <v>4</v>
       </c>
       <c r="F232" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="233" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B233" t="s">
         <v>256</v>
@@ -6978,12 +7025,12 @@
         <v>1</v>
       </c>
       <c r="F233" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="234" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B234" t="s">
         <v>256</v>
@@ -6998,12 +7045,12 @@
         <v>1</v>
       </c>
       <c r="F234" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="235" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B235" t="s">
         <v>256</v>
@@ -7018,12 +7065,12 @@
         <v>1</v>
       </c>
       <c r="F235" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="236" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B236" t="s">
         <v>256</v>
@@ -7038,12 +7085,12 @@
         <v>1</v>
       </c>
       <c r="F236" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="237" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B237" t="s">
         <v>256</v>
@@ -7058,12 +7105,12 @@
         <v>2</v>
       </c>
       <c r="F237" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="238" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B238" t="s">
         <v>256</v>
@@ -7078,12 +7125,12 @@
         <v>2</v>
       </c>
       <c r="F238" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="239" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B239" t="s">
         <v>256</v>
@@ -7098,12 +7145,12 @@
         <v>2</v>
       </c>
       <c r="F239" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="240" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B240" t="s">
         <v>256</v>
@@ -7118,12 +7165,12 @@
         <v>2</v>
       </c>
       <c r="F240" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="241" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="B241" t="s">
         <v>256</v>
@@ -7138,15 +7185,15 @@
         <v>3</v>
       </c>
       <c r="F241" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="242" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B242" t="s">
-        <v>256</v>
+        <v>651</v>
       </c>
       <c r="C242">
         <v>1</v>
@@ -7158,12 +7205,12 @@
         <v>3</v>
       </c>
       <c r="F242" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="243" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B243" t="s">
         <v>256</v>
@@ -7178,12 +7225,12 @@
         <v>3</v>
       </c>
       <c r="F243" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="244" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B244" t="s">
         <v>256</v>
@@ -7198,12 +7245,12 @@
         <v>3</v>
       </c>
       <c r="F244" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="245" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B245" t="s">
         <v>256</v>
@@ -7218,12 +7265,12 @@
         <v>3</v>
       </c>
       <c r="F245" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="246" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B246" t="s">
         <v>256</v>
@@ -7238,12 +7285,12 @@
         <v>3</v>
       </c>
       <c r="F246" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="247" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B247" t="s">
         <v>256</v>
@@ -7258,12 +7305,12 @@
         <v>4</v>
       </c>
       <c r="F247" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="248" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B248" t="s">
         <v>256</v>
@@ -7278,12 +7325,12 @@
         <v>4</v>
       </c>
       <c r="F248" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="249" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B249" t="s">
         <v>256</v>
@@ -7298,12 +7345,12 @@
         <v>1</v>
       </c>
       <c r="F249" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="250" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B250" t="s">
         <v>256</v>
@@ -7318,12 +7365,12 @@
         <v>1</v>
       </c>
       <c r="F250" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="251" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B251" t="s">
         <v>256</v>
@@ -7338,12 +7385,12 @@
         <v>1</v>
       </c>
       <c r="F251" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="252" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B252" t="s">
         <v>256</v>
@@ -7358,12 +7405,12 @@
         <v>2</v>
       </c>
       <c r="F252" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="253" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B253" t="s">
         <v>256</v>
@@ -7378,12 +7425,12 @@
         <v>2</v>
       </c>
       <c r="F253" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="254" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B254" t="s">
         <v>256</v>
@@ -7398,12 +7445,12 @@
         <v>2</v>
       </c>
       <c r="F254" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="255" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B255" t="s">
         <v>256</v>
@@ -7418,12 +7465,12 @@
         <v>2</v>
       </c>
       <c r="F255" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="256" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B256" t="s">
         <v>256</v>
@@ -7438,12 +7485,12 @@
         <v>3</v>
       </c>
       <c r="F256" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="257" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B257" t="s">
         <v>256</v>
@@ -7458,12 +7505,12 @@
         <v>3</v>
       </c>
       <c r="F257" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="258" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B258" t="s">
         <v>256</v>
@@ -7478,12 +7525,12 @@
         <v>3</v>
       </c>
       <c r="F258" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="259" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B259" t="s">
         <v>256</v>
@@ -7498,12 +7545,12 @@
         <v>3</v>
       </c>
       <c r="F259" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="260" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B260" t="s">
         <v>256</v>
@@ -7518,12 +7565,12 @@
         <v>4</v>
       </c>
       <c r="F260" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="261" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B261" t="s">
         <v>256</v>
@@ -7538,15 +7585,15 @@
         <v>4</v>
       </c>
       <c r="F261" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="262" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B262" t="s">
-        <v>256</v>
+        <v>650</v>
       </c>
       <c r="C262">
         <v>1</v>
@@ -7558,12 +7605,12 @@
         <v>4</v>
       </c>
       <c r="F262" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="263" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B263" t="s">
         <v>256</v>
@@ -7578,12 +7625,12 @@
         <v>4</v>
       </c>
       <c r="F263" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="264" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B264" t="s">
         <v>256</v>
@@ -7598,12 +7645,12 @@
         <v>1</v>
       </c>
       <c r="F264" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="265" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B265" t="s">
         <v>256</v>
@@ -7618,12 +7665,12 @@
         <v>1</v>
       </c>
       <c r="F265" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="266" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B266" t="s">
         <v>256</v>
@@ -7638,12 +7685,12 @@
         <v>1</v>
       </c>
       <c r="F266" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="267" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B267" t="s">
         <v>256</v>
@@ -7658,12 +7705,12 @@
         <v>2</v>
       </c>
       <c r="F267" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="268" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B268" t="s">
         <v>256</v>
@@ -7678,12 +7725,12 @@
         <v>2</v>
       </c>
       <c r="F268" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="269" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B269" t="s">
         <v>256</v>
@@ -7698,12 +7745,12 @@
         <v>2</v>
       </c>
       <c r="F269" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="270" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B270" t="s">
         <v>256</v>
@@ -7718,12 +7765,12 @@
         <v>3</v>
       </c>
       <c r="F270" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="271" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B271" t="s">
         <v>256</v>
@@ -7738,12 +7785,12 @@
         <v>3</v>
       </c>
       <c r="F271" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="272" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B272" t="s">
         <v>256</v>
@@ -7758,12 +7805,12 @@
         <v>3</v>
       </c>
       <c r="F272" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="273" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B273" t="s">
         <v>256</v>
@@ -7778,12 +7825,12 @@
         <v>4</v>
       </c>
       <c r="F273" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="274" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B274" t="s">
         <v>256</v>
@@ -7798,15 +7845,15 @@
         <v>4</v>
       </c>
       <c r="F274" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="275" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B275" t="s">
-        <v>256</v>
+        <v>657</v>
       </c>
       <c r="C275">
         <v>1</v>
@@ -7818,10 +7865,10 @@
         <v>1</v>
       </c>
       <c r="F275" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="276" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>89</v>
       </c>
@@ -7838,9 +7885,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="277" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B277" t="s">
         <v>256</v>
@@ -7855,15 +7902,15 @@
         <v>3</v>
       </c>
       <c r="F277" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="278" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B278" t="s">
-        <v>256</v>
+        <v>650</v>
       </c>
       <c r="C278">
         <v>1</v>
@@ -7875,15 +7922,15 @@
         <v>3</v>
       </c>
       <c r="F278" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="279" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B279" t="s">
-        <v>256</v>
+        <v>657</v>
       </c>
       <c r="C279">
         <v>1</v>
@@ -7895,12 +7942,12 @@
         <v>3</v>
       </c>
       <c r="F279" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="280" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B280" t="s">
         <v>256</v>
@@ -7915,12 +7962,12 @@
         <v>4</v>
       </c>
       <c r="F280" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="281" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B281" t="s">
         <v>256</v>
@@ -7935,12 +7982,12 @@
         <v>4</v>
       </c>
       <c r="F281" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="282" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B282" t="s">
         <v>256</v>
@@ -7955,12 +8002,12 @@
         <v>4</v>
       </c>
       <c r="F282" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="283" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B283" t="s">
         <v>256</v>
@@ -7975,15 +8022,15 @@
         <v>4</v>
       </c>
       <c r="F283" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="284" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B284" t="s">
-        <v>256</v>
+        <v>659</v>
       </c>
       <c r="C284">
         <v>1</v>
@@ -7995,15 +8042,15 @@
         <v>1</v>
       </c>
       <c r="F284" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="285" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B285" t="s">
-        <v>256</v>
+        <v>659</v>
       </c>
       <c r="C285">
         <v>1</v>
@@ -8015,15 +8062,15 @@
         <v>1</v>
       </c>
       <c r="F285" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="286" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B286" t="s">
-        <v>256</v>
+        <v>654</v>
       </c>
       <c r="C286">
         <v>1</v>
@@ -8035,12 +8082,12 @@
         <v>1</v>
       </c>
       <c r="F286" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="287" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B287" t="s">
         <v>256</v>
@@ -8055,15 +8102,15 @@
         <v>2</v>
       </c>
       <c r="F287" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="288" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B288" t="s">
-        <v>256</v>
+        <v>660</v>
       </c>
       <c r="C288">
         <v>1</v>
@@ -8075,15 +8122,15 @@
         <v>2</v>
       </c>
       <c r="F288" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="289" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B289" t="s">
-        <v>256</v>
+        <v>651</v>
       </c>
       <c r="C289">
         <v>1</v>
@@ -8095,15 +8142,15 @@
         <v>2</v>
       </c>
       <c r="F289" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="290" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B290" t="s">
-        <v>256</v>
+        <v>660</v>
       </c>
       <c r="C290">
         <v>1</v>
@@ -8115,15 +8162,15 @@
         <v>2</v>
       </c>
       <c r="F290" t="s">
-        <v>622</v>
-      </c>
-    </row>
-    <row r="291" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B291" t="s">
-        <v>256</v>
+        <v>657</v>
       </c>
       <c r="C291">
         <v>1</v>
@@ -8135,15 +8182,15 @@
         <v>3</v>
       </c>
       <c r="F291" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="292" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B292" t="s">
-        <v>256</v>
+        <v>648</v>
       </c>
       <c r="C292">
         <v>1</v>
@@ -8155,15 +8202,15 @@
         <v>3</v>
       </c>
       <c r="F292" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="293" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B293" t="s">
-        <v>256</v>
+        <v>660</v>
       </c>
       <c r="C293">
         <v>1</v>
@@ -8175,12 +8222,12 @@
         <v>3</v>
       </c>
       <c r="F293" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="294" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B294" t="s">
         <v>256</v>
@@ -8195,15 +8242,15 @@
         <v>4</v>
       </c>
       <c r="F294" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="295" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="B295" t="s">
-        <v>256</v>
+        <v>651</v>
       </c>
       <c r="C295">
         <v>1</v>
@@ -8215,15 +8262,15 @@
         <v>4</v>
       </c>
       <c r="F295" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="296" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B296" t="s">
-        <v>256</v>
+        <v>650</v>
       </c>
       <c r="C296">
         <v>1</v>
@@ -8235,12 +8282,12 @@
         <v>4</v>
       </c>
       <c r="F296" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="297" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B297" t="s">
         <v>256</v>
@@ -8255,12 +8302,12 @@
         <v>1</v>
       </c>
       <c r="F297" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="298" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B298" t="s">
         <v>256</v>
@@ -8275,15 +8322,15 @@
         <v>1</v>
       </c>
       <c r="F298" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="299" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B299" t="s">
-        <v>256</v>
+        <v>658</v>
       </c>
       <c r="C299">
         <v>1</v>
@@ -8295,12 +8342,12 @@
         <v>1</v>
       </c>
       <c r="F299" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="300" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B300" t="s">
         <v>256</v>
@@ -8315,12 +8362,12 @@
         <v>2</v>
       </c>
       <c r="F300" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="301" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B301" t="s">
         <v>256</v>
@@ -8335,12 +8382,12 @@
         <v>2</v>
       </c>
       <c r="F301" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="302" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B302" t="s">
         <v>256</v>
@@ -8355,12 +8402,12 @@
         <v>2</v>
       </c>
       <c r="F302" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="303" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B303" t="s">
         <v>256</v>
@@ -8375,12 +8422,12 @@
         <v>2</v>
       </c>
       <c r="F303" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="304" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B304" t="s">
         <v>256</v>
@@ -8395,12 +8442,12 @@
         <v>3</v>
       </c>
       <c r="F304" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="305" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B305" t="s">
         <v>256</v>
@@ -8415,12 +8462,12 @@
         <v>3</v>
       </c>
       <c r="F305" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="306" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B306" t="s">
         <v>256</v>
@@ -8435,15 +8482,15 @@
         <v>3</v>
       </c>
       <c r="F306" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="307" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>129</v>
       </c>
       <c r="B307" t="s">
-        <v>256</v>
+        <v>650</v>
       </c>
       <c r="C307">
         <v>1</v>
@@ -8458,7 +8505,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="308" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>260</v>
       </c>
@@ -8478,12 +8525,12 @@
         <v>267</v>
       </c>
     </row>
-    <row r="309" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>259</v>
       </c>
       <c r="B309" t="s">
-        <v>256</v>
+        <v>657</v>
       </c>
       <c r="C309">
         <v>1</v>
@@ -8498,12 +8545,12 @@
         <v>266</v>
       </c>
     </row>
-    <row r="310" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>257</v>
       </c>
       <c r="B310" t="s">
-        <v>256</v>
+        <v>656</v>
       </c>
       <c r="C310">
         <v>1</v>
@@ -8518,12 +8565,12 @@
         <v>258</v>
       </c>
     </row>
-    <row r="311" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>263</v>
       </c>
       <c r="B311" t="s">
-        <v>256</v>
+        <v>656</v>
       </c>
       <c r="C311">
         <v>1</v>
@@ -8538,7 +8585,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="312" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>262</v>
       </c>
@@ -8558,12 +8605,12 @@
         <v>269</v>
       </c>
     </row>
-    <row r="313" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>261</v>
       </c>
       <c r="B313" t="s">
-        <v>256</v>
+        <v>654</v>
       </c>
       <c r="C313">
         <v>1</v>
@@ -8578,12 +8625,12 @@
         <v>268</v>
       </c>
     </row>
-    <row r="314" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>273</v>
       </c>
       <c r="B314" t="s">
-        <v>256</v>
+        <v>657</v>
       </c>
       <c r="C314">
         <v>1</v>
@@ -8595,12 +8642,12 @@
         <v>3</v>
       </c>
       <c r="F314" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="315" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="B315" t="s">
         <v>256</v>
@@ -8615,15 +8662,15 @@
         <v>3</v>
       </c>
       <c r="F315" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="316" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>265</v>
       </c>
       <c r="B316" t="s">
-        <v>256</v>
+        <v>654</v>
       </c>
       <c r="C316">
         <v>1</v>
@@ -8638,12 +8685,12 @@
         <v>272</v>
       </c>
     </row>
-    <row r="317" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>264</v>
       </c>
       <c r="B317" t="s">
-        <v>256</v>
+        <v>657</v>
       </c>
       <c r="C317">
         <v>1</v>
@@ -8658,12 +8705,12 @@
         <v>271</v>
       </c>
     </row>
-    <row r="318" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B318" t="s">
-        <v>256</v>
+        <v>661</v>
       </c>
       <c r="C318">
         <v>1</v>
@@ -8675,15 +8722,15 @@
         <v>4</v>
       </c>
       <c r="F318" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="319" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B319" t="s">
-        <v>256</v>
+        <v>661</v>
       </c>
       <c r="C319">
         <v>1</v>
@@ -8695,12 +8742,15 @@
         <v>4</v>
       </c>
       <c r="F319" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>644</v>
+        <v>274</v>
+      </c>
+      <c r="B320" t="s">
+        <v>650</v>
       </c>
       <c r="C320">
         <v>1</v>
@@ -8712,28 +8762,23 @@
         <v>4</v>
       </c>
       <c r="F320" t="s">
-        <v>645</v>
-      </c>
-    </row>
-    <row r="321" hidden="1" x14ac:dyDescent="0.25"/>
+        <v>441</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F321" xr:uid="{E6B6791C-A8A7-4753-A504-FAA9E3EE8745}">
-    <filterColumn colId="5">
-      <filters>
-        <filter val="I-1474.jpeg"/>
-      </filters>
-    </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F321">
-      <sortCondition descending="1" ref="C2:C321"/>
-      <sortCondition ref="D2:D321"/>
-      <sortCondition ref="E2:E321"/>
+  <autoFilter ref="A1:F320" xr:uid="{E6B6791C-A8A7-4753-A504-FAA9E3EE8745}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F320">
+      <sortCondition descending="1" ref="C2:C320"/>
+      <sortCondition ref="D2:D320"/>
+      <sortCondition ref="E2:E320"/>
+      <sortCondition descending="1" ref="A2:A320"/>
     </sortState>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F320">
-    <sortCondition descending="1" ref="C2:C320"/>
-    <sortCondition ref="D2:D320"/>
-    <sortCondition ref="E2:E320"/>
-    <sortCondition descending="1" ref="A2:A320"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F319">
+    <sortCondition descending="1" ref="C2:C319"/>
+    <sortCondition ref="D2:D319"/>
+    <sortCondition ref="E2:E319"/>
+    <sortCondition descending="1" ref="A2:A319"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
